--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1931" uniqueCount="1931">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1932">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034394264221</t>
+    <t xml:space="preserve">2.10034418106079</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.150794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13486289978027</t>
+    <t xml:space="preserve">2.15079498291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13486313819885</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768867492676</t>
@@ -56,88 +56,88 @@
     <t xml:space="preserve">2.07379102706909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02334022521973</t>
+    <t xml:space="preserve">2.02334046363831</t>
   </si>
   <si>
     <t xml:space="preserve">2.0631697177887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0525484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.964923620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988354206085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802945137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01696729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0015664100647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05998349189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00528407096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909136772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819972038269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774903774261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943274021149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447269916534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93306005001068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9171279668808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589554309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368147850037</t>
+    <t xml:space="preserve">2.05254864692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492350101471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988366127014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0180299282074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696753501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209784507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00156664848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05998373031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00528430938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774927616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943285942078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447257995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9330598115921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712832450867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633662700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589566230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9436811208725</t>
   </si>
   <si>
     <t xml:space="preserve">2.09237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113599777222</t>
+    <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
     <t xml:space="preserve">2.08441209793091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09450197219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203736305237</t>
+    <t xml:space="preserve">2.09450244903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203760147095</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830974578857</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">2.1396427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10299897193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442205429077</t>
+    <t xml:space="preserve">2.10299921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442181587219</t>
   </si>
   <si>
     <t xml:space="preserve">2.14548420906067</t>
@@ -158,64 +158,64 @@
     <t xml:space="preserve">2.15345001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14813923835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132522583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16831994056702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18265819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16831946372986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18265843391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22248816490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610480308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0870680809021</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219743728638</t>
   </si>
   <si>
-    <t xml:space="preserve">2.121586561203</t>
+    <t xml:space="preserve">2.12158632278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.14017343521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12424182891846</t>
+    <t xml:space="preserve">2.12424206733704</t>
   </si>
   <si>
     <t xml:space="preserve">2.11362075805664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06582498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05307960510254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06848073005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901144981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11840009689331</t>
+    <t xml:space="preserve">2.06582522392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05307936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0684802532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901121139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
     <t xml:space="preserve">2.12477254867554</t>
@@ -227,37 +227,37 @@
     <t xml:space="preserve">2.15557432174683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1773476600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373054504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169658660889</t>
+    <t xml:space="preserve">2.17734789848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373030662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
     <t xml:space="preserve">2.29418110847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25753808021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461223602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21452164649963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638557434082</t>
+    <t xml:space="preserve">2.2575376033783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461199760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21452188491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638533592224</t>
   </si>
   <si>
     <t xml:space="preserve">2.23098468780518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32073402404785</t>
+    <t xml:space="preserve">2.32073426246643</t>
   </si>
   <si>
     <t xml:space="preserve">2.34888029098511</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">2.32604432106018</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44925022125244</t>
+    <t xml:space="preserve">2.4492506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.50288796424866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51775765419006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555342674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547231674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555047035217</t>
+    <t xml:space="preserve">2.51775717735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56555271148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997183799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61547255516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555023193359</t>
   </si>
   <si>
     <t xml:space="preserve">2.66718363761902</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7014753818512</t>
+    <t xml:space="preserve">2.70147562026978</t>
   </si>
   <si>
     <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7216157913208</t>
+    <t xml:space="preserve">2.72161531448364</t>
   </si>
   <si>
     <t xml:space="preserve">2.79346632957458</t>
@@ -305,49 +305,49 @@
     <t xml:space="preserve">2.8152391910553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9589409828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98942255973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00248599052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94587659835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84136700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9175717830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668559074402</t>
+    <t xml:space="preserve">2.95894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98942232131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00248622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94587683677673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91757202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668535232544</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797616004944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81959366798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685669898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954882144928</t>
+    <t xml:space="preserve">2.81959342956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69548773765564</t>
   </si>
   <si>
     <t xml:space="preserve">2.78693437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86531734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289084434509</t>
+    <t xml:space="preserve">2.86531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289060592651</t>
   </si>
   <si>
     <t xml:space="preserve">2.84789848327637</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">2.77604794502258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313939094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97200417518616</t>
+    <t xml:space="preserve">2.86313986778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974902153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97200393676758</t>
   </si>
   <si>
     <t xml:space="preserve">2.99159979820251</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">2.97418141365051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99813199043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9785361289978</t>
+    <t xml:space="preserve">2.99813151359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97853589057922</t>
   </si>
   <si>
     <t xml:space="preserve">3.03514575958252</t>
@@ -383,34 +383,34 @@
     <t xml:space="preserve">3.04820919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15707421302795</t>
+    <t xml:space="preserve">3.06998229026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
     <t xml:space="preserve">3.29859781265259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30730700492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29206609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28988909721375</t>
+    <t xml:space="preserve">3.30730748176575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214377403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771138191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
     <t xml:space="preserve">3.27900242805481</t>
@@ -422,40 +422,40 @@
     <t xml:space="preserve">3.2659387588501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1744921207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25505208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25940704345703</t>
+    <t xml:space="preserve">3.17449259757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25505232810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25940656661987</t>
   </si>
   <si>
     <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35085320472717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34432125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472586631775</t>
+    <t xml:space="preserve">3.35085296630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34432148933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472538948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.28553438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27247023582458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3203706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682566642761</t>
+    <t xml:space="preserve">3.27247047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682518959045</t>
   </si>
   <si>
     <t xml:space="preserve">3.31383895874023</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">3.30948448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15054249763489</t>
+    <t xml:space="preserve">3.15054202079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.18973350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2093288898468</t>
+    <t xml:space="preserve">3.20932912826538</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069761276245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20062017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239255905151</t>
+    <t xml:space="preserve">3.20061993598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239303588867</t>
   </si>
   <si>
     <t xml:space="preserve">3.09175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33343482017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376152038574</t>
+    <t xml:space="preserve">3.33343505859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376128196716</t>
   </si>
   <si>
     <t xml:space="preserve">3.20497488975525</t>
@@ -497,61 +497,61 @@
     <t xml:space="preserve">3.37262606620789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43141293525696</t>
+    <t xml:space="preserve">3.43141269683838</t>
   </si>
   <si>
     <t xml:space="preserve">3.59253263473511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67962408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631186485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824055671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01057386398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09330987930298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
+    <t xml:space="preserve">3.67962431907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824007987976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057291030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831823348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33716630935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23483371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313829421997</t>
+    <t xml:space="preserve">4.19346570968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33716678619385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23483419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313781738281</t>
   </si>
   <si>
     <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68988800048828</t>
+    <t xml:space="preserve">4.68988847732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.65722894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956106185913</t>
+    <t xml:space="preserve">4.64634227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956058502197</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334053039551</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74214267730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73778867721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64416551589966</t>
+    <t xml:space="preserve">4.74214315414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73778820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6441650390625</t>
   </si>
   <si>
     <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37418079376221</t>
+    <t xml:space="preserve">4.37418031692505</t>
   </si>
   <si>
     <t xml:space="preserve">4.35023021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34152173995972</t>
+    <t xml:space="preserve">4.3415207862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.22830200195312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19128799438477</t>
+    <t xml:space="preserve">4.19128751754761</t>
   </si>
   <si>
     <t xml:space="preserve">4.08895540237427</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">4.22612476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24572038650513</t>
+    <t xml:space="preserve">4.24571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547136306763</t>
@@ -605,100 +605,100 @@
     <t xml:space="preserve">4.35458517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33934450149536</t>
+    <t xml:space="preserve">4.3393440246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.65940570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63763284683228</t>
+    <t xml:space="preserve">4.63763236999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.63545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61585998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72254705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59408664703369</t>
+    <t xml:space="preserve">4.61586046218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59408712387085</t>
   </si>
   <si>
     <t xml:space="preserve">4.66376066207886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58973217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51135015487671</t>
+    <t xml:space="preserve">4.5897331237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134967803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.52441358566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73343276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64198780059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78568887710571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77480220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.746497631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7660927772522</t>
+    <t xml:space="preserve">4.73343372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6419882774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7856879234314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77480268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74649715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609325408936</t>
   </si>
   <si>
     <t xml:space="preserve">5.09921932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38662147521973</t>
+    <t xml:space="preserve">5.38662195205688</t>
   </si>
   <si>
     <t xml:space="preserve">5.29082012176514</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25162935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22985649108887</t>
+    <t xml:space="preserve">5.25162982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22985696792603</t>
   </si>
   <si>
     <t xml:space="preserve">5.22767972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372867584229</t>
+    <t xml:space="preserve">5.20372915267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11010599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.225501537323</t>
+    <t xml:space="preserve">5.11010456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22550201416016</t>
   </si>
   <si>
     <t xml:space="preserve">5.27557992935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106962203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14494228363037</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17107057571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14494276046753</t>
   </si>
   <si>
     <t xml:space="preserve">5.06220483779907</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">4.90979433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09050893783569</t>
+    <t xml:space="preserve">5.09050989151001</t>
   </si>
   <si>
     <t xml:space="preserve">5.04043197631836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11445999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1013970375061</t>
+    <t xml:space="preserve">5.11446046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10139560699463</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268665313721</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">5.12752342224121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11663818359375</t>
+    <t xml:space="preserve">5.11663675308228</t>
   </si>
   <si>
     <t xml:space="preserve">5.04478693008423</t>
@@ -734,112 +734,112 @@
     <t xml:space="preserve">4.95769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02736759185791</t>
+    <t xml:space="preserve">5.02736806869507</t>
   </si>
   <si>
     <t xml:space="preserve">4.98817729949951</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88584423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86624908447266</t>
+    <t xml:space="preserve">4.88584470748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8662486076355</t>
   </si>
   <si>
     <t xml:space="preserve">4.85536241531372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84665298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80093002319336</t>
+    <t xml:space="preserve">4.8466534614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
     <t xml:space="preserve">4.73561096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79004383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7443208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052564620972</t>
+    <t xml:space="preserve">4.79004335403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74432039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6811785697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052516937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.91850280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1384105682373</t>
+    <t xml:space="preserve">5.13840961456299</t>
   </si>
   <si>
     <t xml:space="preserve">5.08397769927979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19719743728638</t>
+    <t xml:space="preserve">5.19719791412354</t>
   </si>
   <si>
     <t xml:space="preserve">5.11881446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09486389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444423675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710376739502</t>
+    <t xml:space="preserve">5.09486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4171028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68273401260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63918733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385251998901</t>
+    <t xml:space="preserve">5.6827335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63918685913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385299682617</t>
   </si>
   <si>
     <t xml:space="preserve">5.91134881973267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94400835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383628845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81337118148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87868928909302</t>
+    <t xml:space="preserve">5.94400787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383771896362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81337070465088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87869024276733</t>
   </si>
   <si>
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957691192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89610815048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9766674041748</t>
+    <t xml:space="preserve">5.76329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89610719680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
     <t xml:space="preserve">6.0964183807373</t>
@@ -851,112 +851,112 @@
     <t xml:space="preserve">5.98973178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497198104858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98755407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0419864654541</t>
+    <t xml:space="preserve">6.00497245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9875545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722761154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08335542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96360349655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07464599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42301273345947</t>
+    <t xml:space="preserve">6.08335590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96360397338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07464551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13996458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42301321029663</t>
   </si>
   <si>
     <t xml:space="preserve">6.26842546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.529700756073</t>
+    <t xml:space="preserve">6.52969980239868</t>
   </si>
   <si>
     <t xml:space="preserve">6.54276371002197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58848667144775</t>
+    <t xml:space="preserve">6.58848762512207</t>
   </si>
   <si>
     <t xml:space="preserve">6.80403852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90201759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01088190078735</t>
+    <t xml:space="preserve">6.90201807022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088237762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.06531429290771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11756896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425699234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2220778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321496963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392957687378</t>
+    <t xml:space="preserve">7.11756944656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32005786895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063287734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.37666702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28522062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30481576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19595098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46655893325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705602645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61243724822998</t>
+    <t xml:space="preserve">7.36360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30481624603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19595146179199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40123987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61243772506714</t>
   </si>
   <si>
     <t xml:space="preserve">6.49704074859619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52316856384277</t>
+    <t xml:space="preserve">6.52316761016846</t>
   </si>
   <si>
     <t xml:space="preserve">6.57760047912598</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">6.52464389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290502548218</t>
+    <t xml:space="preserve">6.5621542930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290454864502</t>
   </si>
   <si>
     <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45403623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774164199829</t>
+    <t xml:space="preserve">6.45403575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774211883545</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294755935669</t>
+    <t xml:space="preserve">6.76294803619385</t>
   </si>
   <si>
     <t xml:space="preserve">6.82252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41652536392212</t>
+    <t xml:space="preserve">6.41652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">6.58421993255615</t>
@@ -1007,58 +1007,58 @@
     <t xml:space="preserve">6.35694932937622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33488416671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43417692184448</t>
+    <t xml:space="preserve">6.33488368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43417739868164</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826519012451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33267879486084</t>
+    <t xml:space="preserve">6.33267831802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.3746018409729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16057109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14291858673096</t>
+    <t xml:space="preserve">6.16057062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14291906356812</t>
   </si>
   <si>
     <t xml:space="preserve">6.13850545883179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95757150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91344118118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771314620972</t>
+    <t xml:space="preserve">5.95757102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91344165802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240907669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771362304688</t>
   </si>
   <si>
     <t xml:space="preserve">5.78546380996704</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95977783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9200611114502</t>
+    <t xml:space="preserve">5.95977830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92006063461304</t>
   </si>
   <si>
     <t xml:space="preserve">5.93329954147339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94212675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83621406555176</t>
+    <t xml:space="preserve">5.94212627410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8362135887146</t>
   </si>
   <si>
     <t xml:space="preserve">5.84724617004395</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">5.98846244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720315933228</t>
+    <t xml:space="preserve">5.69720363616943</t>
   </si>
   <si>
     <t xml:space="preserve">5.50744438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4699330329895</t>
+    <t xml:space="preserve">5.46993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692083358765</t>
+    <t xml:space="preserve">5.73691987991333</t>
   </si>
   <si>
     <t xml:space="preserve">5.76119232177734</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">5.89137697219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71485567092896</t>
+    <t xml:space="preserve">5.71485614776611</t>
   </si>
   <si>
     <t xml:space="preserve">5.72147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819416046143</t>
+    <t xml:space="preserve">5.59129190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819463729858</t>
   </si>
   <si>
     <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54495477676392</t>
+    <t xml:space="preserve">5.54495429992676</t>
   </si>
   <si>
     <t xml:space="preserve">5.4434552192688</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">5.45007514953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39932441711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41918420791626</t>
+    <t xml:space="preserve">5.39932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41918325424194</t>
   </si>
   <si>
     <t xml:space="preserve">5.49199867248535</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">5.48096561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52730226516724</t>
+    <t xml:space="preserve">5.52730274200439</t>
   </si>
   <si>
     <t xml:space="preserve">5.45890092849731</t>
@@ -1136,34 +1136,34 @@
     <t xml:space="preserve">5.41256427764893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48979187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56922578811646</t>
+    <t xml:space="preserve">5.48979234695435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56922626495361</t>
   </si>
   <si>
     <t xml:space="preserve">5.73912715911865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66410636901855</t>
+    <t xml:space="preserve">5.6641058921814</t>
   </si>
   <si>
     <t xml:space="preserve">5.80311584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86931133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532264709473</t>
+    <t xml:space="preserve">5.86931180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532217025757</t>
   </si>
   <si>
     <t xml:space="preserve">5.63762760162354</t>
@@ -1172,643 +1172,643 @@
     <t xml:space="preserve">5.56481313705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47875881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49420547485352</t>
+    <t xml:space="preserve">5.52068376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.478759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4942045211792</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181402206421</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22942352294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477060317993</t>
+    <t xml:space="preserve">5.29782581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22942399978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477108001709</t>
   </si>
   <si>
     <t xml:space="preserve">5.39711809158325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796697616577</t>
+    <t xml:space="preserve">5.27796745300293</t>
   </si>
   <si>
     <t xml:space="preserve">5.2228045463562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14116382598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11909818649292</t>
+    <t xml:space="preserve">5.14116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11909866333008</t>
   </si>
   <si>
     <t xml:space="preserve">5.20735931396484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16764211654663</t>
+    <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13675117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03745746612549</t>
+    <t xml:space="preserve">5.1367506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
+    <t xml:space="preserve">4.9646430015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126245498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04848957061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19412040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22501087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87196969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72633981704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131902694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60453033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84503984451294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76781129837036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461540222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63983488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14071130752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526655197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597379684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034439086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65086698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283304214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433212280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243757247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1693959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5559868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202764511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92226791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339864730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089548110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543668746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9284348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90636968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22852039337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908647537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0475869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4933009147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560777664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2594108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260723114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56391048431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4271068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62834978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163354873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796123504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6597785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817632675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31985712051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145795822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14094924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2125129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774709701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821535110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53007125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44509077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42719984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014978408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4629807472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.474524974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3358736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013124465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831531524658</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.96464252471924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802354812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126245498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04849004745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19412088394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22501134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689186096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87197017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72634029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131855010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839189529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6045298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8119421005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76781177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63983392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14071178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80973625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034391403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6508674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03259325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243757247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5559868812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92226696014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339864730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474252700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92843532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90636968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050001144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22852039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.149085521698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04758644104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4933009147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560682296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56391048431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802396774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450225830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247346878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643892288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66424989700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6597785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71345043182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817632675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49428987503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14094972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120336532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356702804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2885479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2125129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774662017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53007125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44509077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4003643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352895736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42719984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43167304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298027038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10069608688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3958911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47452545166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33587265014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013076782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9646430015564</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886209487915</t>
+    <t xml:space="preserve">5.05409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886257171631</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74995565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417427062988</t>
+    <t xml:space="preserve">4.58894109725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74995517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417474746704</t>
   </si>
   <si>
     <t xml:space="preserve">4.37201642990112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12825679779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20876502990723</t>
+    <t xml:space="preserve">4.12825727462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20876455307007</t>
   </si>
   <si>
     <t xml:space="preserve">4.11483907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04103994369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0544581413269</t>
+    <t xml:space="preserve">4.04104042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05445766448975</t>
   </si>
   <si>
     <t xml:space="preserve">3.95829677581787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08353042602539</t>
+    <t xml:space="preserve">4.08353090286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.15509271621704</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">4.1304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01867723464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884260177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559144020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740784645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466444015503</t>
+    <t xml:space="preserve">4.0186767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8688428401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702738761902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466396331787</t>
   </si>
   <si>
     <t xml:space="preserve">3.83753490447998</t>
@@ -1841,34 +1841,34 @@
     <t xml:space="preserve">3.84648060798645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96500587463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15732908248901</t>
+    <t xml:space="preserve">3.96500539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15732955932617</t>
   </si>
   <si>
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146085739136</t>
+    <t xml:space="preserve">3.92475080490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146061897278</t>
   </si>
   <si>
     <t xml:space="preserve">3.94264221191406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87331581115723</t>
+    <t xml:space="preserve">3.87331604957581</t>
   </si>
   <si>
     <t xml:space="preserve">3.86213445663452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84424352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512342453003</t>
+    <t xml:space="preserve">3.8442440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512318611145</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896110534668</t>
@@ -1877,40 +1877,40 @@
     <t xml:space="preserve">3.24267244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03245806694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38803339004517</t>
+    <t xml:space="preserve">3.03245782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140281677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216421127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3835608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38803291320801</t>
   </si>
   <si>
     <t xml:space="preserve">3.26950812339783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22701835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45288634300232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39474248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48866820335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5155041217804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870698928833</t>
+    <t xml:space="preserve">3.22701811790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45288681983948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3947422504425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4886679649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51550388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870722770691</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714493751526</t>
@@ -1922,22 +1922,22 @@
     <t xml:space="preserve">2.92735028266907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182301521301</t>
+    <t xml:space="preserve">2.93182277679443</t>
   </si>
   <si>
     <t xml:space="preserve">3.01009440422058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1040198802948</t>
+    <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
     <t xml:space="preserve">3.03916668891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88486003875732</t>
+    <t xml:space="preserve">2.95642280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88485980033875</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511415481567</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869795799255</t>
+    <t xml:space="preserve">2.78869843482971</t>
   </si>
   <si>
     <t xml:space="preserve">2.83342480659485</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">2.88933277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0727117061615</t>
+    <t xml:space="preserve">3.07271146774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16887331008911</t>
+    <t xml:space="preserve">3.16887354850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.22925424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15992832183838</t>
+    <t xml:space="preserve">3.15992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254538536072</t>
@@ -1979,70 +1979,70 @@
     <t xml:space="preserve">3.23596334457397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18676447868347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19347333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32094383239746</t>
+    <t xml:space="preserve">3.18676400184631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19347286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54234027862549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972297668457</t>
+    <t xml:space="preserve">3.47972273826599</t>
   </si>
   <si>
     <t xml:space="preserve">3.53339457511902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4953773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61166572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533780097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57588481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51103138923645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52221298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58259391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723249435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444911003113</t>
+    <t xml:space="preserve">3.49537706375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61166596412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588458061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51103115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52221274375916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5825936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723273277283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444934844971</t>
   </si>
   <si>
     <t xml:space="preserve">3.58483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69440960884094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62284755706787</t>
+    <t xml:space="preserve">3.69441032409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335555076599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80398988723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567875862122</t>
+    <t xml:space="preserve">3.70335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80399012565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567947387695</t>
   </si>
   <si>
     <t xml:space="preserve">3.77268147468567</t>
@@ -2051,31 +2051,31 @@
     <t xml:space="preserve">3.83306264877319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85766243934631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040608406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99184131622314</t>
+    <t xml:space="preserve">3.85766172409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99184155464172</t>
   </si>
   <si>
     <t xml:space="preserve">4.07011270523071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273000717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09247636795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125503540039</t>
+    <t xml:space="preserve">4.13272953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09247589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125455856323</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94935131072998</t>
+    <t xml:space="preserve">3.94935083389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.00525951385498</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842359542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112821578979</t>
+    <t xml:space="preserve">3.97842383384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112869262695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28256320953369</t>
@@ -2099,79 +2099,79 @@
     <t xml:space="preserve">4.42792463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3541259765625</t>
+    <t xml:space="preserve">4.35412549972534</t>
   </si>
   <si>
     <t xml:space="preserve">4.1662745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27809047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205545425415</t>
+    <t xml:space="preserve">4.20429229736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2780909538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205593109131</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783683776855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29150915145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24901914596558</t>
+    <t xml:space="preserve">4.2915096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24901866912842</t>
   </si>
   <si>
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19981956481934</t>
+    <t xml:space="preserve">4.25349187850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982004165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18640184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171449661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93369698524475</t>
+    <t xml:space="preserve">4.15285682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1864013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171425819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93369674682617</t>
   </si>
   <si>
     <t xml:space="preserve">3.90015196800232</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99631404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880405426025</t>
+    <t xml:space="preserve">3.99631357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0388035774231</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01644039154053</t>
+    <t xml:space="preserve">4.01644086837769</t>
   </si>
   <si>
     <t xml:space="preserve">3.91804265975952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87778949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76820874214172</t>
+    <t xml:space="preserve">3.87778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820850372314</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491760253906</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">3.85095286369324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09918546676636</t>
+    <t xml:space="preserve">4.09918451309204</t>
   </si>
   <si>
     <t xml:space="preserve">3.82411646842957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95693135261536</t>
+    <t xml:space="preserve">3.95693111419678</t>
   </si>
   <si>
     <t xml:space="preserve">3.88136458396912</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">3.76229000091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74626088142395</t>
+    <t xml:space="preserve">3.74626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">3.76458024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901348114014</t>
+    <t xml:space="preserve">3.68901371955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
@@ -2213,55 +2213,55 @@
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243655204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220430374146</t>
+    <t xml:space="preserve">3.84243679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220454216003</t>
   </si>
   <si>
     <t xml:space="preserve">3.92487263679504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96608996391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739394187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006155967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449479103088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655326843262</t>
+    <t xml:space="preserve">3.96609020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655303001404</t>
   </si>
   <si>
     <t xml:space="preserve">3.98440933227539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04165649414062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19736957550049</t>
+    <t xml:space="preserve">4.04165697097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19736909866333</t>
   </si>
   <si>
     <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09203433990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11264276504517</t>
+    <t xml:space="preserve">4.09203386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11264324188232</t>
   </si>
   <si>
     <t xml:space="preserve">4.10119390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14470148086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18820953369141</t>
+    <t xml:space="preserve">4.14470195770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18821048736572</t>
   </si>
   <si>
     <t xml:space="preserve">4.27751541137695</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">4.31415319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803909301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30270385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3507924079895</t>
+    <t xml:space="preserve">4.40803956985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30270433425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
@@ -2288,34 +2288,34 @@
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22255802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
+    <t xml:space="preserve">4.23858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22255754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997610092163</t>
+    <t xml:space="preserve">4.17446994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997562408447</t>
   </si>
   <si>
     <t xml:space="preserve">4.09890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15157127380371</t>
+    <t xml:space="preserve">4.15157079696655</t>
   </si>
   <si>
     <t xml:space="preserve">4.16302061080933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11035394668579</t>
+    <t xml:space="preserve">4.11035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">4.12409257888794</t>
@@ -2327,31 +2327,31 @@
     <t xml:space="preserve">4.00730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05539512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067070007324</t>
+    <t xml:space="preserve">4.05539608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97067046165466</t>
   </si>
   <si>
     <t xml:space="preserve">3.945481300354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84701538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8859441280365</t>
+    <t xml:space="preserve">3.84701609611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594436645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.876784324646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043869018555</t>
+    <t xml:space="preserve">3.85159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235085487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043821334839</t>
   </si>
   <si>
     <t xml:space="preserve">3.98211932182312</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">4.16760063171387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04394674301147</t>
+    <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
     <t xml:space="preserve">4.0531063079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18591976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13554191589355</t>
+    <t xml:space="preserve">4.18592023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1355414390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.06226539611816</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">4.60268020629883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00112056732178</t>
+    <t xml:space="preserve">5.00112104415894</t>
   </si>
   <si>
     <t xml:space="preserve">5.17515277862549</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">5.62855100631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48657655715942</t>
+    <t xml:space="preserve">5.48657703399658</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61023187637329</t>
+    <t xml:space="preserve">5.61023139953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.70640659332275</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45451927185059</t>
+    <t xml:space="preserve">5.45451879501343</t>
   </si>
   <si>
     <t xml:space="preserve">5.48199796676636</t>
@@ -2432,16 +2432,16 @@
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36292362213135</t>
+    <t xml:space="preserve">5.27590751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
     <t xml:space="preserve">5.44993925094604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34460401535034</t>
+    <t xml:space="preserve">5.3446044921875</t>
   </si>
   <si>
     <t xml:space="preserve">5.47283792495728</t>
@@ -2453,13 +2453,13 @@
     <t xml:space="preserve">5.55985403060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69724702835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72930574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.69724750518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7293062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92623662948608</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304580688477</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">5.72472620010376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67892789840698</t>
+    <t xml:space="preserve">5.67892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71556663513184</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">5.80716276168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098661422729</t>
+    <t xml:space="preserve">5.71098756790161</t>
   </si>
   <si>
     <t xml:space="preserve">5.82090139389038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89875745773315</t>
+    <t xml:space="preserve">5.89875841140747</t>
   </si>
   <si>
     <t xml:space="preserve">6.04989099502563</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24224138259888</t>
+    <t xml:space="preserve">6.02241182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24224090576172</t>
   </si>
   <si>
     <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324001312256</t>
+    <t xml:space="preserve">7.10324048995972</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941568374634</t>
@@ -2522,31 +2522,31 @@
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159658432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62533521652222</t>
+    <t xml:space="preserve">7.61159563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235179901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600616455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6253342628479</t>
   </si>
   <si>
     <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28185129165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41924476623535</t>
+    <t xml:space="preserve">7.28185176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
@@ -2555,10 +2555,10 @@
     <t xml:space="preserve">7.29101085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697912216187</t>
+    <t xml:space="preserve">7.27727174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697959899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.15361785888672</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37802696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57495832443237</t>
+    <t xml:space="preserve">7.39634609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37802743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495737075806</t>
   </si>
   <si>
     <t xml:space="preserve">7.91844129562378</t>
@@ -2582,31 +2582,31 @@
     <t xml:space="preserve">7.8589038848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67571353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579732894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655302047729</t>
+    <t xml:space="preserve">7.67571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655397415161</t>
   </si>
   <si>
     <t xml:space="preserve">7.36428737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45130348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12155961990356</t>
+    <t xml:space="preserve">7.45130395889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12155914306641</t>
   </si>
   <si>
     <t xml:space="preserve">7.41466569900513</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25895309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30475044250488</t>
+    <t xml:space="preserve">7.25895261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30474996566772</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231483459473</t>
@@ -2618,10 +2618,10 @@
     <t xml:space="preserve">7.43756437301636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48794269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51999998092651</t>
+    <t xml:space="preserve">7.48794221878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51999950408936</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2633,25 +2633,25 @@
     <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702785491943</t>
+    <t xml:space="preserve">6.51244878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702833175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.7414379119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79639434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71853876113892</t>
+    <t xml:space="preserve">6.79639482498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71853828430176</t>
   </si>
   <si>
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61778259277344</t>
+    <t xml:space="preserve">6.6177830696106</t>
   </si>
   <si>
     <t xml:space="preserve">7.02538394927979</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">6.89715003967285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82845258712769</t>
+    <t xml:space="preserve">6.82845306396484</t>
   </si>
   <si>
     <t xml:space="preserve">6.80097484588623</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76433610916138</t>
+    <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
     <t xml:space="preserve">6.63610219955444</t>
@@ -2699,13 +2699,13 @@
     <t xml:space="preserve">5.72014617919922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1156153678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381278991699</t>
+    <t xml:space="preserve">5.47741842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11561489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381231307983</t>
   </si>
   <si>
     <t xml:space="preserve">4.59809970855713</t>
@@ -2717,16 +2717,16 @@
     <t xml:space="preserve">4.21110820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81495714187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382503509521</t>
+    <t xml:space="preserve">3.81495785713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382479667664</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034134864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22416543960571</t>
+    <t xml:space="preserve">3.22416567802429</t>
   </si>
   <si>
     <t xml:space="preserve">3.18294763565063</t>
@@ -2744,10 +2744,10 @@
     <t xml:space="preserve">3.86304521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61344718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50353240966797</t>
+    <t xml:space="preserve">3.61344742774963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50353264808655</t>
   </si>
   <si>
     <t xml:space="preserve">3.67069458961487</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70962238311768</t>
+    <t xml:space="preserve">3.70962262153625</t>
   </si>
   <si>
     <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79663801193237</t>
+    <t xml:space="preserve">3.79663848876953</t>
   </si>
   <si>
     <t xml:space="preserve">3.74168086051941</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">4.17218065261841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
+    <t xml:space="preserve">4.09432411193848</t>
   </si>
   <si>
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612668991089</t>
+    <t xml:space="preserve">4.45612621307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.35995149612427</t>
@@ -2807,34 +2807,34 @@
     <t xml:space="preserve">4.32331275939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676019668579</t>
+    <t xml:space="preserve">4.35537195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499410629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676067352295</t>
   </si>
   <si>
     <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5248236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38742971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7515230178833</t>
+    <t xml:space="preserve">4.52482414245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4836049079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38743019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406797409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761299133301</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239994049072</t>
+    <t xml:space="preserve">5.23239946365356</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
@@ -2867,28 +2867,28 @@
     <t xml:space="preserve">4.93471384048462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02630949020386</t>
+    <t xml:space="preserve">5.02630996704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.19805145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31254577636719</t>
+    <t xml:space="preserve">5.31254625320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39269161224365</t>
+    <t xml:space="preserve">5.39269208908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.20950078964233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1522536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14080381393433</t>
+    <t xml:space="preserve">5.15225315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14080429077148</t>
   </si>
   <si>
     <t xml:space="preserve">5.27819728851318</t>
@@ -2897,37 +2897,37 @@
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500646591187</t>
+    <t xml:space="preserve">5.09500598907471</t>
   </si>
   <si>
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01485967636108</t>
+    <t xml:space="preserve">5.01486015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.11790561676025</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0606575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22095012664795</t>
+    <t xml:space="preserve">5.06065797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22095060348511</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10645532608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935447692871</t>
+    <t xml:space="preserve">5.10645580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935495376587</t>
   </si>
   <si>
     <t xml:space="preserve">5.3239951133728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544492721558</t>
+    <t xml:space="preserve">5.33544445037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.03775882720947</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">4.96906232833862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051166534424</t>
+    <t xml:space="preserve">4.94616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98051118850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.84311866760254</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99196100234985</t>
+    <t xml:space="preserve">4.9919605255127</t>
   </si>
   <si>
     <t xml:space="preserve">5.00341081619263</t>
@@ -2960,16 +2960,16 @@
     <t xml:space="preserve">4.57978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19049978256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21339845657349</t>
+    <t xml:space="preserve">4.1904993057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21339797973633</t>
   </si>
   <si>
     <t xml:space="preserve">4.08058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30041408538818</t>
+    <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.34163188934326</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">4.61412858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5415358543396</t>
+    <t xml:space="preserve">5.54153490066528</t>
   </si>
   <si>
     <t xml:space="preserve">5.62168073654175</t>
@@ -2993,34 +2993,34 @@
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64457988739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66747951507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89646816253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70182752609253</t>
+    <t xml:space="preserve">5.64457941055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66747903823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89646768569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70182704925537</t>
   </si>
   <si>
     <t xml:space="preserve">5.816321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14835643768311</t>
+    <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516418457031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95371532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87356948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91936683654785</t>
+    <t xml:space="preserve">5.9537148475647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87356901168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91936731338501</t>
   </si>
   <si>
     <t xml:space="preserve">6.09110879898071</t>
@@ -3029,10 +3029,10 @@
     <t xml:space="preserve">6.19415378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1254563331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15980577468872</t>
+    <t xml:space="preserve">6.12545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15980529785156</t>
   </si>
   <si>
     <t xml:space="preserve">6.18270397186279</t>
@@ -3041,43 +3041,43 @@
     <t xml:space="preserve">6.07965898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13690662384033</t>
+    <t xml:space="preserve">6.13690614700317</t>
   </si>
   <si>
     <t xml:space="preserve">6.2170524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009792327881</t>
+    <t xml:space="preserve">6.35444641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009744644165</t>
   </si>
   <si>
     <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48038959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618837356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53763628005981</t>
+    <t xml:space="preserve">6.4803900718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618789672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53763723373413</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60633420944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58343553543091</t>
+    <t xml:space="preserve">6.60633373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923336029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169309616089</t>
+    <t xml:space="preserve">6.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">6.46894073486328</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29719877243042</t>
+    <t xml:space="preserve">6.29719924926758</t>
   </si>
   <si>
     <t xml:space="preserve">6.20560312271118</t>
@@ -3095,13 +3095,13 @@
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328874588013</t>
+    <t xml:space="preserve">6.50328826904297</t>
   </si>
   <si>
     <t xml:space="preserve">6.66358089447021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5147385597229</t>
+    <t xml:space="preserve">6.51473808288574</t>
   </si>
   <si>
     <t xml:space="preserve">6.78952503204346</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77807521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792985916138</t>
+    <t xml:space="preserve">6.77807569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792938232422</t>
   </si>
   <si>
     <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734460830688</t>
+    <t xml:space="preserve">6.37734508514404</t>
   </si>
   <si>
     <t xml:space="preserve">6.33154678344727</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">7.78562784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77417898178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24360466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17490863800049</t>
+    <t xml:space="preserve">7.77417802810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2436056137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1749095916748</t>
   </si>
   <si>
     <t xml:space="preserve">8.01461601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99171829223633</t>
+    <t xml:space="preserve">7.99171733856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041526794434</t>
@@ -3179,46 +3179,46 @@
     <t xml:space="preserve">7.93447017669678</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08331298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31230163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28940296173096</t>
+    <t xml:space="preserve">8.08331394195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3123025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
     <t xml:space="preserve">8.33520126342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27795505523682</t>
+    <t xml:space="preserve">8.2779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766147613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18635845184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34665107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16346073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186412811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925712585449</t>
+    <t xml:space="preserve">8.11766242980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18635940551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34665012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215484619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16345977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925807952881</t>
   </si>
   <si>
     <t xml:space="preserve">7.94592046737671</t>
@@ -3227,25 +3227,25 @@
     <t xml:space="preserve">7.95736932754517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8428750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92301940917969</t>
+    <t xml:space="preserve">7.84287548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92301988601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.81997585296631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86577320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099956512451</t>
+    <t xml:space="preserve">7.86577367782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3809986114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99926853179932</t>
+    <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.20536041259766</t>
@@ -3263,25 +3263,25 @@
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0813264846802</t>
+    <t xml:space="preserve">9.71136856079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0813255310059</t>
   </si>
   <si>
     <t xml:space="preserve">10.2894277572632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3009881973267</t>
+    <t xml:space="preserve">10.300989151001</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5206499099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3587951660156</t>
+    <t xml:space="preserve">10.5206508636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
     <t xml:space="preserve">10.5437726974487</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628438949585</t>
+    <t xml:space="preserve">10.4628448486328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050388336182</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044492721558</t>
+    <t xml:space="preserve">10.1044502258301</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663049697876</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">10.0582046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0235204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1506938934326</t>
+    <t xml:space="preserve">9.95415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0235214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1506948471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.0697650909424</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">10.092887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1160106658936</t>
+    <t xml:space="preserve">10.1160116195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.2547435760498</t>
@@ -3347,16 +3347,16 @@
     <t xml:space="preserve">10.2200613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4859666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853761672974</t>
+    <t xml:space="preserve">10.4859676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1853771209717</t>
   </si>
   <si>
     <t xml:space="preserve">10.0350828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.416600227356</t>
+    <t xml:space="preserve">10.4165992736816</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738157272339</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">10.1391324996948</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1911973953247</t>
+    <t xml:space="preserve">11.191198348999</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056610107422</t>
@@ -3380,16 +3380,16 @@
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.42982006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5796527862549</t>
+    <t xml:space="preserve">11.5611543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426568984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298191070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5796518325806</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501667022705</t>
@@ -3398,13 +3398,13 @@
     <t xml:space="preserve">11.3576765060425</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3206825256348</t>
+    <t xml:space="preserve">11.3206834793091</t>
   </si>
   <si>
     <t xml:space="preserve">11.6536436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3946743011475</t>
+    <t xml:space="preserve">11.3946733474731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686641693115</t>
@@ -3422,19 +3422,19 @@
     <t xml:space="preserve">12.0420989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8941144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.2455739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">13.7254018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631796836853</t>
+    <t xml:space="preserve">14.6317958831787</t>
   </si>
   <si>
     <t xml:space="preserve">14.0398664474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7439002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4109392166138</t>
+    <t xml:space="preserve">13.7438993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4109401702881</t>
   </si>
   <si>
     <t xml:space="preserve">13.7623987197876</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669923782349</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457015991211</t>
+    <t xml:space="preserve">15.4457025527954</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011959075928</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">16.2596092224121</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3520965576172</t>
+    <t xml:space="preserve">16.3520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">16.019136428833</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">16.1486186981201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0006370544434</t>
+    <t xml:space="preserve">16.000638961792</t>
   </si>
   <si>
     <t xml:space="preserve">15.9081506729126</t>
@@ -3545,25 +3545,25 @@
     <t xml:space="preserve">15.4642000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8896522521973</t>
+    <t xml:space="preserve">15.8896503448486</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092645645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283208847046</t>
+    <t xml:space="preserve">15.8341588973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">14.502311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2433414459229</t>
+    <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
     <t xml:space="preserve">13.6329126358032</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369483947754</t>
+    <t xml:space="preserve">13.3369474411011</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">13.7808961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629566192627</t>
+    <t xml:space="preserve">13.2629556655884</t>
   </si>
   <si>
     <t xml:space="preserve">13.5404243469238</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">13.3924407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3554449081421</t>
+    <t xml:space="preserve">13.3554439544678</t>
   </si>
   <si>
     <t xml:space="preserve">13.965874671936</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">14.2988357543945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2803382873535</t>
+    <t xml:space="preserve">14.2803373336792</t>
   </si>
   <si>
     <t xml:space="preserve">14.1138572692871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9484920501709</t>
+    <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
     <t xml:space="preserve">13.1334705352783</t>
@@ -3635,16 +3635,16 @@
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479341506958</t>
+    <t xml:space="preserve">13.4479351043701</t>
   </si>
   <si>
     <t xml:space="preserve">12.2085790634155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3935565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.18896484375</t>
+    <t xml:space="preserve">12.3935575485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1889657974243</t>
   </si>
   <si>
     <t xml:space="preserve">13.4664325714111</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.9496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6721420288086</t>
+    <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681072235107</t>
+    <t xml:space="preserve">11.9681062698364</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">11.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8201236724854</t>
+    <t xml:space="preserve">11.8201246261597</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6710243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265186309814</t>
+    <t xml:space="preserve">12.6710252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265176773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.8005104064941</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">13.2259607315063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3276977539062</t>
+    <t xml:space="preserve">13.3276987075806</t>
   </si>
   <si>
     <t xml:space="preserve">13.3646945953369</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">12.6617765426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
+    <t xml:space="preserve">12.4305534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028062820435</t>
   </si>
   <si>
     <t xml:space="preserve">12.5137929916382</t>
@@ -3743,10 +3743,10 @@
     <t xml:space="preserve">12.3473138809204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4952955245972</t>
+    <t xml:space="preserve">12.3288145065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4952964782715</t>
   </si>
   <si>
     <t xml:space="preserve">12.6155319213867</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">11.8016262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9958534240723</t>
+    <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.3565607070923</t>
@@ -3776,19 +3776,19 @@
     <t xml:space="preserve">11.5519046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2929372787476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">11.2929363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6455097198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0987071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5704050064087</t>
+    <t xml:space="preserve">11.098708152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5704040527344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605554580688</t>
+    <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">11.569953918457</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432819366455</t>
+    <t xml:space="preserve">12.1432809829712</t>
   </si>
   <si>
     <t xml:space="preserve">11.85191822052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7579298019409</t>
+    <t xml:space="preserve">11.6639413833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7579307556152</t>
   </si>
   <si>
     <t xml:space="preserve">11.974102973938</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">10.5642786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0530185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5830764770508</t>
+    <t xml:space="preserve">11.053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5830774307251</t>
   </si>
   <si>
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
+    <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4571666717529</t>
+    <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631801605225</t>
+    <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075487136841</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.096287727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876523971558</t>
+    <t xml:space="preserve">12.0962867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
+    <t xml:space="preserve">12.8481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.998574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1677541732788</t>
+    <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.4685163497925</t>
@@ -3926,37 +3926,37 @@
     <t xml:space="preserve">13.6188974380493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5625057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6094970703125</t>
+    <t xml:space="preserve">13.5625047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6094980239868</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564922332764</t>
+    <t xml:space="preserve">13.6564931869507</t>
   </si>
   <si>
     <t xml:space="preserve">13.741081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6752901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8726654052734</t>
+    <t xml:space="preserve">13.6752910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8726663589478</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3087358474731</t>
+    <t xml:space="preserve">13.3087368011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1583547592163</t>
+    <t xml:space="preserve">13.158353805542</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">13.2335453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0643653869629</t>
+    <t xml:space="preserve">13.0925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0643663406372</t>
   </si>
   <si>
     <t xml:space="preserve">13.1113605499268</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850257873535</t>
+    <t xml:space="preserve">12.5850267410278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756282806396</t>
@@ -4013,13 +4013,13 @@
     <t xml:space="preserve">13.1207599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1056871414185</t>
+    <t xml:space="preserve">12.1056861877441</t>
   </si>
   <si>
     <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692138671875</t>
+    <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
     <t xml:space="preserve">11.391375541687</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548801422119</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">10.6582670211792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9778270721436</t>
+    <t xml:space="preserve">10.3951015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
     <t xml:space="preserve">11.4665660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1939992904663</t>
+    <t xml:space="preserve">11.1940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667667388916</t>
+    <t xml:space="preserve">10.6676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">11.7485313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1150856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">12.1150846481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">12.773003578186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0455684661865</t>
+    <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.0831651687622</t>
@@ -4157,16 +4157,16 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2580184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504816055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2805395126343</t>
+    <t xml:space="preserve">14.258017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2805404663086</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463315963745</t>
+    <t xml:space="preserve">13.3463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523431777954</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">13.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3933248519897</t>
+    <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">13.7598791122437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7316827774048</t>
+    <t xml:space="preserve">13.7316818237305</t>
   </si>
   <si>
     <t xml:space="preserve">14.0606422424316</t>
@@ -4217,58 +4217,58 @@
     <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8914623260498</t>
+    <t xml:space="preserve">13.7786769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4215211868286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0888376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5587797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749528884888</t>
+    <t xml:space="preserve">14.0888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5587787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749519348145</t>
   </si>
   <si>
     <t xml:space="preserve">14.8407440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0193223953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0099239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6997623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7279586791992</t>
+    <t xml:space="preserve">15.0193214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0099229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6997632980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7279596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031492233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7655544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7937507629395</t>
+    <t xml:space="preserve">14.8031482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7655534744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7937498092651</t>
   </si>
   <si>
     <t xml:space="preserve">14.6621675491333</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">14.6903638839722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689413070679</t>
+    <t xml:space="preserve">14.8689403533936</t>
   </si>
   <si>
     <t xml:space="preserve">15.1039113998413</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">11.3725786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9872255325317</t>
+    <t xml:space="preserve">10.9872264862061</t>
   </si>
   <si>
     <t xml:space="preserve">11.269190788269</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">11.4477691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4101734161377</t>
+    <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1846017837524</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">11.1094102859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0812149047852</t>
+    <t xml:space="preserve">11.2221975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0812139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.0342197418213</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">10.8744401931763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9590291976929</t>
+    <t xml:space="preserve">10.9590301513672</t>
   </si>
   <si>
     <t xml:space="preserve">10.9026374816895</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146596908569</t>
+    <t xml:space="preserve">10.7146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8650426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4138975143433</t>
+    <t xml:space="preserve">10.8650417327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4138984680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387069702148</t>
@@ -5805,6 +5805,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.8800001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5699996948242</t>
   </si>
 </sst>
 </file>
@@ -70805,7 +70808,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6496412037</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>66904</v>
@@ -70826,6 +70829,32 @@
         <v>1889</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493055556</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>108428</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>11.3599996566772</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>11.5799999237061</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>11.5699996948242</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1931</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15079426765442</t>
+    <t xml:space="preserve">2.15079474449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.13486289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768843650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07379078865051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02334046363831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06316924095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05254864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96492338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988330364227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802945137024</t>
+    <t xml:space="preserve">2.09768867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07379055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02333998680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06316947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05254817008972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492326259613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988354206085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802968978882</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696753501892</t>
@@ -83,85 +83,85 @@
     <t xml:space="preserve">2.00209784507751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00156688690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.059983253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00528430938721</t>
+    <t xml:space="preserve">2.00156664848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05998349189758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00528407096863</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909184455872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97819995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8985413312912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774951457977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943274021149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447281837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93305993080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712784767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589554309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436811208725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450173377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203736305237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10830974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13964223861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14548397064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15344977378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1481397151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132546424866</t>
+    <t xml:space="preserve">1.97820007801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854109287262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774903774261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9394326210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447269916534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712820529938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633626937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368135929108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441233634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450244903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10831022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1396427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14548444747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813923835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132570266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831970214844</t>
@@ -170,31 +170,31 @@
     <t xml:space="preserve">2.18265795707703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22248792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955212593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10565447807312</t>
+    <t xml:space="preserve">2.22248768806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1056547164917</t>
   </si>
   <si>
     <t xml:space="preserve">2.08706760406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12158608436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1401731967926</t>
+    <t xml:space="preserve">2.07219767570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.121586561203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017295837402</t>
   </si>
   <si>
     <t xml:space="preserve">2.12424159049988</t>
@@ -203,91 +203,91 @@
     <t xml:space="preserve">2.11362051963806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06582498550415</t>
+    <t xml:space="preserve">2.06582522392273</t>
   </si>
   <si>
     <t xml:space="preserve">2.05307960510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0684802532196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901144981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11839985847473</t>
+    <t xml:space="preserve">2.06848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901121139526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11840009689331</t>
   </si>
   <si>
     <t xml:space="preserve">2.12477278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16141605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15557408332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17734789848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373030662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169658660889</t>
+    <t xml:space="preserve">2.16141581535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15557432174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1773476600647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373006820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
     <t xml:space="preserve">2.29418110847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25753808021545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461247444153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21452212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2463858127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098468780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073402404785</t>
+    <t xml:space="preserve">2.25753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21452164649963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638533592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098492622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073378562927</t>
   </si>
   <si>
     <t xml:space="preserve">2.34888005256653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32604455947876</t>
+    <t xml:space="preserve">2.32604432106018</t>
   </si>
   <si>
     <t xml:space="preserve">2.4492506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5028874874115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555318832397</t>
+    <t xml:space="preserve">2.50288820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56555366516113</t>
   </si>
   <si>
     <t xml:space="preserve">2.52997183799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6154727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555070877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66718316078186</t>
+    <t xml:space="preserve">2.61547231674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555047035217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66718339920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.70147585868835</t>
@@ -296,22 +296,22 @@
     <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72161531448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894074440002</t>
+    <t xml:space="preserve">2.72161555290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346585273743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894026756287</t>
   </si>
   <si>
     <t xml:space="preserve">2.98942232131958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00248622894287</t>
+    <t xml:space="preserve">3.00248646736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.94587683677673</t>
@@ -320,43 +320,43 @@
     <t xml:space="preserve">2.8413667678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91757202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685669898987</t>
+    <t xml:space="preserve">2.91757154464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668559074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959366798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685646057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.69548797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531686782837</t>
+    <t xml:space="preserve">2.78693413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531710624695</t>
   </si>
   <si>
     <t xml:space="preserve">2.98289060592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84789872169495</t>
+    <t xml:space="preserve">2.84789848327637</t>
   </si>
   <si>
     <t xml:space="preserve">2.77604794502258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313939094543</t>
+    <t xml:space="preserve">2.86313962936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.91974925994873</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97418093681335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813151359558</t>
+    <t xml:space="preserve">2.97418165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813175201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9785361289978</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">3.03514552116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04820919036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998229026794</t>
+    <t xml:space="preserve">3.04820942878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998252868652</t>
   </si>
   <si>
     <t xml:space="preserve">3.15707421302795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29859781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730700492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771185874939</t>
+    <t xml:space="preserve">3.29859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730748176575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214425086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29206585884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771162033081</t>
   </si>
   <si>
     <t xml:space="preserve">3.26158404350281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24416565895081</t>
+    <t xml:space="preserve">3.24416589736938</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988885879517</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">3.2572295665741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26593899726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17449235916138</t>
+    <t xml:space="preserve">3.26593852043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17449259757996</t>
   </si>
   <si>
     <t xml:space="preserve">3.25505208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25940680503845</t>
+    <t xml:space="preserve">3.25940656661987</t>
   </si>
   <si>
     <t xml:space="preserve">3.33125758171082</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">3.35085320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34432101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472586631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28553438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247071266174</t>
+    <t xml:space="preserve">3.34432125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28553414344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247047424316</t>
   </si>
   <si>
     <t xml:space="preserve">3.35303020477295</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">3.32037091255188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682518959045</t>
+    <t xml:space="preserve">3.27682542800903</t>
   </si>
   <si>
     <t xml:space="preserve">3.31383919715881</t>
@@ -467,46 +467,46 @@
     <t xml:space="preserve">3.15054225921631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18973326683044</t>
+    <t xml:space="preserve">3.18973350524902</t>
   </si>
   <si>
     <t xml:space="preserve">3.20932912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20062017440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239303588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175539016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262606620789</t>
+    <t xml:space="preserve">3.25069761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20061993598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239279747009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175491333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33343482017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497488975525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262582778931</t>
   </si>
   <si>
     <t xml:space="preserve">3.43141293525696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59253239631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962431907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631114959717</t>
+    <t xml:space="preserve">3.59253263473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631138801575</t>
   </si>
   <si>
     <t xml:space="preserve">3.90824055671692</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">4.09330987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831823348999</t>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831751823425</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
@@ -533,40 +533,40 @@
     <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483467102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313829421997</t>
+    <t xml:space="preserve">4.23483371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313924789429</t>
   </si>
   <si>
     <t xml:space="preserve">4.47433567047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68988847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65722894668579</t>
+    <t xml:space="preserve">4.68988800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65722846984863</t>
   </si>
   <si>
     <t xml:space="preserve">4.64634227752686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75956106185913</t>
+    <t xml:space="preserve">4.75956201553345</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334100723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94245338439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72036981582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7421441078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73778915405273</t>
+    <t xml:space="preserve">4.94245386123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72037076950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74214315414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73778867721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.64416456222534</t>
@@ -584,61 +584,61 @@
     <t xml:space="preserve">4.34152126312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22830247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128847122192</t>
+    <t xml:space="preserve">4.22830200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128751754761</t>
   </si>
   <si>
     <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572086334229</t>
+    <t xml:space="preserve">4.22612476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24572038650513</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35458469390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33934450149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
+    <t xml:space="preserve">4.35458421707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940618515015</t>
   </si>
   <si>
     <t xml:space="preserve">4.63763236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63545560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6158595085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851951599121</t>
+    <t xml:space="preserve">4.63545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61586046218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851999282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.72254753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6637601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58973264694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51134967803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5244140625</t>
+    <t xml:space="preserve">4.59408760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66376066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58973217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51135015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52441453933716</t>
   </si>
   <si>
     <t xml:space="preserve">4.73343372344971</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.64198732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78568935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77480173110962</t>
+    <t xml:space="preserve">4.78568887710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77480316162109</t>
   </si>
   <si>
     <t xml:space="preserve">4.746497631073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76609325408936</t>
+    <t xml:space="preserve">4.76609373092651</t>
   </si>
   <si>
     <t xml:space="preserve">5.09921884536743</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">5.38662147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082059860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25162982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22985649108887</t>
+    <t xml:space="preserve">5.29082107543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25162935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22985601425171</t>
   </si>
   <si>
     <t xml:space="preserve">5.22767972946167</t>
@@ -683,70 +683,70 @@
     <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11010551452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22550201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27558040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31041574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106962203979</t>
+    <t xml:space="preserve">5.11010599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22550249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27557992935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17107009887695</t>
   </si>
   <si>
     <t xml:space="preserve">5.14494180679321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09050989151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10139656066895</t>
+    <t xml:space="preserve">5.06220531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09050941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043292999268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11446046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1013970375061</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12752342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95769500732422</t>
+    <t xml:space="preserve">5.12752389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478693008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95769453048706</t>
   </si>
   <si>
     <t xml:space="preserve">5.02736854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98817682266235</t>
+    <t xml:space="preserve">4.98817729949951</t>
   </si>
   <si>
     <t xml:space="preserve">4.88584423065186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86624908447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8553614616394</t>
+    <t xml:space="preserve">4.86624813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85536193847656</t>
   </si>
   <si>
     <t xml:space="preserve">4.84665298461914</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561096191406</t>
+    <t xml:space="preserve">4.7356104850769</t>
   </si>
   <si>
     <t xml:space="preserve">4.79004335403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74432039260864</t>
+    <t xml:space="preserve">4.74431991577148</t>
   </si>
   <si>
     <t xml:space="preserve">4.75738382339478</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">4.68117904663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8205246925354</t>
+    <t xml:space="preserve">4.82052564620972</t>
   </si>
   <si>
     <t xml:space="preserve">4.91850280761719</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">5.1384105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19719791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09486389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170726776123</t>
+    <t xml:space="preserve">5.08397769927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19719696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881494522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170774459839</t>
   </si>
   <si>
     <t xml:space="preserve">5.38444423675537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41710376739502</t>
+    <t xml:space="preserve">5.41710329055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209589004517</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134881973267</t>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385251998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134929656982</t>
   </si>
   <si>
     <t xml:space="preserve">5.94400835037231</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">6.11383724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81337022781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87868928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75893831253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76329326629639</t>
+    <t xml:space="preserve">5.81337118148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87869024276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75893878936768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76329374313354</t>
   </si>
   <si>
     <t xml:space="preserve">5.88957595825195</t>
@@ -839,22 +839,22 @@
     <t xml:space="preserve">5.89610767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9766674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0964183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94836187362671</t>
+    <t xml:space="preserve">5.97666788101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09641885757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94836330413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.98973178863525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98755502700806</t>
+    <t xml:space="preserve">6.0049729347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98755407333374</t>
   </si>
   <si>
     <t xml:space="preserve">6.04198694229126</t>
@@ -866,91 +866,91 @@
     <t xml:space="preserve">6.08335494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96360445022583</t>
+    <t xml:space="preserve">5.96360301971436</t>
   </si>
   <si>
     <t xml:space="preserve">6.07464599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13996458053589</t>
+    <t xml:space="preserve">6.13996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26842546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276323318481</t>
+    <t xml:space="preserve">6.26842594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52969980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276371002197</t>
   </si>
   <si>
     <t xml:space="preserve">6.58848714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80403900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201711654663</t>
+    <t xml:space="preserve">6.80403852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.01088190078735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06531429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063192367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321401596069</t>
+    <t xml:space="preserve">7.06531476974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11756896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32005643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425699234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321449279785</t>
   </si>
   <si>
     <t xml:space="preserve">7.29393005371094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37666797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521966934204</t>
+    <t xml:space="preserve">7.37666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28522062301636</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481624603271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19595098495483</t>
+    <t xml:space="preserve">7.19595050811768</t>
   </si>
   <si>
     <t xml:space="preserve">6.46655893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40124034881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6124382019043</t>
+    <t xml:space="preserve">6.22705698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47308969497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40123987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
     <t xml:space="preserve">6.49704074859619</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">6.52316808700562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57760047912598</t>
+    <t xml:space="preserve">6.57760000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.52464437484741</t>
@@ -974,40 +974,40 @@
     <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45403623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91740274429321</t>
+    <t xml:space="preserve">6.45403575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774164199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91740322113037</t>
   </si>
   <si>
     <t xml:space="preserve">6.76294755935669</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82252264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652536392212</t>
+    <t xml:space="preserve">6.82252359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">6.58421993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50478553771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093896865845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48713397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35694932937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488464355469</t>
+    <t xml:space="preserve">6.50478506088257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48713350296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35694980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
     <t xml:space="preserve">6.43417739868164</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">6.32826519012451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33267831802368</t>
+    <t xml:space="preserve">6.33267784118652</t>
   </si>
   <si>
     <t xml:space="preserve">6.3746018409729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16057109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14291858673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757150650024</t>
+    <t xml:space="preserve">6.16057062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1429181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9575719833374</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344165802002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90240859985352</t>
+    <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771314620972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95977783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92006063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93330001831055</t>
+    <t xml:space="preserve">5.78546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95977830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92006158828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93329906463623</t>
   </si>
   <si>
     <t xml:space="preserve">5.94212627410889</t>
@@ -1061,19 +1061,19 @@
     <t xml:space="preserve">5.8362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84724617004395</t>
+    <t xml:space="preserve">5.8472466468811</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720411300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50744438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46993350982666</t>
+    <t xml:space="preserve">5.69720363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50744390487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46993446350098</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894346237183</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">5.73692035675049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76119232177734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89137601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71485614776611</t>
+    <t xml:space="preserve">5.76119184494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89137697219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71485567092896</t>
   </si>
   <si>
     <t xml:space="preserve">5.72147560119629</t>
@@ -1097,22 +1097,22 @@
     <t xml:space="preserve">5.5912914276123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55819463729858</t>
+    <t xml:space="preserve">5.55819368362427</t>
   </si>
   <si>
     <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54495429992676</t>
+    <t xml:space="preserve">5.54495477676392</t>
   </si>
   <si>
     <t xml:space="preserve">5.4434552192688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932489395142</t>
+    <t xml:space="preserve">5.45007562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932537078857</t>
   </si>
   <si>
     <t xml:space="preserve">5.4191837310791</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">5.49199819564819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56040048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52730274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45890092849731</t>
+    <t xml:space="preserve">5.56040096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52730226516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45890045166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.41256427764893</t>
@@ -1139,31 +1139,31 @@
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922578811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912715911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6641058921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80311584472656</t>
+    <t xml:space="preserve">5.56922626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66410636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80311632156372</t>
   </si>
   <si>
     <t xml:space="preserve">5.86931133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030042648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532217025757</t>
+    <t xml:space="preserve">5.73030185699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532312393188</t>
   </si>
   <si>
     <t xml:space="preserve">5.63762760162354</t>
@@ -1172,40 +1172,40 @@
     <t xml:space="preserve">5.5648136138916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.478759765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4942045211792</t>
+    <t xml:space="preserve">5.52068376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49420547485352</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22942495346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045658111572</t>
+    <t xml:space="preserve">5.29782581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22942352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045610427856</t>
   </si>
   <si>
     <t xml:space="preserve">5.25369596481323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41477155685425</t>
+    <t xml:space="preserve">5.41477108001709</t>
   </si>
   <si>
     <t xml:space="preserve">5.39711856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796792984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22280502319336</t>
+    <t xml:space="preserve">5.27796697616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2228045463562</t>
   </si>
   <si>
     <t xml:space="preserve">5.14116382598877</t>
@@ -1220,70 +1220,70 @@
     <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13233804702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13675117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03745746612549</t>
+    <t xml:space="preserve">5.13233709335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1367506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03745794296265</t>
   </si>
   <si>
     <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96464252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126245498657</t>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126293182373</t>
   </si>
   <si>
     <t xml:space="preserve">5.04849004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19412040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
+    <t xml:space="preserve">5.19411993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576112747192</t>
   </si>
   <si>
     <t xml:space="preserve">5.22501134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24486970901489</t>
+    <t xml:space="preserve">5.24487018585205</t>
   </si>
   <si>
     <t xml:space="preserve">5.11689281463623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87196922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72633981704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131902694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60453033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81194162368774</t>
+    <t xml:space="preserve">5.03083753585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87197017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72634029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9315447807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839189529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60453081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
   </si>
   <si>
     <t xml:space="preserve">5.84503984451294</t>
@@ -1295,10 +1295,10 @@
     <t xml:space="preserve">5.90461540222168</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86489772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663850784302</t>
+    <t xml:space="preserve">5.86489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663898468018</t>
   </si>
   <si>
     <t xml:space="preserve">5.81856155395508</t>
@@ -1310,19 +1310,19 @@
     <t xml:space="preserve">5.63983488082886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376699447632</t>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.023766040802</t>
   </si>
   <si>
     <t xml:space="preserve">6.19366788864136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06348419189453</t>
+    <t xml:space="preserve">6.06348371505737</t>
   </si>
   <si>
     <t xml:space="preserve">6.14071178436279</t>
@@ -1331,22 +1331,22 @@
     <t xml:space="preserve">6.12526607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02597332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80973529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034391403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020227432251</t>
+    <t xml:space="preserve">6.02597379684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479909896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034343719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020275115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.82518148422241</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">6.01935434341431</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85607290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926927566528</t>
+    <t xml:space="preserve">5.85607242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
   </si>
   <si>
     <t xml:space="preserve">5.84283256530762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03259229660034</t>
+    <t xml:space="preserve">6.0325927734375</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95315837860107</t>
+    <t xml:space="preserve">5.95315790176392</t>
   </si>
   <si>
     <t xml:space="preserve">5.94433259963989</t>
@@ -1391,28 +1391,28 @@
     <t xml:space="preserve">6.2885479927063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235250473022</t>
+    <t xml:space="preserve">6.28413438796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
   </si>
   <si>
     <t xml:space="preserve">6.52243757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37239503860474</t>
+    <t xml:space="preserve">6.37239551544189</t>
   </si>
   <si>
     <t xml:space="preserve">6.1693959236145</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09878826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996152877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
+    <t xml:space="preserve">6.09878778457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5559868812561</t>
   </si>
   <si>
     <t xml:space="preserve">6.11202764511108</t>
@@ -1421,22 +1421,22 @@
     <t xml:space="preserve">5.92226791381836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79428958892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072629928589</t>
+    <t xml:space="preserve">5.79429006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072534561157</t>
   </si>
   <si>
     <t xml:space="preserve">5.68396472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4280104637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372446060181</t>
+    <t xml:space="preserve">5.42800903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339864730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372493743896</t>
   </si>
   <si>
     <t xml:space="preserve">5.97963619232178</t>
@@ -1448,34 +1448,34 @@
     <t xml:space="preserve">6.17822217941284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474348068237</t>
+    <t xml:space="preserve">6.27089643478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474300384521</t>
   </si>
   <si>
     <t xml:space="preserve">6.72543668746948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68571901321411</t>
+    <t xml:space="preserve">6.68571949005127</t>
   </si>
   <si>
     <t xml:space="preserve">6.9284348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90637016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697877883911</t>
+    <t xml:space="preserve">6.90636968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697830200195</t>
   </si>
   <si>
     <t xml:space="preserve">7.1005425453186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87106561660767</t>
+    <t xml:space="preserve">6.87106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">6.95050001144409</t>
@@ -1484,16 +1484,16 @@
     <t xml:space="preserve">7.22852039337158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14908599853516</t>
+    <t xml:space="preserve">7.14908647537231</t>
   </si>
   <si>
     <t xml:space="preserve">7.0475869178772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11378192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082534790039</t>
+    <t xml:space="preserve">7.11378240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082630157471</t>
   </si>
   <si>
     <t xml:space="preserve">7.49330139160156</t>
@@ -1505,97 +1505,97 @@
     <t xml:space="preserve">7.18439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147602081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523847579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21969413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127828598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56391000747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062952041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738965988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835073471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61952447891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219682693481</t>
+    <t xml:space="preserve">7.440345287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528196334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5374321937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738870620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450225830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219778060913</t>
   </si>
   <si>
     <t xml:space="preserve">6.38247346878052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30643796920776</t>
+    <t xml:space="preserve">6.30643892288208</t>
   </si>
   <si>
     <t xml:space="preserve">6.59716081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66425037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
+    <t xml:space="preserve">6.66424989700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294124603271</t>
   </si>
   <si>
     <t xml:space="preserve">6.54796123504639</t>
@@ -1604,40 +1604,40 @@
     <t xml:space="preserve">6.65977811813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57926988601685</t>
+    <t xml:space="preserve">6.579270362854</t>
   </si>
   <si>
     <t xml:space="preserve">6.48534488677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370407104492</t>
+    <t xml:space="preserve">6.71344995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">6.75817584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61505174636841</t>
+    <t xml:space="preserve">6.61505222320557</t>
   </si>
   <si>
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
+    <t xml:space="preserve">6.48087167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22145795822144</t>
@@ -1649,79 +1649,79 @@
     <t xml:space="preserve">6.26171159744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14094972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356702804565</t>
+    <t xml:space="preserve">6.14095020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356750488281</t>
   </si>
   <si>
     <t xml:space="preserve">6.34669208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854894638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21251344680786</t>
+    <t xml:space="preserve">6.24829339981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
     <t xml:space="preserve">6.33774709701538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58821487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981761932373</t>
+    <t xml:space="preserve">6.58821535110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981714248657</t>
   </si>
   <si>
     <t xml:space="preserve">6.53007125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44509029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40036392211914</t>
+    <t xml:space="preserve">6.44061756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44509077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
   </si>
   <si>
     <t xml:space="preserve">6.37352800369263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42720031738281</t>
+    <t xml:space="preserve">6.42719984054565</t>
   </si>
   <si>
     <t xml:space="preserve">6.43167304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
+    <t xml:space="preserve">6.50323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
   </si>
   <si>
     <t xml:space="preserve">6.23934888839722</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19014930725098</t>
+    <t xml:space="preserve">6.19014978408813</t>
   </si>
   <si>
     <t xml:space="preserve">6.27960252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46298122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188766479492</t>
+    <t xml:space="preserve">6.46298170089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
   </si>
   <si>
     <t xml:space="preserve">6.10069704055786</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">6.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18567657470703</t>
+    <t xml:space="preserve">6.18567705154419</t>
   </si>
   <si>
     <t xml:space="preserve">5.98440742492676</t>
@@ -1739,31 +1739,31 @@
     <t xml:space="preserve">5.47452545166016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33587312698364</t>
+    <t xml:space="preserve">5.3358736038208</t>
   </si>
   <si>
     <t xml:space="preserve">5.24194717407227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358846664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013124465942</t>
+    <t xml:space="preserve">5.0809326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013076782227</t>
   </si>
   <si>
     <t xml:space="preserve">5.01831483840942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0764594078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700571060181</t>
+    <t xml:space="preserve">5.07645988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700618743896</t>
   </si>
   <si>
     <t xml:space="preserve">4.92886209487915</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577606201172</t>
+    <t xml:space="preserve">4.58894014358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577558517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.74995565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71417474746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201642990112</t>
+    <t xml:space="preserve">4.71417427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201690673828</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876502990723</t>
+    <t xml:space="preserve">4.20876550674438</t>
   </si>
   <si>
     <t xml:space="preserve">4.11483907699585</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">3.95829653739929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08353090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15509366989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049364089966</t>
+    <t xml:space="preserve">4.08353042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15509271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1304931640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.01867723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86884307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559167861938</t>
+    <t xml:space="preserve">3.86884331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559144020081</t>
   </si>
   <si>
     <t xml:space="preserve">3.75702714920044</t>
@@ -1829,16 +1829,16 @@
     <t xml:space="preserve">3.81740760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466396331787</t>
+    <t xml:space="preserve">3.73466467857361</t>
   </si>
   <si>
     <t xml:space="preserve">3.83753418922424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84648060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500515937805</t>
+    <t xml:space="preserve">3.84648036956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500539779663</t>
   </si>
   <si>
     <t xml:space="preserve">4.15733003616333</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475152015686</t>
+    <t xml:space="preserve">3.92475199699402</t>
   </si>
   <si>
     <t xml:space="preserve">3.9314603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94264197349548</t>
+    <t xml:space="preserve">3.9426417350769</t>
   </si>
   <si>
     <t xml:space="preserve">3.87331628799438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86213421821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512270927429</t>
+    <t xml:space="preserve">3.8621346950531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424376487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512318611145</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896134376526</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">3.16216444969177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38803315162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26950788497925</t>
+    <t xml:space="preserve">3.3835608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38803339004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26950812339783</t>
   </si>
   <si>
     <t xml:space="preserve">3.22701811790466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45288681983948</t>
+    <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.39474248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48866820335388</t>
+    <t xml:space="preserve">3.4886679649353</t>
   </si>
   <si>
     <t xml:space="preserve">3.5155041217804</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735052108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182301521301</t>
+    <t xml:space="preserve">2.92735075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182277679443</t>
   </si>
   <si>
     <t xml:space="preserve">3.010094165802</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03916692733765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95642280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88486003875732</t>
+    <t xml:space="preserve">3.03916668891907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95642232894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88485980033875</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511415481567</t>
@@ -1946,31 +1946,31 @@
     <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869843482971</t>
+    <t xml:space="preserve">2.78869819641113</t>
   </si>
   <si>
     <t xml:space="preserve">2.83342480659485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88933253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07271146774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625672340393</t>
+    <t xml:space="preserve">2.88933277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
     <t xml:space="preserve">3.16887354850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22925424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22254514694214</t>
+    <t xml:space="preserve">3.22925448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1599280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22254538536072</t>
   </si>
   <si>
     <t xml:space="preserve">3.23596334457397</t>
@@ -1979,28 +1979,28 @@
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347286224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32094383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54233980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5333948135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49537706375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61166620254517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533756256104</t>
+    <t xml:space="preserve">3.19347310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53339457511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49537754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61166596412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533780097961</t>
   </si>
   <si>
     <t xml:space="preserve">3.57588458061218</t>
@@ -2009,22 +2009,22 @@
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221298217773</t>
+    <t xml:space="preserve">3.52221274375916</t>
   </si>
   <si>
     <t xml:space="preserve">3.5825936794281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444934844971</t>
+    <t xml:space="preserve">3.43723249435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444911003113</t>
   </si>
   <si>
     <t xml:space="preserve">3.58483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69441032409668</t>
+    <t xml:space="preserve">3.69440960884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
@@ -2033,31 +2033,31 @@
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399036407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567923545837</t>
+    <t xml:space="preserve">3.70335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80399012565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567899703979</t>
   </si>
   <si>
     <t xml:space="preserve">3.77268147468567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766172409058</t>
+    <t xml:space="preserve">3.83306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766196250916</t>
   </si>
   <si>
     <t xml:space="preserve">3.94040560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99184203147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011318206787</t>
+    <t xml:space="preserve">3.99184131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011270523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.13272953033447</t>
@@ -2066,22 +2066,22 @@
     <t xml:space="preserve">4.09247589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25125455856323</t>
+    <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9493510723114</t>
+    <t xml:space="preserve">3.94935154914856</t>
   </si>
   <si>
     <t xml:space="preserve">4.00525951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02762222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842335700989</t>
+    <t xml:space="preserve">4.02762317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842359542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.23112821578979</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">4.28256368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38319778442383</t>
+    <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.42792463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3541259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1662745475769</t>
+    <t xml:space="preserve">4.35412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16627407073975</t>
   </si>
   <si>
     <t xml:space="preserve">4.20429229736328</t>
@@ -2108,73 +2108,73 @@
     <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20205593109131</t>
+    <t xml:space="preserve">4.20205545425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2915096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24901866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24007320404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25349187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07458591461182</t>
+    <t xml:space="preserve">4.29150867462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24901914596558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24007272720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25349140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982004165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.15285730361938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171425819397</t>
+    <t xml:space="preserve">4.1864013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171473503113</t>
   </si>
   <si>
     <t xml:space="preserve">3.93369698524475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90015196800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631428718567</t>
+    <t xml:space="preserve">3.9001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
   </si>
   <si>
     <t xml:space="preserve">4.0388035774231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03656768798828</t>
+    <t xml:space="preserve">4.03656721115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.01644086837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804265975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778925895691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76820826530457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77491760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65191960334778</t>
+    <t xml:space="preserve">3.9180428981781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778878211975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820874214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77491784095764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
     <t xml:space="preserve">3.85095262527466</t>
@@ -2183,58 +2183,58 @@
     <t xml:space="preserve">4.0991849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82411670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95693063735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8813648223877</t>
+    <t xml:space="preserve">3.82411694526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
     <t xml:space="preserve">3.76229000091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74626064300537</t>
+    <t xml:space="preserve">3.74626088142395</t>
   </si>
   <si>
     <t xml:space="preserve">3.7645800113678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901371955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67298436164856</t>
+    <t xml:space="preserve">3.68901348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67298460006714</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243631362915</t>
+    <t xml:space="preserve">3.84243607521057</t>
   </si>
   <si>
     <t xml:space="preserve">3.87220478057861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92487215995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96609044075012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739322662354</t>
+    <t xml:space="preserve">3.92487192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96608996391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739394187927</t>
   </si>
   <si>
     <t xml:space="preserve">3.95006108283997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
+    <t xml:space="preserve">3.87449502944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440957069397</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165649414062</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">4.14470195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751588821411</t>
+    <t xml:space="preserve">4.18821048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438520431519</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">4.31415319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803956985474</t>
+    <t xml:space="preserve">4.40803861618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.30270433425903</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2454571723938</t>
+    <t xml:space="preserve">4.24545669555664</t>
   </si>
   <si>
     <t xml:space="preserve">4.3324728012085</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">4.22255754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
+    <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17446994781494</t>
+    <t xml:space="preserve">4.17446947097778</t>
   </si>
   <si>
     <t xml:space="preserve">4.05997562408447</t>
@@ -2312,13 +2312,13 @@
     <t xml:space="preserve">4.16302108764648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11035346984863</t>
+    <t xml:space="preserve">4.11035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.12409257888794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07600498199463</t>
+    <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
     <t xml:space="preserve">4.00730848312378</t>
@@ -2330,52 +2330,52 @@
     <t xml:space="preserve">3.97067022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94548082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701609611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8859441280365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.876784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159540176392</t>
+    <t xml:space="preserve">3.945481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594388961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159587860107</t>
   </si>
   <si>
     <t xml:space="preserve">3.95235085487366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9821195602417</t>
+    <t xml:space="preserve">4.00043869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98211908340454</t>
   </si>
   <si>
     <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493349075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16760063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04394626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0531063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18592023849487</t>
+    <t xml:space="preserve">4.11493301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16760015487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04394674301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05310583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18591976165771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06226539611816</t>
+    <t xml:space="preserve">4.06226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.34392213821411</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60268020629883</t>
+    <t xml:space="preserve">4.60267972946167</t>
   </si>
   <si>
     <t xml:space="preserve">5.00112104415894</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">5.33086490631104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35834407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62855052947998</t>
+    <t xml:space="preserve">5.35834312438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62855100631714</t>
   </si>
   <si>
     <t xml:space="preserve">5.48657703399658</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527448654175</t>
+    <t xml:space="preserve">5.55527496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451927185059</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">5.27590799331665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36292314529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44993877410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34460496902466</t>
+    <t xml:space="preserve">5.36292362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44993925094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3446044921875</t>
   </si>
   <si>
     <t xml:space="preserve">5.47283792495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45909881591797</t>
+    <t xml:space="preserve">5.45909833908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.55985403060913</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">5.7293062210083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92623567581177</t>
+    <t xml:space="preserve">5.92623615264893</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304533004761</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">5.67892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71556663513184</t>
+    <t xml:space="preserve">5.71556615829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716276168823</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">5.71098709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82090187072754</t>
+    <t xml:space="preserve">5.82090139389038</t>
   </si>
   <si>
     <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04989004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12316751480103</t>
+    <t xml:space="preserve">6.04989051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.22392225265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652830123901</t>
+    <t xml:space="preserve">6.08652925491333</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324048995972</t>
+    <t xml:space="preserve">7.10324001312256</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941568374634</t>
@@ -2522,28 +2522,28 @@
     <t xml:space="preserve">7.61159610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61617565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235084533691</t>
+    <t xml:space="preserve">7.61617517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235036849976</t>
   </si>
   <si>
     <t xml:space="preserve">7.83600568771362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67113304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6253342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735649108887</t>
+    <t xml:space="preserve">7.67113256454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62533473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
     <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41924571990967</t>
+    <t xml:space="preserve">7.41924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
@@ -2552,43 +2552,43 @@
     <t xml:space="preserve">7.29101085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697959899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15361785888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26811265945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39634561538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37802743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5749568939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91844177246094</t>
+    <t xml:space="preserve">7.27727222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15361738204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26811218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39634609222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37802696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495737075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91844081878662</t>
   </si>
   <si>
     <t xml:space="preserve">7.85890340805054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655397415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428737640381</t>
+    <t xml:space="preserve">7.67571306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655302047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428785324097</t>
   </si>
   <si>
     <t xml:space="preserve">7.45130395889282</t>
@@ -2603,7 +2603,7 @@
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30474996566772</t>
+    <t xml:space="preserve">7.30475091934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231483459473</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43756437301636</t>
+    <t xml:space="preserve">7.4375638961792</t>
   </si>
   <si>
     <t xml:space="preserve">7.48794221878052</t>
@@ -2627,13 +2627,13 @@
     <t xml:space="preserve">7.17651653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02996349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702880859375</t>
+    <t xml:space="preserve">7.02996397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51244878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702737808228</t>
   </si>
   <si>
     <t xml:space="preserve">6.74143743515015</t>
@@ -2651,13 +2651,13 @@
     <t xml:space="preserve">6.6177830696106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02538442611694</t>
+    <t xml:space="preserve">7.02538394927979</t>
   </si>
   <si>
     <t xml:space="preserve">6.89257049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89715051651001</t>
+    <t xml:space="preserve">6.89715003967285</t>
   </si>
   <si>
     <t xml:space="preserve">6.82845306396484</t>
@@ -2666,19 +2666,19 @@
     <t xml:space="preserve">6.80097436904907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67732000350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83303308486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76433706283569</t>
+    <t xml:space="preserve">6.67732048034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83303356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76433610916138</t>
   </si>
   <si>
     <t xml:space="preserve">6.63610219955444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11858654022217</t>
+    <t xml:space="preserve">6.11858701705933</t>
   </si>
   <si>
     <t xml:space="preserve">5.96745443344116</t>
@@ -2693,31 +2693,31 @@
     <t xml:space="preserve">5.77052402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72014617919922</t>
+    <t xml:space="preserve">5.72014570236206</t>
   </si>
   <si>
     <t xml:space="preserve">5.47741794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11561489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59809970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63931846618652</t>
+    <t xml:space="preserve">5.1156153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59810018539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63931798934937</t>
   </si>
   <si>
     <t xml:space="preserve">4.21110868453979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81495761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382479667664</t>
+    <t xml:space="preserve">3.8149573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382455825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034134864807</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">3.22645592689514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44399523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99356865882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304545402527</t>
+    <t xml:space="preserve">3.44399547576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99356889724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304521560669</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344718933105</t>
@@ -2747,19 +2747,19 @@
     <t xml:space="preserve">3.50353264808655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67069458961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61802697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70962285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6226065158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663848876953</t>
+    <t xml:space="preserve">3.67069435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61802673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70962262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663825035095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74168086051941</t>
@@ -2771,28 +2771,28 @@
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3828501701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11722326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01188802719116</t>
+    <t xml:space="preserve">4.38285064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11722373962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01188850402832</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4881854057312</t>
+    <t xml:space="preserve">4.09432411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48818492889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.45612668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35995149612427</t>
+    <t xml:space="preserve">4.35995101928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
@@ -2804,31 +2804,31 @@
     <t xml:space="preserve">4.32331323623657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537195205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52482414245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38743019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406797409058</t>
+    <t xml:space="preserve">4.35537147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957460403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5248236656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38742971420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406892776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.75152254104614</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">4.90036535263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.888916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04920816421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18660116195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23239946365356</t>
+    <t xml:space="preserve">4.88891649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04920864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18660163879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23239898681641</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16370296478271</t>
+    <t xml:space="preserve">5.16370248794556</t>
   </si>
   <si>
     <t xml:space="preserve">4.93471384048462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02630949020386</t>
+    <t xml:space="preserve">5.02630996704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.19805145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31254625320435</t>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">5.39269161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20950126647949</t>
+    <t xml:space="preserve">5.20950078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
@@ -2888,52 +2888,52 @@
     <t xml:space="preserve">5.14080381393433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27819728851318</t>
+    <t xml:space="preserve">5.27819681167603</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500598907471</t>
+    <t xml:space="preserve">5.09500646591187</t>
   </si>
   <si>
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0148606300354</t>
+    <t xml:space="preserve">5.01485967636108</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06065845489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22095012664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07210731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645532608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3239951133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544445037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03775835037231</t>
+    <t xml:space="preserve">5.06065797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22094964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07210779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32399559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03775882720947</t>
   </si>
   <si>
     <t xml:space="preserve">5.08355665206909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96906280517578</t>
+    <t xml:space="preserve">4.96906232833862</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616365432739</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">4.98051166534424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84311819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181516647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9919605255127</t>
+    <t xml:space="preserve">4.84311771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181564331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.00341081619263</t>
@@ -2957,25 +2957,25 @@
     <t xml:space="preserve">4.57978057861328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19049882888794</t>
+    <t xml:space="preserve">4.1904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">4.21339845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08058452606201</t>
+    <t xml:space="preserve">4.08058404922485</t>
   </si>
   <si>
     <t xml:space="preserve">4.30041408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163236618042</t>
+    <t xml:space="preserve">4.34163188934326</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54153490066528</t>
+    <t xml:space="preserve">5.54153537750244</t>
   </si>
   <si>
     <t xml:space="preserve">5.62168073654175</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">5.73617553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69037818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64457988739014</t>
+    <t xml:space="preserve">5.69037771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64457941055298</t>
   </si>
   <si>
     <t xml:space="preserve">5.66747856140137</t>
@@ -2999,13 +2999,13 @@
     <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70182704925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14835643768311</t>
+    <t xml:space="preserve">5.70182752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.816321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14835548400879</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516418457031</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">5.9537148475647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356901168823</t>
+    <t xml:space="preserve">5.87356948852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
@@ -3029,82 +3029,82 @@
     <t xml:space="preserve">6.12545680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1598048210144</t>
+    <t xml:space="preserve">6.15980529785156</t>
   </si>
   <si>
     <t xml:space="preserve">6.18270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07965898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13690614700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21705198287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35444641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009744644165</t>
+    <t xml:space="preserve">6.07965850830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13690662384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21705293655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35444593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009792327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.36589479446411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48038959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618741989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53763723373413</t>
+    <t xml:space="preserve">6.4803900718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618837356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53763675689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60633373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58343553543091</t>
+    <t xml:space="preserve">6.60633420944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58343458175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3429970741272</t>
+    <t xml:space="preserve">6.41169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
     <t xml:space="preserve">6.46894025802612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29719924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20560359954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4231424331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50328922271729</t>
+    <t xml:space="preserve">6.29719877243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20560312271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42314195632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50328874588013</t>
   </si>
   <si>
     <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51473808288574</t>
+    <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.78952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75517654418945</t>
+    <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.68648052215576</t>
@@ -3113,10 +3113,10 @@
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792985916138</t>
+    <t xml:space="preserve">6.77807521820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792938232422</t>
   </si>
   <si>
     <t xml:space="preserve">6.40024423599243</t>
@@ -3125,52 +3125,52 @@
     <t xml:space="preserve">6.37734460830688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5490870475769</t>
+    <t xml:space="preserve">6.33154726028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
     <t xml:space="preserve">6.86967134475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417802810669</t>
+    <t xml:space="preserve">7.7856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417945861816</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1749095916748</t>
+    <t xml:space="preserve">8.17490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">8.01461696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99171733856201</t>
+    <t xml:space="preserve">7.99171829223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02606582641602</t>
+    <t xml:space="preserve">8.0260648727417</t>
   </si>
   <si>
     <t xml:space="preserve">8.12911128997803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1062126159668</t>
+    <t xml:space="preserve">8.10621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.03751564025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00316715240479</t>
+    <t xml:space="preserve">8.0031681060791</t>
   </si>
   <si>
     <t xml:space="preserve">7.93447113037109</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33520126342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2779541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11766242980957</t>
+    <t xml:space="preserve">8.33520030975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27795314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15200901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11766147613525</t>
   </si>
   <si>
     <t xml:space="preserve">8.18635845184326</t>
@@ -3209,34 +3209,34 @@
     <t xml:space="preserve">8.23215579986572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
+    <t xml:space="preserve">8.16346073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736885070801</t>
   </si>
   <si>
     <t xml:space="preserve">7.84287548065186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92301988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577272415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099765777588</t>
+    <t xml:space="preserve">7.92302083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3809986114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956115722656</t>
@@ -3245,16 +3245,16 @@
     <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536041259766</t>
+    <t xml:space="preserve">9.20535945892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.48014640808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65356349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60731887817383</t>
+    <t xml:space="preserve">9.653564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073692321777</t>
@@ -3266,22 +3266,22 @@
     <t xml:space="preserve">10.0813264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2894277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3009881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241100311279</t>
+    <t xml:space="preserve">10.2894268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.300989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3587942123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437717437744</t>
+    <t xml:space="preserve">10.3587951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.543773651123</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975290298462</t>
@@ -3290,13 +3290,13 @@
     <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628448486328</t>
+    <t xml:space="preserve">10.4628438949585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703556060791</t>
+    <t xml:space="preserve">10.3703546524048</t>
   </si>
   <si>
     <t xml:space="preserve">10.7403125762939</t>
@@ -3314,34 +3314,34 @@
     <t xml:space="preserve">10.2663049697876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.393479347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0582046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0235214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1506938934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.092887878418</t>
+    <t xml:space="preserve">10.3934774398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0582036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0235204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1506929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928888320923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1160106658936</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2547426223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2200613021851</t>
+    <t xml:space="preserve">10.2547435760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859666824341</t>
@@ -3350,10 +3350,10 @@
     <t xml:space="preserve">10.1853771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0350818634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4165992736816</t>
+    <t xml:space="preserve">10.0350828170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.416600227356</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738157272339</t>
@@ -3362,25 +3362,25 @@
     <t xml:space="preserve">10.1391315460205</t>
   </si>
   <si>
-    <t xml:space="preserve">11.191198348999</t>
+    <t xml:space="preserve">11.1911973953247</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9052143096924</t>
+    <t xml:space="preserve">11.9052133560181</t>
   </si>
   <si>
     <t xml:space="preserve">11.901515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.746132850647</t>
+    <t xml:space="preserve">11.7461318969727</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426568984985</t>
+    <t xml:space="preserve">11.5426559448242</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">11.5796527862549</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576765060425</t>
+    <t xml:space="preserve">11.4501676559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576774597168</t>
   </si>
   <si>
     <t xml:space="preserve">11.3206825256348</t>
@@ -3407,16 +3407,16 @@
     <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0975923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8571186065674</t>
+    <t xml:space="preserve">12.0975914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
     <t xml:space="preserve">12.0605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0420980453491</t>
+    <t xml:space="preserve">12.0420989990234</t>
   </si>
   <si>
     <t xml:space="preserve">12.2455749511719</t>
@@ -3428,10 +3428,10 @@
     <t xml:space="preserve">11.894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.9299955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
@@ -3443,13 +3443,13 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817892074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7254018783569</t>
+    <t xml:space="preserve">13.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8178911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7254028320312</t>
   </si>
   <si>
     <t xml:space="preserve">14.631796836853</t>
@@ -3461,10 +3461,10 @@
     <t xml:space="preserve">13.7439002990723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623977661133</t>
+    <t xml:space="preserve">13.4109392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623987197876</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294376373291</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669904708862</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3494,73 +3494,73 @@
     <t xml:space="preserve">13.0779781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4468173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457015991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7786636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.555570602417</t>
+    <t xml:space="preserve">14.4468183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5011949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7786617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">16.3705959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5370750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596073150635</t>
+    <t xml:space="preserve">16.537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596054077148</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7971601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0006370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.908148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8341588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283208847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5023126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2433423995972</t>
+    <t xml:space="preserve">16.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7971620559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1486186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.000638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9081478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5196943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4641990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092645645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.502311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2433414459229</t>
   </si>
   <si>
     <t xml:space="preserve">13.6329126358032</t>
@@ -3569,28 +3569,28 @@
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.3369483947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0583639144897</t>
+    <t xml:space="preserve">14.0583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8918828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098224639893</t>
+    <t xml:space="preserve">13.891884803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098215103149</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993936538696</t>
+    <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7808952331543</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">13.5404233932495</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924398422241</t>
+    <t xml:space="preserve">13.3924417495728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9658756256104</t>
+    <t xml:space="preserve">13.965874671936</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988357543945</t>
+    <t xml:space="preserve">14.2988367080688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2803373336792</t>
@@ -3626,28 +3626,28 @@
     <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1334714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0594806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4479351043701</t>
+    <t xml:space="preserve">13.1334705352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0594797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4479341506958</t>
   </si>
   <si>
     <t xml:space="preserve">12.2085790634155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3935575485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1889657974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4664335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8190078735352</t>
+    <t xml:space="preserve">12.3935565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.18896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8190069198608</t>
   </si>
   <si>
     <t xml:space="preserve">11.9126138687134</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9496097564697</t>
+    <t xml:space="preserve">12.1345872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9496088027954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6721410751343</t>
@@ -3674,43 +3674,43 @@
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0235996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9681062698364</t>
+    <t xml:space="preserve">12.0051031112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0236005783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9681072235107</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582353591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5067768096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1172065734863</t>
+    <t xml:space="preserve">10.8582363128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5067758560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.117205619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8201246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4131717681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6710243225098</t>
+    <t xml:space="preserve">11.4131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265186309814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8005104064941</t>
+    <t xml:space="preserve">12.8005094528198</t>
   </si>
   <si>
     <t xml:space="preserve">13.225959777832</t>
@@ -3725,34 +3725,34 @@
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617765426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3473138809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3288145065308</t>
+    <t xml:space="preserve">12.6617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3473129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3288154602051</t>
   </si>
   <si>
     <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8016262054443</t>
+    <t xml:space="preserve">12.6155309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4398012161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8016271591187</t>
   </si>
   <si>
     <t xml:space="preserve">11.9958543777466</t>
@@ -3764,22 +3764,22 @@
     <t xml:space="preserve">11.764630317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8848676681519</t>
+    <t xml:space="preserve">11.8848657608032</t>
   </si>
   <si>
     <t xml:space="preserve">11.6073989868164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5519046783447</t>
+    <t xml:space="preserve">11.551905632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.2929363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7657470703125</t>
+    <t xml:space="preserve">10.6455116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7657480239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.098708152771</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605554580688</t>
+    <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">11.569953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6827392578125</t>
+    <t xml:space="preserve">11.6827402114868</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.85191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6639423370361</t>
+    <t xml:space="preserve">11.8519172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6639413833618</t>
   </si>
   <si>
     <t xml:space="preserve">11.7579298019409</t>
@@ -3824,25 +3824,25 @@
     <t xml:space="preserve">11.974102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398960113525</t>
+    <t xml:space="preserve">12.0398950576782</t>
   </si>
   <si>
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658039093018</t>
+    <t xml:space="preserve">11.8895130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658048629761</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5642786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0530185699463</t>
+    <t xml:space="preserve">10.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.053017616272</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830764770508</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
+    <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">10.9214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0624170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4571666717529</t>
+    <t xml:space="preserve">11.0624179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631801605225</t>
+    <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075487136841</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">11.9365072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297334671021</t>
+    <t xml:space="preserve">11.7297325134277</t>
   </si>
   <si>
     <t xml:space="preserve">12.096287727356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3876523971558</t>
+    <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6414194107056</t>
+    <t xml:space="preserve">12.6414184570312</t>
   </si>
   <si>
     <t xml:space="preserve">12.6884136199951</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">12.5474319458008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5286331176758</t>
+    <t xml:space="preserve">12.5286340713501</t>
   </si>
   <si>
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998574256897</t>
+    <t xml:space="preserve">12.8481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9985752105713</t>
   </si>
   <si>
     <t xml:space="preserve">13.1677541732788</t>
@@ -3920,22 +3920,22 @@
     <t xml:space="preserve">13.4685163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6188974380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5625057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7034864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6564922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741081237793</t>
+    <t xml:space="preserve">13.618896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5625047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6094980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7034873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6564931869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6752901077271</t>
@@ -3956,25 +3956,25 @@
     <t xml:space="preserve">13.1583547592163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">13.3369312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0643653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113605499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9139842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8199977874756</t>
+    <t xml:space="preserve">13.0925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0643663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113595962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9139852523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8199968338013</t>
   </si>
   <si>
     <t xml:space="preserve">13.0361700057983</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">13.017373085022</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0549688339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8669919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260084152222</t>
+    <t xml:space="preserve">13.054967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8669900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260093688965</t>
   </si>
   <si>
     <t xml:space="preserve">12.4628419876099</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5756282806396</t>
+    <t xml:space="preserve">12.5850276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5756273269653</t>
   </si>
   <si>
     <t xml:space="preserve">12.6602172851562</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692138671875</t>
+    <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
     <t xml:space="preserve">11.391375541687</t>
@@ -4031,22 +4031,22 @@
     <t xml:space="preserve">11.1000127792358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5548801422119</t>
+    <t xml:space="preserve">10.5548791885376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984865188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582670211792</t>
+    <t xml:space="preserve">10.4984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582679748535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951005935669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9778270721436</t>
+    <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
     <t xml:space="preserve">11.4665660858154</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">10.7898502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9684295654297</t>
+    <t xml:space="preserve">10.9684286117554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3255834579468</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">11.2879886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8707151412964</t>
+    <t xml:space="preserve">11.8707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7955255508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6357450485229</t>
+    <t xml:space="preserve">11.795524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">11.6451444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7485313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1150856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">11.7485303878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.115086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4112,13 +4112,13 @@
     <t xml:space="preserve">12.6790151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4722414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.773003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455684661865</t>
+    <t xml:space="preserve">12.472240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7730026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.0831651687622</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256711959839</t>
+    <t xml:space="preserve">13.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9102621078491</t>
+    <t xml:space="preserve">13.9102611541748</t>
   </si>
   <si>
     <t xml:space="preserve">13.8068733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6282968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3275337219238</t>
+    <t xml:space="preserve">13.6282958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3275346755981</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779148101807</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2580184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504816055298</t>
+    <t xml:space="preserve">14.258017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504806518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2805395126343</t>
@@ -4175,16 +4175,16 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523431777954</t>
+    <t xml:space="preserve">13.3463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523441314697</t>
   </si>
   <si>
     <t xml:space="preserve">13.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3933248519897</t>
+    <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">13.5249090194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7598791122437</t>
+    <t xml:space="preserve">13.6470937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.759880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.7316827774048</t>
@@ -4214,28 +4214,28 @@
     <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8914623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4215211868286</t>
+    <t xml:space="preserve">13.7786769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8914642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4215221405029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0888376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5587797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0193223953247</t>
+    <t xml:space="preserve">14.5587787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.840744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0193214416504</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099239349365</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
@@ -4265,28 +4265,28 @@
     <t xml:space="preserve">14.7655544281006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7937507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6621675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8125476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6903638839722</t>
+    <t xml:space="preserve">14.7937498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.662166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8125486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6903629302979</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1039113998413</t>
+    <t xml:space="preserve">15.1039123535156</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8877391815186</t>
+    <t xml:space="preserve">14.8877382278442</t>
   </si>
   <si>
     <t xml:space="preserve">15.122709274292</t>
@@ -4295,13 +4295,13 @@
     <t xml:space="preserve">14.3708028793335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1734275817871</t>
+    <t xml:space="preserve">14.1734285354614</t>
   </si>
   <si>
     <t xml:space="preserve">14.4929876327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299337387085</t>
+    <t xml:space="preserve">13.2993364334106</t>
   </si>
   <si>
     <t xml:space="preserve">11.513560295105</t>
@@ -4313,13 +4313,13 @@
     <t xml:space="preserve">10.9872255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269190788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2785902023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3067855834961</t>
+    <t xml:space="preserve">11.2691917419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2785892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3067865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.231595993042</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">11.4477691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4101734161377</t>
+    <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1846017837524</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">11.2221965789795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9966249465942</t>
+    <t xml:space="preserve">10.9966259002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.0812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0342197418213</t>
+    <t xml:space="preserve">11.0342206954956</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744401931763</t>
@@ -4370,46 +4370,46 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146596908569</t>
+    <t xml:space="preserve">10.7146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8650426864624</t>
+    <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
     <t xml:space="preserve">10.4138975143433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3387069702148</t>
+    <t xml:space="preserve">10.3387079238892</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1549892425537</t>
+    <t xml:space="preserve">10.0303297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.154990196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563623428345</t>
+    <t xml:space="preserve">10.3371849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563632965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5193796157837</t>
+    <t xml:space="preserve">10.519380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235017776489</t>
+    <t xml:space="preserve">11.1235008239746</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412929534912</t>
+    <t xml:space="preserve">10.4906120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412919998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440391540527</t>
+    <t xml:space="preserve">10.6440401077271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960941314697</t>
+    <t xml:space="preserve">10.5960931777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.711163520813</t>
+    <t xml:space="preserve">10.7111644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813404083252</t>
+    <t xml:space="preserve">9.84813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484855651855</t>
+    <t xml:space="preserve">9.92484760284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618444442749</t>
+    <t xml:space="preserve">10.4618434906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361614227295</t>
+    <t xml:space="preserve">9.95361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537982940674</t>
+    <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646450042725</t>
+    <t xml:space="preserve">8.82688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646354675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34741973876953</t>
+    <t xml:space="preserve">8.34742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09810066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960834503174</t>
+    <t xml:space="preserve">8.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084171295166</t>
+    <t xml:space="preserve">8.23234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810676574707</t>
+    <t xml:space="preserve">8.44810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770397186279</t>
+    <t xml:space="preserve">8.80770301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4673,22 +4673,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976409912109</t>
+    <t xml:space="preserve">9.10976314544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14812088012695</t>
+    <t xml:space="preserve">8.67824935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14811992645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798629760742</t>
+    <t xml:space="preserve">9.26798534393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208728790283</t>
+    <t xml:space="preserve">8.82208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907001495361</t>
+    <t xml:space="preserve">8.6590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19127178192139</t>
+    <t xml:space="preserve">9.1912727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921775817871</t>
+    <t xml:space="preserve">9.23921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28237056732178</t>
+    <t xml:space="preserve">9.28236961364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1337366104126</t>
+    <t xml:space="preserve">9.13373565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428199768066</t>
+    <t xml:space="preserve">9.00428295135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8844165802002</t>
+    <t xml:space="preserve">8.88441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318511962891</t>
+    <t xml:space="preserve">8.91318416595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468669891357</t>
+    <t xml:space="preserve">8.64468574523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7166051864624</t>
+    <t xml:space="preserve">8.71660614013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399871826172</t>
+    <t xml:space="preserve">8.54399967193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496292114258</t>
+    <t xml:space="preserve">8.75496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222091674805</t>
+    <t xml:space="preserve">8.70222187042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4850,37 +4850,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605274200439</t>
+    <t xml:space="preserve">8.49605369567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1364574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21796607971191</t>
+    <t xml:space="preserve">8.13645648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2179651260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97344064712524</t>
+    <t xml:space="preserve">7.97343969345093</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467306137085</t>
+    <t xml:space="preserve">7.94467258453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059886932373</t>
+    <t xml:space="preserve">9.79059791564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.42076587677</t>
+    <t xml:space="preserve">11.4207668304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4925,16 +4925,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.593373298645</t>
+    <t xml:space="preserve">11.5933723449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2769289016724</t>
+    <t xml:space="preserve">11.3536424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276927947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796619415283</t>
+    <t xml:space="preserve">10.9796628952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276220321655</t>
+    <t xml:space="preserve">11.1618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276210784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4976,10 +4976,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6084041595459</t>
+    <t xml:space="preserve">9.59881401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60840320587158</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -70857,7 +70857,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6493981481</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>139446</v>
@@ -70878,6 +70878,32 @@
         <v>1930</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494791667</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>115671</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>11.8699998855591</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>11.5799999237061</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>11.8500003814697</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -47,37 +47,37 @@
     <t xml:space="preserve">2.15079474449158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13486337661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09768891334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07379102706909</t>
+    <t xml:space="preserve">2.13486313819885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09768843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07379078865051</t>
   </si>
   <si>
     <t xml:space="preserve">2.02334022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0631697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0525484085083</t>
+    <t xml:space="preserve">2.06316995620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05254864692688</t>
   </si>
   <si>
     <t xml:space="preserve">1.96492338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98988318443298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0180299282074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0169677734375</t>
+    <t xml:space="preserve">1.98988330364227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439290046692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802945137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696729660034</t>
   </si>
   <si>
     <t xml:space="preserve">2.00209784507751</t>
@@ -89,100 +89,100 @@
     <t xml:space="preserve">2.05998349189758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528454780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909136772156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97820019721985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9277491569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943250179291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447269916534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93305993080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712784767151</t>
+    <t xml:space="preserve">2.00528407096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854121208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774951457977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943274021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447293758392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306005001068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712820529938</t>
   </si>
   <si>
     <t xml:space="preserve">1.94633650779724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95589542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368135929108</t>
+    <t xml:space="preserve">1.95589566230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9436811208725</t>
   </si>
   <si>
     <t xml:space="preserve">2.09237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441185951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450197219849</t>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441209793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450221061707</t>
   </si>
   <si>
     <t xml:space="preserve">2.17203736305237</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10831022262573</t>
+    <t xml:space="preserve">2.10830974578857</t>
   </si>
   <si>
     <t xml:space="preserve">2.1396427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10299921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442229270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14548397064209</t>
+    <t xml:space="preserve">2.10299897193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442205429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14548444747925</t>
   </si>
   <si>
     <t xml:space="preserve">2.15345001220703</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14813923835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132546424866</t>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132570266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18265843391418</t>
+    <t xml:space="preserve">2.18265819549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.222487449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15610504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495301246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
+    <t xml:space="preserve">2.15610551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
   </si>
   <si>
     <t xml:space="preserve">2.08706736564636</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.07219791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12158632278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14017343521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12424182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362051963806</t>
+    <t xml:space="preserve">2.12158608436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017367362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12424159049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362028121948</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582522392273</t>
@@ -209,64 +209,64 @@
     <t xml:space="preserve">2.05307936668396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901121139526</t>
+    <t xml:space="preserve">2.06848001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901144981384</t>
   </si>
   <si>
     <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12477278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16141629219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15557432174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17734789848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373006820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169610977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29418087005615</t>
+    <t xml:space="preserve">2.12477254867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16141581535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15557408332825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17734813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373030662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169634819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29418110847473</t>
   </si>
   <si>
     <t xml:space="preserve">2.25753784179688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22461223602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21452188491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514319419861</t>
+    <t xml:space="preserve">2.22461199760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21452212333679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514343261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.24638533592224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2309844493866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34888029098511</t>
+    <t xml:space="preserve">2.23098468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073426246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888052940369</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604455947876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44925045967102</t>
+    <t xml:space="preserve">2.4492506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.50288796424866</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">2.56555318832397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547255516052</t>
+    <t xml:space="preserve">2.52997183799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6154727935791</t>
   </si>
   <si>
     <t xml:space="preserve">2.66555023193359</t>
@@ -290,61 +290,61 @@
     <t xml:space="preserve">2.66718339920044</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70147585868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72161555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346632957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894050598145</t>
+    <t xml:space="preserve">2.70147562026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7216157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8152391910553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894026756287</t>
   </si>
   <si>
     <t xml:space="preserve">2.98942255973816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00248622894287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94587683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84136700630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91757202148438</t>
+    <t xml:space="preserve">3.00248646736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94587659835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9175717830658</t>
   </si>
   <si>
     <t xml:space="preserve">2.90668559074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959342956543</t>
+    <t xml:space="preserve">2.89797639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959366798401</t>
   </si>
   <si>
     <t xml:space="preserve">2.76516151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73685646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69548797607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78693413734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531734466553</t>
+    <t xml:space="preserve">2.73685669898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6954882144928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78693461418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531686782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.98289060592651</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">2.776047706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313986778259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974902153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97200393676758</t>
+    <t xml:space="preserve">2.86313962936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97200417518616</t>
   </si>
   <si>
     <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97418117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813199043274</t>
+    <t xml:space="preserve">2.97418165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813151359558</t>
   </si>
   <si>
     <t xml:space="preserve">2.9785361289978</t>
@@ -380,46 +380,46 @@
     <t xml:space="preserve">3.03514552116394</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04820942878723</t>
+    <t xml:space="preserve">3.04820919036865</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15707421302795</t>
+    <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
     <t xml:space="preserve">3.29859828948975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214377403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771162033081</t>
+    <t xml:space="preserve">3.30730700492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29206609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771138191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.26158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24416565895081</t>
+    <t xml:space="preserve">3.24416589736938</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27900242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2572295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26593852043152</t>
+    <t xml:space="preserve">3.27900266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25722980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2659387588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.17449235916138</t>
@@ -431,43 +431,43 @@
     <t xml:space="preserve">3.25940704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33125758171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35085296630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34432125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472538948059</t>
+    <t xml:space="preserve">3.33125782012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35085320472717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34432101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472586631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.28553438186646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3203706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31383919715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3094847202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15054202079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18973350524902</t>
+    <t xml:space="preserve">3.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682518959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31383895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30948448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15054249763489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18973326683044</t>
   </si>
   <si>
     <t xml:space="preserve">3.20932912826538</t>
@@ -479,49 +479,49 @@
     <t xml:space="preserve">3.20061993598938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22239279747009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175539016724</t>
+    <t xml:space="preserve">3.22239303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175515174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343505859375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26376175880432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262558937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141269683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59253239631653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962408065796</t>
+    <t xml:space="preserve">3.26376128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497441291809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59253287315369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962431907654</t>
   </si>
   <si>
     <t xml:space="preserve">3.78631138801575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90824031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.010573387146</t>
+    <t xml:space="preserve">3.90823984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057291030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.09330940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831823348999</t>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831775665283</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
@@ -536,13 +536,13 @@
     <t xml:space="preserve">4.23483371734619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26313877105713</t>
+    <t xml:space="preserve">4.26313829421997</t>
   </si>
   <si>
     <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68988752365112</t>
+    <t xml:space="preserve">4.68988847732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.65722846984863</t>
@@ -551,61 +551,61 @@
     <t xml:space="preserve">4.6463418006897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75956153869629</t>
+    <t xml:space="preserve">4.75956106185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334053039551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94245433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72037029266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74214363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73778867721558</t>
+    <t xml:space="preserve">4.94245386123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72036981582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74214315414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73778820037842</t>
   </si>
   <si>
     <t xml:space="preserve">4.6441650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37418031692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35022974014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34152173995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22830200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128751754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895540237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22612476348877</t>
+    <t xml:space="preserve">4.57231378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37417984008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34152126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22830152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22612428665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.24572038650513</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36547136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35458517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33934450149536</t>
+    <t xml:space="preserve">4.36547088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35458469390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33934354782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.65940570831299</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">4.63545608520508</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61585998535156</t>
+    <t xml:space="preserve">4.61586046218872</t>
   </si>
   <si>
     <t xml:space="preserve">4.64851951599121</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.72254800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408664703369</t>
+    <t xml:space="preserve">4.59408712387085</t>
   </si>
   <si>
     <t xml:space="preserve">4.6637601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58973217010498</t>
+    <t xml:space="preserve">4.58973264694214</t>
   </si>
   <si>
     <t xml:space="preserve">4.51135015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52441358566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73343372344971</t>
+    <t xml:space="preserve">4.5244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73343420028687</t>
   </si>
   <si>
     <t xml:space="preserve">4.64198732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78568840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77480316162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.746497631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609373092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38662147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29082107543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25162982940674</t>
+    <t xml:space="preserve">4.78568887710571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77480220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74649715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609230041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921884536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38662099838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29082012176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25162935256958</t>
   </si>
   <si>
     <t xml:space="preserve">5.22985649108887</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">5.22767972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11010456085205</t>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11010599136353</t>
   </si>
   <si>
     <t xml:space="preserve">5.22550201416016</t>
@@ -692,25 +692,25 @@
     <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106962203979</t>
+    <t xml:space="preserve">5.31041574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17107009887695</t>
   </si>
   <si>
     <t xml:space="preserve">5.14494228363037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979480743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09050989151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043197631836</t>
+    <t xml:space="preserve">5.06220436096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979385375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09050941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043245315552</t>
   </si>
   <si>
     <t xml:space="preserve">5.11445999145508</t>
@@ -719,16 +719,16 @@
     <t xml:space="preserve">5.10139608383179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09268712997437</t>
+    <t xml:space="preserve">5.09268665313721</t>
   </si>
   <si>
     <t xml:space="preserve">5.12752342224121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11663722991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478597640991</t>
+    <t xml:space="preserve">5.11663770675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478693008423</t>
   </si>
   <si>
     <t xml:space="preserve">4.95769453048706</t>
@@ -737,46 +737,46 @@
     <t xml:space="preserve">5.02736806869507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98817682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86624908447266</t>
+    <t xml:space="preserve">4.9881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88584423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8662486076355</t>
   </si>
   <si>
     <t xml:space="preserve">4.85536193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8466534614563</t>
+    <t xml:space="preserve">4.84665298461914</t>
   </si>
   <si>
     <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561096191406</t>
+    <t xml:space="preserve">4.7356104850769</t>
   </si>
   <si>
     <t xml:space="preserve">4.79004335403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74432134628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6811785697937</t>
+    <t xml:space="preserve">4.74432039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738477706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68117904663086</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052516937256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9185037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841104507446</t>
+    <t xml:space="preserve">4.91850328445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841009140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.08397769927979</t>
@@ -791,73 +791,73 @@
     <t xml:space="preserve">5.09486436843872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710329055786</t>
+    <t xml:space="preserve">5.30170774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4171028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209541320801</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68273401260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63918685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385251998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94400787353516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383676528931</t>
+    <t xml:space="preserve">5.6827335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134929656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94400835037231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383771896362</t>
   </si>
   <si>
     <t xml:space="preserve">5.81337118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87868928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75893878936768</t>
+    <t xml:space="preserve">5.87868976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75893831253052</t>
   </si>
   <si>
     <t xml:space="preserve">5.76329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88957595825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89610815048218</t>
+    <t xml:space="preserve">5.88957548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89610767364502</t>
   </si>
   <si>
     <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09641885757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94836235046387</t>
+    <t xml:space="preserve">6.0964183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94836330413818</t>
   </si>
   <si>
     <t xml:space="preserve">5.9897313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497245788574</t>
+    <t xml:space="preserve">6.0049729347229</t>
   </si>
   <si>
     <t xml:space="preserve">5.9875545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0419864654541</t>
+    <t xml:space="preserve">6.04198598861694</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722761154175</t>
@@ -875,76 +875,76 @@
     <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42301321029663</t>
+    <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.26842546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52969980239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276418685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80403852462769</t>
+    <t xml:space="preserve">6.52969932556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276466369629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848810195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80403900146484</t>
   </si>
   <si>
     <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01088237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06531429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756801605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005739212036</t>
+    <t xml:space="preserve">7.01088190078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06531381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11756896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3200569152832</t>
   </si>
   <si>
     <t xml:space="preserve">7.13063287734985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22425699234009</t>
+    <t xml:space="preserve">7.22425651550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.22207880020142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11321449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28522109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30481624603271</t>
+    <t xml:space="preserve">7.11321353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29392910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666654586792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360216140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521966934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30481576919556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19595146179199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46655893325806</t>
+    <t xml:space="preserve">6.4665584564209</t>
   </si>
   <si>
     <t xml:space="preserve">6.2270565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47309017181396</t>
+    <t xml:space="preserve">6.47309064865112</t>
   </si>
   <si>
     <t xml:space="preserve">6.40123987197876</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704122543335</t>
+    <t xml:space="preserve">6.49704074859619</t>
   </si>
   <si>
     <t xml:space="preserve">6.52316856384277</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">6.56215476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61290407180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891633987427</t>
+    <t xml:space="preserve">6.61290502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
     <t xml:space="preserve">6.45403575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55774164199829</t>
+    <t xml:space="preserve">6.55774116516113</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740322113037</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">6.41652584075928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58422040939331</t>
+    <t xml:space="preserve">6.58421993255615</t>
   </si>
   <si>
     <t xml:space="preserve">6.50478553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42093801498413</t>
+    <t xml:space="preserve">6.42093849182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694932937622</t>
+    <t xml:space="preserve">6.35694885253906</t>
   </si>
   <si>
     <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43417692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826519012451</t>
+    <t xml:space="preserve">6.4341778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826471328735</t>
   </si>
   <si>
     <t xml:space="preserve">6.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37460231781006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057062149048</t>
+    <t xml:space="preserve">6.37460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057109832764</t>
   </si>
   <si>
     <t xml:space="preserve">6.14291858673096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13850545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757150650024</t>
+    <t xml:space="preserve">6.13850593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9575719833374</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344165802002</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771314620972</t>
+    <t xml:space="preserve">5.93771266937256</t>
   </si>
   <si>
     <t xml:space="preserve">5.78546380996704</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">5.95977830886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92006063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93330001831055</t>
+    <t xml:space="preserve">5.9200611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93329954147339</t>
   </si>
   <si>
     <t xml:space="preserve">5.94212675094604</t>
@@ -1064,22 +1064,22 @@
     <t xml:space="preserve">5.84724617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98846292495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720315933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50744438171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46993350982666</t>
+    <t xml:space="preserve">5.98846340179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50744342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4699330329895</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692083358765</t>
+    <t xml:space="preserve">5.73692035675049</t>
   </si>
   <si>
     <t xml:space="preserve">5.76119232177734</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">5.89137649536133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72147464752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59129190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608598709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54495525360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44345569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007514953613</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59129095077515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608551025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54495429992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4434552192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007419586182</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932537078857</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">5.48096561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52730226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45890045166016</t>
+    <t xml:space="preserve">5.52730274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45890092849731</t>
   </si>
   <si>
     <t xml:space="preserve">5.41256427764893</t>
@@ -1139,28 +1139,28 @@
     <t xml:space="preserve">5.48979139328003</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922674179077</t>
+    <t xml:space="preserve">5.56922626495361</t>
   </si>
   <si>
     <t xml:space="preserve">5.73912763595581</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6641058921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80311632156372</t>
+    <t xml:space="preserve">5.66410636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80311584472656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86931180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860456466675</t>
+    <t xml:space="preserve">5.73030138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860408782959</t>
   </si>
   <si>
     <t xml:space="preserve">5.80532264709473</t>
@@ -1169,52 +1169,52 @@
     <t xml:space="preserve">5.63762807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5648136138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068376541138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.478759765625</t>
+    <t xml:space="preserve">5.56481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52068328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875928878784</t>
   </si>
   <si>
     <t xml:space="preserve">5.49420499801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36181449890137</t>
+    <t xml:space="preserve">5.36181354522705</t>
   </si>
   <si>
     <t xml:space="preserve">5.29782581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22942447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477060317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22280406951904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14116382598877</t>
+    <t xml:space="preserve">5.22942352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477012634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39711809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796697616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2228045463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14116334915161</t>
   </si>
   <si>
     <t xml:space="preserve">5.11909818649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.207359790802</t>
+    <t xml:space="preserve">5.20735883712769</t>
   </si>
   <si>
     <t xml:space="preserve">5.16764211654663</t>
@@ -1229,610 +1229,610 @@
     <t xml:space="preserve">5.03745794296265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00656747817993</t>
+    <t xml:space="preserve">5.00656700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96464395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126245498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04849052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19411945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22501039505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87196969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72634029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131902694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839189529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6045298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76781177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.904616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307378768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6398344039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6994104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467245101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1936674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348466873169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14071130752563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526655197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597284317017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419095993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034391403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020227432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354124069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935434341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283304214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433307647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878778457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996248245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9222674369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089548110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543668746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9284348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90636968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697877883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050096511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22851896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0475869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082534790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49330139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941228866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46241044998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6212797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219778060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66424989700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57927083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49429035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31985664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145795822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305927276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14095020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21251344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774709701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821582794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53007125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44509029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42719984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43167304992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47452545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013124465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831483840942</t>
   </si>
   <si>
     <t xml:space="preserve">4.96464347839355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04848957061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22501134872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87197017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72633981704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131855010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60453081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8119421005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76781177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663850784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307378768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63983488082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940996170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467197418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348371505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14071226119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8097357749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034391403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354124069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65086650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935434341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413438796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235202789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372446060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474252700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571996688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9284348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90636968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050096511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22852039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908647537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4933009147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1843900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528196334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5374321937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247346878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65977811813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49429035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3198561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14095020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356702804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2125129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821535110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53007125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44509077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40036487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42719984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43167304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10069704055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39589166641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.474524974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33587312698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9646430015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07645988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886209487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73653841018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58894014358521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577558517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74995613098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12825727462769</t>
+    <t xml:space="preserve">5.07645893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886161804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73653793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58894062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577653884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74995565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417474746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201642990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12825679779053</t>
   </si>
   <si>
     <t xml:space="preserve">4.20876455307007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11483955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04104042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05445861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829653739929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049268722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0186767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740784645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466420173645</t>
+    <t xml:space="preserve">4.11483907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04103994369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0544581413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829677581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15509271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13049364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01867723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8688428401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559144020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466396331787</t>
   </si>
   <si>
     <t xml:space="preserve">3.8375346660614</t>
@@ -1841,76 +1841,76 @@
     <t xml:space="preserve">3.84648036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96500515937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15733003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00302267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92475152015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146061897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264197349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331628799438</t>
+    <t xml:space="preserve">3.96500539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15732860565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92475175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331581115723</t>
   </si>
   <si>
     <t xml:space="preserve">3.8621346950531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84424424171448</t>
+    <t xml:space="preserve">3.8442440032959</t>
   </si>
   <si>
     <t xml:space="preserve">3.45512318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35896134376526</t>
+    <t xml:space="preserve">3.35896110534668</t>
   </si>
   <si>
     <t xml:space="preserve">3.24267244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03245759010315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140329360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216444969177</t>
+    <t xml:space="preserve">3.03245782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216468811035</t>
   </si>
   <si>
     <t xml:space="preserve">3.3835608959198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38803362846375</t>
+    <t xml:space="preserve">3.38803339004517</t>
   </si>
   <si>
     <t xml:space="preserve">3.26950788497925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22701811790466</t>
+    <t xml:space="preserve">3.22701787948608</t>
   </si>
   <si>
     <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39474272727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4886679649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5155041217804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870746612549</t>
+    <t xml:space="preserve">3.3947422504425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48866820335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51550436019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870722770691</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714517593384</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735052108765</t>
+    <t xml:space="preserve">2.92735028266907</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182277679443</t>
@@ -1931,49 +1931,49 @@
     <t xml:space="preserve">3.1040198802948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03916668891907</t>
+    <t xml:space="preserve">3.03916645050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.95642256736755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88485980033875</t>
+    <t xml:space="preserve">2.8848602771759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844455718994</t>
+    <t xml:space="preserve">2.77751660346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83342480659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07271122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625648498535</t>
+    <t xml:space="preserve">2.83342456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625672340393</t>
   </si>
   <si>
     <t xml:space="preserve">3.16887354850769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22925448417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1599280834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22254538536072</t>
+    <t xml:space="preserve">3.22925400733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15992832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22254514694214</t>
   </si>
   <si>
     <t xml:space="preserve">3.23596334457397</t>
@@ -1982,16 +1982,16 @@
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347333908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32094383239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54233956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972297668457</t>
+    <t xml:space="preserve">3.19347310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972273826599</t>
   </si>
   <si>
     <t xml:space="preserve">3.53339457511902</t>
@@ -2000,64 +2000,64 @@
     <t xml:space="preserve">3.4953773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61166572570801</t>
+    <t xml:space="preserve">3.61166596412659</t>
   </si>
   <si>
     <t xml:space="preserve">3.66533756256104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57588458061218</t>
+    <t xml:space="preserve">3.57588481903076</t>
   </si>
   <si>
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221322059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5825936794281</t>
+    <t xml:space="preserve">3.52221274375916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58259391784668</t>
   </si>
   <si>
     <t xml:space="preserve">3.43723273277283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52444911003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58483028411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440984725952</t>
+    <t xml:space="preserve">3.52444958686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58483004570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440960884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61390233039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399012565613</t>
+    <t xml:space="preserve">3.61390209197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398988723755</t>
   </si>
   <si>
     <t xml:space="preserve">3.89567923545837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77268147468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766196250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040560722351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99184107780457</t>
+    <t xml:space="preserve">3.77268171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.857661485672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040608406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99184131622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.07011270523071</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">4.13272953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09247636795044</t>
+    <t xml:space="preserve">4.09247541427612</t>
   </si>
   <si>
     <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863773345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9493510723114</t>
+    <t xml:space="preserve">4.18863725662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94935083389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.00525903701782</t>
@@ -2084,19 +2084,19 @@
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842383384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28256368637085</t>
+    <t xml:space="preserve">3.97842407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28256320953369</t>
   </si>
   <si>
     <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42792463302612</t>
+    <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.35412645339966</t>
@@ -2108,64 +2108,64 @@
     <t xml:space="preserve">4.20429182052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27809047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23783683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2915096282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24901914596558</t>
+    <t xml:space="preserve">4.2780909538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205593109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23783731460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29150915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349092483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07458543777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15285730361938</t>
+    <t xml:space="preserve">4.25349187850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982004165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0745849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15285682678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.1864013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26914596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171473503113</t>
+    <t xml:space="preserve">4.26914548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171449661255</t>
   </si>
   <si>
     <t xml:space="preserve">3.93369650840759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90015172958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631428718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0388035774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03656721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01644086837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9180428981781</t>
+    <t xml:space="preserve">3.90015196800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631357192993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03656768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01644039154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91804265975952</t>
   </si>
   <si>
     <t xml:space="preserve">3.87778902053833</t>
@@ -2174,130 +2174,130 @@
     <t xml:space="preserve">3.76820874214172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77491784095764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65192008018494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85095191001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09918546676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8241171836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95693111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88136434555054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76229000091553</t>
+    <t xml:space="preserve">3.77491736412048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65191984176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85095310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0991849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693063735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136458396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76229023933411</t>
   </si>
   <si>
     <t xml:space="preserve">3.74626088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7645800113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68901371955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67298436164856</t>
+    <t xml:space="preserve">3.76457977294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68901348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67298460006714</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487168312073</t>
+    <t xml:space="preserve">3.84243607521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220454216003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487192153931</t>
   </si>
   <si>
     <t xml:space="preserve">3.96608996391296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89739394187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006108283997</t>
+    <t xml:space="preserve">3.89739370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006060600281</t>
   </si>
   <si>
     <t xml:space="preserve">3.87449502944946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90655279159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
+    <t xml:space="preserve">3.90655303001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440957069397</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19736957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15386056900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09203481674194</t>
+    <t xml:space="preserve">4.19736909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1538610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09203386306763</t>
   </si>
   <si>
     <t xml:space="preserve">4.11264276504517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10119390487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14470195770264</t>
+    <t xml:space="preserve">4.10119342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14470243453979</t>
   </si>
   <si>
     <t xml:space="preserve">4.18821001052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27751588821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28438520431519</t>
+    <t xml:space="preserve">4.27751541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28438472747803</t>
   </si>
   <si>
     <t xml:space="preserve">4.31415319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803861618042</t>
+    <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
     <t xml:space="preserve">4.30270433425903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3507924079895</t>
+    <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33247327804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22255754470825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774599075317</t>
+    <t xml:space="preserve">4.3324728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22255802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774694442749</t>
   </si>
   <si>
     <t xml:space="preserve">4.17446994781494</t>
@@ -2306,16 +2306,16 @@
     <t xml:space="preserve">4.05997562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09890365600586</t>
+    <t xml:space="preserve">4.09890413284302</t>
   </si>
   <si>
     <t xml:space="preserve">4.15157127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16302156448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11035394668579</t>
+    <t xml:space="preserve">4.16302061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11035346984863</t>
   </si>
   <si>
     <t xml:space="preserve">4.12409257888794</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730848312378</t>
+    <t xml:space="preserve">4.00730800628662</t>
   </si>
   <si>
     <t xml:space="preserve">4.05539560317993</t>
@@ -2333,25 +2333,25 @@
     <t xml:space="preserve">3.97067022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.945481300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701585769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594388961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678408622742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235085487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043821334839</t>
+    <t xml:space="preserve">3.94548082351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701561927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594460487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043916702271</t>
   </si>
   <si>
     <t xml:space="preserve">3.98211908340454</t>
@@ -2360,79 +2360,79 @@
     <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493349075317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16760015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04394674301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05310583114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18592023849487</t>
+    <t xml:space="preserve">4.11493301391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16760063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04394626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0531063079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18591928482056</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06226587295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34392213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33705282211304</t>
+    <t xml:space="preserve">4.06226539611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34392261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33705234527588</t>
   </si>
   <si>
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60267972946167</t>
+    <t xml:space="preserve">4.60268020629883</t>
   </si>
   <si>
     <t xml:space="preserve">5.00112104415894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17515277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33086490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35834360122681</t>
+    <t xml:space="preserve">5.17515230178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33086538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">5.62855100631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48657703399658</t>
+    <t xml:space="preserve">5.48657751083374</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61023187637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70640659332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527448654175</t>
+    <t xml:space="preserve">5.61023139953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70640707015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48199796676636</t>
+    <t xml:space="preserve">5.4819974899292</t>
   </si>
   <si>
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590847015381</t>
+    <t xml:space="preserve">5.27590799331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292362213135</t>
@@ -2444,49 +2444,49 @@
     <t xml:space="preserve">5.3446044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47283744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45909833908081</t>
+    <t xml:space="preserve">5.47283840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45909881591797</t>
   </si>
   <si>
     <t xml:space="preserve">5.55985403060913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69724750518799</t>
+    <t xml:space="preserve">5.69724702835083</t>
   </si>
   <si>
     <t xml:space="preserve">5.7293062210083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.92623567581177</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304533004761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7796835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72472620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80716276168823</t>
+    <t xml:space="preserve">5.77968406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7247257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67892837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71556615829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.71098709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82090187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875745773315</t>
+    <t xml:space="preserve">5.82090139389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
     <t xml:space="preserve">6.04989051818848</t>
@@ -2495,52 +2495,52 @@
     <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22392225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652877807617</t>
+    <t xml:space="preserve">6.22392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652925491333</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24224185943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71395874023438</t>
+    <t xml:space="preserve">6.02241182327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24224138259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71395921707153</t>
   </si>
   <si>
     <t xml:space="preserve">7.10324048995972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941568374634</t>
+    <t xml:space="preserve">7.1994161605835</t>
   </si>
   <si>
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235036849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600568771362</t>
+    <t xml:space="preserve">7.61159563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600616455078</t>
   </si>
   <si>
     <t xml:space="preserve">7.67113256454468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62533521652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735649108887</t>
+    <t xml:space="preserve">7.62533473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
     <t xml:space="preserve">7.28185129165649</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">7.35512781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29101085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697912216187</t>
+    <t xml:space="preserve">7.29101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697959899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.15361738204956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26811265945435</t>
+    <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
     <t xml:space="preserve">7.39634609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57495737075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91844081878662</t>
+    <t xml:space="preserve">7.37802696228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91844177246094</t>
   </si>
   <si>
     <t xml:space="preserve">7.85890340805054</t>
@@ -2585,19 +2585,19 @@
     <t xml:space="preserve">7.67571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655302047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12155961990356</t>
+    <t xml:space="preserve">7.56579732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130395889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12156009674072</t>
   </si>
   <si>
     <t xml:space="preserve">7.41466522216797</t>
@@ -2606,19 +2606,19 @@
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30475044250488</t>
+    <t xml:space="preserve">7.30474996566772</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231435775757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5291600227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43756437301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48794221878052</t>
+    <t xml:space="preserve">7.52915954589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43756341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48794174194336</t>
   </si>
   <si>
     <t xml:space="preserve">7.52000045776367</t>
@@ -2639,19 +2639,19 @@
     <t xml:space="preserve">6.51702785491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7414379119873</t>
+    <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639482498169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7185378074646</t>
+    <t xml:space="preserve">6.71853876113892</t>
   </si>
   <si>
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6177830696106</t>
+    <t xml:space="preserve">6.61778354644775</t>
   </si>
   <si>
     <t xml:space="preserve">7.02538394927979</t>
@@ -2660,10 +2660,10 @@
     <t xml:space="preserve">6.89257049560547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89715003967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845306396484</t>
+    <t xml:space="preserve">6.89715051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.828453540802</t>
   </si>
   <si>
     <t xml:space="preserve">6.80097436904907</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">6.67732048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83303356170654</t>
+    <t xml:space="preserve">6.83303308486938</t>
   </si>
   <si>
     <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63610219955444</t>
+    <t xml:space="preserve">6.6361026763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.11858701705933</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">5.77052402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72014570236206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47741746902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1156153678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381231307983</t>
+    <t xml:space="preserve">5.72014617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47741842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11561489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810018539429</t>
@@ -2726,25 +2726,25 @@
     <t xml:space="preserve">3.32034134864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22416591644287</t>
+    <t xml:space="preserve">3.22416543960571</t>
   </si>
   <si>
     <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22645592689514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44399547576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99356865882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304521560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61344718933105</t>
+    <t xml:space="preserve">3.22645545005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44399523735046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99356889724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304545402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61344695091248</t>
   </si>
   <si>
     <t xml:space="preserve">3.50353264808655</t>
@@ -2753,19 +2753,19 @@
     <t xml:space="preserve">3.67069435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61802673339844</t>
+    <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.70962262153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663825035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168086051941</t>
+    <t xml:space="preserve">3.6226065158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663872718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168062210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.06684541702271</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38285064697266</t>
+    <t xml:space="preserve">4.38284969329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722326278687</t>
@@ -2786,43 +2786,43 @@
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48818492889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45612716674805</t>
+    <t xml:space="preserve">4.09432411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4881854057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45612668991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.35995149612427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26835584640503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26377630233765</t>
+    <t xml:space="preserve">4.26835536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26377582550049</t>
   </si>
   <si>
     <t xml:space="preserve">4.32331323623657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957460403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676019668579</t>
+    <t xml:space="preserve">4.35537195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676067352295</t>
   </si>
   <si>
     <t xml:space="preserve">4.67137670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52482414245605</t>
+    <t xml:space="preserve">4.5248236656189</t>
   </si>
   <si>
     <t xml:space="preserve">4.48360586166382</t>
@@ -2837,82 +2837,82 @@
     <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95761251449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90036535263062</t>
+    <t xml:space="preserve">4.95761299133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90036582946777</t>
   </si>
   <si>
     <t xml:space="preserve">4.88891649246216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04920816421509</t>
+    <t xml:space="preserve">5.04920864105225</t>
   </si>
   <si>
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239946365356</t>
+    <t xml:space="preserve">5.23239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34689474105835</t>
+    <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
     <t xml:space="preserve">5.16370248794556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93471384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19805145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254529953003</t>
+    <t xml:space="preserve">4.93471336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19805097579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39269161224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20950078964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15225410461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14080429077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27819681167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09500646591187</t>
+    <t xml:space="preserve">5.39269208908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20950031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1522536277771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14080381393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27819776535034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09500598907471</t>
   </si>
   <si>
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01485967636108</t>
+    <t xml:space="preserve">5.01486015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0606575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22095012664795</t>
+    <t xml:space="preserve">5.06065797805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22094964981079</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210731506348</t>
@@ -2921,25 +2921,25 @@
     <t xml:space="preserve">5.10645580291748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12935495376587</t>
+    <t xml:space="preserve">5.12935447692871</t>
   </si>
   <si>
     <t xml:space="preserve">5.3239951133728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03775835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355665206909</t>
+    <t xml:space="preserve">5.33544445037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03775882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355712890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.96906232833862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616365432739</t>
+    <t xml:space="preserve">4.94616317749023</t>
   </si>
   <si>
     <t xml:space="preserve">4.98051166534424</t>
@@ -2948,19 +2948,19 @@
     <t xml:space="preserve">4.84311819076538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181564331055</t>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341081619263</t>
+    <t xml:space="preserve">5.00341129302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.57978057861328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1904993057251</t>
+    <t xml:space="preserve">4.19049882888794</t>
   </si>
   <si>
     <t xml:space="preserve">4.21339845657349</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">4.08058452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30041408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3416314125061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61412906646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54153537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62168121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73617506027222</t>
+    <t xml:space="preserve">4.30041456222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34163188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61412954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54153442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62168073654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73617553710938</t>
   </si>
   <si>
     <t xml:space="preserve">5.69037771224976</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70182752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81632137298584</t>
+    <t xml:space="preserve">5.70182704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.816321849823</t>
   </si>
   <si>
     <t xml:space="preserve">6.14835596084595</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">5.9537148475647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356901168823</t>
+    <t xml:space="preserve">5.87356948852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">6.09110879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19415378570557</t>
+    <t xml:space="preserve">6.19415330886841</t>
   </si>
   <si>
     <t xml:space="preserve">6.12545680999756</t>
@@ -3035,10 +3035,10 @@
     <t xml:space="preserve">6.15980529785156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18270397186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07965898513794</t>
+    <t xml:space="preserve">6.18270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07965850830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.13690662384033</t>
@@ -3047,22 +3047,22 @@
     <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009744644165</t>
+    <t xml:space="preserve">6.3544454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009792327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4803900718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618789672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53763628005981</t>
+    <t xml:space="preserve">6.48038959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53763723373413</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58343505859375</t>
+    <t xml:space="preserve">6.58343458175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169357299805</t>
+    <t xml:space="preserve">6.41169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">6.50328874588013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66358089447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51473808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78952503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75517654418945</t>
+    <t xml:space="preserve">6.66358137130737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5147385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7895245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.68648052215576</t>
@@ -3116,19 +3116,19 @@
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77807521820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40024423599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154726028442</t>
+    <t xml:space="preserve">6.77807569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792985916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40024328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.3887939453125</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">7.7856273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77417945861816</t>
+    <t xml:space="preserve">7.77417898178101</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.17490863800049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01461696624756</t>
+    <t xml:space="preserve">8.01461601257324</t>
   </si>
   <si>
     <t xml:space="preserve">7.99171829223633</t>
@@ -3161,13 +3161,13 @@
     <t xml:space="preserve">8.06041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0260648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911128997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10621166229248</t>
+    <t xml:space="preserve">8.02606582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911033630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1062126159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.03751564025879</t>
@@ -3188,19 +3188,19 @@
     <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28940391540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33520030975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27795314788818</t>
+    <t xml:space="preserve">8.28940486907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766052246094</t>
+    <t xml:space="preserve">8.11766242980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.18635845184326</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">8.34665107727051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23215675354004</t>
+    <t xml:space="preserve">8.23215579986572</t>
   </si>
   <si>
     <t xml:space="preserve">8.16345977783203</t>
@@ -3221,34 +3221,34 @@
     <t xml:space="preserve">8.20925712585449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94591903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84287548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92302083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997632980347</t>
+    <t xml:space="preserve">7.94592046737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84287452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92301988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
   </si>
   <si>
     <t xml:space="preserve">7.86577320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3809986114502</t>
+    <t xml:space="preserve">8.38099765777588</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956115722656</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99926948547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20535945892334</t>
+    <t xml:space="preserve">8.99927043914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20536041259766</t>
   </si>
   <si>
     <t xml:space="preserve">9.48014640808105</t>
@@ -3257,40 +3257,40 @@
     <t xml:space="preserve">9.653564453125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60731887817383</t>
+    <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137046813965</t>
+    <t xml:space="preserve">9.71136856079102</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2894277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3009881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241100311279</t>
+    <t xml:space="preserve">10.2894268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.300989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241119384766</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3587951660156</t>
+    <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
     <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975290298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3356714248657</t>
+    <t xml:space="preserve">10.4975280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628448486328</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7403125762939</t>
+    <t xml:space="preserve">10.7403116226196</t>
   </si>
   <si>
     <t xml:space="preserve">10.4744052886963</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">10.1044492721558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2663059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3934783935547</t>
+    <t xml:space="preserve">10.2663049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3934774398804</t>
   </si>
   <si>
     <t xml:space="preserve">10.0582036972046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95415306091309</t>
+    <t xml:space="preserve">9.9541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0235204696655</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">10.1506938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.092887878418</t>
+    <t xml:space="preserve">10.0697660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928888320923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1160106658936</t>
@@ -3347,40 +3347,40 @@
     <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4859676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853761672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0350828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.416600227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1738166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1391315460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.191198348999</t>
+    <t xml:space="preserve">10.4859666824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1853771209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0350818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4165992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1738147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1391324996948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9052133560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901515007019</t>
+    <t xml:space="preserve">11.9052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015159606934</t>
   </si>
   <si>
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611534118652</t>
+    <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426559448242</t>
@@ -3389,28 +3389,28 @@
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796527862549</t>
+    <t xml:space="preserve">11.5796518325806</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576774597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3206825256348</t>
+    <t xml:space="preserve">11.3576784133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3206815719604</t>
   </si>
   <si>
     <t xml:space="preserve">11.6536436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3946743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4686641693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0975923538208</t>
+    <t xml:space="preserve">11.3946733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4686651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0975914001465</t>
   </si>
   <si>
     <t xml:space="preserve">11.8571195602417</t>
@@ -3419,34 +3419,34 @@
     <t xml:space="preserve">12.0605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0420989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455759048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.0420980453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8941144943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069053649902</t>
+    <t xml:space="preserve">13.7069044113159</t>
   </si>
   <si>
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
+    <t xml:space="preserve">13.5034275054932</t>
   </si>
   <si>
     <t xml:space="preserve">13.8178911209106</t>
@@ -3461,25 +3461,25 @@
     <t xml:space="preserve">14.0398654937744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7439002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4109392166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4294366836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0409832000732</t>
+    <t xml:space="preserve">13.7438993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4109401702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4294376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0409822463989</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669904708862</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3497,16 +3497,16 @@
     <t xml:space="preserve">13.0779781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4468183517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457035064697</t>
+    <t xml:space="preserve">14.4468173980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457025527954</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7786617279053</t>
+    <t xml:space="preserve">15.7786636352539</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
@@ -3515,19 +3515,19 @@
     <t xml:space="preserve">16.3705959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5370750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596054077148</t>
+    <t xml:space="preserve">16.537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596073150635</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7971601486206</t>
+    <t xml:space="preserve">16.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7971620559692</t>
   </si>
   <si>
     <t xml:space="preserve">16.1486186981201</t>
@@ -3536,37 +3536,37 @@
     <t xml:space="preserve">16.0006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.908148765564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5196943283081</t>
+    <t xml:space="preserve">15.9081497192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5196933746338</t>
   </si>
   <si>
     <t xml:space="preserve">15.4642000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8896522521973</t>
+    <t xml:space="preserve">15.8896532058716</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283208847046</t>
+    <t xml:space="preserve">15.834156036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092645645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283199310303</t>
   </si>
   <si>
     <t xml:space="preserve">14.5023126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2433414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6329116821289</t>
+    <t xml:space="preserve">14.2433423995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6329135894775</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514110565186</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">14.0583629608154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1693515777588</t>
+    <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
     <t xml:space="preserve">13.8918838500977</t>
@@ -3590,40 +3590,40 @@
     <t xml:space="preserve">14.4098224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1508531570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7808952331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629566192627</t>
+    <t xml:space="preserve">14.1508541107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7993946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7808961868286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629556655884</t>
   </si>
   <si>
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924407958984</t>
+    <t xml:space="preserve">13.3924417495728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.965874671936</t>
+    <t xml:space="preserve">13.9658737182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2803363800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1138582229614</t>
+    <t xml:space="preserve">14.2988357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1138572692871</t>
   </si>
   <si>
     <t xml:space="preserve">12.9484930038452</t>
@@ -3635,34 +3635,34 @@
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3935565948486</t>
+    <t xml:space="preserve">13.4479351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085790634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3935575485229</t>
   </si>
   <si>
     <t xml:space="preserve">13.18896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4664335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8190069198608</t>
+    <t xml:space="preserve">13.4664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8190078735352</t>
   </si>
   <si>
     <t xml:space="preserve">11.9126138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6340293884277</t>
+    <t xml:space="preserve">12.6340284347534</t>
   </si>
   <si>
     <t xml:space="preserve">12.3380641937256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8386220932007</t>
+    <t xml:space="preserve">11.838623046875</t>
   </si>
   <si>
     <t xml:space="preserve">12.1345872879028</t>
@@ -3677,10 +3677,10 @@
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">12.0051031112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">10.8582363128662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5067758560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1172065734863</t>
+    <t xml:space="preserve">10.5067777633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.117205619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8201246261597</t>
@@ -3707,52 +3707,52 @@
     <t xml:space="preserve">11.4131717681885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6710243225098</t>
+    <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265186309814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8005094528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3646945953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7172689437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6617746353149</t>
+    <t xml:space="preserve">12.8005104064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3276987075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3646936416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7172698974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6617765426636</t>
   </si>
   <si>
     <t xml:space="preserve">12.4305534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028062820435</t>
+    <t xml:space="preserve">12.4028053283691</t>
   </si>
   <si>
     <t xml:space="preserve">12.5137929916382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3473138809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3288154602051</t>
+    <t xml:space="preserve">12.3473129272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155309677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4398012161255</t>
+    <t xml:space="preserve">12.6155319213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4398021697998</t>
   </si>
   <si>
     <t xml:space="preserve">11.8016262054443</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.764630317688</t>
+    <t xml:space="preserve">11.7646312713623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848667144775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073980331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.551905632019</t>
+    <t xml:space="preserve">11.6073999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5519046783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.2929363250732</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">10.6455106735229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7657480239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0987071990967</t>
+    <t xml:space="preserve">10.7657470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
     <t xml:space="preserve">11.5704030990601</t>
@@ -70915,7 +70915,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6495023148</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>129600</v>
@@ -70924,7 +70924,7 @@
         <v>11.8299999237061</v>
       </c>
       <c r="D2492" t="n">
-        <v>11.6099996566772</v>
+        <v>11.5900001525879</v>
       </c>
       <c r="E2492" t="n">
         <v>11.75</v>
@@ -70936,6 +70936,32 @@
         <v>1932</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6495486111</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>52579</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>11.4099998474121</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>11.5900001525879</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034394264221</t>
+    <t xml:space="preserve">2.10034418106079</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15079474449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13486313819885</t>
+    <t xml:space="preserve">2.150794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13486289978027</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768843650818</t>
@@ -59,25 +59,25 @@
     <t xml:space="preserve">2.02334022521973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06316995620728</t>
+    <t xml:space="preserve">2.06316947937012</t>
   </si>
   <si>
     <t xml:space="preserve">2.05254864692688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96492338180542</t>
+    <t xml:space="preserve">1.96492326259613</t>
   </si>
   <si>
     <t xml:space="preserve">1.98988330364227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96439290046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802945137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01696729660034</t>
+    <t xml:space="preserve">1.96439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802968978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696753501892</t>
   </si>
   <si>
     <t xml:space="preserve">2.00209784507751</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">2.01909160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97819995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854121208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774951457977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943274021149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447293758392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93306005001068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712820529938</t>
+    <t xml:space="preserve">1.97820007801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774927616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943250179291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447257995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93305993080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712784767151</t>
   </si>
   <si>
     <t xml:space="preserve">1.94633650779724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95589566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436811208725</t>
+    <t xml:space="preserve">1.95589578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368124008179</t>
   </si>
   <si>
     <t xml:space="preserve">2.09237813949585</t>
@@ -131,28 +131,28 @@
     <t xml:space="preserve">2.07113575935364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08441209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450221061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203736305237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10830974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1396427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
+    <t xml:space="preserve">2.08441233634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450244903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203712463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10830998420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13964247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299921035767</t>
   </si>
   <si>
     <t xml:space="preserve">2.14442205429077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14548444747925</t>
+    <t xml:space="preserve">2.14548420906067</t>
   </si>
   <si>
     <t xml:space="preserve">2.15345001220703</t>
@@ -167,31 +167,31 @@
     <t xml:space="preserve">2.16831970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18265819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955212593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10565447807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
+    <t xml:space="preserve">2.18265843391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22248792648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1056547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706760406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12158608436584</t>
+    <t xml:space="preserve">2.12158632278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.14017367362976</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">2.05307936668396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06848001480103</t>
+    <t xml:space="preserve">2.06848049163818</t>
   </si>
   <si>
     <t xml:space="preserve">2.06901144981384</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12477254867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16141581535339</t>
+    <t xml:space="preserve">2.12477278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16141605377197</t>
   </si>
   <si>
     <t xml:space="preserve">2.15557408332825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17734813690186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373030662537</t>
+    <t xml:space="preserve">2.17734789848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373054504395</t>
   </si>
   <si>
     <t xml:space="preserve">2.25169634819031</t>
@@ -248,70 +248,70 @@
     <t xml:space="preserve">2.21452212333679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22514343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638533592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098468780518</t>
+    <t xml:space="preserve">2.22514319419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098492622375</t>
   </si>
   <si>
     <t xml:space="preserve">2.32073426246643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888052940369</t>
+    <t xml:space="preserve">2.34888029098511</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604455947876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4492506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288796424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555318832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997183799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6154727935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66718339920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7216157913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8152391910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894026756287</t>
+    <t xml:space="preserve">2.44925093650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5655529499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61547255516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555047035217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66718292236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70147609710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786787986755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72161555290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346632957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894074440002</t>
   </si>
   <si>
     <t xml:space="preserve">2.98942255973816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00248646736145</t>
+    <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
     <t xml:space="preserve">2.94587659835815</t>
@@ -329,85 +329,85 @@
     <t xml:space="preserve">2.89797639846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81959366798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685669898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954882144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78693461418152</t>
+    <t xml:space="preserve">2.81959390640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516175270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69548797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78693413734436</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98289060592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84789872169495</t>
+    <t xml:space="preserve">2.98289084434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84789896011353</t>
   </si>
   <si>
     <t xml:space="preserve">2.776047706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313962936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97200417518616</t>
+    <t xml:space="preserve">2.86313939094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974902153015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97200393676758</t>
   </si>
   <si>
     <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97418165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813151359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9785361289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03514552116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820919036865</t>
+    <t xml:space="preserve">2.97418141365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813199043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97853636741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820895195007</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15707397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29859828948975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730700492859</t>
+    <t xml:space="preserve">3.15707421302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29859805107117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">3.34214401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29206609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771138191223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416589736938</t>
+    <t xml:space="preserve">3.2920663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158404350281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416565895081</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988885879517</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25722980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2659387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17449235916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25505208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25940704345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33125782012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35085320472717</t>
+    <t xml:space="preserve">3.2572295665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593852043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17449259757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25505232810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25940680503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33125758171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35085296630859</t>
   </si>
   <si>
     <t xml:space="preserve">3.34432101249695</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">3.32472586631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28553438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247023582458</t>
+    <t xml:space="preserve">3.28553414344788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247047424316</t>
   </si>
   <si>
     <t xml:space="preserve">3.35303044319153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32037091255188</t>
+    <t xml:space="preserve">3.3203706741333</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682518959045</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">3.31383895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30948448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15054249763489</t>
+    <t xml:space="preserve">3.30948424339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15054225921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.18973326683044</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">3.22239303588867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09175515174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497441291809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262606620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59253287315369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962431907654</t>
+    <t xml:space="preserve">3.09175539016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33343482017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497488975525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59253239631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962408065796</t>
   </si>
   <si>
     <t xml:space="preserve">3.78631138801575</t>
@@ -512,52 +512,52 @@
     <t xml:space="preserve">3.90823984146118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01057291030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09330940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533200263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
+    <t xml:space="preserve">4.010573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09330987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831751823425</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346523284912</t>
+    <t xml:space="preserve">4.19346475601196</t>
   </si>
   <si>
     <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483371734619</t>
+    <t xml:space="preserve">4.23483467102051</t>
   </si>
   <si>
     <t xml:space="preserve">4.26313829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47433614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68988847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65722846984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956106185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95334053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245386123657</t>
+    <t xml:space="preserve">4.47433662414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6898889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65722799301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64634227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95334005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245338439941</t>
   </si>
   <si>
     <t xml:space="preserve">4.72036981582642</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">4.6441650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57231378555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37417984008789</t>
+    <t xml:space="preserve">4.57231473922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37418031692505</t>
   </si>
   <si>
     <t xml:space="preserve">4.35023021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34152126312256</t>
+    <t xml:space="preserve">4.34152173995972</t>
   </si>
   <si>
     <t xml:space="preserve">4.22830152511597</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">4.08895587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612428665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572038650513</t>
+    <t xml:space="preserve">4.22612476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547088623047</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">4.35458469390869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33934354782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63763284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545608520508</t>
+    <t xml:space="preserve">4.3393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940618515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545560836792</t>
   </si>
   <si>
     <t xml:space="preserve">4.61586046218872</t>
@@ -623,25 +623,25 @@
     <t xml:space="preserve">4.64851951599121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72254800796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6637601852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58973264694214</t>
+    <t xml:space="preserve">4.72254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59408760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66376066207886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58973217010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.51135015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73343420028687</t>
+    <t xml:space="preserve">4.52441453933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73343324661255</t>
   </si>
   <si>
     <t xml:space="preserve">4.64198732376099</t>
@@ -650,73 +650,73 @@
     <t xml:space="preserve">4.78568887710571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77480220794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74649715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609230041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921884536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38662099838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29082012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25162935256958</t>
+    <t xml:space="preserve">4.77480268478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.746497631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38662195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29082059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25162982940674</t>
   </si>
   <si>
     <t xml:space="preserve">5.22985649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22767972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607797622681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11010599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22550201416016</t>
+    <t xml:space="preserve">5.22767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11010503768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.225501537323</t>
   </si>
   <si>
     <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041574478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17107009887695</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17106962203979</t>
   </si>
   <si>
     <t xml:space="preserve">5.14494228363037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979385375977</t>
+    <t xml:space="preserve">5.06220483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979433059692</t>
   </si>
   <si>
     <t xml:space="preserve">5.09050941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04043245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10139608383179</t>
+    <t xml:space="preserve">5.04043197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11446046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10139656066895</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268665313721</t>
@@ -728,76 +728,76 @@
     <t xml:space="preserve">5.11663770675659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04478693008423</t>
+    <t xml:space="preserve">5.04478645324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.95769453048706</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02736806869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8662486076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85536193847656</t>
+    <t xml:space="preserve">5.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98817682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8858437538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86624908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85536241531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.84665298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8009295463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7356104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74432039260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738477706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91850328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08397769927979</t>
+    <t xml:space="preserve">4.80092906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74431991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6811785697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8205246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91850423812866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13841104507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0839786529541</t>
   </si>
   <si>
     <t xml:space="preserve">5.19719696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11881494522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09486436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4171028137207</t>
+    <t xml:space="preserve">5.11881446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444423675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710329055786</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209541320801</t>
@@ -806,34 +806,34 @@
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385299682617</t>
+    <t xml:space="preserve">5.63918781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385347366333</t>
   </si>
   <si>
     <t xml:space="preserve">5.91134929656982</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94400835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383771896362</t>
+    <t xml:space="preserve">5.94400787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383724212646</t>
   </si>
   <si>
     <t xml:space="preserve">5.81337118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87868976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75893831253052</t>
+    <t xml:space="preserve">5.87868928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
     <t xml:space="preserve">5.76329326629639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88957548141479</t>
+    <t xml:space="preserve">5.88957643508911</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610767364502</t>
@@ -842,31 +842,31 @@
     <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0964183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94836330413818</t>
+    <t xml:space="preserve">6.09641790390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94836282730103</t>
   </si>
   <si>
     <t xml:space="preserve">5.9897313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0049729347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9875545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198598861694</t>
+    <t xml:space="preserve">6.00497245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98755407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722761154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08335542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96360397338867</t>
+    <t xml:space="preserve">6.08335494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96360349655151</t>
   </si>
   <si>
     <t xml:space="preserve">6.07464599609375</t>
@@ -875,76 +875,76 @@
     <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42301273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26842546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52969932556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276466369629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848810195923</t>
+    <t xml:space="preserve">6.42301321029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26842594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848667144775</t>
   </si>
   <si>
     <t xml:space="preserve">6.80403900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90201759338379</t>
+    <t xml:space="preserve">6.90201711654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.01088190078735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06531381607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756896972656</t>
+    <t xml:space="preserve">7.0653133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1175684928894</t>
   </si>
   <si>
     <t xml:space="preserve">7.3200569152832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13063287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360216140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521966934204</t>
+    <t xml:space="preserve">7.1306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425603866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207927703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321401596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29392957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666749954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28522109985352</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481576919556</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19595146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309064865112</t>
+    <t xml:space="preserve">7.19595193862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46655797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22705698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309017181396</t>
   </si>
   <si>
     <t xml:space="preserve">6.40123987197876</t>
@@ -953,13 +953,13 @@
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704074859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57760000228882</t>
+    <t xml:space="preserve">6.49704122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57760047912598</t>
   </si>
   <si>
     <t xml:space="preserve">6.52464389801025</t>
@@ -968,28 +968,28 @@
     <t xml:space="preserve">6.56215476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61290502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45403575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774116516113</t>
+    <t xml:space="preserve">6.61290407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45403623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774164199829</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740322113037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652584075928</t>
+    <t xml:space="preserve">6.76294755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652536392212</t>
   </si>
   <si>
     <t xml:space="preserve">6.58421993255615</t>
@@ -998,40 +998,40 @@
     <t xml:space="preserve">6.50478553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42093849182129</t>
+    <t xml:space="preserve">6.42093801498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488416671753</t>
+    <t xml:space="preserve">6.35694980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488368988037</t>
   </si>
   <si>
     <t xml:space="preserve">6.4341778755188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32826471328735</t>
+    <t xml:space="preserve">6.32826519012451</t>
   </si>
   <si>
     <t xml:space="preserve">6.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057109832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14291858673096</t>
+    <t xml:space="preserve">6.3746018409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14291763305664</t>
   </si>
   <si>
     <t xml:space="preserve">6.13850593566895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9575719833374</t>
+    <t xml:space="preserve">5.95757150650024</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344165802002</t>
@@ -1040,46 +1040,46 @@
     <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78546380996704</t>
+    <t xml:space="preserve">5.93771314620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7854642868042</t>
   </si>
   <si>
     <t xml:space="preserve">5.95977830886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9200611114502</t>
+    <t xml:space="preserve">5.92006158828735</t>
   </si>
   <si>
     <t xml:space="preserve">5.93329954147339</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94212675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8362135887146</t>
+    <t xml:space="preserve">5.94212627410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83621406555176</t>
   </si>
   <si>
     <t xml:space="preserve">5.84724617004395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98846340179443</t>
+    <t xml:space="preserve">5.98846292495728</t>
   </si>
   <si>
     <t xml:space="preserve">5.69720363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50744342803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4699330329895</t>
+    <t xml:space="preserve">5.50744438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894393920898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692035675049</t>
+    <t xml:space="preserve">5.7369213104248</t>
   </si>
   <si>
     <t xml:space="preserve">5.76119232177734</t>
@@ -1091,34 +1091,34 @@
     <t xml:space="preserve">5.71485567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72147560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59129095077515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608551025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4434552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007419586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199819564819</t>
+    <t xml:space="preserve">5.72147512435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59129190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608646392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54495477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44345569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41918325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">5.56040048599243</t>
@@ -1127,16 +1127,16 @@
     <t xml:space="preserve">5.48096561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52730274200439</t>
+    <t xml:space="preserve">5.52730226516724</t>
   </si>
   <si>
     <t xml:space="preserve">5.45890092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41256427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979139328003</t>
+    <t xml:space="preserve">5.41256475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
     <t xml:space="preserve">5.56922626495361</t>
@@ -1145,64 +1145,64 @@
     <t xml:space="preserve">5.73912763595581</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66410636901855</t>
+    <t xml:space="preserve">5.6641058921814</t>
   </si>
   <si>
     <t xml:space="preserve">5.80311584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86931180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860408782959</t>
+    <t xml:space="preserve">5.86931133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554983139038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.80532264709473</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63762807846069</t>
+    <t xml:space="preserve">5.63762760162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.56481266021729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47875928878784</t>
+    <t xml:space="preserve">5.52068376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875881195068</t>
   </si>
   <si>
     <t xml:space="preserve">5.49420499801636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36181354522705</t>
+    <t xml:space="preserve">5.36181402206421</t>
   </si>
   <si>
     <t xml:space="preserve">5.29782581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22942352294922</t>
+    <t xml:space="preserve">5.22942399978638</t>
   </si>
   <si>
     <t xml:space="preserve">5.24045610427856</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25369596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477012634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39711809158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796697616577</t>
+    <t xml:space="preserve">5.25369548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39711856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796745300293</t>
   </si>
   <si>
     <t xml:space="preserve">5.2228045463562</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">5.14116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11909818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20735883712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16764211654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13233757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1367506980896</t>
+    <t xml:space="preserve">5.11909866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.207359790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16764163970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13233804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
     <t xml:space="preserve">5.03745794296265</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96464395523071</t>
+    <t xml:space="preserve">4.9646430015564</t>
   </si>
   <si>
     <t xml:space="preserve">4.95802307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97126245498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04849052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19411945343018</t>
+    <t xml:space="preserve">4.97126293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04849004745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19411993026733</t>
   </si>
   <si>
     <t xml:space="preserve">5.27576065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22501039505005</t>
+    <t xml:space="preserve">5.22501134872437</t>
   </si>
   <si>
     <t xml:space="preserve">5.24486970901489</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">5.11689186096191</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03083848953247</t>
+    <t xml:space="preserve">5.03083753585815</t>
   </si>
   <si>
     <t xml:space="preserve">4.87196969985962</t>
@@ -1271,40 +1271,40 @@
     <t xml:space="preserve">4.71089458465576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65131902694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839189529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6045298576355</t>
+    <t xml:space="preserve">4.65131855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60453081130981</t>
   </si>
   <si>
     <t xml:space="preserve">5.8119421005249</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84503936767578</t>
+    <t xml:space="preserve">5.84503984451294</t>
   </si>
   <si>
     <t xml:space="preserve">5.76781177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.904616355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663803100586</t>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663850784302</t>
   </si>
   <si>
     <t xml:space="preserve">5.81856155395508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65307378768921</t>
+    <t xml:space="preserve">5.65307331085205</t>
   </si>
   <si>
     <t xml:space="preserve">5.6398344039917</t>
@@ -1313,31 +1313,31 @@
     <t xml:space="preserve">5.6994104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58467245101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1936674118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348466873169</t>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348419189453</t>
   </si>
   <si>
     <t xml:space="preserve">6.14071130752563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12526655197144</t>
+    <t xml:space="preserve">6.12526702880859</t>
   </si>
   <si>
     <t xml:space="preserve">6.02597284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96419095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
+    <t xml:space="preserve">5.96419191360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479909896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.8097357749939</t>
@@ -1346,28 +1346,28 @@
     <t xml:space="preserve">5.88034391403198</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90020227432251</t>
+    <t xml:space="preserve">5.90020275115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.82518100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74354124069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6508674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776876449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935434341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607242584229</t>
+    <t xml:space="preserve">5.74353981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65086698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607290267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.71926879882812</t>
@@ -1376,337 +1376,337 @@
     <t xml:space="preserve">5.84283304214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0325927734375</t>
+    <t xml:space="preserve">6.03259229660034</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95315790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433307647705</t>
+    <t xml:space="preserve">5.95315837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243757247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5559868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9222674369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372493743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543668746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571853637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9284348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90637016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1005425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22852087020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908647537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0475869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4933009147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18439102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.440345287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941228866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528100967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969509124756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127876281738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743171691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802587509155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5445032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219778060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163354873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.579270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534536361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087120056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305927276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14095020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829339981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.2885479927063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372446060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543668746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9284348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90636968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050096511841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22851896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49330139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560682296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941228866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21969413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6212797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743171691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738918304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66424989700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163307189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294219970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65977811813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57927083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49429035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14095020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356702804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.21251344680786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33774709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821582794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981666564941</t>
+    <t xml:space="preserve">6.33774757385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821535110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981761932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.53007125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44061803817749</t>
+    <t xml:space="preserve">6.44061756134033</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4003643989563</t>
+    <t xml:space="preserve">6.39141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40036392211914</t>
   </si>
   <si>
     <t xml:space="preserve">6.37352800369263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42719984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43167304992676</t>
+    <t xml:space="preserve">6.42720031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4316725730896</t>
   </si>
   <si>
     <t xml:space="preserve">6.50323486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32880115509033</t>
+    <t xml:space="preserve">6.32880163192749</t>
   </si>
   <si>
     <t xml:space="preserve">6.23934841156006</t>
@@ -1724,16 +1724,16 @@
     <t xml:space="preserve">6.64188718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1006965637207</t>
+    <t xml:space="preserve">6.10069704055786</t>
   </si>
   <si>
     <t xml:space="preserve">6.3958911895752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440742492676</t>
+    <t xml:space="preserve">6.18567657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440837860107</t>
   </si>
   <si>
     <t xml:space="preserve">5.47452545166016</t>
@@ -1742,34 +1742,34 @@
     <t xml:space="preserve">5.33587265014648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24194717407227</t>
+    <t xml:space="preserve">5.24194765090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.08093214035034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013124465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831483840942</t>
+    <t xml:space="preserve">4.97358894348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013172149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831436157227</t>
   </si>
   <si>
     <t xml:space="preserve">4.96464347839355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07645893096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05409574508667</t>
+    <t xml:space="preserve">5.0764594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05409622192383</t>
   </si>
   <si>
     <t xml:space="preserve">4.98700618743896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92886161804199</t>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">4.58894062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61577653884888</t>
+    <t xml:space="preserve">4.61577606201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.74995565414429</t>
@@ -1793,88 +1793,88 @@
     <t xml:space="preserve">4.12825679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876455307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04103994369507</t>
+    <t xml:space="preserve">4.20876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483860015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04104042053223</t>
   </si>
   <si>
     <t xml:space="preserve">4.0544581413269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95829677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15509271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01867723464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8688428401947</t>
+    <t xml:space="preserve">3.95829606056213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1550931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13049411773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0186767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884307861328</t>
   </si>
   <si>
     <t xml:space="preserve">3.70559144020081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75702691078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8375346660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648036956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15732860565186</t>
+    <t xml:space="preserve">3.75702714920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83753514289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648060798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500587463379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15732955932617</t>
   </si>
   <si>
     <t xml:space="preserve">4.00302314758301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475175857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8621346950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512318611145</t>
+    <t xml:space="preserve">3.92475199699402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9426417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331628799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424424171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512294769287</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24267244338989</t>
+    <t xml:space="preserve">3.24267268180847</t>
   </si>
   <si>
     <t xml:space="preserve">3.03245782852173</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">3.04140305519104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16216468811035</t>
+    <t xml:space="preserve">3.16216421127319</t>
   </si>
   <si>
     <t xml:space="preserve">3.3835608959198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38803339004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26950788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22701787948608</t>
+    <t xml:space="preserve">3.38803315162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26950812339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22701811790466</t>
   </si>
   <si>
     <t xml:space="preserve">3.4528865814209</t>
@@ -1907,55 +1907,55 @@
     <t xml:space="preserve">3.48866820335388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51550436019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870722770691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24714517593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11072897911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92735028266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01009440422058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1040198802948</t>
+    <t xml:space="preserve">3.51550388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870698928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24714493751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92735052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182301521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01009464263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
     <t xml:space="preserve">3.03916645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8848602771759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92511415481567</t>
+    <t xml:space="preserve">2.95642280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88485980033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92511391639709</t>
   </si>
   <si>
     <t xml:space="preserve">2.77751660346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74844431877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83342456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933253288269</t>
+    <t xml:space="preserve">2.74844408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78869795799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83342480659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933277130127</t>
   </si>
   <si>
     <t xml:space="preserve">3.07271146774292</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">3.10625672340393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16887354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22925400733948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15992832183838</t>
+    <t xml:space="preserve">3.16887378692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22925424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1599280834198</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254514694214</t>
@@ -1991,106 +1991,106 @@
     <t xml:space="preserve">3.54234004020691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972273826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339457511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4953773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61166596412659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57588481903076</t>
+    <t xml:space="preserve">3.47972321510315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53339433670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49537706375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533780097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588458061218</t>
   </si>
   <si>
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221274375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58259391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723273277283</t>
+    <t xml:space="preserve">3.52221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5825936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723249435425</t>
   </si>
   <si>
     <t xml:space="preserve">3.52444958686829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58483004570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69440960884094</t>
+    <t xml:space="preserve">3.58483028411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6944100856781</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61390209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80398988723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567923545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77268171310425</t>
+    <t xml:space="preserve">3.61390256881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335507392883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80399012565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567947387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77268123626709</t>
   </si>
   <si>
     <t xml:space="preserve">3.83306193351746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.857661485672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040608406067</t>
+    <t xml:space="preserve">3.85766172409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040560722351</t>
   </si>
   <si>
     <t xml:space="preserve">3.99184131622314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07011270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13272953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09247541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125503540039</t>
+    <t xml:space="preserve">4.07011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13273000717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09247636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125551223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863725662231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94935083389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525903701782</t>
+    <t xml:space="preserve">3.94935059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525951385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842407226562</t>
+    <t xml:space="preserve">3.97842359542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.23112821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28256320953369</t>
+    <t xml:space="preserve">4.28256416320801</t>
   </si>
   <si>
     <t xml:space="preserve">4.38319826126099</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35412645339966</t>
+    <t xml:space="preserve">4.3541259765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.1662745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2780909538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205593109131</t>
+    <t xml:space="preserve">4.20429277420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27809143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205640792847</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783731460571</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24007320404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25349187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19982004165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0745849609375</t>
+    <t xml:space="preserve">4.24901866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24007368087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25349140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982051849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
     <t xml:space="preserve">4.15285682678223</t>
@@ -2141,79 +2141,79 @@
     <t xml:space="preserve">4.1864013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171449661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93369650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015196800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631357192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03656768798828</t>
+    <t xml:space="preserve">4.26914596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171473503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93369698524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0388035774231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03656721115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804265975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778902053833</t>
+    <t xml:space="preserve">3.91804242134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778854370117</t>
   </si>
   <si>
     <t xml:space="preserve">3.76820874214172</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77491736412048</t>
+    <t xml:space="preserve">3.77491760253906</t>
   </si>
   <si>
     <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85095310211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0991849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82411670684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95693063735962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88136458396912</t>
+    <t xml:space="preserve">3.85095286369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09918451309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411694526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
     <t xml:space="preserve">3.76229023933411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74626088142395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76457977294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68901348114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67298460006714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252129554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84243607521057</t>
+    <t xml:space="preserve">3.74626111984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7645800113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68901371955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67298436164856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84243631362915</t>
   </si>
   <si>
     <t xml:space="preserve">3.87220454216003</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">3.92487192153931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96608996391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006060600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449502944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
+    <t xml:space="preserve">3.96609044075012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739346504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449479103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655326843262</t>
   </si>
   <si>
     <t xml:space="preserve">3.98440957069397</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">4.04165649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1538610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09203386306763</t>
+    <t xml:space="preserve">4.19736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15386152267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09203433990479</t>
   </si>
   <si>
     <t xml:space="preserve">4.11264276504517</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">4.10119342803955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14470243453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18821001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751541137695</t>
+    <t xml:space="preserve">4.14470195770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18820953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751493453979</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438472747803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31415319442749</t>
+    <t xml:space="preserve">4.31415367126465</t>
   </si>
   <si>
     <t xml:space="preserve">4.40803909301758</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2454571723938</t>
+    <t xml:space="preserve">4.24545669555664</t>
   </si>
   <si>
     <t xml:space="preserve">4.3324728012085</t>
@@ -2294,22 +2294,22 @@
     <t xml:space="preserve">4.22255802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774694442749</t>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.17446994781494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05997562408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09890413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15157127380371</t>
+    <t xml:space="preserve">4.05997610092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15157079696655</t>
   </si>
   <si>
     <t xml:space="preserve">4.16302061080933</t>
@@ -2324,43 +2324,43 @@
     <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05539560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94548082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701561927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594460487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678480148315</t>
+    <t xml:space="preserve">4.00730848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97066974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.945481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594388961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.876784324646</t>
   </si>
   <si>
     <t xml:space="preserve">3.85159540176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95235133171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98211908340454</t>
+    <t xml:space="preserve">3.9523503780365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9821195602417</t>
   </si>
   <si>
     <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493301391602</t>
+    <t xml:space="preserve">4.11493253707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.16760063171387</t>
@@ -2369,19 +2369,19 @@
     <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0531063079834</t>
+    <t xml:space="preserve">4.05310583114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.18591928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13554191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06226539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34392261505127</t>
+    <t xml:space="preserve">4.1355414390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06226587295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34392213821411</t>
   </si>
   <si>
     <t xml:space="preserve">4.33705234527588</t>
@@ -2390,10 +2390,10 @@
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60268020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00112104415894</t>
+    <t xml:space="preserve">4.60267925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00112056732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.17515230178833</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">5.33086538314819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35834407806396</t>
+    <t xml:space="preserve">5.35834360122681</t>
   </si>
   <si>
     <t xml:space="preserve">5.62855100631714</t>
@@ -2417,40 +2417,40 @@
     <t xml:space="preserve">5.61023139953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70640707015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527496337891</t>
+    <t xml:space="preserve">5.70640659332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451927185059</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4819974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26674795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27590799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36292362213135</t>
+    <t xml:space="preserve">5.48199796676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27590751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36292266845703</t>
   </si>
   <si>
     <t xml:space="preserve">5.44993877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3446044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47283840179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55985403060913</t>
+    <t xml:space="preserve">5.34460496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47283792495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45909833908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.69724702835083</t>
@@ -2465,22 +2465,22 @@
     <t xml:space="preserve">5.74304533004761</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77968406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7247257232666</t>
+    <t xml:space="preserve">5.7796835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72472620010376</t>
   </si>
   <si>
     <t xml:space="preserve">5.67892837524414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71556615829468</t>
+    <t xml:space="preserve">5.71556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098709106445</t>
+    <t xml:space="preserve">5.71098661422729</t>
   </si>
   <si>
     <t xml:space="preserve">5.82090139389038</t>
@@ -2492,52 +2492,52 @@
     <t xml:space="preserve">6.04989051818848</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12316703796387</t>
+    <t xml:space="preserve">6.12316751480103</t>
   </si>
   <si>
     <t xml:space="preserve">6.22392177581787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652925491333</t>
+    <t xml:space="preserve">6.08652877807617</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241182327271</t>
+    <t xml:space="preserve">6.02241134643555</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71395921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10324048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28643131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235132217407</t>
+    <t xml:space="preserve">6.71395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28643083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61159610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235179901123</t>
   </si>
   <si>
     <t xml:space="preserve">7.83600616455078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67113256454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62533473968506</t>
+    <t xml:space="preserve">7.67113304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6253342628479</t>
   </si>
   <si>
     <t xml:space="preserve">7.16735696792603</t>
@@ -2549,28 +2549,28 @@
     <t xml:space="preserve">7.41924524307251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35512781143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29101133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727222442627</t>
+    <t xml:space="preserve">7.35512733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29101181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727174758911</t>
   </si>
   <si>
     <t xml:space="preserve">7.11697959899902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15361738204956</t>
+    <t xml:space="preserve">7.15361785888672</t>
   </si>
   <si>
     <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39634609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37802696228027</t>
+    <t xml:space="preserve">7.39634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37802743911743</t>
   </si>
   <si>
     <t xml:space="preserve">7.57495784759521</t>
@@ -2579,13 +2579,13 @@
     <t xml:space="preserve">7.91844177246094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85890340805054</t>
+    <t xml:space="preserve">7.85890436172485</t>
   </si>
   <si>
     <t xml:space="preserve">7.67571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579732894897</t>
+    <t xml:space="preserve">7.56579828262329</t>
   </si>
   <si>
     <t xml:space="preserve">7.66655349731445</t>
@@ -2594,10 +2594,10 @@
     <t xml:space="preserve">7.36428737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45130395889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12156009674072</t>
+    <t xml:space="preserve">7.45130443572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12155914306641</t>
   </si>
   <si>
     <t xml:space="preserve">7.41466522216797</t>
@@ -2606,13 +2606,13 @@
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30474996566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22231435775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52915954589844</t>
+    <t xml:space="preserve">7.30475044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22231483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
     <t xml:space="preserve">7.43756341934204</t>
@@ -2621,16 +2621,16 @@
     <t xml:space="preserve">7.48794174194336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52000045776367</t>
+    <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17651653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02996349334717</t>
+    <t xml:space="preserve">7.17651700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02996397018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.51244878768921</t>
@@ -2639,25 +2639,25 @@
     <t xml:space="preserve">6.51702785491943</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74143743515015</t>
+    <t xml:space="preserve">6.7414379119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639482498169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71853876113892</t>
+    <t xml:space="preserve">6.71853828430176</t>
   </si>
   <si>
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61778354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257049560547</t>
+    <t xml:space="preserve">6.6177830696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">6.89715051651001</t>
@@ -2666,94 +2666,94 @@
     <t xml:space="preserve">6.828453540802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80097436904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67732048034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83303308486938</t>
+    <t xml:space="preserve">6.80097389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67732095718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6361026763916</t>
+    <t xml:space="preserve">6.63610172271729</t>
   </si>
   <si>
     <t xml:space="preserve">6.11858701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96745443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78884315490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63771057128906</t>
+    <t xml:space="preserve">5.96745491027832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78884267807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63771104812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.77052402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72014617919922</t>
+    <t xml:space="preserve">5.72014665603638</t>
   </si>
   <si>
     <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11561489105225</t>
+    <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
     <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59810018539429</t>
+    <t xml:space="preserve">4.59809970855713</t>
   </si>
   <si>
     <t xml:space="preserve">4.63931798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21110868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382479667664</t>
+    <t xml:space="preserve">4.21110820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382455825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034134864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22416543960571</t>
+    <t xml:space="preserve">3.22416567802429</t>
   </si>
   <si>
     <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22645545005798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44399523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304545402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61344695091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50353264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61802697181702</t>
+    <t xml:space="preserve">3.22645568847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44399499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304497718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61344718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50353240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069458961487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61802673339844</t>
   </si>
   <si>
     <t xml:space="preserve">3.70962262153625</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79663872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168062210083</t>
+    <t xml:space="preserve">3.79663848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168086051941</t>
   </si>
   <si>
     <t xml:space="preserve">4.06684541702271</t>
@@ -2774,10 +2774,10 @@
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38284969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11722326278687</t>
+    <t xml:space="preserve">4.38285064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11722278594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.01188802719116</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">4.09432411193848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4881854057312</t>
+    <t xml:space="preserve">4.48818492889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.45612668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35995149612427</t>
+    <t xml:space="preserve">4.35995101928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
@@ -2813,16 +2813,16 @@
     <t xml:space="preserve">4.30957365036011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30499362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5248236656189</t>
+    <t xml:space="preserve">4.30499410629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17675971984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52482318878174</t>
   </si>
   <si>
     <t xml:space="preserve">4.48360586166382</t>
@@ -2834,25 +2834,25 @@
     <t xml:space="preserve">4.42406845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75152254104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95761299133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90036582946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88891649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04920864105225</t>
+    <t xml:space="preserve">4.75152206420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95761251449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90036535263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.888916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04920816421509</t>
   </si>
   <si>
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239994049072</t>
+    <t xml:space="preserve">5.23239946365356</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
@@ -2864,43 +2864,43 @@
     <t xml:space="preserve">5.16370248794556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93471336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630996704102</t>
+    <t xml:space="preserve">4.93471384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630949020386</t>
   </si>
   <si>
     <t xml:space="preserve">5.19805097579956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31254577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39269208908081</t>
+    <t xml:space="preserve">5.31254529953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25529909133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39269161224365</t>
   </si>
   <si>
     <t xml:space="preserve">5.20950031280518</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1522536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27819776535034</t>
+    <t xml:space="preserve">5.15225315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14080429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27819728851318</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.923264503479</t>
+    <t xml:space="preserve">5.09500646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92326402664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.01486015319824</t>
@@ -2921,64 +2921,64 @@
     <t xml:space="preserve">5.10645580291748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12935447692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3239951133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544445037842</t>
+    <t xml:space="preserve">5.12935400009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32399559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544492721558</t>
   </si>
   <si>
     <t xml:space="preserve">5.03775882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96906232833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84311819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181468963623</t>
+    <t xml:space="preserve">5.08355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96906280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9805121421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84311771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57978057861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19049882888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21339845657349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08058452606201</t>
+    <t xml:space="preserve">5.00341081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57978105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19049978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21339797973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08058500289917</t>
   </si>
   <si>
     <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163188934326</t>
+    <t xml:space="preserve">4.34163236618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412954330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54153442382812</t>
+    <t xml:space="preserve">5.54153490066528</t>
   </si>
   <si>
     <t xml:space="preserve">5.62168073654175</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">5.75907468795776</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73617553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69037771224976</t>
+    <t xml:space="preserve">5.73617506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69037818908691</t>
   </si>
   <si>
     <t xml:space="preserve">5.64457988739014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66747856140137</t>
+    <t xml:space="preserve">5.66747903823853</t>
   </si>
   <si>
     <t xml:space="preserve">5.89646816253662</t>
@@ -3011,43 +3011,43 @@
     <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96516418457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9537148475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87356948852539</t>
+    <t xml:space="preserve">5.96516466140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95371532440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87356901168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09110879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415330886841</t>
+    <t xml:space="preserve">6.09110832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415378570557</t>
   </si>
   <si>
     <t xml:space="preserve">6.12545680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15980529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07965850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13690662384033</t>
+    <t xml:space="preserve">6.1598048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18270397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07965898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13690614700317</t>
   </si>
   <si>
     <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3544454574585</t>
+    <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.32009792327881</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">6.52618741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53763723373413</t>
+    <t xml:space="preserve">6.53763675689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
@@ -3071,31 +3071,31 @@
     <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58343458175659</t>
+    <t xml:space="preserve">6.58343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169309616089</t>
+    <t xml:space="preserve">6.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894025802612</t>
+    <t xml:space="preserve">6.46894073486328</t>
   </si>
   <si>
     <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20560312271118</t>
+    <t xml:space="preserve">6.20560359954834</t>
   </si>
   <si>
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328874588013</t>
+    <t xml:space="preserve">6.50328922271729</t>
   </si>
   <si>
     <t xml:space="preserve">6.66358137130737</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7895245552063</t>
+    <t xml:space="preserve">6.78952503204346</t>
   </si>
   <si>
     <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68648052215576</t>
+    <t xml:space="preserve">6.6864800453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">6.77807569503784</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69792985916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40024328231812</t>
+    <t xml:space="preserve">6.69792938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
     <t xml:space="preserve">6.37734508514404</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33154678344727</t>
+    <t xml:space="preserve">6.33154726028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.3887939453125</t>
@@ -3137,25 +3137,25 @@
     <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86967134475708</t>
+    <t xml:space="preserve">6.86967086791992</t>
   </si>
   <si>
     <t xml:space="preserve">7.7856273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77417898178101</t>
+    <t xml:space="preserve">7.77417802810669</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17490863800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99171829223633</t>
+    <t xml:space="preserve">8.1749095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99171733856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041431427002</t>
@@ -3167,13 +3167,13 @@
     <t xml:space="preserve">8.12911033630371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1062126159668</t>
+    <t xml:space="preserve">8.10621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.03751564025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0031681060791</t>
+    <t xml:space="preserve">8.00316715240479</t>
   </si>
   <si>
     <t xml:space="preserve">7.93447113037109</t>
@@ -3185,16 +3185,16 @@
     <t xml:space="preserve">8.3123025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28940486907959</t>
+    <t xml:space="preserve">8.30085182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
     <t xml:space="preserve">8.33520126342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2779541015625</t>
+    <t xml:space="preserve">8.27795314788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200901031494</t>
@@ -3206,10 +3206,10 @@
     <t xml:space="preserve">8.18635845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34665107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215579986572</t>
+    <t xml:space="preserve">8.34665012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215675354004</t>
   </si>
   <si>
     <t xml:space="preserve">8.16345977783203</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">8.20925712585449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94592046737671</t>
+    <t xml:space="preserve">7.94591951370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.95736980438232</t>
@@ -3233,25 +3233,25 @@
     <t xml:space="preserve">7.92301988601685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997680664062</t>
+    <t xml:space="preserve">7.81997632980347</t>
   </si>
   <si>
     <t xml:space="preserve">7.86577320098877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38099765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15956115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99927043914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20536041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48014640808105</t>
+    <t xml:space="preserve">8.38099956512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15956211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99926853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20535850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48014545440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.653564453125</t>
@@ -3260,22 +3260,22 @@
     <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78073692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71136856079102</t>
+    <t xml:space="preserve">9.78073596954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71136951446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2894268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.300989151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241119384766</t>
+    <t xml:space="preserve">10.2894277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3009881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
@@ -3296,13 +3296,13 @@
     <t xml:space="preserve">10.4628448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4050388336182</t>
+    <t xml:space="preserve">10.4050378799438</t>
   </si>
   <si>
     <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7403116226196</t>
+    <t xml:space="preserve">10.7403125762939</t>
   </si>
   <si>
     <t xml:space="preserve">10.4744052886963</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">10.1044492721558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2663049697876</t>
+    <t xml:space="preserve">10.2663059234619</t>
   </si>
   <si>
     <t xml:space="preserve">10.3934774398804</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">10.0697660446167</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1160106658936</t>
+    <t xml:space="preserve">10.092887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1160097122192</t>
   </si>
   <si>
     <t xml:space="preserve">10.2547435760498</t>
@@ -3350,61 +3350,61 @@
     <t xml:space="preserve">10.4859666824341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1853771209717</t>
+    <t xml:space="preserve">10.185378074646</t>
   </si>
   <si>
     <t xml:space="preserve">10.0350818634033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4165992736816</t>
+    <t xml:space="preserve">10.416600227356</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738147735596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391324996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1911964416504</t>
+    <t xml:space="preserve">10.1391315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1911973953247</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9052152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015159606934</t>
+    <t xml:space="preserve">11.9052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.901515007019</t>
   </si>
   <si>
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611543655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426559448242</t>
+    <t xml:space="preserve">11.5611553192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426568984985</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796518325806</t>
+    <t xml:space="preserve">11.5796527862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576784133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3206815719604</t>
+    <t xml:space="preserve">11.3576774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
     <t xml:space="preserve">11.6536436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3946733474731</t>
+    <t xml:space="preserve">11.3946743011475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686651229858</t>
@@ -3413,10 +3413,10 @@
     <t xml:space="preserve">12.0975914001465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8571195602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0605964660645</t>
+    <t xml:space="preserve">11.857120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0605955123901</t>
   </si>
   <si>
     <t xml:space="preserve">12.0420980453491</t>
@@ -3425,31 +3425,31 @@
     <t xml:space="preserve">12.2455739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3010692596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8941144943237</t>
+    <t xml:space="preserve">12.3010683059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8941164016724</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299955368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6144151687622</t>
+    <t xml:space="preserve">13.6144161224365</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069044113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.151969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5034275054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8178911209106</t>
+    <t xml:space="preserve">13.7069034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817892074585</t>
   </si>
   <si>
     <t xml:space="preserve">13.7254018783569</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">14.631796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0398654937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7438993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4294376373291</t>
+    <t xml:space="preserve">14.0398664474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7439002990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4109392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4294366836548</t>
   </si>
   <si>
     <t xml:space="preserve">13.0409822463989</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0964756011963</t>
+    <t xml:space="preserve">13.096474647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.8929986953735</t>
@@ -3491,34 +3491,34 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0779781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4468173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457025527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5011949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7786636352539</t>
+    <t xml:space="preserve">12.9114971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.077977180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4468183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5011959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3705959320068</t>
+    <t xml:space="preserve">16.3705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596073150635</t>
+    <t xml:space="preserve">16.2596054077148</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520965576172</t>
@@ -3536,43 +3536,43 @@
     <t xml:space="preserve">16.0006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9081497192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896532058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.834156036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092645645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5023126602173</t>
+    <t xml:space="preserve">15.9081478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5196952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4642009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283208847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.502311706543</t>
   </si>
   <si>
     <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6329135894775</t>
+    <t xml:space="preserve">13.6329126358032</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.3369483947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">14.4098224639893</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1508541107178</t>
+    <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
     <t xml:space="preserve">13.7993946075439</t>
@@ -3599,40 +3599,40 @@
     <t xml:space="preserve">13.7808961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629556655884</t>
+    <t xml:space="preserve">13.2629566192627</t>
   </si>
   <si>
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924417495728</t>
+    <t xml:space="preserve">13.3924407958984</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9658737182617</t>
+    <t xml:space="preserve">13.965874671936</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2803373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1138572692871</t>
+    <t xml:space="preserve">14.2988367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2803382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1138582229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1334705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0594806671143</t>
+    <t xml:space="preserve">13.1334714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0594797134399</t>
   </si>
   <si>
     <t xml:space="preserve">13.4479351043701</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">12.3380641937256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.838623046875</t>
+    <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
     <t xml:space="preserve">12.1345872879028</t>
@@ -3677,13 +3677,13 @@
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051031112671</t>
+    <t xml:space="preserve">12.0051021575928</t>
   </si>
   <si>
     <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0236005783081</t>
+    <t xml:space="preserve">12.0236015319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.9681062698364</t>
@@ -3692,16 +3692,16 @@
     <t xml:space="preserve">11.0247173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582363128662</t>
+    <t xml:space="preserve">10.8582353591919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5067777633667</t>
   </si>
   <si>
-    <t xml:space="preserve">11.117205619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8201246261597</t>
+    <t xml:space="preserve">11.1172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8201236724854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131717681885</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265186309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8005104064941</t>
+    <t xml:space="preserve">12.7265195846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8005094528198</t>
   </si>
   <si>
     <t xml:space="preserve">13.2259607315063</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">13.3276987075806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3646936416626</t>
+    <t xml:space="preserve">13.3646945953369</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
@@ -3734,10 +3734,10 @@
     <t xml:space="preserve">12.4305534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137929916382</t>
+    <t xml:space="preserve">12.4028062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137939453125</t>
   </si>
   <si>
     <t xml:space="preserve">12.3473129272461</t>
@@ -3749,10 +3749,10 @@
     <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155319213867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4398021697998</t>
+    <t xml:space="preserve">12.6155309677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4398012161255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8016262054443</t>
@@ -3764,52 +3764,52 @@
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7646312713623</t>
+    <t xml:space="preserve">11.764630317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848667144775</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5519046783447</t>
+    <t xml:space="preserve">11.6073989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.551905632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.2929363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7657470703125</t>
+    <t xml:space="preserve">10.6455116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7657480239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5704030990601</t>
+    <t xml:space="preserve">11.5704040527344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293733596802</t>
+    <t xml:space="preserve">11.8293724060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4007749557495</t>
+    <t xml:space="preserve">11.4007759094238</t>
   </si>
   <si>
     <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.569953918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6827402114868</t>
+    <t xml:space="preserve">11.5699548721313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432819366455</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">10.7522554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5642795562744</t>
+    <t xml:space="preserve">10.5642786026001</t>
   </si>
   <si>
     <t xml:space="preserve">11.053017616272</t>
@@ -3857,16 +3857,16 @@
     <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0248212814331</t>
+    <t xml:space="preserve">11.0248203277588</t>
   </si>
   <si>
     <t xml:space="preserve">10.9214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0624179840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4571676254272</t>
+    <t xml:space="preserve">11.0624170303345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4571666717529</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075487136841</t>
+    <t xml:space="preserve">11.6075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297325134277</t>
+    <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
     <t xml:space="preserve">12.096287727356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3876514434814</t>
+    <t xml:space="preserve">12.3876523971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
@@ -3905,7 +3905,7 @@
     <t xml:space="preserve">12.5474319458008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5286340713501</t>
+    <t xml:space="preserve">12.5286331176758</t>
   </si>
   <si>
     <t xml:space="preserve">12.7636041641235</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">12.8481941223145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9985752105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1677541732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4685163497925</t>
+    <t xml:space="preserve">12.998574256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1677532196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4685153961182</t>
   </si>
   <si>
     <t xml:space="preserve">13.618896484375</t>
@@ -3932,22 +3932,22 @@
     <t xml:space="preserve">13.6094980239868</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7034873962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6564931869507</t>
+    <t xml:space="preserve">13.7034864425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6564922332764</t>
   </si>
   <si>
     <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6752901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8726654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6376953125</t>
+    <t xml:space="preserve">13.6752910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6376943588257</t>
   </si>
   <si>
     <t xml:space="preserve">13.3087358474731</t>
@@ -3971,13 +3971,13 @@
     <t xml:space="preserve">13.0643663406372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113595962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9139852523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8199968338013</t>
+    <t xml:space="preserve">13.1113605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9139862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8199977874756</t>
   </si>
   <si>
     <t xml:space="preserve">13.0361700057983</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">13.017373085022</t>
   </si>
   <si>
-    <t xml:space="preserve">13.054967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8669900894165</t>
+    <t xml:space="preserve">13.0549688339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8669910430908</t>
   </si>
   <si>
     <t xml:space="preserve">12.7260093688965</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">12.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857889175415</t>
+    <t xml:space="preserve">12.8857898712158</t>
   </si>
   <si>
     <t xml:space="preserve">12.5850276947021</t>
@@ -4016,13 +4016,13 @@
     <t xml:space="preserve">12.1056871414185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8237218856812</t>
+    <t xml:space="preserve">11.8237209320068</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.391375541687</t>
+    <t xml:space="preserve">11.3913745880127</t>
   </si>
   <si>
     <t xml:space="preserve">11.1470060348511</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000137329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548791885376</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4665660858154</t>
+    <t xml:space="preserve">11.4665670394897</t>
   </si>
   <si>
     <t xml:space="preserve">11.1939992904663</t>
@@ -4064,13 +4064,13 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667667388916</t>
+    <t xml:space="preserve">10.6676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9684286117554</t>
+    <t xml:space="preserve">10.9684295654297</t>
   </si>
   <si>
     <t xml:space="preserve">11.3255834579468</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">11.9929008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795524597168</t>
+    <t xml:space="preserve">11.7955255508423</t>
   </si>
   <si>
     <t xml:space="preserve">11.6357460021973</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">11.6451444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7485303878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.115086555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244831085205</t>
+    <t xml:space="preserve">11.7485313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1150856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244840621948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7354078292847</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">12.895188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6790151596069</t>
+    <t xml:space="preserve">12.6790142059326</t>
   </si>
   <si>
     <t xml:space="preserve">12.472240447998</t>
@@ -4145,22 +4145,22 @@
     <t xml:space="preserve">13.6282958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3275346755981</t>
+    <t xml:space="preserve">13.3275337219238</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437059402466</t>
+    <t xml:space="preserve">13.5437068939209</t>
   </si>
   <si>
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.258017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170358657837</t>
+    <t xml:space="preserve">14.2580165863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170349121094</t>
   </si>
   <si>
     <t xml:space="preserve">13.7504806518555</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463306427002</t>
+    <t xml:space="preserve">13.3463315963745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523441314697</t>
@@ -4190,10 +4190,10 @@
     <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2711410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5249090194702</t>
+    <t xml:space="preserve">13.2711400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5249099731445</t>
   </si>
   <si>
     <t xml:space="preserve">13.6470937728882</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">14.0512428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0042486190796</t>
+    <t xml:space="preserve">14.0042495727539</t>
   </si>
   <si>
     <t xml:space="preserve">14.079439163208</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">13.7786769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8914642333984</t>
+    <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4215221405029</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">14.5587787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7749538421631</t>
+    <t xml:space="preserve">14.7749528884888</t>
   </si>
   <si>
     <t xml:space="preserve">14.840744972229</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">15.0099239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6997623443604</t>
+    <t xml:space="preserve">14.6997632980347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7279586791992</t>
@@ -4253,7 +4253,7 @@
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9441318511963</t>
+    <t xml:space="preserve">14.944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">14.9347333908081</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031492233276</t>
+    <t xml:space="preserve">14.803150177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.7655544281006</t>
@@ -4271,7 +4271,7 @@
     <t xml:space="preserve">14.7937498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.662166595459</t>
+    <t xml:space="preserve">14.6621675491333</t>
   </si>
   <si>
     <t xml:space="preserve">14.8125486373901</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1039123535156</t>
+    <t xml:space="preserve">15.1039113998413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
@@ -4295,7 +4295,7 @@
     <t xml:space="preserve">15.122709274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3708028793335</t>
+    <t xml:space="preserve">14.3708038330078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1734285354614</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">11.2691917419434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2785892486572</t>
+    <t xml:space="preserve">11.2785902023315</t>
   </si>
   <si>
     <t xml:space="preserve">11.3067865371704</t>
@@ -4337,16 +4337,16 @@
     <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1846017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094102859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966259002686</t>
+    <t xml:space="preserve">11.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966249465942</t>
   </si>
   <si>
     <t xml:space="preserve">11.0812149047852</t>
@@ -4373,7 +4373,7 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146606445312</t>
+    <t xml:space="preserve">10.7146596908569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">10.4138975143433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3387079238892</t>
+    <t xml:space="preserve">10.3387069702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180065155029</t>
@@ -70941,7 +70941,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6495486111</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>52579</v>
@@ -70962,6 +70962,32 @@
         <v>1919</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6493865741</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>58889</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>11.6099996566772</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>11.4499998092651</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>11.5900001525879</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1932" uniqueCount="1932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="1933">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">2.13486289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768867492676</t>
+    <t xml:space="preserve">2.09768843650818</t>
   </si>
   <si>
     <t xml:space="preserve">2.07379102706909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02334046363831</t>
+    <t xml:space="preserve">2.02333998680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.0631697177887</t>
@@ -68,91 +68,91 @@
     <t xml:space="preserve">1.964923620224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98988330364227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439242362976</t>
+    <t xml:space="preserve">1.98988378047943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439254283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.01802945137024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696753501892</t>
+    <t xml:space="preserve">2.01696729660034</t>
   </si>
   <si>
     <t xml:space="preserve">2.00209784507751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00156664848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.059983253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00528430938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97819983959198</t>
+    <t xml:space="preserve">2.0015664100647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05998373031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00528383255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909184455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97819995880127</t>
   </si>
   <si>
     <t xml:space="preserve">1.89854097366333</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9277491569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943309783936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447293758392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93305969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712784767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589554309845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436811208725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450244903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203712463379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10830998420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1396427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442205429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14548397064209</t>
+    <t xml:space="preserve">1.92774939537048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943250179291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447269916534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306016921997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712820529938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633662700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368100166321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113599777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441233634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450221061707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203736305237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10830974578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13964247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299944877625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14548420906067</t>
   </si>
   <si>
     <t xml:space="preserve">2.15345001220703</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">2.14813947677612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15132570266724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16831994056702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18265795707703</t>
+    <t xml:space="preserve">2.15132546424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16831970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18265819549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.22248792648315</t>
@@ -176,46 +176,46 @@
     <t xml:space="preserve">2.15610527992249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14495277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0721971988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12158608436584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14017367362976</t>
+    <t xml:space="preserve">2.14495301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565495491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706760406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219767570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.121586561203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017391204834</t>
   </si>
   <si>
     <t xml:space="preserve">2.12424182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582522392273</t>
+    <t xml:space="preserve">2.11362051963806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582570075989</t>
   </si>
   <si>
     <t xml:space="preserve">2.05307960510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901168823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11840033531189</t>
+    <t xml:space="preserve">2.06848001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901144981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
     <t xml:space="preserve">2.12477278709412</t>
@@ -227,31 +227,31 @@
     <t xml:space="preserve">2.15557408332825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1773476600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373030662537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169634819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29418087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2575376033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461247444153</t>
+    <t xml:space="preserve">2.17734742164612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373054504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169658660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29418110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25753736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461175918579</t>
   </si>
   <si>
     <t xml:space="preserve">2.21452188491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638557434082</t>
+    <t xml:space="preserve">2.22514343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638533592224</t>
   </si>
   <si>
     <t xml:space="preserve">2.23098492622375</t>
@@ -260,46 +260,46 @@
     <t xml:space="preserve">2.32073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888029098511</t>
+    <t xml:space="preserve">2.34888005256653</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604479789734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44925022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288796424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775741577148</t>
+    <t xml:space="preserve">2.44925093650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288820266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775717735291</t>
   </si>
   <si>
     <t xml:space="preserve">2.5655529499054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547303199768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6671826839447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70147585868835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72161531448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346632957458</t>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61547255516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555070877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66718339920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7014753818512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786716461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72161555290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346609115601</t>
   </si>
   <si>
     <t xml:space="preserve">2.81523895263672</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94587683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84136652946472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91757202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797639846802</t>
+    <t xml:space="preserve">2.94587659835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9175717830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9066858291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797616004944</t>
   </si>
   <si>
     <t xml:space="preserve">2.81959366798401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76516151428223</t>
+    <t xml:space="preserve">2.76516127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.73685669898987</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">2.6954882144928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693461418152</t>
+    <t xml:space="preserve">2.78693413734436</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531662940979</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">2.77604794502258</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313962936401</t>
+    <t xml:space="preserve">2.86313939094543</t>
   </si>
   <si>
     <t xml:space="preserve">2.91974925994873</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97200417518616</t>
+    <t xml:space="preserve">2.97200441360474</t>
   </si>
   <si>
     <t xml:space="preserve">2.99159979820251</t>
@@ -374,40 +374,40 @@
     <t xml:space="preserve">2.99813151359558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97853589057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820966720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0699827671051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15707397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29859781265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730724334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214377403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29206657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416542053223</t>
+    <t xml:space="preserve">2.9785361289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03514552116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998252868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15707421302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29859828948975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730676651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158404350281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416565895081</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988885879517</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2572295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2659387588501</t>
+    <t xml:space="preserve">3.25722980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593852043152</t>
   </si>
   <si>
     <t xml:space="preserve">3.17449235916138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25505232810974</t>
+    <t xml:space="preserve">3.25505208969116</t>
   </si>
   <si>
     <t xml:space="preserve">3.25940680503845</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35085296630859</t>
+    <t xml:space="preserve">3.35085320472717</t>
   </si>
   <si>
     <t xml:space="preserve">3.34432101249695</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">3.32472562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28553414344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037091255188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682542800903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31383943557739</t>
+    <t xml:space="preserve">3.28553438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2768247127533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31383895874023</t>
   </si>
   <si>
     <t xml:space="preserve">3.30948448181152</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">3.18973350524902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20932912826538</t>
+    <t xml:space="preserve">3.20932936668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069785118103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2006196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239255905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175539016724</t>
+    <t xml:space="preserve">3.20061993598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175515174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343482017517</t>
@@ -500,46 +500,46 @@
     <t xml:space="preserve">3.43141317367554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59253263473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962455749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823984146118</t>
+    <t xml:space="preserve">3.59253239631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824031829834</t>
   </si>
   <si>
     <t xml:space="preserve">4.01057291030884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09330940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533200263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831727981567</t>
+    <t xml:space="preserve">4.09330987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533176422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831799507141</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346523284912</t>
+    <t xml:space="preserve">4.19346570968628</t>
   </si>
   <si>
     <t xml:space="preserve">4.33716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313781738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47433519363403</t>
+    <t xml:space="preserve">4.23483419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.68988800048828</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">4.65722846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95334053039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245481491089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72037029266357</t>
+    <t xml:space="preserve">4.64634227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95334005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
     <t xml:space="preserve">4.74214315414429</t>
@@ -569,34 +569,34 @@
     <t xml:space="preserve">4.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64416456222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57231378555298</t>
+    <t xml:space="preserve">4.64416551589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.37418031692505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35022974014282</t>
+    <t xml:space="preserve">4.35023021697998</t>
   </si>
   <si>
     <t xml:space="preserve">4.34152126312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22830200195312</t>
+    <t xml:space="preserve">4.22830247879028</t>
   </si>
   <si>
     <t xml:space="preserve">4.19128799438477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08895540237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22612476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572038650513</t>
+    <t xml:space="preserve">4.08895587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22612428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24572086334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547136306763</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">4.35458517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33934354782104</t>
+    <t xml:space="preserve">4.3393440246582</t>
   </si>
   <si>
     <t xml:space="preserve">4.65940570831299</t>
@@ -614,40 +614,40 @@
     <t xml:space="preserve">4.63763332366943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63545560836792</t>
+    <t xml:space="preserve">4.63545608520508</t>
   </si>
   <si>
     <t xml:space="preserve">4.61586046218872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64851903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72254753112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59408760070801</t>
+    <t xml:space="preserve">4.64851999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72254657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59408664703369</t>
   </si>
   <si>
     <t xml:space="preserve">4.6637601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5897331237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51135063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5244140625</t>
+    <t xml:space="preserve">4.58973217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52441310882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.73343324661255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6419882774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78568840026855</t>
+    <t xml:space="preserve">4.64198732376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78568887710571</t>
   </si>
   <si>
     <t xml:space="preserve">4.77480268478394</t>
@@ -656,61 +656,61 @@
     <t xml:space="preserve">4.74649715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7660927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921884536743</t>
+    <t xml:space="preserve">4.76609373092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921932220459</t>
   </si>
   <si>
     <t xml:space="preserve">5.38662147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082059860229</t>
+    <t xml:space="preserve">5.29082155227661</t>
   </si>
   <si>
     <t xml:space="preserve">5.25162982940674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22985601425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2276782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372819900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11010503768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.225501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27557992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31041622161865</t>
+    <t xml:space="preserve">5.22985744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11010456085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22550249099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27557945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31041574478149</t>
   </si>
   <si>
     <t xml:space="preserve">5.17106914520264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14494228363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220531463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979385375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09050893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043245315552</t>
+    <t xml:space="preserve">5.14494180679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979480743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09050989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043197631836</t>
   </si>
   <si>
     <t xml:space="preserve">5.11445999145508</t>
@@ -719,31 +719,31 @@
     <t xml:space="preserve">5.10139656066895</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09268712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752294540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478693008423</t>
+    <t xml:space="preserve">5.09268760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752342224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478645324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.95769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02736854553223</t>
+    <t xml:space="preserve">5.02736806869507</t>
   </si>
   <si>
     <t xml:space="preserve">4.98817682266235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88584470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8662486076355</t>
+    <t xml:space="preserve">4.88584423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86624813079834</t>
   </si>
   <si>
     <t xml:space="preserve">4.85536193847656</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">4.84665298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80093002319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73561143875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74432134628296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738382339478</t>
+    <t xml:space="preserve">4.8009295463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7356104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004335403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74431991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738334655762</t>
   </si>
   <si>
     <t xml:space="preserve">4.6811785697937</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">4.82052564620972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9185037612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841009140015</t>
+    <t xml:space="preserve">4.91850328445435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1384105682373</t>
   </si>
   <si>
     <t xml:space="preserve">5.08397769927979</t>
@@ -785,25 +785,25 @@
     <t xml:space="preserve">5.19719696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11881446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0948634147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170726776123</t>
+    <t xml:space="preserve">5.11881399154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170679092407</t>
   </si>
   <si>
     <t xml:space="preserve">5.38444423675537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41710329055786</t>
+    <t xml:space="preserve">5.41710376739502</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68273305892944</t>
+    <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
     <t xml:space="preserve">5.63918733596802</t>
@@ -815,64 +815,64 @@
     <t xml:space="preserve">5.91134881973267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94400835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383771896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81337070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87869024276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75893878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957548141479</t>
+    <t xml:space="preserve">5.94400882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8133716583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87868928909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75893831253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76329231262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957595825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97666788101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09641933441162</t>
+    <t xml:space="preserve">5.97666835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0964183807373</t>
   </si>
   <si>
     <t xml:space="preserve">5.94836282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98973226547241</t>
+    <t xml:space="preserve">5.98973178863525</t>
   </si>
   <si>
     <t xml:space="preserve">6.00497245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9875545501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198694229126</t>
+    <t xml:space="preserve">5.98755407333374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419864654541</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08335494995117</t>
+    <t xml:space="preserve">6.08335447311401</t>
   </si>
   <si>
     <t xml:space="preserve">5.96360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07464599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13996553421021</t>
+    <t xml:space="preserve">6.07464551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13996505737305</t>
   </si>
   <si>
     <t xml:space="preserve">6.42301321029663</t>
@@ -893,43 +893,43 @@
     <t xml:space="preserve">6.80403852462769</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90201807022095</t>
+    <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.01088190078735</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06531429290771</t>
+    <t xml:space="preserve">7.06531476974487</t>
   </si>
   <si>
     <t xml:space="preserve">7.11756944656372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063144683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321401596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666749954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28521966934204</t>
+    <t xml:space="preserve">7.32005643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063287734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425603866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207975387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29393005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666606903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28522109985352</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481624603271</t>
@@ -938,34 +938,34 @@
     <t xml:space="preserve">7.19595193862915</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705698013306</t>
+    <t xml:space="preserve">6.46655893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22705602645874</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309017181396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4012393951416</t>
+    <t xml:space="preserve">6.40123987197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316761016846</t>
+    <t xml:space="preserve">6.49704074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316808700562</t>
   </si>
   <si>
     <t xml:space="preserve">6.57760047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52464437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215476989746</t>
+    <t xml:space="preserve">6.52464389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5621542930603</t>
   </si>
   <si>
     <t xml:space="preserve">6.61290502548218</t>
@@ -980,64 +980,64 @@
     <t xml:space="preserve">6.55774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91740322113037</t>
+    <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.76294660568237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82252264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652488708496</t>
+    <t xml:space="preserve">6.82252216339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652631759644</t>
   </si>
   <si>
     <t xml:space="preserve">6.58421993255615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50478506088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093849182129</t>
+    <t xml:space="preserve">6.50478553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093944549561</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694932937622</t>
+    <t xml:space="preserve">6.35695028305054</t>
   </si>
   <si>
     <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43417739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826471328735</t>
+    <t xml:space="preserve">6.43417692184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3282642364502</t>
   </si>
   <si>
     <t xml:space="preserve">6.33267831802368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1429181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91344118118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240955352783</t>
+    <t xml:space="preserve">6.37460088729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057109832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14291858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850545883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95757150650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91344165802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240859985352</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771266937256</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">5.83621406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8472466468811</t>
+    <t xml:space="preserve">5.84724617004395</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846292495728</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">5.69720363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50744342803955</t>
+    <t xml:space="preserve">5.50744390487671</t>
   </si>
   <si>
     <t xml:space="preserve">5.46993350982666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60894298553467</t>
+    <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
     <t xml:space="preserve">5.7369213104248</t>
@@ -1094,43 +1094,43 @@
     <t xml:space="preserve">5.72147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608694076538</t>
+    <t xml:space="preserve">5.59129190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.54495477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44345569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007514953613</t>
+    <t xml:space="preserve">5.4434552192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007467269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932489395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41918325424194</t>
+    <t xml:space="preserve">5.4191837310791</t>
   </si>
   <si>
     <t xml:space="preserve">5.49199819564819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56039953231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096656799316</t>
+    <t xml:space="preserve">5.56040000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.52730226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45890140533447</t>
+    <t xml:space="preserve">5.45890045166016</t>
   </si>
   <si>
     <t xml:space="preserve">5.41256475448608</t>
@@ -1139,85 +1139,85 @@
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922674179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912763595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66410684585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80311584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86931180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532312393188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56481266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47876024246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49420499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36181449890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29782629013062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22942447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045705795288</t>
+    <t xml:space="preserve">5.56922626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912715911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66410636901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8031153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86931085586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56481313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52068328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.478759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4942045211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36181497573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29782581329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22942399978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045610427856</t>
   </si>
   <si>
     <t xml:space="preserve">5.25369501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41477108001709</t>
+    <t xml:space="preserve">5.41477060317993</t>
   </si>
   <si>
     <t xml:space="preserve">5.39711856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796745300293</t>
+    <t xml:space="preserve">5.27796792984009</t>
   </si>
   <si>
     <t xml:space="preserve">5.2228045463562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14116287231445</t>
+    <t xml:space="preserve">5.14116382598877</t>
   </si>
   <si>
     <t xml:space="preserve">5.11909818649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20735883712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16764116287231</t>
+    <t xml:space="preserve">5.20735931396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233804702759</t>
@@ -1226,52 +1226,52 @@
     <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03745794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00656700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96464252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126340866089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04849052429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19412040710449</t>
+    <t xml:space="preserve">5.0374584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00656652450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126245498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04849004745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19411993026733</t>
   </si>
   <si>
     <t xml:space="preserve">5.27576065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22501087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
+    <t xml:space="preserve">5.22501182556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486923217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689138412476</t>
   </si>
   <si>
     <t xml:space="preserve">5.03083848953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87196922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72633934020996</t>
+    <t xml:space="preserve">4.87196969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72633981704712</t>
   </si>
   <si>
     <t xml:space="preserve">4.71089458465576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65131950378418</t>
+    <t xml:space="preserve">4.65131807327271</t>
   </si>
   <si>
     <t xml:space="preserve">4.93154525756836</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">5.90461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86489868164062</t>
+    <t xml:space="preserve">5.86489820480347</t>
   </si>
   <si>
     <t xml:space="preserve">5.77663850784302</t>
@@ -1304,22 +1304,22 @@
     <t xml:space="preserve">5.81856203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65307331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6398344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366884231567</t>
+    <t xml:space="preserve">5.65307378768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63983392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6994104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366788864136</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348371505737</t>
@@ -1328,10 +1328,10 @@
     <t xml:space="preserve">6.14071178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12526702880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597236633301</t>
+    <t xml:space="preserve">6.12526655197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597332000732</t>
   </si>
   <si>
     <t xml:space="preserve">5.96419191360474</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">5.90020275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354028701782</t>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354076385498</t>
   </si>
   <si>
     <t xml:space="preserve">5.65086698532104</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">5.61776924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63542222976685</t>
+    <t xml:space="preserve">5.63542175292969</t>
   </si>
   <si>
     <t xml:space="preserve">6.01935386657715</t>
@@ -1373,13 +1373,13 @@
     <t xml:space="preserve">5.71926879882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84283351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03259325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583168029785</t>
+    <t xml:space="preserve">5.84283304214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583215713501</t>
   </si>
   <si>
     <t xml:space="preserve">5.95315837860107</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">6.52243757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939687728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878826141357</t>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">6.08996200561523</t>
@@ -1415,31 +1415,31 @@
     <t xml:space="preserve">5.55598735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11202764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429006576538</t>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92226791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429054260254</t>
   </si>
   <si>
     <t xml:space="preserve">5.67072582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68396520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372541427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963666915894</t>
+    <t xml:space="preserve">5.68396472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963714599609</t>
   </si>
   <si>
     <t xml:space="preserve">5.96198511123657</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">6.17822217941284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474300384521</t>
+    <t xml:space="preserve">6.27089643478394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474348068237</t>
   </si>
   <si>
     <t xml:space="preserve">6.72543668746948</t>
@@ -1463,46 +1463,46 @@
     <t xml:space="preserve">6.92843532562256</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90637016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697877883911</t>
+    <t xml:space="preserve">6.90636968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697830200195</t>
   </si>
   <si>
     <t xml:space="preserve">7.10054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87106609344482</t>
+    <t xml:space="preserve">6.87106657028198</t>
   </si>
   <si>
     <t xml:space="preserve">6.95050001144409</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22852039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082534790039</t>
+    <t xml:space="preserve">7.22851991653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908647537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082582473755</t>
   </si>
   <si>
     <t xml:space="preserve">7.4933009147644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32560777664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18439054489136</t>
+    <t xml:space="preserve">7.32560586929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18439149856567</t>
   </si>
   <si>
     <t xml:space="preserve">7.44034576416016</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">7.06523895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25058507919312</t>
+    <t xml:space="preserve">7.25058603286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.21528100967407</t>
@@ -1529,58 +1529,58 @@
     <t xml:space="preserve">7.19321584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21969366073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56391000747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508470535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710590362549</t>
+    <t xml:space="preserve">7.2196946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46241044998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127828598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5374321937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710638046265</t>
   </si>
   <si>
     <t xml:space="preserve">7.38738870620728</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06965160369873</t>
+    <t xml:space="preserve">7.06965112686157</t>
   </si>
   <si>
     <t xml:space="preserve">6.62835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84017467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717651367188</t>
+    <t xml:space="preserve">6.84017419815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717603683472</t>
   </si>
   <si>
     <t xml:space="preserve">6.51802539825439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6195240020752</t>
+    <t xml:space="preserve">6.61952447891235</t>
   </si>
   <si>
     <t xml:space="preserve">6.5445032119751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71219778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247394561768</t>
+    <t xml:space="preserve">6.71219682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
   </si>
   <si>
     <t xml:space="preserve">6.30643844604492</t>
@@ -1598,52 +1598,52 @@
     <t xml:space="preserve">6.63294172286987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54796171188354</t>
+    <t xml:space="preserve">6.5479621887207</t>
   </si>
   <si>
     <t xml:space="preserve">6.65977811813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505126953125</t>
+    <t xml:space="preserve">6.579270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534440994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817632675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505174636841</t>
   </si>
   <si>
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985712051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
+    <t xml:space="preserve">6.48087167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31985664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22145795822144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12305974960327</t>
+    <t xml:space="preserve">6.12305927276611</t>
   </si>
   <si>
     <t xml:space="preserve">6.26171159744263</t>
@@ -1655,37 +1655,37 @@
     <t xml:space="preserve">6.18120384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20356702804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
+    <t xml:space="preserve">6.20356798171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669160842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829435348511</t>
   </si>
   <si>
     <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33774709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821487426758</t>
+    <t xml:space="preserve">6.33774662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821582794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.48981714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53007078170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061756134033</t>
+    <t xml:space="preserve">6.53007173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141893386841</t>
+    <t xml:space="preserve">6.39141845703125</t>
   </si>
   <si>
     <t xml:space="preserve">6.4003643989563</t>
@@ -1697,40 +1697,40 @@
     <t xml:space="preserve">6.42719984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43167304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298122406006</t>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298170089722</t>
   </si>
   <si>
     <t xml:space="preserve">6.64188718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1006965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3958911895752</t>
+    <t xml:space="preserve">6.10069608688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39589166641235</t>
   </si>
   <si>
     <t xml:space="preserve">6.18567705154419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98440742492676</t>
+    <t xml:space="preserve">5.98440837860107</t>
   </si>
   <si>
     <t xml:space="preserve">5.474524974823</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">5.33587312698364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358798980713</t>
+    <t xml:space="preserve">5.24194765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358846664429</t>
   </si>
   <si>
     <t xml:space="preserve">5.13013124465942</t>
@@ -1754,16 +1754,16 @@
     <t xml:space="preserve">5.01831483840942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0764594078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886257171631</t>
+    <t xml:space="preserve">5.07645988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
@@ -1775,100 +1775,100 @@
     <t xml:space="preserve">4.61577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417474746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201690673828</t>
+    <t xml:space="preserve">4.74995613098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201642990112</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876407623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483860015869</t>
+    <t xml:space="preserve">4.20876455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483907699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.04104089736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05445861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829629898071</t>
+    <t xml:space="preserve">4.0544581413269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829606056213</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353042602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15509271621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1304931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01867771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884331703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559144020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702714920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740736961365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466396331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8375346660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648036956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500492095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15732955932617</t>
+    <t xml:space="preserve">4.15509366989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13049364089966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0186767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884307861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740808486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648013114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500515937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15732908248901</t>
   </si>
   <si>
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475128173828</t>
+    <t xml:space="preserve">3.9247510433197</t>
   </si>
   <si>
     <t xml:space="preserve">3.93146014213562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94264221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331604957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8621346950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512294769287</t>
+    <t xml:space="preserve">3.94264149665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331581115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424424171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512318611145</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896134376526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24267196655273</t>
+    <t xml:space="preserve">3.24267220497131</t>
   </si>
   <si>
     <t xml:space="preserve">3.03245782852173</t>
@@ -1895,16 +1895,16 @@
     <t xml:space="preserve">3.45288681983948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39474272727966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4886679649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51550388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870770454407</t>
+    <t xml:space="preserve">3.39474248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48866820335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5155041217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870722770691</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714493751526</t>
@@ -1913,64 +1913,64 @@
     <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735028266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01009440422058</t>
+    <t xml:space="preserve">2.92735052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182253837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01009464263916</t>
   </si>
   <si>
     <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03916645050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95642256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88485980033875</t>
+    <t xml:space="preserve">3.03916621208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95642280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88486003875732</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751660346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844431877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83342456817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933300971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0727117061615</t>
+    <t xml:space="preserve">2.77751636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74844408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78869795799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83342480659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271146774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16887354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22925424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15992856025696</t>
+    <t xml:space="preserve">3.16887331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22925448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254538536072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23596334457397</t>
+    <t xml:space="preserve">3.2359631061554</t>
   </si>
   <si>
     <t xml:space="preserve">3.18676400184631</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54234004020691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972273826599</t>
+    <t xml:space="preserve">3.54233980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972249984741</t>
   </si>
   <si>
     <t xml:space="preserve">3.53339457511902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49537706375122</t>
+    <t xml:space="preserve">3.49537682533264</t>
   </si>
   <si>
     <t xml:space="preserve">3.61166572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66533803939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5758843421936</t>
+    <t xml:space="preserve">3.66533780097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588505744934</t>
   </si>
   <si>
     <t xml:space="preserve">3.51103115081787</t>
@@ -2012,34 +2012,34 @@
     <t xml:space="preserve">3.5825936794281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444934844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58483028411865</t>
+    <t xml:space="preserve">3.43723249435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444958686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58483004570007</t>
   </si>
   <si>
     <t xml:space="preserve">3.6944100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62284755706787</t>
+    <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399012565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567947387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77268123626709</t>
+    <t xml:space="preserve">3.70335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398988723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567971229553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77268147468567</t>
   </si>
   <si>
     <t xml:space="preserve">3.83306217193604</t>
@@ -2048,43 +2048,43 @@
     <t xml:space="preserve">3.85766172409058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94040584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99184155464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13272953033447</t>
+    <t xml:space="preserve">3.94040608406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99184203147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13273000717163</t>
   </si>
   <si>
     <t xml:space="preserve">4.09247589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25125503540039</t>
+    <t xml:space="preserve">4.25125551223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94935131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
+    <t xml:space="preserve">3.94935059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842335700989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28256320953369</t>
+    <t xml:space="preserve">3.97842383384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28256368637085</t>
   </si>
   <si>
     <t xml:space="preserve">4.38319826126099</t>
@@ -2096,43 +2096,43 @@
     <t xml:space="preserve">4.3541259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16627502441406</t>
+    <t xml:space="preserve">4.1662745475769</t>
   </si>
   <si>
     <t xml:space="preserve">4.20429229736328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2780909538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23783779144287</t>
+    <t xml:space="preserve">4.27809047698975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205640792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
     <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24901819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24007320404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25349187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19982004165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07458543777466</t>
+    <t xml:space="preserve">4.24901866912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24007368087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25349140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982051849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0745849609375</t>
   </si>
   <si>
     <t xml:space="preserve">4.15285682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1864013671875</t>
+    <t xml:space="preserve">4.18640089035034</t>
   </si>
   <si>
     <t xml:space="preserve">4.26914548873901</t>
@@ -2141,16 +2141,16 @@
     <t xml:space="preserve">3.97171473503113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93369674682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015244483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880453109741</t>
+    <t xml:space="preserve">3.93369698524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90015268325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631476402283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880310058594</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804265975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7682089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77491784095764</t>
+    <t xml:space="preserve">3.9180428981781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820874214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77491760253906</t>
   </si>
   <si>
     <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85095286369324</t>
+    <t xml:space="preserve">3.85095262527466</t>
   </si>
   <si>
     <t xml:space="preserve">4.0991849899292</t>
@@ -2183,22 +2183,22 @@
     <t xml:space="preserve">3.82411694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95693111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88136458396912</t>
+    <t xml:space="preserve">3.95693039894104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
     <t xml:space="preserve">3.76229000091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7645800113678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68901348114014</t>
+    <t xml:space="preserve">3.74626088142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76458024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68901371955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
@@ -2207,16 +2207,16 @@
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243679046631</t>
+    <t xml:space="preserve">3.84243655204773</t>
   </si>
   <si>
     <t xml:space="preserve">3.87220454216003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92487215995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9660906791687</t>
+    <t xml:space="preserve">3.92487168312073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96608996391296</t>
   </si>
   <si>
     <t xml:space="preserve">3.89739322662354</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">3.95006108283997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87449502944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
+    <t xml:space="preserve">3.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9065535068512</t>
   </si>
   <si>
     <t xml:space="preserve">3.98440933227539</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">4.04165601730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19736909866333</t>
+    <t xml:space="preserve">4.19736957550049</t>
   </si>
   <si>
     <t xml:space="preserve">4.1538610458374</t>
@@ -2246,70 +2246,70 @@
     <t xml:space="preserve">4.09203433990479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11264324188232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10119342803955</t>
+    <t xml:space="preserve">4.11264276504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10119390487671</t>
   </si>
   <si>
     <t xml:space="preserve">4.14470195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751493453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28438520431519</t>
+    <t xml:space="preserve">4.18820953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28438472747803</t>
   </si>
   <si>
     <t xml:space="preserve">4.31415367126465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803956985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30270433425903</t>
+    <t xml:space="preserve">4.40803909301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30270481109619</t>
   </si>
   <si>
     <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24545669555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3324728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23858690261841</t>
+    <t xml:space="preserve">4.2454571723938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33247232437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">4.22255802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
+    <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997610092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15157079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16302061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11035346984863</t>
+    <t xml:space="preserve">4.17447090148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997562408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16302108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11035394668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.12409257888794</t>
@@ -2321,28 +2321,28 @@
     <t xml:space="preserve">4.00730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05539560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067046165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94548082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701609611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8859441280365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235133171082</t>
+    <t xml:space="preserve">4.05539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97067022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.945481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594365119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678456306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8515956401825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235061645508</t>
   </si>
   <si>
     <t xml:space="preserve">4.00043869018555</t>
@@ -2351,13 +2351,13 @@
     <t xml:space="preserve">3.98211979866028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13096237182617</t>
+    <t xml:space="preserve">4.13096189498901</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16760015487671</t>
+    <t xml:space="preserve">4.16760110855103</t>
   </si>
   <si>
     <t xml:space="preserve">4.04394626617432</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">4.18592023849487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1355414390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06226587295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34392213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33705282211304</t>
+    <t xml:space="preserve">4.13554191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06226634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34392166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3370532989502</t>
   </si>
   <si>
     <t xml:space="preserve">4.31873369216919</t>
@@ -2390,16 +2390,16 @@
     <t xml:space="preserve">5.00112056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17515230178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33086490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35834360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62855100631714</t>
+    <t xml:space="preserve">5.17515277862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33086538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35834312438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62855052947998</t>
   </si>
   <si>
     <t xml:space="preserve">5.48657703399658</t>
@@ -2414,16 +2414,16 @@
     <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527400970459</t>
+    <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4819974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26674795150757</t>
+    <t xml:space="preserve">5.48199796676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26674842834473</t>
   </si>
   <si>
     <t xml:space="preserve">5.27590751647949</t>
@@ -2432,112 +2432,112 @@
     <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993925094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3446044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47283792495728</t>
+    <t xml:space="preserve">5.44993877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34460496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47283744812012</t>
   </si>
   <si>
     <t xml:space="preserve">5.45909881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55985403060913</t>
+    <t xml:space="preserve">5.55985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.69724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7293062210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.72930574417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92623662948608</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304580688477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7796835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71556615829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80716276168823</t>
+    <t xml:space="preserve">5.77968311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72472620010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67892837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71556663513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.71098709106445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82090139389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875841140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04989051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12316703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22392177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652925491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99493360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02241182327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24224138259888</t>
+    <t xml:space="preserve">5.82090187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875745773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12316751480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22392225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99493312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02241134643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24224090576172</t>
   </si>
   <si>
     <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994161605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28643178939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6253342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28185176849365</t>
+    <t xml:space="preserve">7.10324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941568374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28643131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61159610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235084533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600616455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113304138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62533473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
     <t xml:space="preserve">7.41924524307251</t>
@@ -2555,16 +2555,16 @@
     <t xml:space="preserve">7.11697959899902</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26811170578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39634609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37802696228027</t>
+    <t xml:space="preserve">7.15361785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26811218261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37802743911743</t>
   </si>
   <si>
     <t xml:space="preserve">7.57495784759521</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">7.56579828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66655302047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130395889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12155914306641</t>
+    <t xml:space="preserve">7.66655349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12155866622925</t>
   </si>
   <si>
     <t xml:space="preserve">7.41466569900513</t>
@@ -2603,19 +2603,19 @@
     <t xml:space="preserve">7.30475044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22231435775757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5291600227356</t>
+    <t xml:space="preserve">7.22231483459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52916049957275</t>
   </si>
   <si>
     <t xml:space="preserve">7.4375638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48794221878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52000093460083</t>
+    <t xml:space="preserve">7.48794174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52000045776367</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51244878768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7414379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79639482498169</t>
+    <t xml:space="preserve">6.51244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74143743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79639434814453</t>
   </si>
   <si>
     <t xml:space="preserve">6.71853828430176</t>
@@ -2645,43 +2645,43 @@
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61778354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89715003967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097436904907</t>
+    <t xml:space="preserve">6.6177830696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89256954193115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89715051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.828453540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097484588623</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83303308486938</t>
+    <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
     <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6361026763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11858749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96745443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78884315490723</t>
+    <t xml:space="preserve">6.63610219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11858654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.967453956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78884267807007</t>
   </si>
   <si>
     <t xml:space="preserve">5.63771057128906</t>
@@ -2693,10 +2693,10 @@
     <t xml:space="preserve">5.72014617919922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11561489105225</t>
+    <t xml:space="preserve">5.47741842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
     <t xml:space="preserve">4.75381231307983</t>
@@ -2708,43 +2708,43 @@
     <t xml:space="preserve">4.63931846618652</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21110820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81495761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382455825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32034134864807</t>
+    <t xml:space="preserve">4.21110773086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8149573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382503509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32034111022949</t>
   </si>
   <si>
     <t xml:space="preserve">3.22416567802429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18294787406921</t>
+    <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
     <t xml:space="preserve">3.22645568847656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44399523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304569244385</t>
+    <t xml:space="preserve">3.44399499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304521560669</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344718933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50353264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069458961487</t>
+    <t xml:space="preserve">3.50353240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069435119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.61802697181702</t>
@@ -2756,34 +2756,34 @@
     <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79663848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168062210083</t>
+    <t xml:space="preserve">3.79663825035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168109893799</t>
   </si>
   <si>
     <t xml:space="preserve">4.06684589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03020763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38284969329834</t>
+    <t xml:space="preserve">4.03020715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3828501701355</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722278594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.011887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17218065261841</t>
+    <t xml:space="preserve">4.01188850402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
     <t xml:space="preserve">4.09432411193848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4881854057312</t>
+    <t xml:space="preserve">4.48818588256836</t>
   </si>
   <si>
     <t xml:space="preserve">4.45612668991089</t>
@@ -2798,28 +2798,28 @@
     <t xml:space="preserve">4.26377630233765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32331228256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35537195205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676067352295</t>
+    <t xml:space="preserve">4.32331275939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35537147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499410629272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17675971984863</t>
   </si>
   <si>
     <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5248236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
+    <t xml:space="preserve">4.52482318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4836049079895</t>
   </si>
   <si>
     <t xml:space="preserve">4.38743019104004</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">4.42406845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7515230178833</t>
+    <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761299133301</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">4.90036535263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88891649246216</t>
+    <t xml:space="preserve">4.888916015625</t>
   </si>
   <si>
     <t xml:space="preserve">5.04920816421509</t>
@@ -2846,43 +2846,43 @@
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239946365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48428773880005</t>
+    <t xml:space="preserve">5.23239994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48428821563721</t>
   </si>
   <si>
     <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1637020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471384048462</t>
+    <t xml:space="preserve">5.16370296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93471431732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.02630996704102</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19805192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254625320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39269256591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20950078964233</t>
+    <t xml:space="preserve">5.19805145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254577636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25529909133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39269161224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20950126647949</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14080476760864</t>
+    <t xml:space="preserve">5.14080429077148</t>
   </si>
   <si>
     <t xml:space="preserve">5.27819728851318</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500646591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92326402664185</t>
+    <t xml:space="preserve">5.09500598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
     <t xml:space="preserve">5.01486015319824</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06065797805786</t>
+    <t xml:space="preserve">5.0606575012207</t>
   </si>
   <si>
     <t xml:space="preserve">5.22095012664795</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">5.07210683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10645580291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935447692871</t>
+    <t xml:space="preserve">5.10645484924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935495376587</t>
   </si>
   <si>
     <t xml:space="preserve">5.3239951133728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544397354126</t>
+    <t xml:space="preserve">5.33544445037842</t>
   </si>
   <si>
     <t xml:space="preserve">5.03775882720947</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">4.96906232833862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616317749023</t>
+    <t xml:space="preserve">4.94616365432739</t>
   </si>
   <si>
     <t xml:space="preserve">4.98051166534424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84311866760254</t>
+    <t xml:space="preserve">4.84311819076538</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181468963623</t>
@@ -2948,43 +2948,43 @@
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341081619263</t>
+    <t xml:space="preserve">5.00341033935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.57978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1904993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21339797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08058500289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3004150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34163188934326</t>
+    <t xml:space="preserve">4.19049978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21339845657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08058452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30041456222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34163236618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54153490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62168121337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907516479492</t>
+    <t xml:space="preserve">5.54153537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62168073654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907468795776</t>
   </si>
   <si>
     <t xml:space="preserve">5.73617553710938</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6903772354126</t>
+    <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
     <t xml:space="preserve">5.64457988739014</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">5.66747903823853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89646768569946</t>
+    <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
     <t xml:space="preserve">5.70182704925537</t>
@@ -3002,82 +3002,82 @@
     <t xml:space="preserve">5.81632137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14835548400879</t>
+    <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516466140747</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95371532440186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87356901168823</t>
+    <t xml:space="preserve">5.95371580123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87356948852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09110879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415330886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12545728683472</t>
+    <t xml:space="preserve">6.09110832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">6.1598048210144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07965898513794</t>
+    <t xml:space="preserve">6.18270349502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07965850830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.13690614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2170524597168</t>
+    <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
     <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32009792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36589574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4803900718689</t>
+    <t xml:space="preserve">6.32009744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36589527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48038911819458</t>
   </si>
   <si>
     <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53763723373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56053590774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60633373260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58343458175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62923336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41169261932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34299659729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46894073486328</t>
+    <t xml:space="preserve">6.53763675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56053638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60633420944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58343553543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62923288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34299612045288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46894025802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.29719877243042</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">6.20560312271118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4231424331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50328826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66358089447021</t>
+    <t xml:space="preserve">6.42314291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50328922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147385597229</t>
@@ -3104,40 +3104,40 @@
     <t xml:space="preserve">6.75517654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6864800453186</t>
+    <t xml:space="preserve">6.68648052215576</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77807569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792938232422</t>
+    <t xml:space="preserve">6.778076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792985916138</t>
   </si>
   <si>
     <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734508514404</t>
+    <t xml:space="preserve">6.37734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54908657073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86967134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417802810669</t>
+    <t xml:space="preserve">6.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5490870475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86967086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78562688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417850494385</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3149,28 +3149,28 @@
     <t xml:space="preserve">8.01461601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06041526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02606678009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911224365234</t>
+    <t xml:space="preserve">7.99171829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0260648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911033630371</t>
   </si>
   <si>
     <t xml:space="preserve">8.10621166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03751564025879</t>
+    <t xml:space="preserve">8.03751468658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.00316715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93447017669678</t>
+    <t xml:space="preserve">7.93447113037109</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331203460693</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">8.3123025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085372924805</t>
+    <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33520030975342</t>
+    <t xml:space="preserve">8.33520221710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.2779541015625</t>
@@ -3206,34 +3206,34 @@
     <t xml:space="preserve">8.23215675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16345882415771</t>
+    <t xml:space="preserve">8.16346073150635</t>
   </si>
   <si>
     <t xml:space="preserve">8.07186317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20925712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94592046737671</t>
+    <t xml:space="preserve">8.20925807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591951370239</t>
   </si>
   <si>
     <t xml:space="preserve">7.95736932754517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84287452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92302083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997680664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577367782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3809986114502</t>
+    <t xml:space="preserve">7.84287405014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.923020362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997632980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577224731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956211090088</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">9.48014736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65356349945068</t>
+    <t xml:space="preserve">9.653564453125</t>
   </si>
   <si>
     <t xml:space="preserve">9.60731887817383</t>
@@ -3257,28 +3257,28 @@
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136856079102</t>
+    <t xml:space="preserve">9.71136951446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2894277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3009881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241109848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5206508636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3587942123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437726974487</t>
+    <t xml:space="preserve">10.2894268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3009872436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241100311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5206499099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3587951660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437717437744</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975290298462</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7403116226196</t>
+    <t xml:space="preserve">10.7403125762939</t>
   </si>
   <si>
     <t xml:space="preserve">10.4744062423706</t>
@@ -3305,10 +3305,10 @@
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2663059234619</t>
+    <t xml:space="preserve">10.1044483184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2663049697876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3934783935547</t>
@@ -3317,13 +3317,13 @@
     <t xml:space="preserve">10.0582046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95415306091309</t>
+    <t xml:space="preserve">9.9541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0235204696655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1506948471069</t>
+    <t xml:space="preserve">10.1506938934326</t>
   </si>
   <si>
     <t xml:space="preserve">10.0697650909424</t>
@@ -3332,13 +3332,13 @@
     <t xml:space="preserve">10.092887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1160116195679</t>
+    <t xml:space="preserve">10.1160097122192</t>
   </si>
   <si>
     <t xml:space="preserve">10.2547435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2200613021851</t>
+    <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859666824341</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">10.0350828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4165992736816</t>
+    <t xml:space="preserve">10.416600227356</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738157272339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391334533691</t>
+    <t xml:space="preserve">10.1391315460205</t>
   </si>
   <si>
     <t xml:space="preserve">11.191198348999</t>
@@ -3365,25 +3365,25 @@
     <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9052152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.901515007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7461318969727</t>
+    <t xml:space="preserve">11.9052143096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9015140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426559448242</t>
+    <t xml:space="preserve">11.5426568984985</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796518325806</t>
+    <t xml:space="preserve">11.5796527862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
@@ -3395,16 +3395,16 @@
     <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6536445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3946733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4686641693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0975914001465</t>
+    <t xml:space="preserve">11.6536436080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3946743011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4686651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0975923538208</t>
   </si>
   <si>
     <t xml:space="preserve">11.8571195602417</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">12.0605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0420999526978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010692596436</t>
+    <t xml:space="preserve">12.0420989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455749511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010683059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299955368042</t>
+    <t xml:space="preserve">12.9299945831299</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144151687622</t>
@@ -3440,16 +3440,16 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034284591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.817892074585</t>
+    <t xml:space="preserve">13.5034294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8178911209106</t>
   </si>
   <si>
     <t xml:space="preserve">13.7254018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6317958831787</t>
+    <t xml:space="preserve">14.631796836853</t>
   </si>
   <si>
     <t xml:space="preserve">14.0398664474487</t>
@@ -3458,19 +3458,19 @@
     <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4109401702881</t>
+    <t xml:space="preserve">13.4109392166138</t>
   </si>
   <si>
     <t xml:space="preserve">13.7623987197876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4294376373291</t>
+    <t xml:space="preserve">13.4294366836548</t>
   </si>
   <si>
     <t xml:space="preserve">13.0409822463989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4860467910767</t>
+    <t xml:space="preserve">12.4860458374023</t>
   </si>
   <si>
     <t xml:space="preserve">12.9669914245605</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114971160889</t>
+    <t xml:space="preserve">12.9114961624146</t>
   </si>
   <si>
     <t xml:space="preserve">13.0779781341553</t>
@@ -3494,13 +3494,13 @@
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457025527954</t>
+    <t xml:space="preserve">15.445704460144</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011959075928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7786626815796</t>
+    <t xml:space="preserve">15.7786645889282</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
@@ -3512,13 +3512,13 @@
     <t xml:space="preserve">16.5370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.019136428833</t>
+    <t xml:space="preserve">16.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520946502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0191345214844</t>
   </si>
   <si>
     <t xml:space="preserve">15.7971611022949</t>
@@ -3527,25 +3527,25 @@
     <t xml:space="preserve">16.1486186981201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.000638961792</t>
+    <t xml:space="preserve">16.0006351470947</t>
   </si>
   <si>
     <t xml:space="preserve">15.908148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5196943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4641981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896503448486</t>
+    <t xml:space="preserve">15.5196952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4642000198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896522521973</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341569900513</t>
+    <t xml:space="preserve">15.8341579437256</t>
   </si>
   <si>
     <t xml:space="preserve">14.9092655181885</t>
@@ -3554,10 +3554,10 @@
     <t xml:space="preserve">14.4283208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5023126602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2433414459229</t>
+    <t xml:space="preserve">14.502311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
     <t xml:space="preserve">13.6329135894775</t>
@@ -3566,22 +3566,22 @@
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369464874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9288787841797</t>
+    <t xml:space="preserve">13.3369474411011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.928879737854</t>
   </si>
   <si>
     <t xml:space="preserve">14.0583639144897</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1693506240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8918838500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098224639893</t>
+    <t xml:space="preserve">14.1693496704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8918828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098234176636</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7808952331543</t>
+    <t xml:space="preserve">13.7808961868286</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629556655884</t>
@@ -3599,46 +3599,46 @@
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3554439544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9658737182617</t>
+    <t xml:space="preserve">13.3924398422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3554458618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9658756256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988367080688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2803373336792</t>
+    <t xml:space="preserve">14.2988357543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2803382873535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1138582229614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9484930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1334705352783</t>
+    <t xml:space="preserve">12.9484920501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1334714889526</t>
   </si>
   <si>
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479360580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3935575485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1889657974243</t>
+    <t xml:space="preserve">13.4479351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085790634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3935565948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.18896484375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4664325714111</t>
@@ -3659,31 +3659,31 @@
     <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1345872879028</t>
+    <t xml:space="preserve">12.1345863342285</t>
   </si>
   <si>
     <t xml:space="preserve">11.9496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6721410751343</t>
+    <t xml:space="preserve">11.6721420288086</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051021575928</t>
+    <t xml:space="preserve">12.0051012039185</t>
   </si>
   <si>
     <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0236005783081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9681053161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0247173309326</t>
+    <t xml:space="preserve">12.0236015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9681072235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0247163772583</t>
   </si>
   <si>
     <t xml:space="preserve">10.8582353591919</t>
@@ -3695,67 +3695,67 @@
     <t xml:space="preserve">11.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8201246261597</t>
+    <t xml:space="preserve">11.8201236724854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6710243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265186309814</t>
+    <t xml:space="preserve">12.6710252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265195846558</t>
   </si>
   <si>
     <t xml:space="preserve">12.8005104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2259607315063</t>
+    <t xml:space="preserve">13.2259616851807</t>
   </si>
   <si>
     <t xml:space="preserve">13.3276987075806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3646955490112</t>
+    <t xml:space="preserve">13.3646945953369</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4305534362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137939453125</t>
+    <t xml:space="preserve">12.6617765426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.430552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137929916382</t>
   </si>
   <si>
     <t xml:space="preserve">12.3473138809204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288145065308</t>
+    <t xml:space="preserve">12.3288154602051</t>
   </si>
   <si>
     <t xml:space="preserve">12.4952964782715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155319213867</t>
+    <t xml:space="preserve">12.6155309677124</t>
   </si>
   <si>
     <t xml:space="preserve">12.4398012161255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8016271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9958543777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3565616607666</t>
+    <t xml:space="preserve">11.8016262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9958534240723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3565607070923</t>
   </si>
   <si>
     <t xml:space="preserve">11.7646312713623</t>
@@ -3764,19 +3764,19 @@
     <t xml:space="preserve">11.8848676681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073999404907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5519046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2929353713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6455097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7657470703125</t>
+    <t xml:space="preserve">11.6073989868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2929363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6455106735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7657480239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.098708152771</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293733596802</t>
+    <t xml:space="preserve">11.8293724060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432809829712</t>
+    <t xml:space="preserve">12.1432819366455</t>
   </si>
   <si>
     <t xml:space="preserve">11.85191822052</t>
@@ -3815,25 +3815,25 @@
     <t xml:space="preserve">11.6639413833618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7579307556152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.974102973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0398960113525</t>
+    <t xml:space="preserve">11.7579298019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9741020202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0398950576782</t>
   </si>
   <si>
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895120620728</t>
+    <t xml:space="preserve">11.8895130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.1658039093018</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7522554397583</t>
+    <t xml:space="preserve">10.7522563934326</t>
   </si>
   <si>
     <t xml:space="preserve">10.5642786026001</t>
@@ -3842,13 +3842,13 @@
     <t xml:space="preserve">11.053017616272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5830774307251</t>
+    <t xml:space="preserve">10.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838386535645</t>
+    <t xml:space="preserve">10.8838396072388</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3863,7 +3863,7 @@
     <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4947624206543</t>
+    <t xml:space="preserve">11.49476146698</t>
   </si>
   <si>
     <t xml:space="preserve">11.4853639602661</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075487136841</t>
+    <t xml:space="preserve">11.6075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365072250366</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0962867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876514434814</t>
+    <t xml:space="preserve">12.096287727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876523971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6414194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6884136199951</t>
+    <t xml:space="preserve">12.6414184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6884126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.5474319458008</t>
@@ -3905,16 +3905,16 @@
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481941223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998574256897</t>
+    <t xml:space="preserve">12.8481931686401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9985752105713</t>
   </si>
   <si>
     <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685163497925</t>
+    <t xml:space="preserve">13.4685153961182</t>
   </si>
   <si>
     <t xml:space="preserve">13.6188974380493</t>
@@ -3923,13 +3923,13 @@
     <t xml:space="preserve">13.5625047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6094980239868</t>
+    <t xml:space="preserve">13.6094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564931869507</t>
+    <t xml:space="preserve">13.6564912796021</t>
   </si>
   <si>
     <t xml:space="preserve">13.741081237793</t>
@@ -3938,22 +3938,22 @@
     <t xml:space="preserve">13.6752910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8726663589478</t>
+    <t xml:space="preserve">13.8726654052734</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3087368011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">13.3087358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9891748428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1583547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
@@ -3968,16 +3968,16 @@
     <t xml:space="preserve">13.1113605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9139842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8199977874756</t>
+    <t xml:space="preserve">12.9139852523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8199968338013</t>
   </si>
   <si>
     <t xml:space="preserve">13.0361700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.017373085022</t>
+    <t xml:space="preserve">13.0173721313477</t>
   </si>
   <si>
     <t xml:space="preserve">13.0549688339233</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">12.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1207599639893</t>
+    <t xml:space="preserve">13.1207590103149</t>
   </si>
   <si>
     <t xml:space="preserve">12.1056861877441</t>
@@ -4025,22 +4025,22 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5548801422119</t>
+    <t xml:space="preserve">11.1000127792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5548791885376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984865188599</t>
+    <t xml:space="preserve">10.4984874725342</t>
   </si>
   <si>
     <t xml:space="preserve">10.6582670211792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951015472412</t>
+    <t xml:space="preserve">10.3951005935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.9778280258179</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6676664352417</t>
+    <t xml:space="preserve">10.667667388916</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
@@ -4067,10 +4067,10 @@
     <t xml:space="preserve">10.9684295654297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3255834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2879886627197</t>
+    <t xml:space="preserve">11.3255844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.287989616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.8707151412964</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">11.7955255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6357450485229</t>
+    <t xml:space="preserve">11.6357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4094,49 +4094,49 @@
     <t xml:space="preserve">11.7485313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1150846481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7354078292847</t>
+    <t xml:space="preserve">12.1150856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244840621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6790151596069</t>
+    <t xml:space="preserve">12.6790142059326</t>
   </si>
   <si>
     <t xml:space="preserve">12.4722414016724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.773003578186</t>
+    <t xml:space="preserve">12.7730026245117</t>
   </si>
   <si>
     <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0831651687622</t>
+    <t xml:space="preserve">13.0831642150879</t>
   </si>
   <si>
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256711959839</t>
+    <t xml:space="preserve">13.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9102621078491</t>
+    <t xml:space="preserve">13.9102611541748</t>
   </si>
   <si>
     <t xml:space="preserve">13.8068733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6282968521118</t>
+    <t xml:space="preserve">13.6282958984375</t>
   </si>
   <si>
     <t xml:space="preserve">13.3275337219238</t>
@@ -4145,7 +4145,7 @@
     <t xml:space="preserve">13.4779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437059402466</t>
+    <t xml:space="preserve">13.5437068939209</t>
   </si>
   <si>
     <t xml:space="preserve">13.7222852706909</t>
@@ -4154,34 +4154,34 @@
     <t xml:space="preserve">14.258017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1170358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2805404663086</t>
+    <t xml:space="preserve">14.1170349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504816055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2805395126343</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4403190612793</t>
+    <t xml:space="preserve">13.4403200149536</t>
   </si>
   <si>
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463306427002</t>
+    <t xml:space="preserve">13.3463315963745</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523431777954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5719022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3933258056641</t>
+    <t xml:space="preserve">13.5719032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3933248519897</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4190,13 +4190,13 @@
     <t xml:space="preserve">13.5249090194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7598791122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7316818237305</t>
+    <t xml:space="preserve">13.6470937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.759880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.0606422424316</t>
@@ -4220,13 +4220,13 @@
     <t xml:space="preserve">13.4215211868286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0888385772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5587787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749519348145</t>
+    <t xml:space="preserve">14.0888376235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5587797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749528884888</t>
   </si>
   <si>
     <t xml:space="preserve">14.8407440185547</t>
@@ -4235,31 +4235,31 @@
     <t xml:space="preserve">15.0193214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0099229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6997632980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7279596328735</t>
+    <t xml:space="preserve">15.0099239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6997623443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7279586791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9441318511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347333908081</t>
+    <t xml:space="preserve">14.944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347324371338</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031482696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7655534744263</t>
+    <t xml:space="preserve">14.8031492233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7655544281006</t>
   </si>
   <si>
     <t xml:space="preserve">14.7937498092651</t>
@@ -4268,37 +4268,37 @@
     <t xml:space="preserve">14.6621675491333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8125476837158</t>
+    <t xml:space="preserve">14.8125486373901</t>
   </si>
   <si>
     <t xml:space="preserve">14.6903638839722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689403533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1039113998413</t>
+    <t xml:space="preserve">14.8689413070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.103910446167</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8877391815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.122709274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3708028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1734275817871</t>
+    <t xml:space="preserve">14.8877382278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1227102279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3708038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1734285354614</t>
   </si>
   <si>
     <t xml:space="preserve">14.4929876327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299337387085</t>
+    <t xml:space="preserve">13.2993364334106</t>
   </si>
   <si>
     <t xml:space="preserve">11.513560295105</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.3725786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9872264862061</t>
+    <t xml:space="preserve">10.9872255325317</t>
   </si>
   <si>
     <t xml:space="preserve">11.269190788269</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">11.3067855834961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.231595993042</t>
+    <t xml:space="preserve">11.2315950393677</t>
   </si>
   <si>
     <t xml:space="preserve">11.5041618347168</t>
@@ -4331,31 +4331,31 @@
     <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1846017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094102859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0812139511108</t>
+    <t xml:space="preserve">11.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966249465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0812149047852</t>
   </si>
   <si>
     <t xml:space="preserve">11.0342197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744401931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9590301513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9026374816895</t>
+    <t xml:space="preserve">10.874439239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9590291976929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9026365280151</t>
   </si>
   <si>
     <t xml:space="preserve">10.893238067627</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146606445312</t>
+    <t xml:space="preserve">10.7146596908569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4138984680176</t>
+    <t xml:space="preserve">10.4138975143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387069702148</t>
@@ -4385,28 +4385,28 @@
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1549892425537</t>
+    <t xml:space="preserve">10.0303297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.154990196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563623428345</t>
+    <t xml:space="preserve">10.3371849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563632965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5193796157837</t>
+    <t xml:space="preserve">10.519380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235017776489</t>
+    <t xml:space="preserve">11.1235008239746</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412929534912</t>
+    <t xml:space="preserve">10.4906120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412919998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440391540527</t>
+    <t xml:space="preserve">10.6440401077271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960941314697</t>
+    <t xml:space="preserve">10.5960931777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.711163520813</t>
+    <t xml:space="preserve">10.7111644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813404083252</t>
+    <t xml:space="preserve">9.84813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484855651855</t>
+    <t xml:space="preserve">9.92484760284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618444442749</t>
+    <t xml:space="preserve">10.4618434906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4547,22 +4547,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361614227295</t>
+    <t xml:space="preserve">9.95361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537982940674</t>
+    <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646450042725</t>
+    <t xml:space="preserve">8.82688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646354675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34741973876953</t>
+    <t xml:space="preserve">8.34742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09810066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960834503174</t>
+    <t xml:space="preserve">8.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084171295166</t>
+    <t xml:space="preserve">8.23234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4643,13 +4643,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810676574707</t>
+    <t xml:space="preserve">8.44810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770397186279</t>
+    <t xml:space="preserve">8.80770301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4670,22 +4670,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976409912109</t>
+    <t xml:space="preserve">9.10976314544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14812088012695</t>
+    <t xml:space="preserve">8.67824935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14811992645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798629760742</t>
+    <t xml:space="preserve">9.26798534393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208728790283</t>
+    <t xml:space="preserve">8.82208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907001495361</t>
+    <t xml:space="preserve">8.6590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19127178192139</t>
+    <t xml:space="preserve">9.1912727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921775817871</t>
+    <t xml:space="preserve">9.23921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28237056732178</t>
+    <t xml:space="preserve">9.28236961364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1337366104126</t>
+    <t xml:space="preserve">9.13373565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428199768066</t>
+    <t xml:space="preserve">9.00428295135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8844165802002</t>
+    <t xml:space="preserve">8.88441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4787,25 +4787,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318511962891</t>
+    <t xml:space="preserve">8.91318416595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468669891357</t>
+    <t xml:space="preserve">8.64468574523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7166051864624</t>
+    <t xml:space="preserve">8.71660614013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399871826172</t>
+    <t xml:space="preserve">8.54399967193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496292114258</t>
+    <t xml:space="preserve">8.75496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222091674805</t>
+    <t xml:space="preserve">8.70222187042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4847,37 +4847,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605274200439</t>
+    <t xml:space="preserve">8.49605369567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1364574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21796607971191</t>
+    <t xml:space="preserve">8.13645648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2179651260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97344064712524</t>
+    <t xml:space="preserve">7.97343969345093</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467306137085</t>
+    <t xml:space="preserve">7.94467258453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059886932373</t>
+    <t xml:space="preserve">9.79059791564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.42076587677</t>
+    <t xml:space="preserve">11.4207668304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4922,16 +4922,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.593373298645</t>
+    <t xml:space="preserve">11.5933723449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2769289016724</t>
+    <t xml:space="preserve">11.3536424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276927947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4940,16 +4940,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796619415283</t>
+    <t xml:space="preserve">10.9796628952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276220321655</t>
+    <t xml:space="preserve">11.1618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276210784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4973,10 +4973,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6084041595459</t>
+    <t xml:space="preserve">9.59881401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60840320587158</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -5808,6 +5808,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.6199998855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8400001525879</t>
   </si>
 </sst>
 </file>
@@ -71042,7 +71045,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6493287037</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>78432</v>
@@ -71063,6 +71066,32 @@
         <v>1908</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6910532407</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>71033</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>11.9799995422363</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>11.6899995803833</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>11.8299999237061</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>11.8400001525879</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="1935">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1936">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034418106079</t>
+    <t xml:space="preserve">2.10034394264221</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.150794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13486289978027</t>
+    <t xml:space="preserve">2.15079474449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13486266136169</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07379126548767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02333998680115</t>
+    <t xml:space="preserve">2.07379055023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02333974838257</t>
   </si>
   <si>
     <t xml:space="preserve">2.06316947937012</t>
@@ -65,79 +65,79 @@
     <t xml:space="preserve">2.05254864692688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96492326259613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988330364227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439218521118</t>
+    <t xml:space="preserve">1.964923620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439230442047</t>
   </si>
   <si>
     <t xml:space="preserve">2.01802968978882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209784507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00156688690186</t>
+    <t xml:space="preserve">2.0169677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209760665894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00156664848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.059983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528383255005</t>
+    <t xml:space="preserve">2.00528407096863</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909184455872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97820019721985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774927616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943250179291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447269916534</t>
+    <t xml:space="preserve">1.97819995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854097366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774903774261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943285942078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447281837463</t>
   </si>
   <si>
     <t xml:space="preserve">1.93305993080139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91712784767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633686542511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368135929108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113599777222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441233634949</t>
+    <t xml:space="preserve">1.9171279668808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589554309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237790107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441209793091</t>
   </si>
   <si>
     <t xml:space="preserve">2.09450221061707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17203760147095</t>
+    <t xml:space="preserve">2.17203712463379</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830974578857</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">2.10299897193909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14442229270935</t>
+    <t xml:space="preserve">2.14442181587219</t>
   </si>
   <si>
     <t xml:space="preserve">2.14548420906067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15344977378845</t>
+    <t xml:space="preserve">2.15345001220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.1481397151947</t>
@@ -167,49 +167,49 @@
     <t xml:space="preserve">2.16831970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18265819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222487449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495325088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
+    <t xml:space="preserve">2.18265795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22248792648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955188751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
   </si>
   <si>
     <t xml:space="preserve">2.08706736564636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219815254211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.121586561203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14017343521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12424182891846</t>
+    <t xml:space="preserve">2.07219743728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12158632278442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1401731967926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12424159049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.11362075805664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06582474708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05307936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06848049163818</t>
+    <t xml:space="preserve">2.06582522392273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05307984352112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0684802532196</t>
   </si>
   <si>
     <t xml:space="preserve">2.06901144981384</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">2.12477254867554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16141605377197</t>
+    <t xml:space="preserve">2.16141557693481</t>
   </si>
   <si>
     <t xml:space="preserve">2.15557432174683</t>
@@ -230,100 +230,100 @@
     <t xml:space="preserve">2.17734789848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24373006820679</t>
+    <t xml:space="preserve">2.24373054504395</t>
   </si>
   <si>
     <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29418087005615</t>
+    <t xml:space="preserve">2.29418158531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.25753784179688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22461199760437</t>
+    <t xml:space="preserve">2.22461223602295</t>
   </si>
   <si>
     <t xml:space="preserve">2.21452212333679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22514343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098492622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34888029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44925117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555318832397</t>
+    <t xml:space="preserve">2.22514319419861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2463858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073426246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888005256653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604479789734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44925093650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5028874874115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5655529499054</t>
   </si>
   <si>
     <t xml:space="preserve">2.52997183799744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61547207832336</t>
+    <t xml:space="preserve">2.61547255516052</t>
   </si>
   <si>
     <t xml:space="preserve">2.66555047035217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66718339920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70147562026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786764144897</t>
+    <t xml:space="preserve">2.66718316078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70147585868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786787986755</t>
   </si>
   <si>
     <t xml:space="preserve">2.72161555290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79346609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8152391910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894074440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98942255973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00248599052429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94587683677673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8413667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9175717830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668535232544</t>
+    <t xml:space="preserve">2.79346632957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894026756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.989422082901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00248622894287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94587659835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84136652946472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91757202148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668559074402</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797616004944</t>
@@ -335,52 +335,52 @@
     <t xml:space="preserve">2.76516151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73685669898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954882144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78693413734436</t>
+    <t xml:space="preserve">2.73685646057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69548797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78693437576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531686782837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98289060592651</t>
+    <t xml:space="preserve">2.98289036750793</t>
   </si>
   <si>
     <t xml:space="preserve">2.84789848327637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77604818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86313939094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974878311157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972003698349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99159979820251</t>
+    <t xml:space="preserve">2.77604794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86313962936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97200393676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99159932136536</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418141365051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99813199043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97853660583496</t>
+    <t xml:space="preserve">2.99813151359558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97853589057922</t>
   </si>
   <si>
     <t xml:space="preserve">3.03514575958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04820919036865</t>
+    <t xml:space="preserve">3.04820966720581</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998229026794</t>
@@ -392,37 +392,37 @@
     <t xml:space="preserve">3.29859805107117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30730700492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214425086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29206657409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771162033081</t>
+    <t xml:space="preserve">3.30730748176575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771185874939</t>
   </si>
   <si>
     <t xml:space="preserve">3.26158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24416589736938</t>
+    <t xml:space="preserve">3.24416565895081</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988909721375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27900242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25722932815552</t>
+    <t xml:space="preserve">3.27900266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25722980499268</t>
   </si>
   <si>
     <t xml:space="preserve">3.26593899726868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17449235916138</t>
+    <t xml:space="preserve">3.1744921207428</t>
   </si>
   <si>
     <t xml:space="preserve">3.25505208969116</t>
@@ -431,28 +431,28 @@
     <t xml:space="preserve">3.25940704345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33125734329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35085320472717</t>
+    <t xml:space="preserve">3.33125758171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35085344314575</t>
   </si>
   <si>
     <t xml:space="preserve">3.34432125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32472562789917</t>
+    <t xml:space="preserve">3.32472586631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.28553414344788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037115097046</t>
+    <t xml:space="preserve">3.27247071266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303068161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037138938904</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682542800903</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">3.3094847202301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15054225921631</t>
+    <t xml:space="preserve">3.15054202079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.18973302841187</t>
@@ -473,94 +473,94 @@
     <t xml:space="preserve">3.20932912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20061993598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239255905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175515174866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497465133667</t>
+    <t xml:space="preserve">3.25069785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2006196975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239279747009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175539016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33343482017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376175880432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497417449951</t>
   </si>
   <si>
     <t xml:space="preserve">3.37262606620789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43141317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59253287315369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962431907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631162643433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9082396030426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01057291030884</t>
+    <t xml:space="preserve">3.43141293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59253263473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631138801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057243347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.09330987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533104896545</t>
+    <t xml:space="preserve">3.99533176422119</t>
   </si>
   <si>
     <t xml:space="preserve">3.95831775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11508226394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19346570968628</t>
+    <t xml:space="preserve">4.11508321762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19346523284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.33716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483324050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47433519363403</t>
+    <t xml:space="preserve">4.23483371734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47433567047119</t>
   </si>
   <si>
     <t xml:space="preserve">4.68988847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65722846984863</t>
+    <t xml:space="preserve">4.65722894668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.6463418006897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75956106185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95334005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245386123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72037076950073</t>
+    <t xml:space="preserve">4.75956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95334100723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245433807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72037029266357</t>
   </si>
   <si>
     <t xml:space="preserve">4.74214315414429</t>
@@ -572,49 +572,49 @@
     <t xml:space="preserve">4.64416456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37418079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35023069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3415207862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22830200195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128751754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895587921143</t>
+    <t xml:space="preserve">4.57231378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37418031692505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34152126312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22830152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128704071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
     <t xml:space="preserve">4.22612476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24572038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36547183990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35458517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940618515015</t>
+    <t xml:space="preserve">4.24571990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36547088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35458469390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940570831299</t>
   </si>
   <si>
     <t xml:space="preserve">4.63763284683228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63545608520508</t>
+    <t xml:space="preserve">4.63545560836792</t>
   </si>
   <si>
     <t xml:space="preserve">4.61586046218872</t>
@@ -626,13 +626,13 @@
     <t xml:space="preserve">4.72254753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66376066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58973264694214</t>
+    <t xml:space="preserve">4.59408712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6637601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58973169326782</t>
   </si>
   <si>
     <t xml:space="preserve">4.51135015487671</t>
@@ -644,40 +644,40 @@
     <t xml:space="preserve">4.73343372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64198637008667</t>
+    <t xml:space="preserve">4.64198732376099</t>
   </si>
   <si>
     <t xml:space="preserve">4.78568935394287</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77480220794678</t>
+    <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
     <t xml:space="preserve">4.74649715423584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76609325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921884536743</t>
+    <t xml:space="preserve">4.76609373092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921932220459</t>
   </si>
   <si>
     <t xml:space="preserve">5.38662195205688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082059860229</t>
+    <t xml:space="preserve">5.29082012176514</t>
   </si>
   <si>
     <t xml:space="preserve">5.25162982940674</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22985696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22767925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2037296295166</t>
+    <t xml:space="preserve">5.22985649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
   </si>
   <si>
     <t xml:space="preserve">5.03607749938965</t>
@@ -686,61 +686,61 @@
     <t xml:space="preserve">5.11010551452637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22550106048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27557897567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106962203979</t>
+    <t xml:space="preserve">5.22550201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27557992935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17107009887695</t>
   </si>
   <si>
     <t xml:space="preserve">5.14494180679321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220436096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979385375977</t>
+    <t xml:space="preserve">5.06220483779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979480743408</t>
   </si>
   <si>
     <t xml:space="preserve">5.09050941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04043197631836</t>
+    <t xml:space="preserve">5.04043245315552</t>
   </si>
   <si>
     <t xml:space="preserve">5.11445999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10139656066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09268712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663770675659</t>
+    <t xml:space="preserve">5.10139608383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09268760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752294540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663675308228</t>
   </si>
   <si>
     <t xml:space="preserve">5.04478645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736902236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98817777633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584470748901</t>
+    <t xml:space="preserve">4.95769548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736806869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98817682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88584518432617</t>
   </si>
   <si>
     <t xml:space="preserve">4.8662486076355</t>
@@ -755,19 +755,19 @@
     <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74431991577148</t>
+    <t xml:space="preserve">4.73561191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004383087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7443208694458</t>
   </si>
   <si>
     <t xml:space="preserve">4.75738430023193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68117904663086</t>
+    <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052564620972</t>
@@ -776,73 +776,73 @@
     <t xml:space="preserve">4.91850423812866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13841104507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19719696044922</t>
+    <t xml:space="preserve">5.1384105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08397817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19719743728638</t>
   </si>
   <si>
     <t xml:space="preserve">5.11881446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09486436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444519042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710424423218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55209636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6827335357666</t>
+    <t xml:space="preserve">5.09486389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710329055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55209589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68273305892944</t>
   </si>
   <si>
     <t xml:space="preserve">5.63918685913086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84385251998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.944007396698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81337070465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87868928909302</t>
+    <t xml:space="preserve">5.84385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94400787353516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81337118148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87868976593018</t>
   </si>
   <si>
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957643508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89610815048218</t>
+    <t xml:space="preserve">5.76329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89610767364502</t>
   </si>
   <si>
     <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0964183807373</t>
+    <t xml:space="preserve">6.09641933441162</t>
   </si>
   <si>
     <t xml:space="preserve">5.94836282730103</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">5.9897313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497198104858</t>
+    <t xml:space="preserve">6.00497245788574</t>
   </si>
   <si>
     <t xml:space="preserve">5.98755407333374</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">6.05722713470459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08335542678833</t>
+    <t xml:space="preserve">6.08335447311401</t>
   </si>
   <si>
     <t xml:space="preserve">5.96360397338867</t>
@@ -875,25 +875,25 @@
     <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42301177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26842498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52969980239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80403900146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201711654663</t>
+    <t xml:space="preserve">6.42301273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26842546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52970027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276418685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848714828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80403852462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.01088190078735</t>
@@ -905,13 +905,13 @@
     <t xml:space="preserve">7.11756944656372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3200569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063192367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425603866577</t>
+    <t xml:space="preserve">7.32005739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063287734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425699234009</t>
   </si>
   <si>
     <t xml:space="preserve">7.22207880020142</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">7.29392910003662</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37666797637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360359191895</t>
+    <t xml:space="preserve">7.37666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360311508179</t>
   </si>
   <si>
     <t xml:space="preserve">7.28522062301636</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30481624603271</t>
+    <t xml:space="preserve">7.30481576919556</t>
   </si>
   <si>
     <t xml:space="preserve">7.19595146179199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46655893325806</t>
+    <t xml:space="preserve">6.4665584564209</t>
   </si>
   <si>
     <t xml:space="preserve">6.22705602645874</t>
@@ -947,28 +947,28 @@
     <t xml:space="preserve">6.47309017181396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40123987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61243724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49704074859619</t>
+    <t xml:space="preserve">6.4012393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61243772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49704122543335</t>
   </si>
   <si>
     <t xml:space="preserve">6.52316856384277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57760047912598</t>
+    <t xml:space="preserve">6.57760095596313</t>
   </si>
   <si>
     <t xml:space="preserve">6.52464389801025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290407180786</t>
+    <t xml:space="preserve">6.56215524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290454864502</t>
   </si>
   <si>
     <t xml:space="preserve">6.54891586303711</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">6.45403623580933</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55774164199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91740322113037</t>
+    <t xml:space="preserve">6.55774116516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.76294708251953</t>
@@ -989,34 +989,34 @@
     <t xml:space="preserve">6.82252311706543</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58421993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50478553771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093801498413</t>
+    <t xml:space="preserve">6.41652631759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58422040939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50478601455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093849182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694885253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488464355469</t>
+    <t xml:space="preserve">6.35694980621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
     <t xml:space="preserve">6.43417739868164</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3282642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33267784118652</t>
+    <t xml:space="preserve">6.32826519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33267831802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.37460136413574</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">6.16057014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291906356812</t>
+    <t xml:space="preserve">6.1429181098938</t>
   </si>
   <si>
     <t xml:space="preserve">6.13850498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95757150650024</t>
+    <t xml:space="preserve">5.95757102966309</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344118118286</t>
@@ -1040,67 +1040,67 @@
     <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771314620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78546380996704</t>
+    <t xml:space="preserve">5.93771266937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78546333312988</t>
   </si>
   <si>
     <t xml:space="preserve">5.95977783203125</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92006063461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93329954147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94212627410889</t>
+    <t xml:space="preserve">5.9200611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93330049514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94212532043457</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84724617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98846292495728</t>
+    <t xml:space="preserve">5.8472466468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98846244812012</t>
   </si>
   <si>
     <t xml:space="preserve">5.69720363616943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50744295120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46993398666382</t>
+    <t xml:space="preserve">5.50744438171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692083358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7611927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89137649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72147512435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5912914276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608551025391</t>
+    <t xml:space="preserve">5.7369213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89137601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59129190444946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.54495429992676</t>
@@ -1118,25 +1118,25 @@
     <t xml:space="preserve">5.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49199867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56040048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52730274200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45890140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41256427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4897928237915</t>
+    <t xml:space="preserve">5.49199914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56040000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52730226516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45890045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41256475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
     <t xml:space="preserve">5.56922578811646</t>
@@ -1148,37 +1148,37 @@
     <t xml:space="preserve">5.66410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80311584472656</t>
+    <t xml:space="preserve">5.8031153678894</t>
   </si>
   <si>
     <t xml:space="preserve">5.86931133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56481313705444</t>
+    <t xml:space="preserve">5.73030042648315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5648136138916</t>
   </si>
   <si>
     <t xml:space="preserve">5.52068328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47875881195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49420499801636</t>
+    <t xml:space="preserve">5.47875928878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4942045211792</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
@@ -1193,19 +1193,19 @@
     <t xml:space="preserve">5.24045658111572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25369596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477060317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796697616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2228045463562</t>
+    <t xml:space="preserve">5.25369548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39711809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796745300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22280502319336</t>
   </si>
   <si>
     <t xml:space="preserve">5.14116382598877</t>
@@ -1214,31 +1214,31 @@
     <t xml:space="preserve">5.11909914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.207359790802</t>
+    <t xml:space="preserve">5.20735931396484</t>
   </si>
   <si>
     <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13233757019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1367506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03745794296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00656652450562</t>
+    <t xml:space="preserve">5.13233852386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13675117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03745746612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
     <t xml:space="preserve">4.9646430015564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802354812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126293182373</t>
+    <t xml:space="preserve">4.95802307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126197814941</t>
   </si>
   <si>
     <t xml:space="preserve">5.04849004745483</t>
@@ -1253,16 +1253,16 @@
     <t xml:space="preserve">5.22501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
+    <t xml:space="preserve">5.24487018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689186096191</t>
   </si>
   <si>
     <t xml:space="preserve">5.03083801269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87196922302246</t>
+    <t xml:space="preserve">4.87196969985962</t>
   </si>
   <si>
     <t xml:space="preserve">4.72634029388428</t>
@@ -1274,49 +1274,49 @@
     <t xml:space="preserve">4.65131902694702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93154525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60453033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81194162368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76781129837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663850784302</t>
+    <t xml:space="preserve">4.93154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839189529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6045298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8450403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76781177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663803100586</t>
   </si>
   <si>
     <t xml:space="preserve">5.81856203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65307331085205</t>
+    <t xml:space="preserve">5.65307426452637</t>
   </si>
   <si>
     <t xml:space="preserve">5.6398344039917</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.023766040802</t>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376699447632</t>
   </si>
   <si>
     <t xml:space="preserve">6.19366788864136</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">6.06348419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14071178436279</t>
+    <t xml:space="preserve">6.14071130752563</t>
   </si>
   <si>
     <t xml:space="preserve">6.12526655197144</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">5.96419095993042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03480005264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80973482131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034439086914</t>
+    <t xml:space="preserve">6.03479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034343719482</t>
   </si>
   <si>
     <t xml:space="preserve">5.90020227432251</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">5.82518100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74354028701782</t>
+    <t xml:space="preserve">5.74354124069214</t>
   </si>
   <si>
     <t xml:space="preserve">5.65086698532104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61776924133301</t>
+    <t xml:space="preserve">5.61776971817017</t>
   </si>
   <si>
     <t xml:space="preserve">5.63542175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01935386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926784515381</t>
+    <t xml:space="preserve">6.01935338973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
   </si>
   <si>
     <t xml:space="preserve">5.84283304214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03259372711182</t>
+    <t xml:space="preserve">6.0325927734375</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95315885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413438796997</t>
+    <t xml:space="preserve">5.95315790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
   </si>
   <si>
     <t xml:space="preserve">6.22235250473022</t>
@@ -1400,88 +1400,88 @@
     <t xml:space="preserve">6.52243804931641</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878873825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
+    <t xml:space="preserve">6.37239551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1693959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878778457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996200561523</t>
   </si>
   <si>
     <t xml:space="preserve">5.55598735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11202716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92226696014404</t>
+    <t xml:space="preserve">6.11202669143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9222674369812</t>
   </si>
   <si>
     <t xml:space="preserve">5.79429054260254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67072629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800998687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571949005127</t>
+    <t xml:space="preserve">5.67072582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396425247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198511123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089691162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474395751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543668746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571901321411</t>
   </si>
   <si>
     <t xml:space="preserve">6.9284348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90637016296387</t>
+    <t xml:space="preserve">6.90636968612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.10495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97697925567627</t>
+    <t xml:space="preserve">6.97697830200195</t>
   </si>
   <si>
     <t xml:space="preserve">7.10054302215576</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87106561660767</t>
+    <t xml:space="preserve">6.87106657028198</t>
   </si>
   <si>
     <t xml:space="preserve">6.95050048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22851991653442</t>
+    <t xml:space="preserve">7.22852039337158</t>
   </si>
   <si>
     <t xml:space="preserve">7.14908647537231</t>
@@ -1490,40 +1490,40 @@
     <t xml:space="preserve">7.0475869178772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11378240585327</t>
+    <t xml:space="preserve">7.11378192901611</t>
   </si>
   <si>
     <t xml:space="preserve">7.06082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49330139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560634613037</t>
+    <t xml:space="preserve">7.4933009147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560682296753</t>
   </si>
   <si>
     <t xml:space="preserve">7.18439054489136</t>
   </si>
   <si>
-    <t xml:space="preserve">7.440345287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528148651123</t>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941181182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523847579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528053283691</t>
   </si>
   <si>
     <t xml:space="preserve">7.19321537017822</t>
@@ -1532,34 +1532,34 @@
     <t xml:space="preserve">7.2196946144104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56391000747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508518218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
+    <t xml:space="preserve">7.46240997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5374321937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508279800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
   </si>
   <si>
     <t xml:space="preserve">7.38738918304443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06965208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835073471069</t>
+    <t xml:space="preserve">7.06965160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
   </si>
   <si>
     <t xml:space="preserve">6.84017515182495</t>
@@ -1574,28 +1574,28 @@
     <t xml:space="preserve">6.61952447891235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5445032119751</t>
+    <t xml:space="preserve">6.54450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38247299194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716033935547</t>
+    <t xml:space="preserve">6.38247394561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643796920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
   </si>
   <si>
     <t xml:space="preserve">6.66425085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60163402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294267654419</t>
+    <t xml:space="preserve">6.60163354873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
   </si>
   <si>
     <t xml:space="preserve">6.54796171188354</t>
@@ -1604,31 +1604,31 @@
     <t xml:space="preserve">6.65977811813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.579270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534393310547</t>
+    <t xml:space="preserve">6.57926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534440994263</t>
   </si>
   <si>
     <t xml:space="preserve">6.71344947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75370359420776</t>
+    <t xml:space="preserve">6.75370407104492</t>
   </si>
   <si>
     <t xml:space="preserve">6.75817632675171</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61505126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49429035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087120056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956398010254</t>
+    <t xml:space="preserve">6.61505174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956302642822</t>
   </si>
   <si>
     <t xml:space="preserve">6.41825485229492</t>
@@ -1643,7 +1643,7 @@
     <t xml:space="preserve">6.22145795822144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12305974960327</t>
+    <t xml:space="preserve">6.12305927276611</t>
   </si>
   <si>
     <t xml:space="preserve">6.26171207427979</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">6.14095020294189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18120431900024</t>
+    <t xml:space="preserve">6.18120336532593</t>
   </si>
   <si>
     <t xml:space="preserve">6.20356750488281</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">6.34669160842896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24829435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2885479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21251249313354</t>
+    <t xml:space="preserve">6.24829387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
     <t xml:space="preserve">6.33774709701538</t>
@@ -1679,61 +1679,61 @@
     <t xml:space="preserve">6.48981714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53007078170776</t>
+    <t xml:space="preserve">6.53007125854492</t>
   </si>
   <si>
     <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44509029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141893386841</t>
+    <t xml:space="preserve">6.44509077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141798019409</t>
   </si>
   <si>
     <t xml:space="preserve">6.4003643989563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37352752685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42719984054565</t>
+    <t xml:space="preserve">6.37352800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42720031738281</t>
   </si>
   <si>
     <t xml:space="preserve">6.43167304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50323486328125</t>
+    <t xml:space="preserve">6.50323534011841</t>
   </si>
   <si>
     <t xml:space="preserve">6.32880115509033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23934888839722</t>
+    <t xml:space="preserve">6.23934841156006</t>
   </si>
   <si>
     <t xml:space="preserve">6.19014930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27960205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188766479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10069608688354</t>
+    <t xml:space="preserve">6.27960300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298170089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1006965637207</t>
   </si>
   <si>
     <t xml:space="preserve">6.39589166641235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18567752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440790176392</t>
+    <t xml:space="preserve">6.18567657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440742492676</t>
   </si>
   <si>
     <t xml:space="preserve">5.47452545166016</t>
@@ -1742,16 +1742,16 @@
     <t xml:space="preserve">5.33587312698364</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093118667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013124465942</t>
+    <t xml:space="preserve">5.24194765090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093166351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358846664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013172149658</t>
   </si>
   <si>
     <t xml:space="preserve">5.01831483840942</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886161804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73653793334961</t>
+    <t xml:space="preserve">5.05409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73653888702393</t>
   </si>
   <si>
     <t xml:space="preserve">4.58894062042236</t>
@@ -1781,10 +1781,10 @@
     <t xml:space="preserve">4.74995565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71417474746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201642990112</t>
+    <t xml:space="preserve">4.71417427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201690673828</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825727462769</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">4.11483907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04104042053223</t>
+    <t xml:space="preserve">4.04104089736938</t>
   </si>
   <si>
     <t xml:space="preserve">4.05445861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95829701423645</t>
+    <t xml:space="preserve">3.95829606056213</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353042602539</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">4.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1304931640625</t>
+    <t xml:space="preserve">4.13049364089966</t>
   </si>
   <si>
     <t xml:space="preserve">4.01867723464966</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">3.86884307861328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70559144020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702667236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466420173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8375346660614</t>
+    <t xml:space="preserve">3.70559167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702714920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740784645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466444015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83753490447998</t>
   </si>
   <si>
     <t xml:space="preserve">3.84648036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96500587463379</t>
+    <t xml:space="preserve">3.96500515937805</t>
   </si>
   <si>
     <t xml:space="preserve">4.15732955932617</t>
@@ -1850,67 +1850,67 @@
     <t xml:space="preserve">3.92475152015686</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264221191406</t>
+    <t xml:space="preserve">3.9314603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264149665833</t>
   </si>
   <si>
     <t xml:space="preserve">3.87331581115723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86213445663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84424376487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35896134376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24267196655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03245759010315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140305519104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3835608959198</t>
+    <t xml:space="preserve">3.86213421821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8442440032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24267220497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03245782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140329360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216444969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38356065750122</t>
   </si>
   <si>
     <t xml:space="preserve">3.38803315162659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26950812339783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22701811790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4528865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39474248886108</t>
+    <t xml:space="preserve">3.26950788497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22701787948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45288681983948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3947422504425</t>
   </si>
   <si>
     <t xml:space="preserve">3.48866820335388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51550388336182</t>
+    <t xml:space="preserve">3.5155041217804</t>
   </si>
   <si>
     <t xml:space="preserve">3.31870722770691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24714517593384</t>
+    <t xml:space="preserve">3.24714493751526</t>
   </si>
   <si>
     <t xml:space="preserve">3.11072897911072</t>
@@ -1919,10 +1919,10 @@
     <t xml:space="preserve">2.92735028266907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01009464263916</t>
+    <t xml:space="preserve">2.93182301521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01009440422058</t>
   </si>
   <si>
     <t xml:space="preserve">3.10402011871338</t>
@@ -1940,25 +1940,25 @@
     <t xml:space="preserve">2.92511391639709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751660346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844455718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869795799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83342480659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07271146774292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625624656677</t>
+    <t xml:space="preserve">2.77751612663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74844408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78869819641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83342504501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0727117061615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
     <t xml:space="preserve">3.16887354850769</t>
@@ -1970,28 +1970,28 @@
     <t xml:space="preserve">3.1599280834198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22254514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23596334457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18676376342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19347357749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32094383239746</t>
+    <t xml:space="preserve">3.22254538536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23596358299255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18676400184631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19347286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
     <t xml:space="preserve">3.54233980178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972273826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339457511902</t>
+    <t xml:space="preserve">3.47972249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5333948135376</t>
   </si>
   <si>
     <t xml:space="preserve">3.49537706375122</t>
@@ -2000,73 +2000,73 @@
     <t xml:space="preserve">3.61166596412659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66533756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57588458061218</t>
+    <t xml:space="preserve">3.66533803939819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588481903076</t>
   </si>
   <si>
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221322059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58259391784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444934844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58482980728149</t>
+    <t xml:space="preserve">3.52221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5825936794281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723249435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444958686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58483004570007</t>
   </si>
   <si>
     <t xml:space="preserve">3.6944100856781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62284803390503</t>
+    <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80398988723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567971229553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77268147468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766172409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040632247925</t>
+    <t xml:space="preserve">3.70335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80399036407471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567923545837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77268171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.857661485672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040608406067</t>
   </si>
   <si>
     <t xml:space="preserve">3.99184155464172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07011270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13272953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09247636795044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125551223755</t>
+    <t xml:space="preserve">4.07011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13273000717163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09247589111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
@@ -2078,82 +2078,82 @@
     <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02762269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112821578979</t>
+    <t xml:space="preserve">4.02762222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842383384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112773895264</t>
   </si>
   <si>
     <t xml:space="preserve">4.28256368637085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38319873809814</t>
+    <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.42792463302612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3541259765625</t>
+    <t xml:space="preserve">4.35412645339966</t>
   </si>
   <si>
     <t xml:space="preserve">4.16627502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429277420044</t>
+    <t xml:space="preserve">4.20429229736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20205688476562</t>
+    <t xml:space="preserve">4.20205593109131</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29150819778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24901914596558</t>
+    <t xml:space="preserve">4.29150915145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24901819229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0745849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15285634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1864013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171425819397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93369722366333</t>
+    <t xml:space="preserve">4.25349187850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982004165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07458543777466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15285682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18640089035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171473503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93369650840759</t>
   </si>
   <si>
     <t xml:space="preserve">3.90015244483948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99631452560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880405426025</t>
+    <t xml:space="preserve">3.99631428718567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880310058594</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
@@ -2162,13 +2162,13 @@
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804218292236</t>
+    <t xml:space="preserve">3.91804313659668</t>
   </si>
   <si>
     <t xml:space="preserve">3.87778902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76820874214172</t>
+    <t xml:space="preserve">3.7682089805603</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491760253906</t>
@@ -2180,10 +2180,10 @@
     <t xml:space="preserve">3.85095262527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0991849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82411766052246</t>
+    <t xml:space="preserve">4.09918546676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411742210388</t>
   </si>
   <si>
     <t xml:space="preserve">3.95693063735962</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76229047775269</t>
+    <t xml:space="preserve">3.76229000091553</t>
   </si>
   <si>
     <t xml:space="preserve">3.74626088142395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76458024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68901348114014</t>
+    <t xml:space="preserve">3.7645800113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68901371955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
@@ -2210,43 +2210,43 @@
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243607521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220501899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487239837646</t>
+    <t xml:space="preserve">3.84243655204773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487168312073</t>
   </si>
   <si>
     <t xml:space="preserve">3.96608996391296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89739346504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449479103088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9065523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440980911255</t>
+    <t xml:space="preserve">3.89739322662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9065535068512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440933227539</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165601730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19737005233765</t>
+    <t xml:space="preserve">4.19736957550049</t>
   </si>
   <si>
     <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09203481674194</t>
+    <t xml:space="preserve">4.09203433990479</t>
   </si>
   <si>
     <t xml:space="preserve">4.11264276504517</t>
@@ -2258,16 +2258,16 @@
     <t xml:space="preserve">4.14470195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751541137695</t>
+    <t xml:space="preserve">4.18820953369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751588821411</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438472747803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31415319442749</t>
+    <t xml:space="preserve">4.31415367126465</t>
   </si>
   <si>
     <t xml:space="preserve">4.40803909301758</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">4.30270433425903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3507924079895</t>
+    <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
@@ -2285,97 +2285,97 @@
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858690261841</t>
+    <t xml:space="preserve">4.23858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">4.22255754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
+    <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17446994781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997610092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09890365600586</t>
+    <t xml:space="preserve">4.1744704246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997562408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890413284302</t>
   </si>
   <si>
     <t xml:space="preserve">4.15157127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16302061080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11035299301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1240930557251</t>
+    <t xml:space="preserve">4.16302108764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12409210205078</t>
   </si>
   <si>
     <t xml:space="preserve">4.07600498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05539560317993</t>
+    <t xml:space="preserve">4.00730848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05539512634277</t>
   </si>
   <si>
     <t xml:space="preserve">3.97067022323608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.945481300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701561927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594388961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678503990173</t>
+    <t xml:space="preserve">3.94548082351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701609611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594365119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.876784324646</t>
   </si>
   <si>
     <t xml:space="preserve">3.8515956401825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95235061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98211932182312</t>
+    <t xml:space="preserve">3.95235085487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98212003707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.13096237182617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493253707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16760110855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04394626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0531063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18591976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13554239273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06226539611816</t>
+    <t xml:space="preserve">4.11493349075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16760063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04394578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05310583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18592023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1355414390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.34392166137695</t>
@@ -2384,73 +2384,73 @@
     <t xml:space="preserve">4.33705282211304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31873321533203</t>
+    <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
     <t xml:space="preserve">4.60267972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00112056732178</t>
+    <t xml:space="preserve">5.00112104415894</t>
   </si>
   <si>
     <t xml:space="preserve">5.17515277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33086490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35834407806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6285514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39040279388428</t>
+    <t xml:space="preserve">5.33086538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35834360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62855052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48657751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61023139953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70640707015991</t>
+    <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45451879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4819974899292</t>
+    <t xml:space="preserve">5.45451927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48199796676636</t>
   </si>
   <si>
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590751647949</t>
+    <t xml:space="preserve">5.27590799331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993925094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34460401535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47283792495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45909929275513</t>
+    <t xml:space="preserve">5.44993829727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34460496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47283744812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45909881591797</t>
   </si>
   <si>
     <t xml:space="preserve">5.55985450744629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69724750518799</t>
+    <t xml:space="preserve">5.69724702835083</t>
   </si>
   <si>
     <t xml:space="preserve">5.72930574417114</t>
@@ -2471,22 +2471,22 @@
     <t xml:space="preserve">5.67892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71556615829468</t>
+    <t xml:space="preserve">5.71556711196899</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098661422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82090139389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875793457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04989099502563</t>
+    <t xml:space="preserve">5.71098709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82090187072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875745773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04989051818848</t>
   </si>
   <si>
     <t xml:space="preserve">6.12316751480103</t>
@@ -2495,43 +2495,43 @@
     <t xml:space="preserve">6.22392225265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99493360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02241134643555</t>
+    <t xml:space="preserve">6.08652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99493312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02241086959839</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71395921707153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10324048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1994161605835</t>
+    <t xml:space="preserve">6.71395874023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941568374634</t>
   </si>
   <si>
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159658432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617612838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235132217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113256454468</t>
+    <t xml:space="preserve">7.61159610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235084533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600568771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113304138184</t>
   </si>
   <si>
     <t xml:space="preserve">7.62533473968506</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">7.16735649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28185176849365</t>
+    <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
     <t xml:space="preserve">7.41924571990967</t>
@@ -2549,46 +2549,46 @@
     <t xml:space="preserve">7.35512781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29101085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697912216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15361833572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26811218261719</t>
+    <t xml:space="preserve">7.29101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697959899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15361785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26811265945435</t>
   </si>
   <si>
     <t xml:space="preserve">7.39634561538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57495832443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91844129562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85890340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571210861206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579828262329</t>
+    <t xml:space="preserve">7.37802743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91844177246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85890436172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579875946045</t>
   </si>
   <si>
     <t xml:space="preserve">7.66655349731445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36428737640381</t>
+    <t xml:space="preserve">7.36428689956665</t>
   </si>
   <si>
     <t xml:space="preserve">7.45130395889282</t>
@@ -2597,10 +2597,10 @@
     <t xml:space="preserve">7.12155914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41466569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25895261764526</t>
+    <t xml:space="preserve">7.41466522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25895309448242</t>
   </si>
   <si>
     <t xml:space="preserve">7.30475044250488</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">7.22231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52916049957275</t>
+    <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
     <t xml:space="preserve">7.4375638961792</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">7.48794174194336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51999998092651</t>
+    <t xml:space="preserve">7.52000045776367</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2627,64 +2627,64 @@
     <t xml:space="preserve">7.17651700973511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02996397018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51244878768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702785491943</t>
+    <t xml:space="preserve">7.02996349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702833175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79639434814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71853876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76891660690308</t>
+    <t xml:space="preserve">6.79639482498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71853828430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
     <t xml:space="preserve">6.61778354644775</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02538347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257049560547</t>
+    <t xml:space="preserve">7.02538442611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">6.89715051651001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82845306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097484588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67732048034668</t>
+    <t xml:space="preserve">6.828453540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097436904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67732000350952</t>
   </si>
   <si>
     <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76433658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63610172271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11858701705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96745443344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78884363174438</t>
+    <t xml:space="preserve">6.76433706283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63610219955444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11858654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.967453956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78884267807007</t>
   </si>
   <si>
     <t xml:space="preserve">5.63771057128906</t>
@@ -2702,61 +2702,61 @@
     <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75381278991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59810018539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63931798934937</t>
+    <t xml:space="preserve">4.75381231307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63931846618652</t>
   </si>
   <si>
     <t xml:space="preserve">4.21110820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81495761871338</t>
+    <t xml:space="preserve">3.8149573802948</t>
   </si>
   <si>
     <t xml:space="preserve">3.66382479667664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32034087181091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22416591644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18294739723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22645545005798</t>
+    <t xml:space="preserve">3.32034111022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22416567802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18294763565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22645568847656</t>
   </si>
   <si>
     <t xml:space="preserve">3.44399499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356961250305</t>
+    <t xml:space="preserve">3.99356913566589</t>
   </si>
   <si>
     <t xml:space="preserve">3.86304545402527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6134467124939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50353240966797</t>
+    <t xml:space="preserve">3.61344718933105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50353264808655</t>
   </si>
   <si>
     <t xml:space="preserve">3.67069435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61802673339844</t>
+    <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.70962285995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62260675430298</t>
+    <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
     <t xml:space="preserve">3.79663825035095</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">3.74168109893799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06684494018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03020763397217</t>
+    <t xml:space="preserve">4.06684589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.3828501701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11722230911255</t>
+    <t xml:space="preserve">4.11722278594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.01188802719116</t>
@@ -2783,34 +2783,34 @@
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432411193848</t>
+    <t xml:space="preserve">4.09432363510132</t>
   </si>
   <si>
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35995149612427</t>
+    <t xml:space="preserve">4.45612716674805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35995197296143</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2637767791748</t>
+    <t xml:space="preserve">4.26377630233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.32331275939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537195205688</t>
+    <t xml:space="preserve">4.35537147521973</t>
   </si>
   <si>
     <t xml:space="preserve">4.30957412719727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30499458312988</t>
+    <t xml:space="preserve">4.30499410629272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17675971984863</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">4.48360538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38742971420288</t>
+    <t xml:space="preserve">4.38743019104004</t>
   </si>
   <si>
     <t xml:space="preserve">4.42406845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7515230178833</t>
+    <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761251449585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90036582946777</t>
+    <t xml:space="preserve">4.90036535263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.888916015625</t>
@@ -2846,40 +2846,40 @@
     <t xml:space="preserve">5.04920816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1866021156311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23239994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48428726196289</t>
+    <t xml:space="preserve">5.18660163879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23239946365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
     <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1637020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471336364746</t>
+    <t xml:space="preserve">5.16370296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93471431732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.02630949020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19805192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254625320435</t>
+    <t xml:space="preserve">5.19805145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39269208908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20950078964233</t>
+    <t xml:space="preserve">5.39269161224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20950126647949</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">5.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2438497543335</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.09500598907471</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0148606300354</t>
+    <t xml:space="preserve">5.01486015319824</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
@@ -2912,52 +2912,52 @@
     <t xml:space="preserve">5.22095012664795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210731506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645580291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935447692871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3239951133728</t>
+    <t xml:space="preserve">5.07210683822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645484924316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935495376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32399559020996</t>
   </si>
   <si>
     <t xml:space="preserve">5.33544445037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03775930404663</t>
+    <t xml:space="preserve">5.03775882720947</t>
   </si>
   <si>
     <t xml:space="preserve">5.08355712890625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96906280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051118850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84311866760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.96906232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616413116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98051166534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84311819076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.9919605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341081619263</t>
+    <t xml:space="preserve">5.00341033935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.57978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19049978256226</t>
+    <t xml:space="preserve">4.1904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">4.21339845657349</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163188934326</t>
+    <t xml:space="preserve">4.34163236618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412906646729</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">5.75907421112061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73617601394653</t>
+    <t xml:space="preserve">5.73617506027222</t>
   </si>
   <si>
     <t xml:space="preserve">5.69037771224976</t>
@@ -3005,34 +3005,34 @@
     <t xml:space="preserve">5.81632137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14835548400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96516418457031</t>
+    <t xml:space="preserve">6.14835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96516466140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.95371532440186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356853485107</t>
+    <t xml:space="preserve">5.87356901168823</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09110879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415330886841</t>
+    <t xml:space="preserve">6.09110832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415378570557</t>
   </si>
   <si>
     <t xml:space="preserve">6.12545728683472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15980529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18270397186279</t>
+    <t xml:space="preserve">6.1598048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18270349502563</t>
   </si>
   <si>
     <t xml:space="preserve">6.07965898513794</t>
@@ -3041,25 +3041,25 @@
     <t xml:space="preserve">6.13690614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2170524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35444593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009744644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36589479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48038959503174</t>
+    <t xml:space="preserve">6.21705293655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35444641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36589527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48038911819458</t>
   </si>
   <si>
     <t xml:space="preserve">6.52618741989136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53763723373413</t>
+    <t xml:space="preserve">6.53763675689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">6.58343553543091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62923336029053</t>
+    <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
     <t xml:space="preserve">6.41169309616089</t>
@@ -3080,100 +3080,100 @@
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894073486328</t>
+    <t xml:space="preserve">6.46894025802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20560264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4231424331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50328874588013</t>
+    <t xml:space="preserve">6.20560359954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42314291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50328922271729</t>
   </si>
   <si>
     <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5147385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78952550888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75517702102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6864800453186</t>
+    <t xml:space="preserve">6.51473808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78952503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75517654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68648052215576</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77807569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792938232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40024423599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154726028442</t>
+    <t xml:space="preserve">6.778076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792985916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37734460830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.3887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54908657073975</t>
+    <t xml:space="preserve">6.5490870475769</t>
   </si>
   <si>
     <t xml:space="preserve">6.86967134475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7856273651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417755126953</t>
+    <t xml:space="preserve">7.78562688827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417850494385</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17490863800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99171781539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06041526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02606582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911033630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1062126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03751468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447208404541</t>
+    <t xml:space="preserve">8.1749095916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99171733856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0260648727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911128997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03751564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447113037109</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331203460693</t>
@@ -3182,16 +3182,16 @@
     <t xml:space="preserve">8.3123025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085372924805</t>
+    <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33520221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27795505523682</t>
+    <t xml:space="preserve">8.33520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2779541015625</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200996398926</t>
@@ -3200,55 +3200,55 @@
     <t xml:space="preserve">8.11766147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18635749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34665203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16346073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736980438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8428750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92302083969116</t>
+    <t xml:space="preserve">8.18635845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34665107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16345977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591903686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736932754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84287452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92301988601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.81997585296631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86577367782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099956512451</t>
+    <t xml:space="preserve">7.86577272415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3809986114502</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99926853179932</t>
+    <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.20535945892334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48014736175537</t>
+    <t xml:space="preserve">9.48014640808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.65356349945068</t>
@@ -3257,37 +3257,37 @@
     <t xml:space="preserve">9.60731887817383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78073692321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0813255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2894268035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3009881973267</t>
+    <t xml:space="preserve">9.78073596954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71137046813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0813264846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2894277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3009872436523</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241100311279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5206508636475</t>
+    <t xml:space="preserve">10.5206499099731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437726974487</t>
+    <t xml:space="preserve">10.5437717437744</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975290298462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.33567237854</t>
+    <t xml:space="preserve">10.3356714248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628448486328</t>
@@ -3296,10 +3296,10 @@
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703546524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7403116226196</t>
+    <t xml:space="preserve">10.3703565597534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7403125762939</t>
   </si>
   <si>
     <t xml:space="preserve">10.4744062423706</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">10.2663059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3934774398804</t>
+    <t xml:space="preserve">10.393479347229</t>
   </si>
   <si>
     <t xml:space="preserve">10.0582036972046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95415306091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0235204696655</t>
+    <t xml:space="preserve">9.9541540145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0235214233398</t>
   </si>
   <si>
     <t xml:space="preserve">10.1506938934326</t>
@@ -3332,40 +3332,40 @@
     <t xml:space="preserve">10.0697650909424</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0928869247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1160106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2547435760498</t>
+    <t xml:space="preserve">10.092887878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1160097122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2547426223755</t>
   </si>
   <si>
     <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4859676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853761672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0350828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4165992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1738166809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1391324996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1911973953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5056610107422</t>
+    <t xml:space="preserve">10.4859666824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1853771209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0350818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.416600227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1738157272339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1391315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.191198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
     <t xml:space="preserve">11.9052143096924</t>
@@ -3374,19 +3374,19 @@
     <t xml:space="preserve">11.901515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7461318969727</t>
+    <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426559448242</t>
+    <t xml:space="preserve">11.5426568984985</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796527862549</t>
+    <t xml:space="preserve">11.5796537399292</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
@@ -3398,19 +3398,19 @@
     <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6536436080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3946733474731</t>
+    <t xml:space="preserve">11.6536426544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3946743011475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0975914001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8571186065674</t>
+    <t xml:space="preserve">12.0975923538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
     <t xml:space="preserve">12.0605964660645</t>
@@ -3425,13 +3425,13 @@
     <t xml:space="preserve">12.3010683059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.894115447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144151687622</t>
+    <t xml:space="preserve">11.8941164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144161224365</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
@@ -3443,10 +3443,10 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034284591675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8178911209106</t>
+    <t xml:space="preserve">13.5034294128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817892074585</t>
   </si>
   <si>
     <t xml:space="preserve">13.7254018783569</t>
@@ -3461,13 +3461,13 @@
     <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4109382629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4294385910034</t>
+    <t xml:space="preserve">13.4109392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4294366836548</t>
   </si>
   <si>
     <t xml:space="preserve">13.0409822463989</t>
@@ -3494,40 +3494,40 @@
     <t xml:space="preserve">13.0779781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4468193054199</t>
+    <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
     <t xml:space="preserve">15.4457035064697</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5011949539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.778660774231</t>
+    <t xml:space="preserve">15.5011959075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7786655426025</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3705959320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5370750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520965576172</t>
+    <t xml:space="preserve">16.3705940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520946502686</t>
   </si>
   <si>
     <t xml:space="preserve">16.0191345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7971611022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1486186981201</t>
+    <t xml:space="preserve">15.7971620559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1486206054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.0006370544434</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">15.908148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4641990661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896503448486</t>
+    <t xml:space="preserve">15.5196952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4642000198364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896522521973</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416677474976</t>
@@ -3551,22 +3551,22 @@
     <t xml:space="preserve">15.8341588973999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9092664718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.502311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2433414459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6329126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514120101929</t>
+    <t xml:space="preserve">14.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283208847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5023126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2433423995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6329135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
     <t xml:space="preserve">13.3369474411011</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8918838500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098224639893</t>
+    <t xml:space="preserve">13.8918828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098234176636</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
@@ -3593,22 +3593,22 @@
     <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7808961868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629556655884</t>
+    <t xml:space="preserve">13.7808952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629566192627</t>
   </si>
   <si>
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3554449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9658737182617</t>
+    <t xml:space="preserve">13.3924398422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3554458618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9658756256104</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">14.2803373336792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1138572692871</t>
+    <t xml:space="preserve">14.1138582229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.9484930038452</t>
@@ -3629,37 +3629,37 @@
     <t xml:space="preserve">13.1334714889526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4479351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085781097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3935565948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.18896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4664325714111</t>
+    <t xml:space="preserve">13.0594806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4479360580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085790634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3935575485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1889657974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4664335250854</t>
   </si>
   <si>
     <t xml:space="preserve">12.8190078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9126138687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6340284347534</t>
+    <t xml:space="preserve">11.9126129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6340293884277</t>
   </si>
   <si>
     <t xml:space="preserve">12.3380641937256</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8386211395264</t>
+    <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
     <t xml:space="preserve">12.1345872879028</t>
@@ -3668,16 +3668,16 @@
     <t xml:space="preserve">11.9496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6721420288086</t>
+    <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051031112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">12.0051012039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">10.8582353591919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5067758560181</t>
+    <t xml:space="preserve">10.5067768096924</t>
   </si>
   <si>
     <t xml:space="preserve">11.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8201246261597</t>
+    <t xml:space="preserve">11.8201236724854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131717681885</t>
@@ -3725,43 +3725,43 @@
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4305543899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3473129272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3288154602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4952955245972</t>
+    <t xml:space="preserve">12.6617765426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.430552482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028072357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3473138809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3288145065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4952964782715</t>
   </si>
   <si>
     <t xml:space="preserve">12.6155309677124</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8016271591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9958543777466</t>
+    <t xml:space="preserve">12.4398012161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8016262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9958534240723</t>
   </si>
   <si>
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.764630317688</t>
+    <t xml:space="preserve">11.7646312713623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848676681519</t>
@@ -3773,25 +3773,25 @@
     <t xml:space="preserve">11.551905632019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2929353713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6455097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7657470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0987071990967</t>
+    <t xml:space="preserve">11.2929363250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6455106735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7657480239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
     <t xml:space="preserve">11.5704030990601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4316682815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8293733596802</t>
+    <t xml:space="preserve">11.4316692352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8293724060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -3800,19 +3800,19 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605535507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5699529647827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6827402114868</t>
+    <t xml:space="preserve">11.5605545043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.569953918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8519172668457</t>
+    <t xml:space="preserve">11.85191822052</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639413833618</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">11.7579298019409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.974102973938</t>
+    <t xml:space="preserve">11.9741020202637</t>
   </si>
   <si>
     <t xml:space="preserve">12.0398950576782</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895120620728</t>
+    <t xml:space="preserve">11.8895130157471</t>
   </si>
   <si>
     <t xml:space="preserve">11.1658039093018</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">10.5830764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8274459838867</t>
+    <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
     <t xml:space="preserve">10.8838396072388</t>
@@ -3866,16 +3866,16 @@
     <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4947624206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4853649139404</t>
+    <t xml:space="preserve">11.49476146698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075487136841</t>
+    <t xml:space="preserve">11.6075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365072250366</t>
@@ -3884,13 +3884,13 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0962867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876514434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5380334854126</t>
+    <t xml:space="preserve">12.096287727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876523971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5380325317383</t>
   </si>
   <si>
     <t xml:space="preserve">12.6414184570312</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">12.5474319458008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5286340713501</t>
+    <t xml:space="preserve">12.5286331176758</t>
   </si>
   <si>
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481941223145</t>
+    <t xml:space="preserve">12.8481931686401</t>
   </si>
   <si>
     <t xml:space="preserve">12.9985752105713</t>
@@ -3917,31 +3917,31 @@
     <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.618896484375</t>
+    <t xml:space="preserve">13.4685153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6188974380493</t>
   </si>
   <si>
     <t xml:space="preserve">13.5625047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6094989776611</t>
+    <t xml:space="preserve">13.6094970703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7410821914673</t>
+    <t xml:space="preserve">13.6564912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.741081237793</t>
   </si>
   <si>
     <t xml:space="preserve">13.6752910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8726663589478</t>
+    <t xml:space="preserve">13.8726654052734</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
@@ -3950,13 +3950,13 @@
     <t xml:space="preserve">13.3087358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9891757965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">12.9891748428345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1583547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">13.1113605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9139842987061</t>
+    <t xml:space="preserve">12.9139852523804</t>
   </si>
   <si>
     <t xml:space="preserve">12.8199968338013</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">13.0173721313477</t>
   </si>
   <si>
-    <t xml:space="preserve">13.054967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8669910430908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260093688965</t>
+    <t xml:space="preserve">13.0549688339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8669919967651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260084152222</t>
   </si>
   <si>
     <t xml:space="preserve">12.4628419876099</t>
@@ -3998,7 +3998,7 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850276947021</t>
+    <t xml:space="preserve">12.5850267410278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756282806396</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">12.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1207599639893</t>
+    <t xml:space="preserve">13.1207590103149</t>
   </si>
   <si>
     <t xml:space="preserve">12.1056861877441</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8237209320068</t>
+    <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921377182007</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000118255615</t>
+    <t xml:space="preserve">11.1000127792358</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548791885376</t>
@@ -4037,10 +4037,10 @@
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984865188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582679748535</t>
+    <t xml:space="preserve">10.4984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582670211792</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951005935669</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">11.1188097000122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.949631690979</t>
+    <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
     <t xml:space="preserve">10.667667388916</t>
@@ -4067,16 +4067,16 @@
     <t xml:space="preserve">10.7898502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9684286117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3255834579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2879886627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8707160949707</t>
+    <t xml:space="preserve">10.9684295654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3255844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.287989616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8707151412964</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929008483887</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">11.7955255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6357450485229</t>
+    <t xml:space="preserve">11.6357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">12.1150856018066</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7354078292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8951873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6790151596069</t>
+    <t xml:space="preserve">12.1244840621948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.735408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.895188331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6790142059326</t>
   </si>
   <si>
     <t xml:space="preserve">12.4722414016724</t>
@@ -4121,13 +4121,13 @@
     <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0831651687622</t>
+    <t xml:space="preserve">13.0831642150879</t>
   </si>
   <si>
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256711959839</t>
+    <t xml:space="preserve">13.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
@@ -4142,7 +4142,7 @@
     <t xml:space="preserve">13.6282958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3275346755981</t>
+    <t xml:space="preserve">13.3275337219238</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779148101807</t>
@@ -4151,25 +4151,25 @@
     <t xml:space="preserve">13.5437068939209</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7222843170166</t>
+    <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
     <t xml:space="preserve">14.258017539978</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1170358657837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504806518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2805404663086</t>
+    <t xml:space="preserve">14.1170349121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504816055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2805395126343</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4403190612793</t>
+    <t xml:space="preserve">13.4403200149536</t>
   </si>
   <si>
     <t xml:space="preserve">13.5531053543091</t>
@@ -4181,10 +4181,10 @@
     <t xml:space="preserve">13.2523431777954</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5719022750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3933258056641</t>
+    <t xml:space="preserve">13.5719032287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3933248519897</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">13.5249090194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7598791122437</t>
+    <t xml:space="preserve">13.6470937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.759880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.7316827774048</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">14.0042486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0794401168823</t>
+    <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
     <t xml:space="preserve">13.7786769866943</t>
@@ -4226,7 +4226,7 @@
     <t xml:space="preserve">14.0888376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5587787628174</t>
+    <t xml:space="preserve">14.5587797164917</t>
   </si>
   <si>
     <t xml:space="preserve">14.7749528884888</t>
@@ -4235,7 +4235,7 @@
     <t xml:space="preserve">14.8407440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0193204879761</t>
+    <t xml:space="preserve">15.0193214416504</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099239349365</t>
@@ -4244,16 +4244,16 @@
     <t xml:space="preserve">14.6997623443604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7279596328735</t>
+    <t xml:space="preserve">14.7279586791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9441318511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347333908081</t>
+    <t xml:space="preserve">14.944130897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347324371338</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
@@ -4262,7 +4262,7 @@
     <t xml:space="preserve">14.8031492233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7655534744263</t>
+    <t xml:space="preserve">14.7655544281006</t>
   </si>
   <si>
     <t xml:space="preserve">14.7937498092651</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">14.8125486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903629302979</t>
+    <t xml:space="preserve">14.6903638839722</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1039113998413</t>
+    <t xml:space="preserve">15.103910446167</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
@@ -4289,10 +4289,10 @@
     <t xml:space="preserve">14.8877382278442</t>
   </si>
   <si>
-    <t xml:space="preserve">15.122709274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3708028793335</t>
+    <t xml:space="preserve">15.1227102279663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3708038330078</t>
   </si>
   <si>
     <t xml:space="preserve">14.1734285354614</t>
@@ -4307,13 +4307,13 @@
     <t xml:space="preserve">11.513560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3725776672363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9872264862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2691917419434</t>
+    <t xml:space="preserve">11.3725786209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9872255325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.269190788269</t>
   </si>
   <si>
     <t xml:space="preserve">11.2785902023315</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">11.3067855834961</t>
   </si>
   <si>
-    <t xml:space="preserve">11.231595993042</t>
+    <t xml:space="preserve">11.2315950393677</t>
   </si>
   <si>
     <t xml:space="preserve">11.5041618347168</t>
@@ -4334,16 +4334,16 @@
     <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1846017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094102859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966259002686</t>
+    <t xml:space="preserve">11.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966249465942</t>
   </si>
   <si>
     <t xml:space="preserve">11.0812149047852</t>
@@ -4352,13 +4352,13 @@
     <t xml:space="preserve">11.0342197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8744401931763</t>
+    <t xml:space="preserve">10.874439239502</t>
   </si>
   <si>
     <t xml:space="preserve">10.9590291976929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9026374816895</t>
+    <t xml:space="preserve">10.9026365280151</t>
   </si>
   <si>
     <t xml:space="preserve">10.893238067627</t>
@@ -4370,7 +4370,7 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146606445312</t>
+    <t xml:space="preserve">10.7146596908569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
@@ -4379,37 +4379,37 @@
     <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4138984680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3387079238892</t>
+    <t xml:space="preserve">10.4138975143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3387069702148</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1549892425537</t>
+    <t xml:space="preserve">10.0303297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.154990196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563623428345</t>
+    <t xml:space="preserve">10.3371849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563632965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5193796157837</t>
+    <t xml:space="preserve">10.519380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235017776489</t>
+    <t xml:space="preserve">11.1235008239746</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412929534912</t>
+    <t xml:space="preserve">10.4906120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412919998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440391540527</t>
+    <t xml:space="preserve">10.6440401077271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960941314697</t>
+    <t xml:space="preserve">10.5960931777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.711163520813</t>
+    <t xml:space="preserve">10.7111644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813404083252</t>
+    <t xml:space="preserve">9.84813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484855651855</t>
+    <t xml:space="preserve">9.92484760284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618444442749</t>
+    <t xml:space="preserve">10.4618434906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361614227295</t>
+    <t xml:space="preserve">9.95361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537982940674</t>
+    <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646450042725</t>
+    <t xml:space="preserve">8.82688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646354675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34741973876953</t>
+    <t xml:space="preserve">8.34742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09810066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960834503174</t>
+    <t xml:space="preserve">8.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084171295166</t>
+    <t xml:space="preserve">8.23234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810676574707</t>
+    <t xml:space="preserve">8.44810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770397186279</t>
+    <t xml:space="preserve">8.80770301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4673,22 +4673,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976409912109</t>
+    <t xml:space="preserve">9.10976314544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14812088012695</t>
+    <t xml:space="preserve">8.67824935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14811992645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798629760742</t>
+    <t xml:space="preserve">9.26798534393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208728790283</t>
+    <t xml:space="preserve">8.82208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907001495361</t>
+    <t xml:space="preserve">8.6590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19127178192139</t>
+    <t xml:space="preserve">9.1912727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921775817871</t>
+    <t xml:space="preserve">9.23921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28237056732178</t>
+    <t xml:space="preserve">9.28236961364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1337366104126</t>
+    <t xml:space="preserve">9.13373565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428199768066</t>
+    <t xml:space="preserve">9.00428295135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8844165802002</t>
+    <t xml:space="preserve">8.88441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318511962891</t>
+    <t xml:space="preserve">8.91318416595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468669891357</t>
+    <t xml:space="preserve">8.64468574523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7166051864624</t>
+    <t xml:space="preserve">8.71660614013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399871826172</t>
+    <t xml:space="preserve">8.54399967193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496292114258</t>
+    <t xml:space="preserve">8.75496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222091674805</t>
+    <t xml:space="preserve">8.70222187042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4850,37 +4850,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605274200439</t>
+    <t xml:space="preserve">8.49605369567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1364574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21796607971191</t>
+    <t xml:space="preserve">8.13645648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2179651260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97344064712524</t>
+    <t xml:space="preserve">7.97343969345093</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467306137085</t>
+    <t xml:space="preserve">7.94467258453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059886932373</t>
+    <t xml:space="preserve">9.79059791564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.42076587677</t>
+    <t xml:space="preserve">11.4207668304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4925,16 +4925,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.593373298645</t>
+    <t xml:space="preserve">11.5933723449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2769289016724</t>
+    <t xml:space="preserve">11.3536424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276927947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796619415283</t>
+    <t xml:space="preserve">10.9796628952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276220321655</t>
+    <t xml:space="preserve">11.1618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276210784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4976,10 +4976,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6084041595459</t>
+    <t xml:space="preserve">9.59881401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60840320587158</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -5817,6 +5817,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.4399995803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4200000762939</t>
   </si>
 </sst>
 </file>
@@ -71103,7 +71106,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6909722222</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>91198</v>
@@ -71124,6 +71127,32 @@
         <v>1934</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.691099537</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>57742</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>11.5299997329712</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>11.3299999237061</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>11.4399995803833</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>11.4200000762939</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>1935</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1936" uniqueCount="1936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="1937">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">2.09768867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07379055023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02333974838257</t>
+    <t xml:space="preserve">2.07379078865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02334022521973</t>
   </si>
   <si>
     <t xml:space="preserve">2.06316947937012</t>
@@ -65,28 +65,28 @@
     <t xml:space="preserve">2.05254864692688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.964923620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439230442047</t>
+    <t xml:space="preserve">1.96492350101471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988378047943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439242362976</t>
   </si>
   <si>
     <t xml:space="preserve">2.01802968978882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0169677734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209760665894</t>
+    <t xml:space="preserve">2.01696729660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209808349609</t>
   </si>
   <si>
     <t xml:space="preserve">2.00156664848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.059983253479</t>
+    <t xml:space="preserve">2.05998349189758</t>
   </si>
   <si>
     <t xml:space="preserve">2.00528407096863</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">2.01909184455872</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97819995880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854097366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774903774261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943285942078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447281837463</t>
+    <t xml:space="preserve">1.97820007801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774951457977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943274021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447246074677</t>
   </si>
   <si>
     <t xml:space="preserve">1.93305993080139</t>
@@ -122,235 +122,235 @@
     <t xml:space="preserve">1.95589554309845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94368076324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237790107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441209793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450221061707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203712463379</t>
+    <t xml:space="preserve">1.94368088245392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237766265869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113599777222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441233634949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450197219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13964223861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
+    <t xml:space="preserve">2.1396427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299921035767</t>
   </si>
   <si>
     <t xml:space="preserve">2.14442181587219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14548420906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15345001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1481397151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18265795707703</t>
+    <t xml:space="preserve">2.14548444747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15344977378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132570266724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16831994056702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18265843391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.22248792648315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15610504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955188751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10565447807312</t>
+    <t xml:space="preserve">2.15610527992249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495325088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1056547164917</t>
   </si>
   <si>
     <t xml:space="preserve">2.08706736564636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07219743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12158632278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1401731967926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12424159049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362075805664</t>
+    <t xml:space="preserve">2.07219767570496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.121586561203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017367362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1242413520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362051963806</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582522392273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05307984352112</t>
+    <t xml:space="preserve">2.05307960510254</t>
   </si>
   <si>
     <t xml:space="preserve">2.0684802532196</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06901144981384</t>
+    <t xml:space="preserve">2.06901121139526</t>
   </si>
   <si>
     <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12477254867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16141557693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15557432174683</t>
+    <t xml:space="preserve">2.1247730255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16141581535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15557408332825</t>
   </si>
   <si>
     <t xml:space="preserve">2.17734789848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24373054504395</t>
+    <t xml:space="preserve">2.24373030662537</t>
   </si>
   <si>
     <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29418158531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461223602295</t>
+    <t xml:space="preserve">2.29418110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2575376033783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461199760437</t>
   </si>
   <si>
     <t xml:space="preserve">2.21452212333679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2463858127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098468780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073426246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34888005256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604479789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44925093650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5028874874115</t>
+    <t xml:space="preserve">2.22514343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638533592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098492622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888052940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4492506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288796424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.51775765419006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5655529499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997183799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547255516052</t>
+    <t xml:space="preserve">2.56555318832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61547231674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.66555047035217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66718316078186</t>
+    <t xml:space="preserve">2.66718292236328</t>
   </si>
   <si>
     <t xml:space="preserve">2.70147585868835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68786787986755</t>
+    <t xml:space="preserve">2.6878674030304</t>
   </si>
   <si>
     <t xml:space="preserve">2.72161555290222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79346632957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894026756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.989422082901</t>
+    <t xml:space="preserve">2.79346609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894074440002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98942232131958</t>
   </si>
   <si>
     <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94587659835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84136652946472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91757202148438</t>
+    <t xml:space="preserve">2.94587707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8413667678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91757225990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.90668559074402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959342956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685646057129</t>
+    <t xml:space="preserve">2.89797639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959366798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516103744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685622215271</t>
   </si>
   <si>
     <t xml:space="preserve">2.69548797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531686782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289036750793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84789848327637</t>
+    <t xml:space="preserve">2.78693413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531710624695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289060592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84789872169495</t>
   </si>
   <si>
     <t xml:space="preserve">2.77604794502258</t>
@@ -362,223 +362,223 @@
     <t xml:space="preserve">2.91974949836731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99159932136536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418141365051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813151359558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97853589057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820966720581</t>
+    <t xml:space="preserve">2.97200441360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99159979820251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418165206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97853636741638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03514552116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820942878723</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1570737361908</t>
+    <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
     <t xml:space="preserve">3.29859805107117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30730748176575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920663356781</t>
+    <t xml:space="preserve">3.30730700492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214425086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29206585884094</t>
   </si>
   <si>
     <t xml:space="preserve">3.28771185874939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26158428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416565895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28988909721375</t>
+    <t xml:space="preserve">3.26158404350281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
     <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25722980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26593899726868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1744921207428</t>
+    <t xml:space="preserve">3.2572295665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593852043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17449259757996</t>
   </si>
   <si>
     <t xml:space="preserve">3.25505208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25940704345703</t>
+    <t xml:space="preserve">3.25940680503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35085344314575</t>
+    <t xml:space="preserve">3.35085296630859</t>
   </si>
   <si>
     <t xml:space="preserve">3.34432125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32472586631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28553414344788</t>
+    <t xml:space="preserve">3.32472538948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28553462028503</t>
   </si>
   <si>
     <t xml:space="preserve">3.27247071266174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35303068161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037138938904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682542800903</t>
+    <t xml:space="preserve">3.35303020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682518959045</t>
   </si>
   <si>
     <t xml:space="preserve">3.31383919715881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3094847202301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15054202079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18973302841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20932912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2006196975708</t>
+    <t xml:space="preserve">3.30948448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18973326683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2093288898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20061993598938</t>
   </si>
   <si>
     <t xml:space="preserve">3.22239279747009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09175539016724</t>
+    <t xml:space="preserve">3.09175491333008</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343482017517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26376175880432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497417449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262606620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141293525696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59253263473511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90823984146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01057243347168</t>
+    <t xml:space="preserve">3.26376104354858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497465133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141317367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59253239631653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962431907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824007987976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057291030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.09330987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11508321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19346523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33716678619385</t>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831799507141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11508274078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19346570968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.23483371734619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26313829421997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47433567047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68988847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65722894668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6463418006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95334100723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245433807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72037029266357</t>
+    <t xml:space="preserve">4.26313877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47433614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68988800048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65722799301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64634227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245386123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
     <t xml:space="preserve">4.74214315414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73778867721558</t>
+    <t xml:space="preserve">4.73778820037842</t>
   </si>
   <si>
     <t xml:space="preserve">4.64416456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57231378555298</t>
+    <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.37418031692505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35023021697998</t>
+    <t xml:space="preserve">4.35022974014282</t>
   </si>
   <si>
     <t xml:space="preserve">4.34152126312256</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">4.22830152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19128704071045</t>
+    <t xml:space="preserve">4.19128799438477</t>
   </si>
   <si>
     <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24571990966797</t>
+    <t xml:space="preserve">4.22612428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24572038650513</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547088623047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35458469390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3393440246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63763284683228</t>
+    <t xml:space="preserve">4.35458421707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33934354782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940618515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63763236999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.63545560836792</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">4.72254753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408712387085</t>
+    <t xml:space="preserve">4.59408760070801</t>
   </si>
   <si>
     <t xml:space="preserve">4.6637601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58973169326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51135015487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5244140625</t>
+    <t xml:space="preserve">4.58973217010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134967803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52441358566284</t>
   </si>
   <si>
     <t xml:space="preserve">4.73343372344971</t>
@@ -653,58 +653,58 @@
     <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74649715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609373092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921932220459</t>
+    <t xml:space="preserve">4.74649667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921979904175</t>
   </si>
   <si>
     <t xml:space="preserve">5.38662195205688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25162982940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22985649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22767877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607749938965</t>
+    <t xml:space="preserve">5.29082059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25162935256958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22985601425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607797622681</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010551452637</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22550201416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27557992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31041622161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17107009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14494180679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979480743408</t>
+    <t xml:space="preserve">5.225501537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27557897567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31041574478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17106914520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14494228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979433059692</t>
   </si>
   <si>
     <t xml:space="preserve">5.09050941467285</t>
@@ -716,31 +716,31 @@
     <t xml:space="preserve">5.11445999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10139608383179</t>
+    <t xml:space="preserve">5.1013970375061</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268760681152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12752294540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663675308228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95769548416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736806869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98817682266235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584518432617</t>
+    <t xml:space="preserve">5.12752389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478740692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95769453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98817729949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88584423065186</t>
   </si>
   <si>
     <t xml:space="preserve">4.8662486076355</t>
@@ -749,31 +749,31 @@
     <t xml:space="preserve">4.85536193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84665298461914</t>
+    <t xml:space="preserve">4.8466534614563</t>
   </si>
   <si>
     <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561191558838</t>
+    <t xml:space="preserve">4.73561143875122</t>
   </si>
   <si>
     <t xml:space="preserve">4.79004383087158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7443208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738430023193</t>
+    <t xml:space="preserve">4.74431991577148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738382339478</t>
   </si>
   <si>
     <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82052564620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91850423812866</t>
+    <t xml:space="preserve">4.82052516937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91850328445435</t>
   </si>
   <si>
     <t xml:space="preserve">5.1384105682373</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">5.08397817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19719743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09486389160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710329055786</t>
+    <t xml:space="preserve">5.19719648361206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881494522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486532211304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170679092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444375991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4171028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209589004517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68273305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63918685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94400787353516</t>
+    <t xml:space="preserve">5.6827335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94400882720947</t>
   </si>
   <si>
     <t xml:space="preserve">6.11383724212646</t>
@@ -830,46 +830,46 @@
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329278945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957548141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89610767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97666788101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09641933441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94836282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9897313117981</t>
+    <t xml:space="preserve">5.76329374313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957643508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89610815048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97666835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09641885757446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94836330413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98973226547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.00497245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98755407333374</t>
+    <t xml:space="preserve">5.9875545501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05722713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08335447311401</t>
+    <t xml:space="preserve">6.05722808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08335494995117</t>
   </si>
   <si>
     <t xml:space="preserve">5.96360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07464599609375</t>
+    <t xml:space="preserve">6.07464551925659</t>
   </si>
   <si>
     <t xml:space="preserve">6.13996458053589</t>
@@ -878,58 +878,58 @@
     <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26842546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276418685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848714828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80403852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01088190078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06531429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756944656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425699234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392910003662</t>
+    <t xml:space="preserve">6.26842594146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52969980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80403900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201711654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06531381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11756896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3200569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321401596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29393005371094</t>
   </si>
   <si>
     <t xml:space="preserve">7.37666702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28522062301636</t>
+    <t xml:space="preserve">7.36360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852201461792</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481576919556</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">7.19595146179199</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705602645874</t>
+    <t xml:space="preserve">6.46655893325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2270565032959</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309017181396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4012393951416</t>
+    <t xml:space="preserve">6.40123987197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.61243772506714</t>
@@ -956,106 +956,106 @@
     <t xml:space="preserve">6.49704122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52316856384277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57760095596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52464389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45403623580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774116516113</t>
+    <t xml:space="preserve">6.52316808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57760047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52464437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56215476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45403575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774164199829</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652631759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58422040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50478601455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093849182129</t>
+    <t xml:space="preserve">6.76294755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252359390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58421993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50478553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093801498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694980621338</t>
+    <t xml:space="preserve">6.35694932937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43417739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33267831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37460136413574</t>
+    <t xml:space="preserve">6.4341778755188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826566696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3746018409729</t>
   </si>
   <si>
     <t xml:space="preserve">6.16057014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1429181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757102966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91344118118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240907669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78546333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95977783203125</t>
+    <t xml:space="preserve">6.14291858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9575719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91344165802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240955352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771314620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95977830886841</t>
   </si>
   <si>
     <t xml:space="preserve">5.9200611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93330049514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94212532043457</t>
+    <t xml:space="preserve">5.93329954147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94212579727173</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621406555176</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">5.8472466468811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98846244812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720363616943</t>
+    <t xml:space="preserve">5.98846292495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720411300659</t>
   </si>
   <si>
     <t xml:space="preserve">5.50744438171387</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7369213104248</t>
+    <t xml:space="preserve">5.73692083358765</t>
   </si>
   <si>
     <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89137601852417</t>
+    <t xml:space="preserve">5.89137649536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.71485567092896</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">5.72147560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59129190444946</t>
+    <t xml:space="preserve">5.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">5.55819368362427</t>
@@ -1103,64 +1103,64 @@
     <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54495429992676</t>
+    <t xml:space="preserve">5.5449538230896</t>
   </si>
   <si>
     <t xml:space="preserve">5.4434552192688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932489395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199914932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56040000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096561431885</t>
+    <t xml:space="preserve">5.45007514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932537078857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41918277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56040096282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.52730226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45890045166016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41256475448608</t>
+    <t xml:space="preserve">5.45890140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41256427764893</t>
   </si>
   <si>
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922578811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912715911865</t>
+    <t xml:space="preserve">5.56922626495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912763595581</t>
   </si>
   <si>
     <t xml:space="preserve">5.66410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8031153678894</t>
+    <t xml:space="preserve">5.80311584472656</t>
   </si>
   <si>
     <t xml:space="preserve">5.86931133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030042648315</t>
+    <t xml:space="preserve">5.73030090332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.08554935455322</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96860361099243</t>
+    <t xml:space="preserve">5.96860456466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.80532264709473</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">5.63762760162354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5648136138916</t>
+    <t xml:space="preserve">5.56481313705444</t>
   </si>
   <si>
     <t xml:space="preserve">5.52068328857422</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">5.47875928878784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4942045211792</t>
+    <t xml:space="preserve">5.49420499801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
@@ -1187,13 +1187,13 @@
     <t xml:space="preserve">5.29782581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22942447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369548797607</t>
+    <t xml:space="preserve">5.22942352294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045610427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369644165039</t>
   </si>
   <si>
     <t xml:space="preserve">5.41477108001709</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">5.39711809158325</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796745300293</t>
+    <t xml:space="preserve">5.27796792984009</t>
   </si>
   <si>
     <t xml:space="preserve">5.22280502319336</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">5.14116382598877</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11909914016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20735931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16764163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13233852386475</t>
+    <t xml:space="preserve">5.11909866333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.207359790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16764116287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03745746612549</t>
+    <t xml:space="preserve">5.0374584197998</t>
   </si>
   <si>
     <t xml:space="preserve">5.00656700134277</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">4.9646430015564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126197814941</t>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126245498657</t>
   </si>
   <si>
     <t xml:space="preserve">5.04849004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19412040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22501087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24487018585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689186096191</t>
+    <t xml:space="preserve">5.19411993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576017379761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22501134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689233779907</t>
   </si>
   <si>
     <t xml:space="preserve">5.03083801269531</t>
@@ -1268,103 +1268,103 @@
     <t xml:space="preserve">4.72634029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71089458465576</t>
+    <t xml:space="preserve">4.71089506149292</t>
   </si>
   <si>
     <t xml:space="preserve">4.65131902694702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93154573440552</t>
+    <t xml:space="preserve">4.93154525756836</t>
   </si>
   <si>
     <t xml:space="preserve">5.21839189529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6045298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8119421005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8450403213501</t>
+    <t xml:space="preserve">5.60453081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81194257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84503984451294</t>
   </si>
   <si>
     <t xml:space="preserve">5.76781177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90461587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6398344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940996170044</t>
+    <t xml:space="preserve">5.904616355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489772796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856155395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63983488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6994104385376</t>
   </si>
   <si>
     <t xml:space="preserve">5.58467197418213</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366788864136</t>
+    <t xml:space="preserve">6.02376651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366836547852</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348419189453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14071130752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419095993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
+    <t xml:space="preserve">6.14071178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479909896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.8097357749939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020227432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354124069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65086698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776971817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935338973999</t>
+    <t xml:space="preserve">5.88034391403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518148422241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935386657715</t>
   </si>
   <si>
     <t xml:space="preserve">5.85607290267944</t>
@@ -1373,16 +1373,16 @@
     <t xml:space="preserve">5.71926879882812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84283304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325927734375</t>
+    <t xml:space="preserve">5.84283256530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03259229660034</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95315790176392</t>
+    <t xml:space="preserve">5.95315837860107</t>
   </si>
   <si>
     <t xml:space="preserve">5.94433259963989</t>
@@ -1394,16 +1394,16 @@
     <t xml:space="preserve">6.28413486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1693959236145</t>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243757247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
   </si>
   <si>
     <t xml:space="preserve">6.09878778457642</t>
@@ -1415,19 +1415,19 @@
     <t xml:space="preserve">5.55598735809326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11202669143677</t>
+    <t xml:space="preserve">6.11202764511108</t>
   </si>
   <si>
     <t xml:space="preserve">5.9222674369812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79429054260254</t>
+    <t xml:space="preserve">5.79429006576538</t>
   </si>
   <si>
     <t xml:space="preserve">5.67072582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68396425247192</t>
+    <t xml:space="preserve">5.68396472930908</t>
   </si>
   <si>
     <t xml:space="preserve">5.42800951004028</t>
@@ -1439,19 +1439,19 @@
     <t xml:space="preserve">5.87372446060181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97963666915894</t>
+    <t xml:space="preserve">5.97963762283325</t>
   </si>
   <si>
     <t xml:space="preserve">5.96198511123657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089691162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474395751953</t>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474348068237</t>
   </si>
   <si>
     <t xml:space="preserve">6.72543668746948</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">6.9284348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90636968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697830200195</t>
+    <t xml:space="preserve">6.90637063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495662689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697877883911</t>
   </si>
   <si>
     <t xml:space="preserve">7.10054302215576</t>
@@ -1490,31 +1490,31 @@
     <t xml:space="preserve">7.0475869178772</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11378192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4933009147644</t>
+    <t xml:space="preserve">7.11378240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082630157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49330043792725</t>
   </si>
   <si>
     <t xml:space="preserve">7.32560682296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
+    <t xml:space="preserve">7.18439102172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.440345287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147602081299</t>
   </si>
   <si>
     <t xml:space="preserve">7.25941181182861</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12260818481445</t>
+    <t xml:space="preserve">7.12260770797729</t>
   </si>
   <si>
     <t xml:space="preserve">7.06523847579956</t>
@@ -1523,46 +1523,46 @@
     <t xml:space="preserve">7.25058555603027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21528053283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321537017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46240997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5374321937561</t>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969556808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6212797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743171691895</t>
   </si>
   <si>
     <t xml:space="preserve">7.40062856674194</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55508279800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710590362549</t>
+    <t xml:space="preserve">7.55508470535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710638046265</t>
   </si>
   <si>
     <t xml:space="preserve">7.38738918304443</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06965160369873</t>
+    <t xml:space="preserve">7.06965208053589</t>
   </si>
   <si>
     <t xml:space="preserve">6.62835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84017515182495</t>
+    <t xml:space="preserve">6.84017467498779</t>
   </si>
   <si>
     <t xml:space="preserve">6.63717603683472</t>
@@ -1571,31 +1571,31 @@
     <t xml:space="preserve">6.51802539825439</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61952447891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450225830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425085067749</t>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
   </si>
   <si>
     <t xml:space="preserve">6.60163354873657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63294172286987</t>
+    <t xml:space="preserve">6.63294124603271</t>
   </si>
   <si>
     <t xml:space="preserve">6.54796171188354</t>
@@ -1604,16 +1604,16 @@
     <t xml:space="preserve">6.65977811813354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534440994263</t>
+    <t xml:space="preserve">6.579270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534488677979</t>
   </si>
   <si>
     <t xml:space="preserve">6.71344947814941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75370407104492</t>
+    <t xml:space="preserve">6.75370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">6.75817632675171</t>
@@ -1625,46 +1625,43 @@
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
+    <t xml:space="preserve">6.48087167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825437545776</t>
   </si>
   <si>
     <t xml:space="preserve">6.3198561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22593069076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171207427979</t>
+    <t xml:space="preserve">6.22593116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171159744263</t>
   </si>
   <si>
     <t xml:space="preserve">6.14095020294189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18120336532593</t>
+    <t xml:space="preserve">6.18120384216309</t>
   </si>
   <si>
     <t xml:space="preserve">6.20356750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34669160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829339981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.2125129699707</t>
@@ -1676,7 +1673,7 @@
     <t xml:space="preserve">6.58821535110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48981714248657</t>
+    <t xml:space="preserve">6.48981761932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.53007125854492</t>
@@ -1685,13 +1682,13 @@
     <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44509077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141798019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4003643989563</t>
+    <t xml:space="preserve">6.44509029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40036392211914</t>
   </si>
   <si>
     <t xml:space="preserve">6.37352800369263</t>
@@ -1700,13 +1697,13 @@
     <t xml:space="preserve">6.42720031738281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43167304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323486328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
   </si>
   <si>
     <t xml:space="preserve">6.23934841156006</t>
@@ -1715,7 +1712,7 @@
     <t xml:space="preserve">6.19014930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27960300445557</t>
+    <t xml:space="preserve">6.27960252761841</t>
   </si>
   <si>
     <t xml:space="preserve">6.46298170089722</t>
@@ -1727,13 +1724,13 @@
     <t xml:space="preserve">6.1006965637207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39589166641235</t>
+    <t xml:space="preserve">6.3958911895752</t>
   </si>
   <si>
     <t xml:space="preserve">6.18567657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98440742492676</t>
+    <t xml:space="preserve">5.98440837860107</t>
   </si>
   <si>
     <t xml:space="preserve">5.47452545166016</t>
@@ -1745,10 +1742,10 @@
     <t xml:space="preserve">5.24194765090942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08093166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358846664429</t>
+    <t xml:space="preserve">5.08093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358894348145</t>
   </si>
   <si>
     <t xml:space="preserve">5.13013172149658</t>
@@ -1757,6 +1754,9 @@
     <t xml:space="preserve">5.01831483840942</t>
   </si>
   <si>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
@@ -1769,61 +1769,61 @@
     <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73653888702393</t>
+    <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
     <t xml:space="preserve">4.58894062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61577606201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74995565414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417427062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201690673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12825727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04104089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05445861816406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829606056213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01867723464966</t>
+    <t xml:space="preserve">4.61577558517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74995517730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417474746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201595306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12825679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20876550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483860015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04104042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05445766448975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829653739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15509366989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13049411773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0186767578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.86884307861328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70559167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702714920044</t>
+    <t xml:space="preserve">3.70559144020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702691078186</t>
   </si>
   <si>
     <t xml:space="preserve">3.81740784645081</t>
@@ -1832,19 +1832,19 @@
     <t xml:space="preserve">3.73466444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648036956787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500515937805</t>
+    <t xml:space="preserve">3.83753514289856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648013114929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500587463379</t>
   </si>
   <si>
     <t xml:space="preserve">4.15732955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00302314758301</t>
+    <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
     <t xml:space="preserve">3.92475152015686</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">3.9314603805542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94264149665833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86213421821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
+    <t xml:space="preserve">3.9426417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331628799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424376487732</t>
   </si>
   <si>
     <t xml:space="preserve">3.45512294769287</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">3.35896110534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24267220497131</t>
+    <t xml:space="preserve">3.24267244338989</t>
   </si>
   <si>
     <t xml:space="preserve">3.03245782852173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140329360962</t>
+    <t xml:space="preserve">3.04140305519104</t>
   </si>
   <si>
     <t xml:space="preserve">3.16216444969177</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">3.38803315162659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26950788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22701787948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45288681983948</t>
+    <t xml:space="preserve">3.26950812339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22701811790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.3947422504425</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">3.48866820335388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5155041217804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870722770691</t>
+    <t xml:space="preserve">3.51550388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870698928833</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714493751526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11072897911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92735028266907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182301521301</t>
+    <t xml:space="preserve">3.1107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92735052108765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182277679443</t>
   </si>
   <si>
     <t xml:space="preserve">3.01009440422058</t>
@@ -1928,34 +1928,34 @@
     <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03916668891907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95642280578613</t>
+    <t xml:space="preserve">3.03916645050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95642256736755</t>
   </si>
   <si>
     <t xml:space="preserve">2.88486003875732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92511391639709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77751612663269</t>
+    <t xml:space="preserve">2.92511415481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77751660346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.74844408035278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869819641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83342504501343</t>
+    <t xml:space="preserve">2.78869795799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83342480659485</t>
   </si>
   <si>
     <t xml:space="preserve">2.88933253288269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0727117061615</t>
+    <t xml:space="preserve">3.07271146774292</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625648498535</t>
@@ -1970,37 +1970,37 @@
     <t xml:space="preserve">3.1599280834198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22254538536072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23596358299255</t>
+    <t xml:space="preserve">3.22254514694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23596334457397</t>
   </si>
   <si>
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347286224365</t>
+    <t xml:space="preserve">3.19347310066223</t>
   </si>
   <si>
     <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54233980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5333948135376</t>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53339457511902</t>
   </si>
   <si>
     <t xml:space="preserve">3.49537706375122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61166596412659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533803939819</t>
+    <t xml:space="preserve">3.61166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533780097961</t>
   </si>
   <si>
     <t xml:space="preserve">3.57588481903076</t>
@@ -2021,55 +2021,55 @@
     <t xml:space="preserve">3.52444958686829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58483004570007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6944100856781</t>
+    <t xml:space="preserve">3.58483028411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69441032409668</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61390233039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399036407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567923545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77268171310425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306193351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.857661485672</t>
+    <t xml:space="preserve">3.61390256881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398988723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567899703979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77268147468567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766172409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.94040608406067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99184155464172</t>
+    <t xml:space="preserve">3.99184131622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.07011318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13273000717163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09247589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18863773345947</t>
+    <t xml:space="preserve">4.13272953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09247636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18863725662231</t>
   </si>
   <si>
     <t xml:space="preserve">3.94935059547424</t>
@@ -2081,40 +2081,40 @@
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842383384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112773895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28256368637085</t>
+    <t xml:space="preserve">3.97842359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28256416320801</t>
   </si>
   <si>
     <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42792463302612</t>
+    <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.35412645339966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16627502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20429229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2780909538269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23783731460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29150915145874</t>
+    <t xml:space="preserve">4.1662745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20429277420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27809143066406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205640792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23783683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29150867462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901819229126</t>
@@ -2123,79 +2123,79 @@
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349187850952</t>
+    <t xml:space="preserve">4.25349140167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.19982004165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07458543777466</t>
+    <t xml:space="preserve">4.07458591461182</t>
   </si>
   <si>
     <t xml:space="preserve">4.15285682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914548873901</t>
+    <t xml:space="preserve">4.1864013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914596557617</t>
   </si>
   <si>
     <t xml:space="preserve">3.97171473503113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93369650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015244483948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631428718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880310058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03656768798828</t>
+    <t xml:space="preserve">3.93369698524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631500244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03656721115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7682089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77491760253906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65191984176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85095262527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09918546676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95693063735962</t>
+    <t xml:space="preserve">3.9180428981781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820874214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77491736412048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65192008018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85095286369324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0991849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693111419678</t>
   </si>
   <si>
     <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626088142395</t>
+    <t xml:space="preserve">3.76229023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626111984253</t>
   </si>
   <si>
     <t xml:space="preserve">3.7645800113678</t>
@@ -2207,43 +2207,43 @@
     <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73252129554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84243655204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487168312073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96608996391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739322662354</t>
+    <t xml:space="preserve">3.73252153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84243631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220454216003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96609044075012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739346504211</t>
   </si>
   <si>
     <t xml:space="preserve">3.95006108283997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9065535068512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04165601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19736957550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1538610458374</t>
+    <t xml:space="preserve">3.87449479103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655326843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04165649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15386152267456</t>
   </si>
   <si>
     <t xml:space="preserve">4.09203433990479</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">4.11264276504517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10119390487671</t>
+    <t xml:space="preserve">4.10119342803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.14470195770264</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">4.18820953369141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27751588821411</t>
+    <t xml:space="preserve">4.27751493453979</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438472747803</t>
@@ -2279,16 +2279,16 @@
     <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2454571723938</t>
+    <t xml:space="preserve">4.24545669555664</t>
   </si>
   <si>
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22255754470825</t>
+    <t xml:space="preserve">4.23858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22255802154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.19507884979248</t>
@@ -2297,28 +2297,28 @@
     <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997562408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09890413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16302108764648</t>
+    <t xml:space="preserve">4.17446994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997610092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15157079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">4.11035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12409210205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07600498199463</t>
+    <t xml:space="preserve">4.12409257888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
     <t xml:space="preserve">4.00730848312378</t>
@@ -2327,49 +2327,49 @@
     <t xml:space="preserve">4.05539512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97067022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94548082351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701609611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594365119934</t>
+    <t xml:space="preserve">3.97066974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.945481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594388961792</t>
   </si>
   <si>
     <t xml:space="preserve">3.876784324646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8515956401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235085487366</t>
+    <t xml:space="preserve">3.85159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9523503780365</t>
   </si>
   <si>
     <t xml:space="preserve">4.00043869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98212003707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13096237182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11493349075317</t>
+    <t xml:space="preserve">3.9821195602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13096284866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11493253707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.16760063171387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04394578933716</t>
+    <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
     <t xml:space="preserve">4.05310583114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18592023849487</t>
+    <t xml:space="preserve">4.18591928482056</t>
   </si>
   <si>
     <t xml:space="preserve">4.1355414390564</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">4.06226587295532</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34392166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33705282211304</t>
+    <t xml:space="preserve">4.34392213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33705234527588</t>
   </si>
   <si>
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60267972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00112104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17515277862549</t>
+    <t xml:space="preserve">4.60267925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00112056732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17515230178833</t>
   </si>
   <si>
     <t xml:space="preserve">5.33086538314819</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">5.35834360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62855052947998</t>
+    <t xml:space="preserve">5.62855100631714</t>
   </si>
   <si>
     <t xml:space="preserve">5.48657751083374</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">5.48199796676636</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26674795150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27590799331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36292314529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44993829727173</t>
+    <t xml:space="preserve">5.26674842834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27590751647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36292266845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44993877410889</t>
   </si>
   <si>
     <t xml:space="preserve">5.34460496902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47283744812012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45909881591797</t>
+    <t xml:space="preserve">5.47283792495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45909833908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.55985450744629</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">5.69724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72930574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.7293062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92623567581177</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304533004761</t>
@@ -2468,22 +2468,22 @@
     <t xml:space="preserve">5.72472620010376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67892789840698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71556711196899</t>
+    <t xml:space="preserve">5.67892837524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71556663513184</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82090187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875745773315</t>
+    <t xml:space="preserve">5.71098661422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82090139389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
     <t xml:space="preserve">6.04989051818848</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">6.12316751480103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22392225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652830123901</t>
+    <t xml:space="preserve">6.22392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652877807617</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241086959839</t>
+    <t xml:space="preserve">6.02241134643555</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
@@ -2513,46 +2513,46 @@
     <t xml:space="preserve">7.10324001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28643131256104</t>
+    <t xml:space="preserve">7.19941520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28643083572388</t>
   </si>
   <si>
     <t xml:space="preserve">7.61159610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61617469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600568771362</t>
+    <t xml:space="preserve">7.61617517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235179901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600616455078</t>
   </si>
   <si>
     <t xml:space="preserve">7.67113304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62533473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735649108887</t>
+    <t xml:space="preserve">7.6253342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
     <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41924571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35512781143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29101133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727127075195</t>
+    <t xml:space="preserve">7.41924524307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35512733459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29101181030273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727174758911</t>
   </si>
   <si>
     <t xml:space="preserve">7.11697959899902</t>
@@ -2561,7 +2561,7 @@
     <t xml:space="preserve">7.15361785888672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26811265945435</t>
+    <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
     <t xml:space="preserve">7.39634561538696</t>
@@ -2579,19 +2579,19 @@
     <t xml:space="preserve">7.85890436172485</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579875946045</t>
+    <t xml:space="preserve">7.67571306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579828262329</t>
   </si>
   <si>
     <t xml:space="preserve">7.66655349731445</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36428689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130395889282</t>
+    <t xml:space="preserve">7.36428737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130443572998</t>
   </si>
   <si>
     <t xml:space="preserve">7.12155914306641</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">7.41466522216797</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25895309448242</t>
+    <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
     <t xml:space="preserve">7.30475044250488</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4375638961792</t>
+    <t xml:space="preserve">7.43756341934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.48794174194336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52000045776367</t>
+    <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">7.17651700973511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02996349334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74143743515015</t>
+    <t xml:space="preserve">7.02996397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51244878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7414379119873</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639482498169</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61778354644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538442611694</t>
+    <t xml:space="preserve">6.6177830696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538347244263</t>
   </si>
   <si>
     <t xml:space="preserve">6.89257001876831</t>
@@ -2663,64 +2663,64 @@
     <t xml:space="preserve">6.828453540802</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80097436904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67732000350952</t>
+    <t xml:space="preserve">6.80097389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67732095718384</t>
   </si>
   <si>
     <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76433706283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63610219955444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11858654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.967453956604</t>
+    <t xml:space="preserve">6.76433658599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63610172271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11858701705933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96745491027832</t>
   </si>
   <si>
     <t xml:space="preserve">5.78884267807007</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63771057128906</t>
+    <t xml:space="preserve">5.63771104812622</t>
   </si>
   <si>
     <t xml:space="preserve">5.77052402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72014617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47741794586182</t>
+    <t xml:space="preserve">5.72014665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75381231307983</t>
+    <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.59809970855713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63931846618652</t>
+    <t xml:space="preserve">4.63931798934937</t>
   </si>
   <si>
     <t xml:space="preserve">4.21110820770264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382479667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32034111022949</t>
+    <t xml:space="preserve">3.81495714187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382455825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32034134864807</t>
   </si>
   <si>
     <t xml:space="preserve">3.22416567802429</t>
@@ -2735,43 +2735,43 @@
     <t xml:space="preserve">3.44399499893188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356913566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304545402527</t>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304497718811</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344718933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50353264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069435119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61802697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70962285995483</t>
+    <t xml:space="preserve">3.50353240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069458961487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61802673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70962262153625</t>
   </si>
   <si>
     <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79663825035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06684589385986</t>
+    <t xml:space="preserve">3.79663848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168086051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06684541702271</t>
   </si>
   <si>
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3828501701355</t>
+    <t xml:space="preserve">4.38285064697266</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722278594971</t>
@@ -2783,31 +2783,31 @@
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4881854057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45612716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35995197296143</t>
+    <t xml:space="preserve">4.09432411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48818492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45612668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35995101928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26377630233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32331275939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35537147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957412719727</t>
+    <t xml:space="preserve">4.26377582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32331323623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35537195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957365036011</t>
   </si>
   <si>
     <t xml:space="preserve">4.30499410629272</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5248236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38743019104004</t>
+    <t xml:space="preserve">4.52482318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38742971420288</t>
   </si>
   <si>
     <t xml:space="preserve">4.42406845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75152254104614</t>
+    <t xml:space="preserve">4.75152206420898</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761251449585</t>
@@ -2858,31 +2858,31 @@
     <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16370296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471431732178</t>
+    <t xml:space="preserve">5.16370248794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93471384048462</t>
   </si>
   <si>
     <t xml:space="preserve">5.02630949020386</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19805145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25529861450195</t>
+    <t xml:space="preserve">5.19805097579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254529953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25529909133911</t>
   </si>
   <si>
     <t xml:space="preserve">5.39269161224365</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20950126647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1522536277771</t>
+    <t xml:space="preserve">5.20950031280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15225315093994</t>
   </si>
   <si>
     <t xml:space="preserve">5.14080429077148</t>
@@ -2894,10 +2894,10 @@
     <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.923264503479</t>
+    <t xml:space="preserve">5.09500646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92326402664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.01486015319824</t>
@@ -2909,58 +2909,58 @@
     <t xml:space="preserve">5.06065797805786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22095012664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07210683822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645484924316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935495376587</t>
+    <t xml:space="preserve">5.22094964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07210731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645580291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935400009155</t>
   </si>
   <si>
     <t xml:space="preserve">5.32399559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544445037842</t>
+    <t xml:space="preserve">5.33544492721558</t>
   </si>
   <si>
     <t xml:space="preserve">5.03775882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96906232833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616413116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84311819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181468963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9919605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00341033935547</t>
+    <t xml:space="preserve">5.08355760574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96906280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9805121421814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84311771392822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181516647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99196100234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00341081619263</t>
   </si>
   <si>
     <t xml:space="preserve">4.57978105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1904993057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21339845657349</t>
+    <t xml:space="preserve">4.19049978256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21339797973633</t>
   </si>
   <si>
     <t xml:space="preserve">4.08058500289917</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">4.34163236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61412906646729</t>
+    <t xml:space="preserve">4.61412954330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.54153490066528</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">5.62168073654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75907421112061</t>
+    <t xml:space="preserve">5.75907468795776</t>
   </si>
   <si>
     <t xml:space="preserve">5.73617506027222</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69037771224976</t>
+    <t xml:space="preserve">5.69037818908691</t>
   </si>
   <si>
     <t xml:space="preserve">5.64457988739014</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">5.70182704925537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81632137298584</t>
+    <t xml:space="preserve">5.816321849823</t>
   </si>
   <si>
     <t xml:space="preserve">6.14835596084595</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">6.19415378570557</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12545728683472</t>
+    <t xml:space="preserve">6.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">6.1598048210144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18270349502563</t>
+    <t xml:space="preserve">6.18270397186279</t>
   </si>
   <si>
     <t xml:space="preserve">6.07965898513794</t>
@@ -3044,7 +3044,7 @@
     <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444641113281</t>
+    <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.32009792327881</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48038911819458</t>
+    <t xml:space="preserve">6.48038959503174</t>
   </si>
   <si>
     <t xml:space="preserve">6.52618741989136</t>
@@ -3068,19 +3068,19 @@
     <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58343553543091</t>
+    <t xml:space="preserve">6.58343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169309616089</t>
+    <t xml:space="preserve">6.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894025802612</t>
+    <t xml:space="preserve">6.46894073486328</t>
   </si>
   <si>
     <t xml:space="preserve">6.29719877243042</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">6.20560359954834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42314291000366</t>
+    <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.50328922271729</t>
@@ -3098,49 +3098,49 @@
     <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51473808288574</t>
+    <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.78952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75517654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68648052215576</t>
+    <t xml:space="preserve">6.75517702102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6864800453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792985916138</t>
+    <t xml:space="preserve">6.77807569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792938232422</t>
   </si>
   <si>
     <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154678344727</t>
+    <t xml:space="preserve">6.37734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154726028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.3887939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5490870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86967134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78562688827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417850494385</t>
+    <t xml:space="preserve">6.54908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86967086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417802810669</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">8.06041431427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0260648727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911128997803</t>
+    <t xml:space="preserve">8.02606582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911033630371</t>
   </si>
   <si>
     <t xml:space="preserve">8.10621166229248</t>
@@ -3170,19 +3170,19 @@
     <t xml:space="preserve">8.03751564025879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00316619873047</t>
+    <t xml:space="preserve">8.00316715240479</t>
   </si>
   <si>
     <t xml:space="preserve">7.93447113037109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08331203460693</t>
+    <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.3123025894165</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085277557373</t>
+    <t xml:space="preserve">8.30085182189941</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940391540527</t>
@@ -3191,19 +3191,19 @@
     <t xml:space="preserve">8.33520126342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2779541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15200996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11766147613525</t>
+    <t xml:space="preserve">8.27795314788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15200901031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11766242980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.18635845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34665107727051</t>
+    <t xml:space="preserve">8.34665012359619</t>
   </si>
   <si>
     <t xml:space="preserve">8.23215675354004</t>
@@ -3212,16 +3212,16 @@
     <t xml:space="preserve">8.16345977783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591903686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
+    <t xml:space="preserve">8.07186412811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925712585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736980438232</t>
   </si>
   <si>
     <t xml:space="preserve">7.84287452697754</t>
@@ -3230,37 +3230,37 @@
     <t xml:space="preserve">7.92301988601685</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577272415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3809986114502</t>
+    <t xml:space="preserve">7.81997632980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577320098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099956512451</t>
   </si>
   <si>
     <t xml:space="preserve">9.15956211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99926948547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20535945892334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48014640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65356349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60731887817383</t>
+    <t xml:space="preserve">8.99926853179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20535850524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48014545440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.653564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073596954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71137046813965</t>
+    <t xml:space="preserve">9.71136951446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
@@ -3269,10 +3269,10 @@
     <t xml:space="preserve">10.2894277572632</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3009872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241100311279</t>
+    <t xml:space="preserve">10.3009881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
@@ -3281,28 +3281,28 @@
     <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437717437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4975290298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3356714248657</t>
+    <t xml:space="preserve">10.5437726974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4975280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628448486328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4050388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3703565597534</t>
+    <t xml:space="preserve">10.4050378799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7403125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4744062423706</t>
+    <t xml:space="preserve">10.4744052886963</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819169998169</t>
@@ -3314,7 +3314,7 @@
     <t xml:space="preserve">10.2663059234619</t>
   </si>
   <si>
-    <t xml:space="preserve">10.393479347229</t>
+    <t xml:space="preserve">10.3934774398804</t>
   </si>
   <si>
     <t xml:space="preserve">10.0582036972046</t>
@@ -3323,13 +3323,13 @@
     <t xml:space="preserve">9.9541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0235214233398</t>
+    <t xml:space="preserve">10.0235204696655</t>
   </si>
   <si>
     <t xml:space="preserve">10.1506938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697650909424</t>
+    <t xml:space="preserve">10.0697660446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.092887878418</t>
@@ -3338,7 +3338,7 @@
     <t xml:space="preserve">10.1160097122192</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2547426223755</t>
+    <t xml:space="preserve">10.2547435760498</t>
   </si>
   <si>
     <t xml:space="preserve">10.2200603485107</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">10.4859666824341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1853771209717</t>
+    <t xml:space="preserve">10.185378074646</t>
   </si>
   <si>
     <t xml:space="preserve">10.0350818634033</t>
@@ -3356,13 +3356,13 @@
     <t xml:space="preserve">10.416600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1738157272339</t>
+    <t xml:space="preserve">10.1738147735596</t>
   </si>
   <si>
     <t xml:space="preserve">10.1391315460205</t>
   </si>
   <si>
-    <t xml:space="preserve">11.191198348999</t>
+    <t xml:space="preserve">11.1911973953247</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056600570679</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611543655396</t>
+    <t xml:space="preserve">11.5611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426568984985</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796537399292</t>
+    <t xml:space="preserve">11.5796527862549</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
@@ -3398,28 +3398,28 @@
     <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6536426544189</t>
+    <t xml:space="preserve">11.6536436080933</t>
   </si>
   <si>
     <t xml:space="preserve">11.3946743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4686641693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0975923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8571195602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0605964660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0420989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455749511719</t>
+    <t xml:space="preserve">11.4686651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0975914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.857120513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0605955123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0420980453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455739974976</t>
   </si>
   <si>
     <t xml:space="preserve">12.3010683059692</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">11.8941164016724</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299945831299</t>
+    <t xml:space="preserve">12.9299955368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144161224365</t>
@@ -3437,13 +3437,13 @@
     <t xml:space="preserve">13.854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069044113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.151969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5034294128418</t>
+    <t xml:space="preserve">13.7069034576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1519689559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5034284591675</t>
   </si>
   <si>
     <t xml:space="preserve">13.817892074585</t>
@@ -3455,16 +3455,16 @@
     <t xml:space="preserve">14.631796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0398654937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7438993453979</t>
+    <t xml:space="preserve">14.0398664474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7439002990723</t>
   </si>
   <si>
     <t xml:space="preserve">13.4109392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7623977661133</t>
+    <t xml:space="preserve">13.7623987197876</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294366836548</t>
@@ -3473,13 +3473,13 @@
     <t xml:space="preserve">13.0409822463989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4860458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9669904708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0964756011963</t>
+    <t xml:space="preserve">12.4860467910767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9669914245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.096474647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.8929986953735</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">12.9114971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0779781341553</t>
+    <t xml:space="preserve">13.077977180481</t>
   </si>
   <si>
     <t xml:space="preserve">14.4468183517456</t>
@@ -3515,10 +3515,10 @@
     <t xml:space="preserve">16.537073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520946502686</t>
+    <t xml:space="preserve">16.2596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520965576172</t>
   </si>
   <si>
     <t xml:space="preserve">16.0191345214844</t>
@@ -3527,28 +3527,28 @@
     <t xml:space="preserve">15.7971620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1486206054688</t>
+    <t xml:space="preserve">16.1486186981201</t>
   </si>
   <si>
     <t xml:space="preserve">16.0006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.908148765564</t>
+    <t xml:space="preserve">15.9081478118896</t>
   </si>
   <si>
     <t xml:space="preserve">15.5196952819824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8341588973999</t>
+    <t xml:space="preserve">15.4642009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416667938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8341579437256</t>
   </si>
   <si>
     <t xml:space="preserve">14.9092655181885</t>
@@ -3557,34 +3557,34 @@
     <t xml:space="preserve">14.4283208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5023126602173</t>
+    <t xml:space="preserve">14.502311706543</t>
   </si>
   <si>
     <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6329135894775</t>
+    <t xml:space="preserve">13.6329126358032</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369474411011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.928879737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0583639144897</t>
+    <t xml:space="preserve">13.3369483947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9288787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8918828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098234176636</t>
+    <t xml:space="preserve">13.8918838500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098224639893</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7808952331543</t>
+    <t xml:space="preserve">13.7808961868286</t>
   </si>
   <si>
     <t xml:space="preserve">13.2629566192627</t>
@@ -3602,22 +3602,22 @@
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924398422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3554458618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9658756256104</t>
+    <t xml:space="preserve">13.3924407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3554449081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.965874671936</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2803373336792</t>
+    <t xml:space="preserve">14.2988367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2803382873535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1138582229614</t>
@@ -3629,10 +3629,10 @@
     <t xml:space="preserve">13.1334714889526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4479360580444</t>
+    <t xml:space="preserve">13.0594797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4479351043701</t>
   </si>
   <si>
     <t xml:space="preserve">12.2085790634155</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">12.3935575485229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1889657974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4664335250854</t>
+    <t xml:space="preserve">13.18896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8190078735352</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9126129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6340293884277</t>
+    <t xml:space="preserve">11.9126138687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6340284347534</t>
   </si>
   <si>
     <t xml:space="preserve">12.3380641937256</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051012039185</t>
+    <t xml:space="preserve">12.0051021575928</t>
   </si>
   <si>
     <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0236005783081</t>
+    <t xml:space="preserve">12.0236015319824</t>
   </si>
   <si>
     <t xml:space="preserve">11.9681062698364</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">10.8582353591919</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5067768096924</t>
+    <t xml:space="preserve">10.5067777633667</t>
   </si>
   <si>
     <t xml:space="preserve">11.1172065734863</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265186309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8005104064941</t>
+    <t xml:space="preserve">12.7265195846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8005094528198</t>
   </si>
   <si>
     <t xml:space="preserve">13.2259607315063</t>
@@ -3728,22 +3728,22 @@
     <t xml:space="preserve">12.6617765426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3473138809204</t>
+    <t xml:space="preserve">12.4305534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028062820435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3473129272461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4952964782715</t>
+    <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
     <t xml:space="preserve">12.6155309677124</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">11.8016262054443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9958534240723</t>
+    <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7646312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8848676681519</t>
+    <t xml:space="preserve">11.764630317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8848667144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.6073989868164</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">11.2929363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">10.6455116271973</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657480239868</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5704030990601</t>
+    <t xml:space="preserve">11.5704040527344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">11.8331203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4007749557495</t>
+    <t xml:space="preserve">11.4007759094238</t>
   </si>
   <si>
     <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.569953918457</t>
+    <t xml:space="preserve">11.5699548721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6827392578125</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">12.1432819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.85191822052</t>
+    <t xml:space="preserve">11.8519172668457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639413833618</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">11.7579298019409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9741020202637</t>
+    <t xml:space="preserve">11.974102973938</t>
   </si>
   <si>
     <t xml:space="preserve">12.0398950576782</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">11.8895130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1658039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522563934326</t>
+    <t xml:space="preserve">11.1658048629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522554397583</t>
   </si>
   <si>
     <t xml:space="preserve">10.5642786026001</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0248212814331</t>
+    <t xml:space="preserve">10.8838386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0248203277588</t>
   </si>
   <si>
     <t xml:space="preserve">10.9214344024658</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4571676254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.49476146698</t>
+    <t xml:space="preserve">11.4571666717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4947624206543</t>
   </si>
   <si>
     <t xml:space="preserve">11.4853639602661</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">12.6414184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6884126663208</t>
+    <t xml:space="preserve">12.6884136199951</t>
   </si>
   <si>
     <t xml:space="preserve">12.5474319458008</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9985752105713</t>
+    <t xml:space="preserve">12.8481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.998574256897</t>
   </si>
   <si>
     <t xml:space="preserve">13.1677532196045</t>
@@ -3920,37 +3920,37 @@
     <t xml:space="preserve">13.4685153961182</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6188974380493</t>
+    <t xml:space="preserve">13.618896484375</t>
   </si>
   <si>
     <t xml:space="preserve">13.5625047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6094970703125</t>
+    <t xml:space="preserve">13.6094980239868</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564912796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741081237793</t>
+    <t xml:space="preserve">13.6564922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6752910614014</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8726654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6376953125</t>
+    <t xml:space="preserve">13.8726663589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6376943588257</t>
   </si>
   <si>
     <t xml:space="preserve">13.3087358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9891748428345</t>
+    <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
     <t xml:space="preserve">13.1583547592163</t>
@@ -3971,55 +3971,55 @@
     <t xml:space="preserve">13.1113605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9139852523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8199968338013</t>
+    <t xml:space="preserve">12.9139862060547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8199977874756</t>
   </si>
   <si>
     <t xml:space="preserve">13.0361700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0173721313477</t>
+    <t xml:space="preserve">13.017373085022</t>
   </si>
   <si>
     <t xml:space="preserve">13.0549688339233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8669919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260084152222</t>
+    <t xml:space="preserve">12.8669910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260093688965</t>
   </si>
   <si>
     <t xml:space="preserve">12.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5850267410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5756282806396</t>
+    <t xml:space="preserve">12.8857898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5850276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5756273269653</t>
   </si>
   <si>
     <t xml:space="preserve">12.6602172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1207590103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1056861877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8237218856812</t>
+    <t xml:space="preserve">13.1207599639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1056871414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8237209320068</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.391375541687</t>
+    <t xml:space="preserve">11.3913745880127</t>
   </si>
   <si>
     <t xml:space="preserve">11.1470060348511</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000137329102</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548791885376</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">10.4984874725342</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6582670211792</t>
+    <t xml:space="preserve">10.6582679748535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951005935669</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4665660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1940002441406</t>
+    <t xml:space="preserve">11.4665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1939992904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667667388916</t>
+    <t xml:space="preserve">10.6676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
@@ -4070,13 +4070,13 @@
     <t xml:space="preserve">10.9684295654297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3255844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.287989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8707151412964</t>
+    <t xml:space="preserve">11.3255834579468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2879886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929008483887</t>
@@ -4103,7 +4103,7 @@
     <t xml:space="preserve">12.1244840621948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">12.6790142059326</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4722414016724</t>
+    <t xml:space="preserve">12.472240447998</t>
   </si>
   <si>
     <t xml:space="preserve">12.7730026245117</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0831642150879</t>
+    <t xml:space="preserve">13.0831651687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.8350706100464</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.258017539978</t>
+    <t xml:space="preserve">14.2580165863037</t>
   </si>
   <si>
     <t xml:space="preserve">14.1170349121094</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7504816055298</t>
+    <t xml:space="preserve">13.7504806518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2805395126343</t>
@@ -4169,7 +4169,7 @@
     <t xml:space="preserve">13.3745279312134</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4403200149536</t>
+    <t xml:space="preserve">13.4403190612793</t>
   </si>
   <si>
     <t xml:space="preserve">13.5531053543091</t>
@@ -4178,19 +4178,19 @@
     <t xml:space="preserve">13.3463315963745</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2523431777954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5719032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3933248519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2711410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5249090194702</t>
+    <t xml:space="preserve">13.2523441314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5719022750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3933258056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2711400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5249099731445</t>
   </si>
   <si>
     <t xml:space="preserve">13.6470937728882</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">14.0512428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0042486190796</t>
+    <t xml:space="preserve">14.0042495727539</t>
   </si>
   <si>
     <t xml:space="preserve">14.079439163208</t>
@@ -4220,19 +4220,19 @@
     <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4215211868286</t>
+    <t xml:space="preserve">13.4215221405029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0888376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5587797164917</t>
+    <t xml:space="preserve">14.5587787628174</t>
   </si>
   <si>
     <t xml:space="preserve">14.7749528884888</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8407440185547</t>
+    <t xml:space="preserve">14.840744972229</t>
   </si>
   <si>
     <t xml:space="preserve">15.0193214416504</t>
@@ -4241,7 +4241,7 @@
     <t xml:space="preserve">15.0099239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6997623443604</t>
+    <t xml:space="preserve">14.6997632980347</t>
   </si>
   <si>
     <t xml:space="preserve">14.7279586791992</t>
@@ -4253,13 +4253,13 @@
     <t xml:space="preserve">14.944130897522</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031492233276</t>
+    <t xml:space="preserve">14.803150177002</t>
   </si>
   <si>
     <t xml:space="preserve">14.7655544281006</t>
@@ -4274,13 +4274,13 @@
     <t xml:space="preserve">14.8125486373901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6903638839722</t>
+    <t xml:space="preserve">14.6903629302979</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.103910446167</t>
+    <t xml:space="preserve">15.1039113998413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">14.8877382278442</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1227102279663</t>
+    <t xml:space="preserve">15.122709274292</t>
   </si>
   <si>
     <t xml:space="preserve">14.3708038330078</t>
@@ -4313,16 +4313,16 @@
     <t xml:space="preserve">10.9872255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269190788269</t>
+    <t xml:space="preserve">11.2691917419434</t>
   </si>
   <si>
     <t xml:space="preserve">11.2785902023315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3067855834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2315950393677</t>
+    <t xml:space="preserve">11.3067865371704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.231595993042</t>
   </si>
   <si>
     <t xml:space="preserve">11.5041618347168</t>
@@ -4349,16 +4349,16 @@
     <t xml:space="preserve">11.0812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0342197418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.874439239502</t>
+    <t xml:space="preserve">11.0342206954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8744401931763</t>
   </si>
   <si>
     <t xml:space="preserve">10.9590291976929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9026365280151</t>
+    <t xml:space="preserve">10.9026374816895</t>
   </si>
   <si>
     <t xml:space="preserve">10.893238067627</t>
@@ -5820,6 +5820,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.4200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2299995422363</t>
   </si>
 </sst>
 </file>
@@ -22894,7 +22897,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G644" t="s">
-        <v>550</v>
+        <v>458</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22920,7 +22923,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G645" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22946,7 +22949,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22972,7 +22975,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G647" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23024,7 +23027,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23076,7 +23079,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G651" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -23128,7 +23131,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G653" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23154,7 +23157,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G654" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23180,7 +23183,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G655" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23206,7 +23209,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23232,7 +23235,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G657" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23258,7 +23261,7 @@
         <v>7.125</v>
       </c>
       <c r="G658" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23310,7 +23313,7 @@
         <v>7.125</v>
       </c>
       <c r="G660" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23336,7 +23339,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23362,7 +23365,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G662" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23414,7 +23417,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G664" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23466,7 +23469,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23492,7 +23495,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G667" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23518,7 +23521,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G668" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23544,7 +23547,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23622,7 +23625,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23648,7 +23651,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G673" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23674,7 +23677,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G674" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23726,7 +23729,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G676" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23752,7 +23755,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23882,7 +23885,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G682" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23908,7 +23911,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G683" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23934,7 +23937,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G684" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23960,7 +23963,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -24012,7 +24015,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G687" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -24038,7 +24041,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G688" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -24064,7 +24067,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G689" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -24090,7 +24093,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G690" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -24116,7 +24119,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G691" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -24142,7 +24145,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -24168,7 +24171,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G693" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -24194,7 +24197,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G694" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -24220,7 +24223,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>406</v>
+        <v>580</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -24272,7 +24275,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G697" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -71132,7 +71135,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.691099537</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>57742</v>
@@ -71153,6 +71156,32 @@
         <v>1935</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6912847222</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>76803</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>11.460000038147</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>11.3699998855591</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1937" uniqueCount="1937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1938" uniqueCount="1938">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034394264221</t>
+    <t xml:space="preserve">2.10034418106079</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.150794506073</t>
+    <t xml:space="preserve">2.15079474449158</t>
   </si>
   <si>
     <t xml:space="preserve">2.13486266136169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07379102706909</t>
+    <t xml:space="preserve">2.09768843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07379126548767</t>
   </si>
   <si>
     <t xml:space="preserve">2.02333998680115</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0631697177887</t>
+    <t xml:space="preserve">2.06316947937012</t>
   </si>
   <si>
     <t xml:space="preserve">2.05254864692688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96492338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988330364227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802921295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01696729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209784507751</t>
+    <t xml:space="preserve">1.96492326259613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988354206085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802945137024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696753501892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209760665894</t>
   </si>
   <si>
     <t xml:space="preserve">2.00156664848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05998373031616</t>
+    <t xml:space="preserve">2.05998349189758</t>
   </si>
   <si>
     <t xml:space="preserve">2.00528407096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01909136772156</t>
+    <t xml:space="preserve">2.01909160614014</t>
   </si>
   <si>
     <t xml:space="preserve">1.97820007801056</t>
@@ -101,55 +101,55 @@
     <t xml:space="preserve">1.89854085445404</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774939537048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943274021149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447281837463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93306040763855</t>
+    <t xml:space="preserve">1.92774927616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9394326210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447246074677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306005001068</t>
   </si>
   <si>
     <t xml:space="preserve">1.91712772846222</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94633650779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9558961391449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9436811208725</t>
+    <t xml:space="preserve">1.94633638858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589566230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368088245392</t>
   </si>
   <si>
     <t xml:space="preserve">2.09237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441233634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450197219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17203688621521</t>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441257476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450244903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17203712463379</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830998420715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1396427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442229270935</t>
+    <t xml:space="preserve">2.13964247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299944877625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442181587219</t>
   </si>
   <si>
     <t xml:space="preserve">2.14548444747925</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">2.15344977378845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1481397151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132570266724</t>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132546424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831994056702</t>
@@ -170,22 +170,22 @@
     <t xml:space="preserve">2.18265843391418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22248792648315</t>
+    <t xml:space="preserve">2.22248768806458</t>
   </si>
   <si>
     <t xml:space="preserve">2.15610527992249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14495277404785</t>
+    <t xml:space="preserve">2.14495301246643</t>
   </si>
   <si>
     <t xml:space="preserve">2.12955236434937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10565495491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
+    <t xml:space="preserve">2.1056547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706760406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219767570496</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">2.121586561203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14017343521118</t>
+    <t xml:space="preserve">2.14017367362976</t>
   </si>
   <si>
     <t xml:space="preserve">2.12424182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362028121948</t>
+    <t xml:space="preserve">2.11362051963806</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582498550415</t>
@@ -209,67 +209,67 @@
     <t xml:space="preserve">2.05307936668396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901144981384</t>
+    <t xml:space="preserve">2.0684802532196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901168823242</t>
   </si>
   <si>
     <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12477254867554</t>
+    <t xml:space="preserve">2.12477278709412</t>
   </si>
   <si>
     <t xml:space="preserve">2.16141605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15557408332825</t>
+    <t xml:space="preserve">2.15557432174683</t>
   </si>
   <si>
     <t xml:space="preserve">2.17734789848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24373006820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169587135315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29418087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25753736495972</t>
+    <t xml:space="preserve">2.24373030662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169634819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29418110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25753784179688</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461175918579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21452212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514319419861</t>
+    <t xml:space="preserve">2.21452188491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514343261719</t>
   </si>
   <si>
     <t xml:space="preserve">2.24638533592224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23098492622375</t>
+    <t xml:space="preserve">2.2309844493866</t>
   </si>
   <si>
     <t xml:space="preserve">2.32073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604432106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4492506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288772583008</t>
+    <t xml:space="preserve">2.34888052940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44925093650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288796424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.51775741577148</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">2.56555318832397</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52997183799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547255516052</t>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6154727935791</t>
   </si>
   <si>
     <t xml:space="preserve">2.66555047035217</t>
@@ -290,10 +290,10 @@
     <t xml:space="preserve">2.66718316078186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70147633552551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786811828613</t>
+    <t xml:space="preserve">2.70147585868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
     <t xml:space="preserve">2.72161555290222</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">2.79346609115601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8152391910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894026756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98942232131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00248622894287</t>
+    <t xml:space="preserve">2.81523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98942255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00248599052429</t>
   </si>
   <si>
     <t xml:space="preserve">2.94587659835815</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.8979766368866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81959342956543</t>
+    <t xml:space="preserve">2.81959366798401</t>
   </si>
   <si>
     <t xml:space="preserve">2.76516127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73685646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954882144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78693413734436</t>
+    <t xml:space="preserve">2.73685669898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69548797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78693389892578</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531686782837</t>
@@ -350,31 +350,31 @@
     <t xml:space="preserve">2.98289060592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84789824485779</t>
+    <t xml:space="preserve">2.84789848327637</t>
   </si>
   <si>
     <t xml:space="preserve">2.776047706604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86313962936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974925994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97200345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99160003662109</t>
+    <t xml:space="preserve">2.86313939094543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972003698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99159955978394</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418141365051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99813175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97853636741638</t>
+    <t xml:space="preserve">2.99813199043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9785361289978</t>
   </si>
   <si>
     <t xml:space="preserve">3.03514575958252</t>
@@ -383,43 +383,43 @@
     <t xml:space="preserve">3.04820919036865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998252868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15707397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29859805107117</t>
+    <t xml:space="preserve">3.06998229026794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15707421302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29859781265259</t>
   </si>
   <si>
     <t xml:space="preserve">3.30730724334717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34214401245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771185874939</t>
+    <t xml:space="preserve">3.34214425086975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29206609725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771138191223</t>
   </si>
   <si>
     <t xml:space="preserve">3.26158404350281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24416589736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28988885879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27900266647339</t>
+    <t xml:space="preserve">3.24416565895081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28988862037659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27900242805481</t>
   </si>
   <si>
     <t xml:space="preserve">3.25722980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26593852043152</t>
+    <t xml:space="preserve">3.2659387588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.17449235916138</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">3.25505208969116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25940680503845</t>
+    <t xml:space="preserve">3.25940704345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.33125758171082</t>
@@ -437,46 +437,46 @@
     <t xml:space="preserve">3.35085344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34432125091553</t>
+    <t xml:space="preserve">3.34432101249695</t>
   </si>
   <si>
     <t xml:space="preserve">3.32472538948059</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28553462028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303020477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31383895874023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30948448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15054202079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18973326683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20932912826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2006196975708</t>
+    <t xml:space="preserve">3.28553438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247071266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303068161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682518959045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31383919715881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30948424339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1897337436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2093288898468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20061993598938</t>
   </si>
   <si>
     <t xml:space="preserve">3.22239279747009</t>
@@ -485,55 +485,55 @@
     <t xml:space="preserve">3.09175539016724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33343482017517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376152038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497441291809</t>
+    <t xml:space="preserve">3.33343458175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376128196716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497488975525</t>
   </si>
   <si>
     <t xml:space="preserve">3.37262606620789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43141317367554</t>
+    <t xml:space="preserve">3.43141293525696</t>
   </si>
   <si>
     <t xml:space="preserve">3.59253239631653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67962408065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631186485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824031829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.010573387146</t>
+    <t xml:space="preserve">3.67962384223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631210327148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824007987976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057386398315</t>
   </si>
   <si>
     <t xml:space="preserve">4.09330940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533176422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11508321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19346523284912</t>
+    <t xml:space="preserve">3.99533128738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831704139709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11508226394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19346570968628</t>
   </si>
   <si>
     <t xml:space="preserve">4.33716678619385</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483371734619</t>
+    <t xml:space="preserve">4.23483419418335</t>
   </si>
   <si>
     <t xml:space="preserve">4.26313829421997</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6898889541626</t>
+    <t xml:space="preserve">4.68988847732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.65722799301147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64634227752686</t>
+    <t xml:space="preserve">4.6463418006897</t>
   </si>
   <si>
     <t xml:space="preserve">4.75956153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95334053039551</t>
+    <t xml:space="preserve">4.95334005355835</t>
   </si>
   <si>
     <t xml:space="preserve">4.94245386123657</t>
@@ -569,40 +569,40 @@
     <t xml:space="preserve">4.73778820037842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6441650390625</t>
+    <t xml:space="preserve">4.64416551589966</t>
   </si>
   <si>
     <t xml:space="preserve">4.57231378555298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37418079376221</t>
+    <t xml:space="preserve">4.37417984008789</t>
   </si>
   <si>
     <t xml:space="preserve">4.35023021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34152126312256</t>
+    <t xml:space="preserve">4.3415207862854</t>
   </si>
   <si>
     <t xml:space="preserve">4.22830152511597</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19128847122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895587921143</t>
+    <t xml:space="preserve">4.19128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
     <t xml:space="preserve">4.22612380981445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24571990966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36547136306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35458517074585</t>
+    <t xml:space="preserve">4.24572038650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36547088623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35458469390869</t>
   </si>
   <si>
     <t xml:space="preserve">4.3393440246582</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">4.65940523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63763236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6158595085144</t>
+    <t xml:space="preserve">4.63763332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61586046218872</t>
   </si>
   <si>
     <t xml:space="preserve">4.64851951599121</t>
@@ -626,49 +626,49 @@
     <t xml:space="preserve">4.72254753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408664703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66376066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58973169326782</t>
+    <t xml:space="preserve">4.59408712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6637601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58973217010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.51134967803955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5244140625</t>
+    <t xml:space="preserve">4.52441310882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.73343372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64198732376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78568887710571</t>
+    <t xml:space="preserve">4.64198780059814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78568935394287</t>
   </si>
   <si>
     <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74649715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609325408936</t>
+    <t xml:space="preserve">4.746497631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7660927772522</t>
   </si>
   <si>
     <t xml:space="preserve">5.09921884536743</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38662242889404</t>
+    <t xml:space="preserve">5.38662195205688</t>
   </si>
   <si>
     <t xml:space="preserve">5.29082059860229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25162982940674</t>
+    <t xml:space="preserve">5.25162887573242</t>
   </si>
   <si>
     <t xml:space="preserve">5.22985696792603</t>
@@ -680,40 +680,40 @@
     <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03607702255249</t>
+    <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010503768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.225501537323</t>
+    <t xml:space="preserve">5.22550249099731</t>
   </si>
   <si>
     <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106914520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14494276046753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220483779907</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17106962203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14494228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220531463623</t>
   </si>
   <si>
     <t xml:space="preserve">4.90979433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09050941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0404314994812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445951461792</t>
+    <t xml:space="preserve">5.09050989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11445999145508</t>
   </si>
   <si>
     <t xml:space="preserve">5.10139656066895</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">5.11663722991943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04478597640991</t>
+    <t xml:space="preserve">5.04478645324707</t>
   </si>
   <si>
     <t xml:space="preserve">4.95769500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02736806869507</t>
+    <t xml:space="preserve">5.02736854553223</t>
   </si>
   <si>
     <t xml:space="preserve">4.98817729949951</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">4.88584423065186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8662486076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85536193847656</t>
+    <t xml:space="preserve">4.86624908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85536241531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.84665298461914</t>
@@ -755,49 +755,49 @@
     <t xml:space="preserve">4.80093002319336</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004287719727</t>
+    <t xml:space="preserve">4.73561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004383087158</t>
   </si>
   <si>
     <t xml:space="preserve">4.74432039260864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75738382339478</t>
+    <t xml:space="preserve">4.75738430023193</t>
   </si>
   <si>
     <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82052564620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91850423812866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841009140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08397769927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19719648361206</t>
+    <t xml:space="preserve">4.8205246925354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9185037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1384105682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08397817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19719696044922</t>
   </si>
   <si>
     <t xml:space="preserve">5.11881494522095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09486389160156</t>
+    <t xml:space="preserve">5.09486436843872</t>
   </si>
   <si>
     <t xml:space="preserve">5.30170726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38444471359253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710376739502</t>
+    <t xml:space="preserve">5.38444375991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4171028137207</t>
   </si>
   <si>
     <t xml:space="preserve">5.55209541320801</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918685913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134834289551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94400691986084</t>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.944007396698</t>
   </si>
   <si>
     <t xml:space="preserve">6.11383724212646</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329326629639</t>
+    <t xml:space="preserve">5.76329278945923</t>
   </si>
   <si>
     <t xml:space="preserve">5.88957595825195</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">5.89610767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9766674041748</t>
+    <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
     <t xml:space="preserve">6.0964183807373</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">5.9897313117981</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497245788574</t>
+    <t xml:space="preserve">6.00497198104858</t>
   </si>
   <si>
     <t xml:space="preserve">5.98755407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04198741912842</t>
+    <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722761154175</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">6.07464599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13996505737305</t>
+    <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
     <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26842498779297</t>
+    <t xml:space="preserve">6.26842546463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.52969980239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54276323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848714828491</t>
+    <t xml:space="preserve">6.54276371002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848667144775</t>
   </si>
   <si>
     <t xml:space="preserve">6.80403900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90201711654663</t>
+    <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.01088190078735</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">7.11756896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063287734985</t>
+    <t xml:space="preserve">7.3200569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1306324005127</t>
   </si>
   <si>
     <t xml:space="preserve">7.22425699234009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22207927703857</t>
+    <t xml:space="preserve">7.22207880020142</t>
   </si>
   <si>
     <t xml:space="preserve">7.11321401596069</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">7.2939305305481</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37666749954224</t>
+    <t xml:space="preserve">7.37666702270508</t>
   </si>
   <si>
     <t xml:space="preserve">7.36360311508179</t>
@@ -932,25 +932,25 @@
     <t xml:space="preserve">7.28522109985352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3048152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19595146179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46655797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4012393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61243772506714</t>
+    <t xml:space="preserve">7.30481481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19595193862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22705698013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40123987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61243677139282</t>
   </si>
   <si>
     <t xml:space="preserve">6.49704074859619</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">6.52464437484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5621542930603</t>
+    <t xml:space="preserve">6.56215476989746</t>
   </si>
   <si>
     <t xml:space="preserve">6.61290407180786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54891633987427</t>
+    <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
     <t xml:space="preserve">6.45403623580933</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">6.41652584075928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58421993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50478601455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093944549561</t>
+    <t xml:space="preserve">6.58421945571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50478553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093849182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">6.32826519012451</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33267831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3746018409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057062149048</t>
+    <t xml:space="preserve">6.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057014465332</t>
   </si>
   <si>
     <t xml:space="preserve">6.1429181098938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13850498199463</t>
+    <t xml:space="preserve">6.13850545883179</t>
   </si>
   <si>
     <t xml:space="preserve">5.95757102966309</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9134407043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240859985352</t>
+    <t xml:space="preserve">5.91344118118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771266937256</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">5.7854642868042</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95977783203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9200611114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93330001831055</t>
+    <t xml:space="preserve">5.95977830886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92006063461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93329954147339</t>
   </si>
   <si>
     <t xml:space="preserve">5.94212627410889</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">5.8362135887146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84724617004395</t>
+    <t xml:space="preserve">5.8472466468811</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846292495728</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">5.50744438171387</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46993398666382</t>
+    <t xml:space="preserve">5.46993350982666</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894346237183</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">5.73692083358765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7611927986145</t>
+    <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
     <t xml:space="preserve">5.89137649536133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72147512435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59129190444946</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">5.55819416046143</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54495429992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4434552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007467269897</t>
+    <t xml:space="preserve">5.5449538230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44345569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007514953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932489395142</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">5.4191837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49199867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56040000915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096656799316</t>
+    <t xml:space="preserve">5.49199819564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56040048599243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.52730226516724</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922626495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912763595581</t>
+    <t xml:space="preserve">5.56922578811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912811279297</t>
   </si>
   <si>
     <t xml:space="preserve">5.66410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80311584472656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86931085586548</t>
+    <t xml:space="preserve">5.8031153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86931133270264</t>
   </si>
   <si>
     <t xml:space="preserve">5.73030090332031</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">5.96860408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80532217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762760162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56481266021729</t>
+    <t xml:space="preserve">5.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762712478638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56481218338013</t>
   </si>
   <si>
     <t xml:space="preserve">5.52068281173706</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">5.47875928878784</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4942045211792</t>
+    <t xml:space="preserve">5.49420404434204</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">5.22942447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24045610427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369596481323</t>
+    <t xml:space="preserve">5.24045658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369644165039</t>
   </si>
   <si>
     <t xml:space="preserve">5.41477108001709</t>
@@ -1202,10 +1202,10 @@
     <t xml:space="preserve">5.39711856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796745300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22280502319336</t>
+    <t xml:space="preserve">5.27796792984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2228045463562</t>
   </si>
   <si>
     <t xml:space="preserve">5.14116382598877</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">5.20735931396484</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16764211654663</t>
+    <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233804702759</t>
@@ -1226,28 +1226,28 @@
     <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03745746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00656652450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96464252471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126245498657</t>
+    <t xml:space="preserve">5.0374584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00656700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9646430015564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126197814941</t>
   </si>
   <si>
     <t xml:space="preserve">5.04849052429199</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19412040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
+    <t xml:space="preserve">5.19411945343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576112747192</t>
   </si>
   <si>
     <t xml:space="preserve">5.22501134872437</t>
@@ -1256,43 +1256,43 @@
     <t xml:space="preserve">5.24486970901489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11689281463623</t>
+    <t xml:space="preserve">5.11689233779907</t>
   </si>
   <si>
     <t xml:space="preserve">5.03083801269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87196969985962</t>
+    <t xml:space="preserve">4.87197017669678</t>
   </si>
   <si>
     <t xml:space="preserve">4.72634029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71089458465576</t>
+    <t xml:space="preserve">4.71089506149292</t>
   </si>
   <si>
     <t xml:space="preserve">4.65131807327271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93154525756836</t>
+    <t xml:space="preserve">4.93154573440552</t>
   </si>
   <si>
     <t xml:space="preserve">5.21839141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60453033447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81194305419922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503984451294</t>
+    <t xml:space="preserve">5.60453081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81194257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84503936767578</t>
   </si>
   <si>
     <t xml:space="preserve">5.76781225204468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90461540222168</t>
+    <t xml:space="preserve">5.90461587905884</t>
   </si>
   <si>
     <t xml:space="preserve">5.86489820480347</t>
@@ -1301,31 +1301,31 @@
     <t xml:space="preserve">5.77663803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81856203079224</t>
+    <t xml:space="preserve">5.81856250762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.65307331085205</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6398344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467197418213</t>
+    <t xml:space="preserve">5.63983392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467245101929</t>
   </si>
   <si>
     <t xml:space="preserve">6.02376556396484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14071178436279</t>
+    <t xml:space="preserve">6.19366884231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348371505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14071130752563</t>
   </si>
   <si>
     <t xml:space="preserve">6.12526655197144</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">6.02597284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96419143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479909896851</t>
+    <t xml:space="preserve">5.96419191360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479957580566</t>
   </si>
   <si>
     <t xml:space="preserve">5.8097357749939</t>
@@ -1355,13 +1355,13 @@
     <t xml:space="preserve">5.74354076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65086698532104</t>
+    <t xml:space="preserve">5.6508674621582</t>
   </si>
   <si>
     <t xml:space="preserve">5.61776924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63542175292969</t>
+    <t xml:space="preserve">5.63542127609253</t>
   </si>
   <si>
     <t xml:space="preserve">6.01935386657715</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">5.95315790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94433259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
+    <t xml:space="preserve">5.94433212280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
   </si>
   <si>
     <t xml:space="preserve">6.28413486480713</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">6.22235298156738</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52243757247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239503860474</t>
+    <t xml:space="preserve">6.52243709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239456176758</t>
   </si>
   <si>
     <t xml:space="preserve">6.16939640045166</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">6.09878778457642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08996200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
+    <t xml:space="preserve">6.08996248245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5559868812561</t>
   </si>
   <si>
     <t xml:space="preserve">6.11202716827393</t>
@@ -1427,19 +1427,19 @@
     <t xml:space="preserve">5.67072582244873</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68396425247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372493743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963619232178</t>
+    <t xml:space="preserve">5.68396472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
   </si>
   <si>
     <t xml:space="preserve">5.96198511123657</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">6.17822217941284</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27089643478394</t>
+    <t xml:space="preserve">6.27089595794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.35474348068237</t>
@@ -1466,28 +1466,28 @@
     <t xml:space="preserve">6.90637016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10495567321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050048828125</t>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697877883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050096511841</t>
   </si>
   <si>
     <t xml:space="preserve">7.22852039337158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14908599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04758596420288</t>
+    <t xml:space="preserve">7.14908647537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04758644104004</t>
   </si>
   <si>
     <t xml:space="preserve">7.11378240585327</t>
@@ -1502,16 +1502,16 @@
     <t xml:space="preserve">7.32560634613037</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18439102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034624099731</t>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
   </si>
   <si>
     <t xml:space="preserve">7.28147602081299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25941133499146</t>
+    <t xml:space="preserve">7.25941228866577</t>
   </si>
   <si>
     <t xml:space="preserve">7.12260770797729</t>
@@ -1520,28 +1520,28 @@
     <t xml:space="preserve">7.06523847579956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25058555603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321584701538</t>
+    <t xml:space="preserve">7.25058603286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321537017822</t>
   </si>
   <si>
     <t xml:space="preserve">7.21969509124756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46241044998169</t>
+    <t xml:space="preserve">7.46240997314453</t>
   </si>
   <si>
     <t xml:space="preserve">7.62127876281738</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5374321937561</t>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743171691895</t>
   </si>
   <si>
     <t xml:space="preserve">7.40062856674194</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">7.55508375167847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738965988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965160369873</t>
+    <t xml:space="preserve">7.42710542678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965208053589</t>
   </si>
   <si>
     <t xml:space="preserve">6.62835025787354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84017467498779</t>
+    <t xml:space="preserve">6.84017515182495</t>
   </si>
   <si>
     <t xml:space="preserve">6.63717651367188</t>
@@ -1574,58 +1574,58 @@
     <t xml:space="preserve">6.6195240020752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54450225830078</t>
+    <t xml:space="preserve">6.54450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163354873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294219970703</t>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
   </si>
   <si>
     <t xml:space="preserve">6.54796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6597785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.579270362854</t>
   </si>
   <si>
     <t xml:space="preserve">6.48534440994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370311737061</t>
+    <t xml:space="preserve">6.71344995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">6.75817584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61505079269409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49429035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087167739868</t>
+    <t xml:space="preserve">6.61505126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
   </si>
   <si>
     <t xml:space="preserve">6.44956302642822</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">6.41825437545776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3198561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
+    <t xml:space="preserve">6.31985664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22145843505859</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">6.12305974960327</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26171207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14094972610474</t>
+    <t xml:space="preserve">6.26171159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14095020294189</t>
   </si>
   <si>
     <t xml:space="preserve">6.18120384216309</t>
@@ -1658,19 +1658,19 @@
     <t xml:space="preserve">6.20356750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34669160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2125129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774614334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821487426758</t>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829387664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21251344680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821582794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.48981714248657</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">6.53007125854492</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44061756134033</t>
+    <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509029388428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40036487579346</t>
+    <t xml:space="preserve">6.39141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
   </si>
   <si>
     <t xml:space="preserve">6.37352800369263</t>
@@ -1700,16 +1700,16 @@
     <t xml:space="preserve">6.43167304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50323534011841</t>
+    <t xml:space="preserve">6.50323486328125</t>
   </si>
   <si>
     <t xml:space="preserve">6.32880163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23934841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.27960252761841</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">6.10069608688354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39589214324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567657470703</t>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567705154419</t>
   </si>
   <si>
     <t xml:space="preserve">5.98440790176392</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">5.08093214035034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97358846664429</t>
+    <t xml:space="preserve">4.97358894348145</t>
   </si>
   <si>
     <t xml:space="preserve">5.13013124465942</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">5.01831436157227</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9646430015564</t>
+    <t xml:space="preserve">4.96464347839355</t>
   </si>
   <si>
     <t xml:space="preserve">5.07645988464355</t>
@@ -1766,43 +1766,43 @@
     <t xml:space="preserve">4.98700571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92886257171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73653888702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58894062042236</t>
+    <t xml:space="preserve">4.92886209487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73653793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58894109725952</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74995613098145</t>
+    <t xml:space="preserve">4.74995565414429</t>
   </si>
   <si>
     <t xml:space="preserve">4.71417427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37201642990112</t>
+    <t xml:space="preserve">4.37201690673828</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483907699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04104089736938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05445909500122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829653739929</t>
+    <t xml:space="preserve">4.20876550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483860015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04104042053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05445861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829606056213</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353090286255</t>
@@ -1814,22 +1814,22 @@
     <t xml:space="preserve">4.13049364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01867723464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884307861328</t>
+    <t xml:space="preserve">4.01867771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884331703186</t>
   </si>
   <si>
     <t xml:space="preserve">3.70559167861938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75702714920044</t>
+    <t xml:space="preserve">3.75702691078186</t>
   </si>
   <si>
     <t xml:space="preserve">3.81740808486938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466396331787</t>
+    <t xml:space="preserve">3.73466420173645</t>
   </si>
   <si>
     <t xml:space="preserve">3.8375346660614</t>
@@ -1838,34 +1838,34 @@
     <t xml:space="preserve">3.84648036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96500515937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15733003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00302267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9247510433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146061897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264197349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8621346950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512318611145</t>
+    <t xml:space="preserve">3.96500492095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15732955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00302314758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92475152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9426417350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331557273865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424448013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512294769287</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896110534668</t>
@@ -1874,19 +1874,19 @@
     <t xml:space="preserve">3.24267220497131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03245782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140329360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216444969177</t>
+    <t xml:space="preserve">3.03245759010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216468811035</t>
   </si>
   <si>
     <t xml:space="preserve">3.38356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38803339004517</t>
+    <t xml:space="preserve">3.38803315162659</t>
   </si>
   <si>
     <t xml:space="preserve">3.26950812339783</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">3.3947422504425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48866820335388</t>
+    <t xml:space="preserve">3.48866844177246</t>
   </si>
   <si>
     <t xml:space="preserve">3.51550388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31870746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24714517593384</t>
+    <t xml:space="preserve">3.31870722770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24714493751526</t>
   </si>
   <si>
     <t xml:space="preserve">3.1107292175293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735028266907</t>
+    <t xml:space="preserve">2.92735004425049</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182277679443</t>
@@ -1925,49 +1925,49 @@
     <t xml:space="preserve">3.01009440422058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10402011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03916692733765</t>
+    <t xml:space="preserve">3.1040198802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03916668891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.95642280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88485980033875</t>
+    <t xml:space="preserve">2.88486003875732</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511391639709</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844431877136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869795799255</t>
+    <t xml:space="preserve">2.77751660346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74844408035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78869819641113</t>
   </si>
   <si>
     <t xml:space="preserve">2.83342480659485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88933277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07271122932434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16887307167053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22925424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1599280834198</t>
+    <t xml:space="preserve">2.88933300971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625672340393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16887331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22925448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254514694214</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54233956336975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972249984741</t>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972273826599</t>
   </si>
   <si>
     <t xml:space="preserve">3.53339457511902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49537706375122</t>
+    <t xml:space="preserve">3.4953773021698</t>
   </si>
   <si>
     <t xml:space="preserve">3.61166596412659</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">3.51103138923645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221322059631</t>
+    <t xml:space="preserve">3.52221298217773</t>
   </si>
   <si>
     <t xml:space="preserve">3.58259391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43723273277283</t>
+    <t xml:space="preserve">3.43723225593567</t>
   </si>
   <si>
     <t xml:space="preserve">3.52444958686829</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399012565613</t>
+    <t xml:space="preserve">3.70335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398964881897</t>
   </si>
   <si>
     <t xml:space="preserve">3.89567971229553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77268171310425</t>
+    <t xml:space="preserve">3.77268195152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.83306241035461</t>
@@ -2054,10 +2054,10 @@
     <t xml:space="preserve">3.94040560722351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99184107780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011318206787</t>
+    <t xml:space="preserve">3.99184131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011270523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.13273000717163</t>
@@ -2066,25 +2066,25 @@
     <t xml:space="preserve">4.09247589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25125503540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18863773345947</t>
+    <t xml:space="preserve">4.25125551223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18863725662231</t>
   </si>
   <si>
     <t xml:space="preserve">3.9493510723114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00525903701782</t>
+    <t xml:space="preserve">4.00525951385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.02762222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842383384705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112773895264</t>
+    <t xml:space="preserve">3.97842407226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112821578979</t>
   </si>
   <si>
     <t xml:space="preserve">4.28256368637085</t>
@@ -2096,25 +2096,25 @@
     <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35412645339966</t>
+    <t xml:space="preserve">4.3541259765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.1662745475769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429182052612</t>
+    <t xml:space="preserve">4.20429229736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20205593109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23783683776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2915096282959</t>
+    <t xml:space="preserve">4.20205640792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23783731460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901914596558</t>
@@ -2123,43 +2123,43 @@
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19981956481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07458543777466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15285730361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18640089035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914548873901</t>
+    <t xml:space="preserve">4.25349092483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19982004165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07458591461182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15285682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1864013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914596557617</t>
   </si>
   <si>
     <t xml:space="preserve">3.97171521186829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93369650840759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631381034851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0388035774231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03656721115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01644039154053</t>
+    <t xml:space="preserve">3.93369698524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90015244483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880405426025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03656768798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01643991470337</t>
   </si>
   <si>
     <t xml:space="preserve">3.9180428981781</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">3.87778854370117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7682089805603</t>
+    <t xml:space="preserve">3.76820874214172</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65191984176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85095262527466</t>
+    <t xml:space="preserve">3.65192008018494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85095238685608</t>
   </si>
   <si>
     <t xml:space="preserve">4.09918451309204</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82411742210388</t>
+    <t xml:space="preserve">3.82411694526672</t>
   </si>
   <si>
     <t xml:space="preserve">3.95693111419678</t>
@@ -2192,7 +2192,7 @@
     <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76229000091553</t>
+    <t xml:space="preserve">3.76229023933411</t>
   </si>
   <si>
     <t xml:space="preserve">3.74626088142395</t>
@@ -2201,22 +2201,22 @@
     <t xml:space="preserve">3.7645800113678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901371955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67298412322998</t>
+    <t xml:space="preserve">3.68901348114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243655204773</t>
+    <t xml:space="preserve">3.84243631362915</t>
   </si>
   <si>
     <t xml:space="preserve">3.87220478057861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92487215995789</t>
+    <t xml:space="preserve">3.92487239837646</t>
   </si>
   <si>
     <t xml:space="preserve">3.96608948707581</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">3.8744945526123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90655326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
+    <t xml:space="preserve">3.90655303001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440957069397</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165601730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1538610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09203433990479</t>
+    <t xml:space="preserve">4.19736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15386152267456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09203386306763</t>
   </si>
   <si>
     <t xml:space="preserve">4.11264228820801</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">4.14470195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821001052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751588821411</t>
+    <t xml:space="preserve">4.18821048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438472747803</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">4.30270433425903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3507924079895</t>
+    <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33247327804565</t>
+    <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.23858737945557</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774646759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1744704246521</t>
+    <t xml:space="preserve">4.24774694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17446994781494</t>
   </si>
   <si>
     <t xml:space="preserve">4.05997562408447</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">4.09890413284302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15157175064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16302108764648</t>
+    <t xml:space="preserve">4.15157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16302061080933</t>
   </si>
   <si>
     <t xml:space="preserve">4.11035346984863</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">3.95235133171082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00043821334839</t>
+    <t xml:space="preserve">4.00043869018555</t>
   </si>
   <si>
     <t xml:space="preserve">3.98211908340454</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">4.13096237182617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493349075317</t>
+    <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
     <t xml:space="preserve">4.16760063171387</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">4.05310583114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18591976165771</t>
+    <t xml:space="preserve">4.18591928482056</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554191589355</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">5.33086538314819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35834360122681</t>
+    <t xml:space="preserve">5.35834312438965</t>
   </si>
   <si>
     <t xml:space="preserve">5.62855052947998</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">5.48657751083374</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39040184020996</t>
+    <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
     <t xml:space="preserve">5.61023139953613</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527448654175</t>
+    <t xml:space="preserve">5.55527496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451927185059</t>
@@ -2429,25 +2429,25 @@
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590847015381</t>
+    <t xml:space="preserve">5.27590799331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292362213135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993877410889</t>
+    <t xml:space="preserve">5.44993925094604</t>
   </si>
   <si>
     <t xml:space="preserve">5.34460496902466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47283792495728</t>
+    <t xml:space="preserve">5.47283840179443</t>
   </si>
   <si>
     <t xml:space="preserve">5.45909833908081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55985403060913</t>
+    <t xml:space="preserve">5.55985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.69724750518799</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">5.67892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71556663513184</t>
+    <t xml:space="preserve">5.71556615829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716276168823</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">5.71098661422729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82090187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875745773315</t>
+    <t xml:space="preserve">5.82090139389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
     <t xml:space="preserve">6.04989099502563</t>
@@ -2495,7 +2495,7 @@
     <t xml:space="preserve">6.22392225265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652877807617</t>
+    <t xml:space="preserve">6.08652925491333</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493265151978</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">6.02241134643555</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24224138259888</t>
+    <t xml:space="preserve">6.24224090576172</t>
   </si>
   <si>
     <t xml:space="preserve">6.71395826339722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324048995972</t>
+    <t xml:space="preserve">7.10324001312256</t>
   </si>
   <si>
     <t xml:space="preserve">7.19941520690918</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">7.61159610748291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61617422103882</t>
+    <t xml:space="preserve">7.61617469787598</t>
   </si>
   <si>
     <t xml:space="preserve">7.71235132217407</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">7.67113351821899</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62533473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735649108887</t>
+    <t xml:space="preserve">7.6253342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
     <t xml:space="preserve">7.28185129165649</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">7.29101133346558</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727127075195</t>
+    <t xml:space="preserve">7.27727174758911</t>
   </si>
   <si>
     <t xml:space="preserve">7.11697959899902</t>
@@ -2561,13 +2561,13 @@
     <t xml:space="preserve">7.15361785888672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26811265945435</t>
+    <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
     <t xml:space="preserve">7.39634609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802743911743</t>
+    <t xml:space="preserve">7.37802696228027</t>
   </si>
   <si>
     <t xml:space="preserve">7.57495737075806</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">7.67571306228638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579875946045</t>
+    <t xml:space="preserve">7.56579828262329</t>
   </si>
   <si>
     <t xml:space="preserve">7.66655349731445</t>
@@ -2591,7 +2591,7 @@
     <t xml:space="preserve">7.36428737640381</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45130348205566</t>
+    <t xml:space="preserve">7.45130395889282</t>
   </si>
   <si>
     <t xml:space="preserve">7.12155961990356</t>
@@ -2603,22 +2603,22 @@
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30474996566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22231435775757</t>
+    <t xml:space="preserve">7.30475044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22231483459473</t>
   </si>
   <si>
     <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4375638961792</t>
+    <t xml:space="preserve">7.43756341934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.48794174194336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52000045776367</t>
+    <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2627,22 +2627,22 @@
     <t xml:space="preserve">7.17651653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02996349334717</t>
+    <t xml:space="preserve">7.02996397018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.51244878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7414379119873</t>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639482498169</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7185378074646</t>
+    <t xml:space="preserve">6.71853828430176</t>
   </si>
   <si>
     <t xml:space="preserve">6.76891613006592</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">6.83303356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76433706283569</t>
+    <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
     <t xml:space="preserve">6.63610219955444</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">5.72014617919922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47741794586182</t>
+    <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75381231307983</t>
+    <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.59809970855713</t>
@@ -2711,22 +2711,22 @@
     <t xml:space="preserve">4.63931798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21110820770264</t>
+    <t xml:space="preserve">4.21110868453979</t>
   </si>
   <si>
     <t xml:space="preserve">3.8149573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66382479667664</t>
+    <t xml:space="preserve">3.66382455825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034111022949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22416615486145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18294787406921</t>
+    <t xml:space="preserve">3.22416591644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
     <t xml:space="preserve">3.22645568847656</t>
@@ -2735,10 +2735,10 @@
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356913566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304545402527</t>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304569244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344742774963</t>
@@ -2774,28 +2774,28 @@
     <t xml:space="preserve">4.3828501701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11722278594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01188802719116</t>
+    <t xml:space="preserve">4.11722326278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01188850402832</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218065261841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
+    <t xml:space="preserve">4.09432411193848</t>
   </si>
   <si>
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612716674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35995149612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26835584640503</t>
+    <t xml:space="preserve">4.45612668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35995101928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
     <t xml:space="preserve">4.26377630233765</t>
@@ -2810,25 +2810,25 @@
     <t xml:space="preserve">4.30957412719727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5248236656189</t>
+    <t xml:space="preserve">4.30499362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52482318878174</t>
   </si>
   <si>
     <t xml:space="preserve">4.48360586166382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3874306678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406845092773</t>
+    <t xml:space="preserve">4.38743019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406892776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.75152254104614</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">4.888916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04920768737793</t>
+    <t xml:space="preserve">5.04920816421509</t>
   </si>
   <si>
     <t xml:space="preserve">5.1866021156311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239946365356</t>
+    <t xml:space="preserve">5.23239898681641</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34689474105835</t>
+    <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
     <t xml:space="preserve">5.16370296478271</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">4.93471431732178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02630949020386</t>
+    <t xml:space="preserve">5.02630996704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.19805145263672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31254577636719</t>
+    <t xml:space="preserve">5.31254625320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529909133911</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">5.20950078964233</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1522536277771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14080429077148</t>
+    <t xml:space="preserve">5.15225315093994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14080381393433</t>
   </si>
   <si>
     <t xml:space="preserve">5.27819728851318</t>
@@ -2906,28 +2906,28 @@
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06065797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22095012664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07210683822632</t>
+    <t xml:space="preserve">5.06065845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22094964981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07210731506348</t>
   </si>
   <si>
     <t xml:space="preserve">5.10645532608032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12935495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3239951133728</t>
+    <t xml:space="preserve">5.12935447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32399559020996</t>
   </si>
   <si>
     <t xml:space="preserve">5.33544492721558</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03775882720947</t>
+    <t xml:space="preserve">5.03775930404663</t>
   </si>
   <si>
     <t xml:space="preserve">5.08355712890625</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">4.98051118850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84311819076538</t>
+    <t xml:space="preserve">4.84311771392822</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">4.21339797973633</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08058500289917</t>
+    <t xml:space="preserve">4.08058452606201</t>
   </si>
   <si>
     <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163188934326</t>
+    <t xml:space="preserve">4.34163236618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412954330444</t>
@@ -2978,19 +2978,19 @@
     <t xml:space="preserve">5.54153442382812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62168073654175</t>
+    <t xml:space="preserve">5.62168025970459</t>
   </si>
   <si>
     <t xml:space="preserve">5.75907373428345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73617506027222</t>
+    <t xml:space="preserve">5.73617553710938</t>
   </si>
   <si>
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64458036422729</t>
+    <t xml:space="preserve">5.64457988739014</t>
   </si>
   <si>
     <t xml:space="preserve">5.66747856140137</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">5.70182704925537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14835643768311</t>
+    <t xml:space="preserve">5.816321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516466140747</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">5.9537148475647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356901168823</t>
+    <t xml:space="preserve">5.87356948852539</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936683654785</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">6.18270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07965898513794</t>
+    <t xml:space="preserve">6.07965850830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.13690614700317</t>
@@ -3044,19 +3044,19 @@
     <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009696960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36589574813843</t>
+    <t xml:space="preserve">6.35444593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
     <t xml:space="preserve">6.48038959503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52618741989136</t>
+    <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
     <t xml:space="preserve">6.53763675689697</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58343553543091</t>
+    <t xml:space="preserve">6.58343505859375</t>
   </si>
   <si>
     <t xml:space="preserve">6.62923336029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169357299805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3429970741272</t>
+    <t xml:space="preserve">6.41169309616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
     <t xml:space="preserve">6.46894025802612</t>
@@ -3089,16 +3089,16 @@
     <t xml:space="preserve">6.20560312271118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42314291000366</t>
+    <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
     <t xml:space="preserve">6.50328922271729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66358137130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51473808288574</t>
+    <t xml:space="preserve">6.66358184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.7895245552063</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">8.15200901031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766147613525</t>
+    <t xml:space="preserve">8.11766242980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.18635845184326</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">8.34665012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23215675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16345882415771</t>
+    <t xml:space="preserve">8.23215579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16345977783203</t>
   </si>
   <si>
     <t xml:space="preserve">8.07186508178711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20925712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
+    <t xml:space="preserve">8.20925617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94592046737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736885070801</t>
   </si>
   <si>
     <t xml:space="preserve">7.84287452697754</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">7.92302083969116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81997632980347</t>
+    <t xml:space="preserve">7.81997680664062</t>
   </si>
   <si>
     <t xml:space="preserve">7.86577320098877</t>
@@ -3254,25 +3254,25 @@
     <t xml:space="preserve">9.65356349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60731887817383</t>
+    <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073596954346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136951446533</t>
+    <t xml:space="preserve">9.71136856079102</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2894277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3009872436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241100311279</t>
+    <t xml:space="preserve">10.2894268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3009881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
@@ -3281,22 +3281,22 @@
     <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437717437744</t>
+    <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3356714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4628448486328</t>
+    <t xml:space="preserve">10.33567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4628438949585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703565597534</t>
+    <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7403125762939</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">10.1044483184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2663059234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3934783935547</t>
+    <t xml:space="preserve">10.2663049697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3934774398804</t>
   </si>
   <si>
     <t xml:space="preserve">10.0582036972046</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">10.0235214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1506948471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.092887878418</t>
+    <t xml:space="preserve">10.1506938934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928888320923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1160106658936</t>
@@ -3344,10 +3344,10 @@
     <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4859666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853771209717</t>
+    <t xml:space="preserve">10.4859657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.185378074646</t>
   </si>
   <si>
     <t xml:space="preserve">10.0350818634033</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">10.416600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1738157272339</t>
+    <t xml:space="preserve">10.1738147735596</t>
   </si>
   <si>
     <t xml:space="preserve">10.1391315460205</t>
   </si>
   <si>
-    <t xml:space="preserve">11.191198348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5056600570679</t>
+    <t xml:space="preserve">11.1911973953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056610107422</t>
   </si>
   <si>
     <t xml:space="preserve">11.9052143096924</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611543655396</t>
+    <t xml:space="preserve">11.5611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426568984985</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0975923538208</t>
+    <t xml:space="preserve">12.0975914001465</t>
   </si>
   <si>
     <t xml:space="preserve">11.8571195602417</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">12.0420989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2455749511719</t>
+    <t xml:space="preserve">12.2455739974976</t>
   </si>
   <si>
     <t xml:space="preserve">12.3010683059692</t>
@@ -3428,28 +3428,28 @@
     <t xml:space="preserve">11.894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.9299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069044113159</t>
+    <t xml:space="preserve">13.7069034576416</t>
   </si>
   <si>
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
+    <t xml:space="preserve">13.5034284591675</t>
   </si>
   <si>
     <t xml:space="preserve">13.817892074585</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7254018783569</t>
+    <t xml:space="preserve">13.7254028320312</t>
   </si>
   <si>
     <t xml:space="preserve">14.631796836853</t>
@@ -3467,16 +3467,16 @@
     <t xml:space="preserve">13.7623977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4294366836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0409832000732</t>
+    <t xml:space="preserve">13.4294376373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0409822463989</t>
   </si>
   <si>
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669904708862</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">16.3705940246582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5370750427246</t>
+    <t xml:space="preserve">16.537073135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596054077148</t>
@@ -3521,55 +3521,55 @@
     <t xml:space="preserve">16.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7971601486206</t>
+    <t xml:space="preserve">16.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7971620559692</t>
   </si>
   <si>
     <t xml:space="preserve">16.1486206054688</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0006370544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.908148765564</t>
+    <t xml:space="preserve">16.000638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9081478118896</t>
   </si>
   <si>
     <t xml:space="preserve">15.5196943283081</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896522521973</t>
+    <t xml:space="preserve">15.4641990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896512985229</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416687011719</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092655181885</t>
+    <t xml:space="preserve">15.8341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092645645142</t>
   </si>
   <si>
     <t xml:space="preserve">14.4283208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5023126602173</t>
+    <t xml:space="preserve">14.502311706543</t>
   </si>
   <si>
     <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6329126358032</t>
+    <t xml:space="preserve">13.6329135894775</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514120101929</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.3369483947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3578,19 +3578,19 @@
     <t xml:space="preserve">14.0583629608154</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1693515777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8918828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098234176636</t>
+    <t xml:space="preserve">14.1693506240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8918838500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098224639893</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993936538696</t>
+    <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7808961868286</t>
@@ -3599,10 +3599,10 @@
     <t xml:space="preserve">13.2629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5404243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924407958984</t>
+    <t xml:space="preserve">13.5404233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924417495728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">14.2988367080688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2803373336792</t>
+    <t xml:space="preserve">14.2803382873535</t>
   </si>
   <si>
     <t xml:space="preserve">14.1138582229614</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">13.1334714889526</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0594797134399</t>
+    <t xml:space="preserve">13.0594787597656</t>
   </si>
   <si>
     <t xml:space="preserve">13.4479351043701</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2085781097412</t>
+    <t xml:space="preserve">12.2085790634155</t>
   </si>
   <si>
     <t xml:space="preserve">12.3935575485229</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">13.18896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4664335250854</t>
+    <t xml:space="preserve">13.4664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8190078735352</t>
@@ -3665,25 +3665,25 @@
     <t xml:space="preserve">12.1345872879028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9496097564697</t>
+    <t xml:space="preserve">11.9496088027954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5981502532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0051012039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">11.5981492996216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0051021575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681062698364</t>
+    <t xml:space="preserve">11.9681072235107</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
@@ -3701,10 +3701,10 @@
     <t xml:space="preserve">11.8201236724854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4131717681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6710243225098</t>
+    <t xml:space="preserve">11.4131727218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
     <t xml:space="preserve">12.7265186309814</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">13.3646945953369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7172698974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6617755889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.430552482605</t>
+    <t xml:space="preserve">12.7172708511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6617765426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305534362793</t>
   </si>
   <si>
     <t xml:space="preserve">12.4028062820435</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">12.5137939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3473138809204</t>
+    <t xml:space="preserve">12.3473129272461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288145065308</t>
@@ -3752,22 +3752,22 @@
     <t xml:space="preserve">12.4398012161255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8016262054443</t>
+    <t xml:space="preserve">11.8016271591187</t>
   </si>
   <si>
     <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3565616607666</t>
+    <t xml:space="preserve">12.3565626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.764630317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8848676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6073989868164</t>
+    <t xml:space="preserve">11.8848667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073999404907</t>
   </si>
   <si>
     <t xml:space="preserve">11.551905632019</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">11.2929363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">10.6455116271973</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657480239868</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293724060059</t>
+    <t xml:space="preserve">11.8293714523315</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -5823,6 +5823,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.2299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.210000038147</t>
   </si>
 </sst>
 </file>
@@ -71213,7 +71216,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6911921296</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>61446</v>
@@ -71234,6 +71237,32 @@
         <v>1884</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6910763889</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>99150</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>11.3299999237061</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>11.1599998474121</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>11.2299995422363</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>11.210000038147</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -44,37 +44,37 @@
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15079474449158</t>
+    <t xml:space="preserve">2.150794506073</t>
   </si>
   <si>
     <t xml:space="preserve">2.13486289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07379078865051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02334046363831</t>
+    <t xml:space="preserve">2.09768843650818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07379102706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02333998680115</t>
   </si>
   <si>
     <t xml:space="preserve">2.06316995620728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05254864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.964923620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988354206085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439254283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802945137024</t>
+    <t xml:space="preserve">2.05254912376404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988330364227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439242362976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802968978882</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696753501892</t>
@@ -83,85 +83,85 @@
     <t xml:space="preserve">2.00209760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00156688690186</t>
+    <t xml:space="preserve">2.00156664848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.05998349189758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528454780579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909208297729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97820019721985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854121208191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774951457977</t>
+    <t xml:space="preserve">2.00528407096863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97820007801056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774927616119</t>
   </si>
   <si>
     <t xml:space="preserve">1.93943285942078</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91447269916534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9330598115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712832450867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633626937866</t>
+    <t xml:space="preserve">1.91447281837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306005001068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712784767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633650779724</t>
   </si>
   <si>
     <t xml:space="preserve">1.95589566230774</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94368100166321</t>
+    <t xml:space="preserve">1.94368124008179</t>
   </si>
   <si>
     <t xml:space="preserve">2.09237813949585</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07113575935364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441233634949</t>
+    <t xml:space="preserve">2.07113552093506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441257476807</t>
   </si>
   <si>
     <t xml:space="preserve">2.09450221061707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17203760147095</t>
+    <t xml:space="preserve">2.17203736305237</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13964247703552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299921035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442229270935</t>
+    <t xml:space="preserve">2.13964223861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299897193909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442205429077</t>
   </si>
   <si>
     <t xml:space="preserve">2.14548420906067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15344977378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14813923835754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132546424866</t>
+    <t xml:space="preserve">2.15344953536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132570266724</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831970214844</t>
@@ -170,52 +170,52 @@
     <t xml:space="preserve">2.18265843391418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22248792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495253562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955260276794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706712722778</t>
+    <t xml:space="preserve">2.22248768806458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565495491028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706736564636</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219791412354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.121586561203</t>
+    <t xml:space="preserve">2.12158632278442</t>
   </si>
   <si>
     <t xml:space="preserve">2.14017343521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12424159049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362075805664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582522392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05307984352112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06848001480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901097297668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11840009689331</t>
+    <t xml:space="preserve">2.12424182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1136200428009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582474708557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05307936668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06848049163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901144981384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11839962005615</t>
   </si>
   <si>
     <t xml:space="preserve">2.12477278709412</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">2.16141581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15557408332825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1773476600647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373054504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169658660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29418087005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25753784179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461175918579</t>
+    <t xml:space="preserve">2.15557432174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17734813690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373030662537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169634819031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29418134689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25753736495972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461199760437</t>
   </si>
   <si>
     <t xml:space="preserve">2.21452212333679</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">2.32073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888005256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604479789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44925093650818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5028874874115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775741577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555342674255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547255516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555023193359</t>
+    <t xml:space="preserve">2.34888052940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604432106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4492506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288796424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775717735291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5655529499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555047035217</t>
   </si>
   <si>
     <t xml:space="preserve">2.66718316078186</t>
@@ -296,52 +296,52 @@
     <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72161555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894074440002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98942255973816</t>
+    <t xml:space="preserve">2.72161531448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346632957458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523966789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894026756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98942279815674</t>
   </si>
   <si>
     <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94587635993958</t>
+    <t xml:space="preserve">2.94587683677673</t>
   </si>
   <si>
     <t xml:space="preserve">2.8413667678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91757225990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668559074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8979766368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959366798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516151428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685669898987</t>
+    <t xml:space="preserve">2.91757154464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959390640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516127586365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685646057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954882144928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693413734436</t>
+    <t xml:space="preserve">2.78693437576294</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531662940979</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">2.98289060592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84789872169495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77604794502258</t>
+    <t xml:space="preserve">2.84789824485779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.776047706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.86313939094543</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97418165206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813222885132</t>
+    <t xml:space="preserve">2.97418141365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813175201416</t>
   </si>
   <si>
     <t xml:space="preserve">2.9785361289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03514575958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820942878723</t>
+    <t xml:space="preserve">3.03514552116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820966720581</t>
   </si>
   <si>
     <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15707397460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29859757423401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730700492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214425086975</t>
+    <t xml:space="preserve">3.15707421302795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29859781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
   </si>
   <si>
     <t xml:space="preserve">3.29206657409668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28771185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158404350281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416565895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28988885879517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27900242805481</t>
+    <t xml:space="preserve">3.28771162033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28988909721375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
     <t xml:space="preserve">3.25722932815552</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">3.17449259757996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25505232810974</t>
+    <t xml:space="preserve">3.25505208969116</t>
   </si>
   <si>
     <t xml:space="preserve">3.25940680503845</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35085344314575</t>
+    <t xml:space="preserve">3.35085320472717</t>
   </si>
   <si>
     <t xml:space="preserve">3.34432125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32472586631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28553462028503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247047424316</t>
+    <t xml:space="preserve">3.32472562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28553438186646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247071266174</t>
   </si>
   <si>
     <t xml:space="preserve">3.35303044319153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3203706741333</t>
+    <t xml:space="preserve">3.32037091255188</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682518959045</t>
@@ -461,7 +461,7 @@
     <t xml:space="preserve">3.31383919715881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3094847202301</t>
+    <t xml:space="preserve">3.30948448181152</t>
   </si>
   <si>
     <t xml:space="preserve">3.15054225921631</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">3.2093288898468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069761276245</t>
+    <t xml:space="preserve">3.25069785118103</t>
   </si>
   <si>
     <t xml:space="preserve">3.20061993598938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22239303588867</t>
+    <t xml:space="preserve">3.22239327430725</t>
   </si>
   <si>
     <t xml:space="preserve">3.09175515174866</t>
@@ -494,73 +494,73 @@
     <t xml:space="preserve">3.20497465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37262606620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141293525696</t>
+    <t xml:space="preserve">3.37262558937073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141269683838</t>
   </si>
   <si>
     <t xml:space="preserve">3.59253263473511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67962384223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824055671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01057243347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09330940246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
+    <t xml:space="preserve">3.67962431907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824031829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.010573387146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09330987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831751823425</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346570968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33716678619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23483419418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313829421997</t>
+    <t xml:space="preserve">4.19346475601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33716630935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23483324050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313877105713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68988847732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65722894668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64634227752686</t>
+    <t xml:space="preserve">4.68988752365112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65722799301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6463418006897</t>
   </si>
   <si>
     <t xml:space="preserve">4.75956153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95334053039551</t>
+    <t xml:space="preserve">4.95334005355835</t>
   </si>
   <si>
     <t xml:space="preserve">4.94245433807373</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72037029266357</t>
+    <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
     <t xml:space="preserve">4.74214267730713</t>
@@ -569,67 +569,67 @@
     <t xml:space="preserve">4.73778867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6441650390625</t>
+    <t xml:space="preserve">4.64416456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37418127059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35023069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34152126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22830152511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128799438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895492553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22612524032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572038650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36547231674194</t>
+    <t xml:space="preserve">4.37418079376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3415207862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22830247879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128751754761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895540237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22612476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24571990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36547136306763</t>
   </si>
   <si>
     <t xml:space="preserve">4.35458517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3393440246582</t>
+    <t xml:space="preserve">4.33934354782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.65940570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63763284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6158595085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851856231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72254705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59408712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66376066207886</t>
+    <t xml:space="preserve">4.63763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61586046218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72254800796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59408664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6637601852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.58973264694214</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">4.52441453933716</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73343324661255</t>
+    <t xml:space="preserve">4.73343372344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.64198732376099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78568935394287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77480173110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74649715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609325408936</t>
+    <t xml:space="preserve">4.78568840026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77480220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.746497631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7660927772522</t>
   </si>
   <si>
     <t xml:space="preserve">5.09921932220459</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38662147521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29082012176514</t>
+    <t xml:space="preserve">5.38662195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29082059860229</t>
   </si>
   <si>
     <t xml:space="preserve">5.25162935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22985696792603</t>
+    <t xml:space="preserve">5.22985649108887</t>
   </si>
   <si>
     <t xml:space="preserve">5.22767925262451</t>
@@ -680,16 +680,16 @@
     <t xml:space="preserve">5.20372915267944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03607749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11010551452637</t>
+    <t xml:space="preserve">5.03607797622681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11010599136353</t>
   </si>
   <si>
     <t xml:space="preserve">5.225501537323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27557992935181</t>
+    <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
     <t xml:space="preserve">5.31041669845581</t>
@@ -701,52 +701,52 @@
     <t xml:space="preserve">5.14494132995605</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220483779907</t>
+    <t xml:space="preserve">5.06220579147339</t>
   </si>
   <si>
     <t xml:space="preserve">4.90979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09050941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445999145508</t>
+    <t xml:space="preserve">5.09050989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043245315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11446046829224</t>
   </si>
   <si>
     <t xml:space="preserve">5.10139608383179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09268712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663770675659</t>
+    <t xml:space="preserve">5.09268760681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663722991943</t>
   </si>
   <si>
     <t xml:space="preserve">5.04478693008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736806869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98817729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584423065186</t>
+    <t xml:space="preserve">4.95769453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736854553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9881763458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8858437538147</t>
   </si>
   <si>
     <t xml:space="preserve">4.8662486076355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8553614616394</t>
+    <t xml:space="preserve">4.85536193847656</t>
   </si>
   <si>
     <t xml:space="preserve">4.8466534614563</t>
@@ -755,43 +755,43 @@
     <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73561191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004383087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7443208694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738430023193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117904663086</t>
+    <t xml:space="preserve">4.73561096191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004335403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74432039260864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738382339478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68117809295654</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052564620972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91850328445435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13841009140015</t>
+    <t xml:space="preserve">4.9185037612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1384105682373</t>
   </si>
   <si>
     <t xml:space="preserve">5.08397817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19719791412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881446838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0948634147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170679092407</t>
+    <t xml:space="preserve">5.19719696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881494522095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486484527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170774459839</t>
   </si>
   <si>
     <t xml:space="preserve">5.38444423675537</t>
@@ -800,28 +800,28 @@
     <t xml:space="preserve">5.41710376739502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55209589004517</t>
+    <t xml:space="preserve">5.55209541320801</t>
   </si>
   <si>
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134834289551</t>
+    <t xml:space="preserve">5.63918781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385251998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134929656982</t>
   </si>
   <si>
     <t xml:space="preserve">5.94400787353516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11383676528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81337118148804</t>
+    <t xml:space="preserve">6.11383724212646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81337070465088</t>
   </si>
   <si>
     <t xml:space="preserve">5.87868928909302</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97666788101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09641885757446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94836330413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98973178863525</t>
+    <t xml:space="preserve">5.97666835784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09641933441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94836282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98973226547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.00497245788574</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">5.98755407333374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0419864654541</t>
+    <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
     <t xml:space="preserve">6.05722761154175</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">5.96360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07464647293091</t>
+    <t xml:space="preserve">6.07464551925659</t>
   </si>
   <si>
     <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42301321029663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26842546463013</t>
+    <t xml:space="preserve">6.42301225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26842498779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.52969980239868</t>
@@ -890,58 +890,58 @@
     <t xml:space="preserve">6.58848762512207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80403852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0108814239502</t>
+    <t xml:space="preserve">6.804039478302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201711654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088237762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.06531429290771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1175684928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063287734985</t>
+    <t xml:space="preserve">7.11756896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3200569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1306324005127</t>
   </si>
   <si>
     <t xml:space="preserve">7.22425651550293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22207927703857</t>
+    <t xml:space="preserve">7.2220778465271</t>
   </si>
   <si>
     <t xml:space="preserve">7.11321449279785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29392957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666654586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360359191895</t>
+    <t xml:space="preserve">7.29392862319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666702270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360263824463</t>
   </si>
   <si>
     <t xml:space="preserve">7.2852201461792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30481576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19595050811768</t>
+    <t xml:space="preserve">7.30481481552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19595193862915</t>
   </si>
   <si>
     <t xml:space="preserve">6.46655893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22705602645874</t>
+    <t xml:space="preserve">6.2270565032959</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309064865112</t>
@@ -950,49 +950,49 @@
     <t xml:space="preserve">6.40123987197876</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61243772506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49704027175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316808700562</t>
+    <t xml:space="preserve">6.61243724822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49704122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316761016846</t>
   </si>
   <si>
     <t xml:space="preserve">6.57760047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52464389801025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45403575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91740274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76294612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652584075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58421945571899</t>
+    <t xml:space="preserve">6.52464437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56215524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45403623580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774164199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91740322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76294755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652536392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58422040939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.50478506088257</t>
@@ -1004,25 +1004,25 @@
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694980621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4341778755188</t>
+    <t xml:space="preserve">6.35694932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488416671753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43417739868164</t>
   </si>
   <si>
     <t xml:space="preserve">6.32826471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33267831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37460088729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057062149048</t>
+    <t xml:space="preserve">6.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3746018409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057014465332</t>
   </si>
   <si>
     <t xml:space="preserve">6.14291858673096</t>
@@ -1034,22 +1034,22 @@
     <t xml:space="preserve">5.95757150650024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91344213485718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240859985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93771314620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7854642868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95977830886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92006063461304</t>
+    <t xml:space="preserve">5.91344118118286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240907669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93771362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95977783203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9200611114502</t>
   </si>
   <si>
     <t xml:space="preserve">5.93329954147339</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">5.83621406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8472466468811</t>
+    <t xml:space="preserve">5.84724569320679</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846244812012</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">5.50744390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4699330329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60894393920898</t>
+    <t xml:space="preserve">5.46993350982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
     <t xml:space="preserve">5.73692083358765</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">5.76119232177734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89137697219849</t>
+    <t xml:space="preserve">5.89137649536133</t>
   </si>
   <si>
     <t xml:space="preserve">5.71485567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72147607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5912914276123</t>
+    <t xml:space="preserve">5.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59129095077515</t>
   </si>
   <si>
     <t xml:space="preserve">5.55819416046143</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">5.44345569610596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45007514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932441711426</t>
+    <t xml:space="preserve">5.45007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932537078857</t>
   </si>
   <si>
     <t xml:space="preserve">5.41918325424194</t>
@@ -1124,58 +1124,58 @@
     <t xml:space="preserve">5.56040048599243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48096609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52730226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45890092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41256475448608</t>
+    <t xml:space="preserve">5.48096561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52730178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45890140533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41256427764893</t>
   </si>
   <si>
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922578811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912763595581</t>
+    <t xml:space="preserve">5.56922674179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912715911865</t>
   </si>
   <si>
     <t xml:space="preserve">5.66410636901855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80311584472656</t>
+    <t xml:space="preserve">5.80311632156372</t>
   </si>
   <si>
     <t xml:space="preserve">5.86931133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030042648315</t>
+    <t xml:space="preserve">5.73030138015747</t>
   </si>
   <si>
     <t xml:space="preserve">6.08554887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96860408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532312393188</t>
+    <t xml:space="preserve">5.96860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532217025757</t>
   </si>
   <si>
     <t xml:space="preserve">5.63762807846069</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56481266021729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.478759765625</t>
+    <t xml:space="preserve">5.56481313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52068328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875928878784</t>
   </si>
   <si>
     <t xml:space="preserve">5.49420499801636</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">5.36181402206421</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782581329346</t>
+    <t xml:space="preserve">5.29782629013062</t>
   </si>
   <si>
     <t xml:space="preserve">5.22942447662354</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">5.25369548797607</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41477108001709</t>
+    <t xml:space="preserve">5.41477060317993</t>
   </si>
   <si>
     <t xml:space="preserve">5.39711904525757</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">5.2228045463562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14116382598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11909866333008</t>
+    <t xml:space="preserve">5.14116334915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11909914016724</t>
   </si>
   <si>
     <t xml:space="preserve">5.20735883712769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16764211654663</t>
+    <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233757019043</t>
@@ -1226,49 +1226,49 @@
     <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03745794296265</t>
+    <t xml:space="preserve">5.03745746612549</t>
   </si>
   <si>
     <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9646430015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95802402496338</t>
+    <t xml:space="preserve">4.96464395523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
   </si>
   <si>
     <t xml:space="preserve">4.97126245498657</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04848957061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576065063477</t>
+    <t xml:space="preserve">5.04849004745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19412040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576017379761</t>
   </si>
   <si>
     <t xml:space="preserve">5.22501134872437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24486923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689186096191</t>
+    <t xml:space="preserve">5.24486970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689233779907</t>
   </si>
   <si>
     <t xml:space="preserve">5.03083801269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87197017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72634029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089363098145</t>
+    <t xml:space="preserve">4.87196969985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72633981704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089458465576</t>
   </si>
   <si>
     <t xml:space="preserve">4.65131902694702</t>
@@ -1280,7 +1280,7 @@
     <t xml:space="preserve">5.21839141845703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60453081130981</t>
+    <t xml:space="preserve">5.60453033447266</t>
   </si>
   <si>
     <t xml:space="preserve">5.8119421005249</t>
@@ -1289,70 +1289,70 @@
     <t xml:space="preserve">5.84503984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76781177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.904616355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663850784302</t>
+    <t xml:space="preserve">5.76781225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663898468018</t>
   </si>
   <si>
     <t xml:space="preserve">5.81856203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65307426452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6398344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467197418213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376651763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348419189453</t>
+    <t xml:space="preserve">5.65307331085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63983488082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467149734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.023766040802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348323822021</t>
   </si>
   <si>
     <t xml:space="preserve">6.14071178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12526607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597379684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419191360474</t>
+    <t xml:space="preserve">6.12526559829712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
   </si>
   <si>
     <t xml:space="preserve">6.03479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80973529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034439086914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020275115967</t>
+    <t xml:space="preserve">5.80973625183105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034343719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020227432251</t>
   </si>
   <si>
     <t xml:space="preserve">5.82518100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74354028701782</t>
+    <t xml:space="preserve">5.74353981018066</t>
   </si>
   <si>
     <t xml:space="preserve">5.65086698532104</t>
@@ -1361,61 +1361,61 @@
     <t xml:space="preserve">5.61776924133301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63542175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935386657715</t>
+    <t xml:space="preserve">5.63542127609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935338973999</t>
   </si>
   <si>
     <t xml:space="preserve">5.85607290267944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71926879882812</t>
+    <t xml:space="preserve">5.71926832199097</t>
   </si>
   <si>
     <t xml:space="preserve">5.84283304214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03259372711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315837860107</t>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315885543823</t>
   </si>
   <si>
     <t xml:space="preserve">5.94433259963989</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235250473022</t>
+    <t xml:space="preserve">6.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235155105591</t>
   </si>
   <si>
     <t xml:space="preserve">6.52243757247925</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37239503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878730773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202716827393</t>
+    <t xml:space="preserve">6.37239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1693959236145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878778457642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202764511108</t>
   </si>
   <si>
     <t xml:space="preserve">5.9222674369812</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">5.68396472930908</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42800998687744</t>
+    <t xml:space="preserve">5.42800951004028</t>
   </si>
   <si>
     <t xml:space="preserve">5.76339912414551</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">5.87372493743896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97963666915894</t>
+    <t xml:space="preserve">5.97963714599609</t>
   </si>
   <si>
     <t xml:space="preserve">5.96198463439941</t>
@@ -1451,13 +1451,13 @@
     <t xml:space="preserve">6.27089595794678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35474300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543573379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571853637695</t>
+    <t xml:space="preserve">6.35474348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543668746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571949005127</t>
   </si>
   <si>
     <t xml:space="preserve">6.9284348487854</t>
@@ -1466,130 +1466,130 @@
     <t xml:space="preserve">6.90637016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10495567321777</t>
+    <t xml:space="preserve">7.10495615005493</t>
   </si>
   <si>
     <t xml:space="preserve">6.97697830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10054206848145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050001144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22851943969727</t>
+    <t xml:space="preserve">7.10054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22851991653442</t>
   </si>
   <si>
     <t xml:space="preserve">7.14908647537231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04758739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378240585327</t>
+    <t xml:space="preserve">7.0475869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378192901611</t>
   </si>
   <si>
     <t xml:space="preserve">7.06082582473755</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49330043792725</t>
+    <t xml:space="preserve">7.4933009147644</t>
   </si>
   <si>
     <t xml:space="preserve">7.32560682296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1843900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034481048584</t>
   </si>
   <si>
     <t xml:space="preserve">7.28147649765015</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25941181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
+    <t xml:space="preserve">7.25941133499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
   </si>
   <si>
     <t xml:space="preserve">7.06523895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25058507919312</t>
+    <t xml:space="preserve">7.25058603286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.21528100967407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21969413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6212797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5374321937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2196946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127828598022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56391000747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062808990479</t>
   </si>
   <si>
     <t xml:space="preserve">7.55508422851562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42710590362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738965988159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965112686157</t>
+    <t xml:space="preserve">7.42710638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965255737305</t>
   </si>
   <si>
     <t xml:space="preserve">6.62835073471069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84017419815063</t>
+    <t xml:space="preserve">6.84017515182495</t>
   </si>
   <si>
     <t xml:space="preserve">6.63717651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51802587509155</t>
+    <t xml:space="preserve">6.51802539825439</t>
   </si>
   <si>
     <t xml:space="preserve">6.6195240020752</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5445032119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219682693481</t>
+    <t xml:space="preserve">6.54450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
     <t xml:space="preserve">6.38247346878052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66424989700317</t>
+    <t xml:space="preserve">6.30643796920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
   </si>
   <si>
     <t xml:space="preserve">6.60163354873657</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">6.54796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65977716445923</t>
+    <t xml:space="preserve">6.65977764129639</t>
   </si>
   <si>
     <t xml:space="preserve">6.57926988601685</t>
@@ -1610,43 +1610,43 @@
     <t xml:space="preserve">6.48534440994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71344947814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817632675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505174636841</t>
+    <t xml:space="preserve">6.71344995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505126953125</t>
   </si>
   <si>
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087167739868</t>
+    <t xml:space="preserve">6.48087120056152</t>
   </si>
   <si>
     <t xml:space="preserve">6.44956350326538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41825437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985712051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593069076538</t>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31985664367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593116760254</t>
   </si>
   <si>
     <t xml:space="preserve">6.22145795822144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171159744263</t>
+    <t xml:space="preserve">6.12305879592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171207427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.14095020294189</t>
@@ -1658,19 +1658,16 @@
     <t xml:space="preserve">6.20356750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34669160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854894638062</t>
+    <t xml:space="preserve">6.34669256210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829387664795</t>
   </si>
   <si>
     <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33774662017822</t>
+    <t xml:space="preserve">6.33774709701538</t>
   </si>
   <si>
     <t xml:space="preserve">6.58821535110474</t>
@@ -1679,76 +1676,76 @@
     <t xml:space="preserve">6.48981761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53007125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061756134033</t>
+    <t xml:space="preserve">6.53007078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141845703125</t>
+    <t xml:space="preserve">6.39141893386841</t>
   </si>
   <si>
     <t xml:space="preserve">6.4003643989563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37352848052979</t>
+    <t xml:space="preserve">6.37352752685547</t>
   </si>
   <si>
     <t xml:space="preserve">6.42719984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4316725730896</t>
+    <t xml:space="preserve">6.43167304992676</t>
   </si>
   <si>
     <t xml:space="preserve">6.50323486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934936523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298170089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1006965637207</t>
+    <t xml:space="preserve">6.32880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014978408813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10069608688354</t>
   </si>
   <si>
     <t xml:space="preserve">6.39589166641235</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.474524974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33587312698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194765090942</t>
+    <t xml:space="preserve">6.18567752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47452592849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3358736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
   </si>
   <si>
     <t xml:space="preserve">5.08093214035034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97358798980713</t>
+    <t xml:space="preserve">4.97358846664429</t>
   </si>
   <si>
     <t xml:space="preserve">5.13013124465942</t>
@@ -1757,16 +1754,19 @@
     <t xml:space="preserve">5.01831483840942</t>
   </si>
   <si>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05409622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886161804199</t>
+    <t xml:space="preserve">5.05409669876099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653745651245</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">4.61577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74995565414429</t>
+    <t xml:space="preserve">4.74995517730713</t>
   </si>
   <si>
     <t xml:space="preserve">4.71417474746704</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">4.37201642990112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12825727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20876502990723</t>
+    <t xml:space="preserve">4.12825679779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20876550674438</t>
   </si>
   <si>
     <t xml:space="preserve">4.11483907699585</t>
@@ -1805,13 +1805,13 @@
     <t xml:space="preserve">3.95829653739929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08353042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15509366989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049364089966</t>
+    <t xml:space="preserve">4.08353090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1550931930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1304931640625</t>
   </si>
   <si>
     <t xml:space="preserve">4.01867723464966</t>
@@ -1820,7 +1820,7 @@
     <t xml:space="preserve">3.86884307861328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70559167861938</t>
+    <t xml:space="preserve">3.70559144020081</t>
   </si>
   <si>
     <t xml:space="preserve">3.75702691078186</t>
@@ -1829,46 +1829,46 @@
     <t xml:space="preserve">3.81740760803223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73466372489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648060798645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500515937805</t>
+    <t xml:space="preserve">3.73466420173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8375346660614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84647989273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500587463379</t>
   </si>
   <si>
     <t xml:space="preserve">4.15732955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00302267074585</t>
+    <t xml:space="preserve">4.00302314758301</t>
   </si>
   <si>
     <t xml:space="preserve">3.9247510433197</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93146061897278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264197349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331581115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86213493347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35896134376526</t>
+    <t xml:space="preserve">3.93146085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331604957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213421821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424424171448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35896158218384</t>
   </si>
   <si>
     <t xml:space="preserve">3.24267220497131</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">3.03245782852173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140257835388</t>
+    <t xml:space="preserve">3.04140329360962</t>
   </si>
   <si>
     <t xml:space="preserve">3.16216468811035</t>
@@ -1886,28 +1886,28 @@
     <t xml:space="preserve">3.38356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38803315162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26950836181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22701811790466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45288681983948</t>
+    <t xml:space="preserve">3.38803339004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26950812339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22701835632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.39474248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4886679649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5155041217804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870746612549</t>
+    <t xml:space="preserve">3.48866820335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51550388336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870698928833</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714493751526</t>
@@ -1916,130 +1916,130 @@
     <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735052108765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182253837585</t>
+    <t xml:space="preserve">2.92735075950623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182277679443</t>
   </si>
   <si>
     <t xml:space="preserve">3.01009440422058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10402011871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03916668891907</t>
+    <t xml:space="preserve">3.1040198802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03916645050049</t>
   </si>
   <si>
     <t xml:space="preserve">2.95642280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88486003875732</t>
+    <t xml:space="preserve">2.88485980033875</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751660346985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844408035278</t>
+    <t xml:space="preserve">2.77751636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83342480659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933253288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07271146774292</t>
+    <t xml:space="preserve">2.83342456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933277130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271099090576</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16887331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22925448417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15992856025696</t>
+    <t xml:space="preserve">3.16887354850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22925400733948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254538536072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2359631061554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18676424026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19347262382507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3209433555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54233980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339505195618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49537682533264</t>
+    <t xml:space="preserve">3.23596334457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18676376342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19347286224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972273826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53339457511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4953773021698</t>
   </si>
   <si>
     <t xml:space="preserve">3.61166596412659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66533780097961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57588481903076</t>
+    <t xml:space="preserve">3.66533756256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588458061218</t>
   </si>
   <si>
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221274375916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5825936794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444911003113</t>
+    <t xml:space="preserve">3.52221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58259391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723225593567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444934844971</t>
   </si>
   <si>
     <t xml:space="preserve">3.58483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69441032409668</t>
+    <t xml:space="preserve">3.6944100856781</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61390233039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399012565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89567971229553</t>
+    <t xml:space="preserve">3.61390256881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335483551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398988723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89567995071411</t>
   </si>
   <si>
     <t xml:space="preserve">3.77268123626709</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">3.83306241035461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85766196250916</t>
+    <t xml:space="preserve">3.85766124725342</t>
   </si>
   <si>
     <t xml:space="preserve">3.94040608406067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99184155464172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011318206787</t>
+    <t xml:space="preserve">3.99184131622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011270523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.13272953033447</t>
@@ -2075,22 +2075,22 @@
     <t xml:space="preserve">3.9493510723114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00525903701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02762222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842335700989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112869262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28256320953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38319778442383</t>
+    <t xml:space="preserve">4.00525951385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02762269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842311859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112821578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28256368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.42792463302612</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">4.16627502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27809047698975</t>
+    <t xml:space="preserve">4.20429277420044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27809143066406</t>
   </si>
   <si>
     <t xml:space="preserve">4.20205640792847</t>
@@ -2114,46 +2114,46 @@
     <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29150915145874</t>
+    <t xml:space="preserve">4.29150867462158</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24007368087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25349187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19982004165649</t>
+    <t xml:space="preserve">4.24007272720337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25349140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19981956481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1864013671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914548873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171473503113</t>
+    <t xml:space="preserve">4.15285682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18640184402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914644241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171378135681</t>
   </si>
   <si>
     <t xml:space="preserve">3.93369698524475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631381034851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0388035774231</t>
+    <t xml:space="preserve">3.90015244483948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880405426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9180428981781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778902053833</t>
+    <t xml:space="preserve">3.91804265975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778925895691</t>
   </si>
   <si>
     <t xml:space="preserve">3.76820874214172</t>
@@ -2183,19 +2183,19 @@
     <t xml:space="preserve">4.0991849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82411742210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9569308757782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8813648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76228976249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626088142395</t>
+    <t xml:space="preserve">3.8241171836853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693063735962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136410713196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76229023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626064300537</t>
   </si>
   <si>
     <t xml:space="preserve">3.76458024978638</t>
@@ -2207,34 +2207,34 @@
     <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73252129554749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84243631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220454216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487215995789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96609044075012</t>
+    <t xml:space="preserve">3.73252105712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84243607521057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96608996391296</t>
   </si>
   <si>
     <t xml:space="preserve">3.89739370346069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95006155967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
+    <t xml:space="preserve">3.95006108283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449479103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655255317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440909385681</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165601730347</t>
@@ -2252,25 +2252,25 @@
     <t xml:space="preserve">4.11264276504517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10119390487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14470148086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18820953369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28438520431519</t>
+    <t xml:space="preserve">4.10119342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14470195770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18821048736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751493453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28438472747803</t>
   </si>
   <si>
     <t xml:space="preserve">4.31415319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803909301758</t>
+    <t xml:space="preserve">4.40803861618042</t>
   </si>
   <si>
     <t xml:space="preserve">4.30270433425903</t>
@@ -2282,16 +2282,16 @@
     <t xml:space="preserve">4.2454571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33247232437134</t>
+    <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.23858737945557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22255802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19507884979248</t>
+    <t xml:space="preserve">4.22255754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774694442749</t>
@@ -2300,7 +2300,7 @@
     <t xml:space="preserve">4.1744704246521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05997562408447</t>
+    <t xml:space="preserve">4.05997610092163</t>
   </si>
   <si>
     <t xml:space="preserve">4.09890365600586</t>
@@ -2309,13 +2309,13 @@
     <t xml:space="preserve">4.15157127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16302108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1240930557251</t>
+    <t xml:space="preserve">4.16302061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12409257888794</t>
   </si>
   <si>
     <t xml:space="preserve">4.07600498199463</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">4.00730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05539512634277</t>
+    <t xml:space="preserve">4.05539560317993</t>
   </si>
   <si>
     <t xml:space="preserve">3.97067022323608</t>
@@ -2333,37 +2333,37 @@
     <t xml:space="preserve">3.945481300354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84701538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594365119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678456306458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159587860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235061645508</t>
+    <t xml:space="preserve">3.84701561927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594388961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678480148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235085487366</t>
   </si>
   <si>
     <t xml:space="preserve">4.00043869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98211932182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13096237182617</t>
+    <t xml:space="preserve">3.98211908340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16760110855103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04394674301147</t>
+    <t xml:space="preserve">4.16760063171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
     <t xml:space="preserve">4.0531063079834</t>
@@ -2378,10 +2378,10 @@
     <t xml:space="preserve">4.06226539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34392213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3370532989502</t>
+    <t xml:space="preserve">4.34392166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33705186843872</t>
   </si>
   <si>
     <t xml:space="preserve">4.31873369216919</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">4.60268020629883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00112009048462</t>
+    <t xml:space="preserve">5.00112056732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.17515277862549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33086490631104</t>
+    <t xml:space="preserve">5.33086538314819</t>
   </si>
   <si>
     <t xml:space="preserve">5.35834360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62855052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48657655715942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39040231704712</t>
+    <t xml:space="preserve">5.62855100631714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48657703399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39040279388428</t>
   </si>
   <si>
     <t xml:space="preserve">5.61023187637329</t>
@@ -2417,40 +2417,40 @@
     <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527448654175</t>
+    <t xml:space="preserve">5.55527496337891</t>
   </si>
   <si>
     <t xml:space="preserve">5.45451879501343</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48199796676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27590799331665</t>
+    <t xml:space="preserve">5.4819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26674795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27590751647949</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993925094604</t>
+    <t xml:space="preserve">5.4499397277832</t>
   </si>
   <si>
     <t xml:space="preserve">5.3446044921875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47283792495728</t>
+    <t xml:space="preserve">5.47283840179443</t>
   </si>
   <si>
     <t xml:space="preserve">5.45909881591797</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55985403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69724702835083</t>
+    <t xml:space="preserve">5.55985450744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69724750518799</t>
   </si>
   <si>
     <t xml:space="preserve">5.72930574417114</t>
@@ -2462,10 +2462,10 @@
     <t xml:space="preserve">5.74304580688477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77968311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72472620010376</t>
+    <t xml:space="preserve">5.7796835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7247257232666</t>
   </si>
   <si>
     <t xml:space="preserve">5.67892789840698</t>
@@ -2474,22 +2474,22 @@
     <t xml:space="preserve">5.71556615829468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80716276168823</t>
+    <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.71098661422729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82090187072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89875745773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04989051818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12316751480103</t>
+    <t xml:space="preserve">5.82090091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89875793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04989099502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.22392225265503</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">6.08652877807617</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99493312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02241182327271</t>
+    <t xml:space="preserve">5.99493360519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02241134643555</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">7.10324001312256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941568374634</t>
+    <t xml:space="preserve">7.1994161605835</t>
   </si>
   <si>
     <t xml:space="preserve">7.28643131256104</t>
@@ -2522,19 +2522,19 @@
     <t xml:space="preserve">7.61159706115723</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61617469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600521087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62533521652222</t>
+    <t xml:space="preserve">7.61617612838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600568771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113256454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62533473968506</t>
   </si>
   <si>
     <t xml:space="preserve">7.16735696792603</t>
@@ -2543,19 +2543,19 @@
     <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41924476623535</t>
+    <t xml:space="preserve">7.41924571990967</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29101085662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697912216187</t>
+    <t xml:space="preserve">7.29101133346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697959899902</t>
   </si>
   <si>
     <t xml:space="preserve">7.15361785888672</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3963451385498</t>
+    <t xml:space="preserve">7.39634561538696</t>
   </si>
   <si>
     <t xml:space="preserve">7.37802743911743</t>
@@ -2573,31 +2573,31 @@
     <t xml:space="preserve">7.57495784759521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9184422492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85890293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571353912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655302047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428737640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12155914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41466522216797</t>
+    <t xml:space="preserve">7.91844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85890340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655349731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428785324097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130395889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12155961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41466569900513</t>
   </si>
   <si>
     <t xml:space="preserve">7.25895309448242</t>
@@ -2606,34 +2606,34 @@
     <t xml:space="preserve">7.30475044250488</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22231483459473</t>
+    <t xml:space="preserve">7.22231435775757</t>
   </si>
   <si>
     <t xml:space="preserve">7.52916049957275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43756437301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48794269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52000045776367</t>
+    <t xml:space="preserve">7.4375638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48794174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17651653289795</t>
+    <t xml:space="preserve">7.17651700973511</t>
   </si>
   <si>
     <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51244831085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702785491943</t>
+    <t xml:space="preserve">6.51244878768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702833175659</t>
   </si>
   <si>
     <t xml:space="preserve">6.74143743515015</t>
@@ -2642,28 +2642,28 @@
     <t xml:space="preserve">6.79639434814453</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71853828430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76891613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61778259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538442611694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89714956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097484588623</t>
+    <t xml:space="preserve">6.71853876113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76891660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6177830696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89257001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89715051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.828453540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097436904907</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732048034668</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">6.83303308486938</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76433610916138</t>
+    <t xml:space="preserve">6.76433706283569</t>
   </si>
   <si>
     <t xml:space="preserve">6.63610219955444</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11858654022217</t>
+    <t xml:space="preserve">6.11858701705933</t>
   </si>
   <si>
     <t xml:space="preserve">5.96745443344116</t>
@@ -2690,37 +2690,37 @@
     <t xml:space="preserve">5.63771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77052402496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72014617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47741794586182</t>
+    <t xml:space="preserve">5.77052354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72014665603638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47741746902466</t>
   </si>
   <si>
     <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75381231307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59809970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63931846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21110820770264</t>
+    <t xml:space="preserve">4.75381278991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59810018539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63931798934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21110868453979</t>
   </si>
   <si>
     <t xml:space="preserve">3.8149573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66382503509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32034134864807</t>
+    <t xml:space="preserve">3.66382455825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32034111022949</t>
   </si>
   <si>
     <t xml:space="preserve">3.22416567802429</t>
@@ -2729,49 +2729,49 @@
     <t xml:space="preserve">3.18294739723206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22645592689514</t>
+    <t xml:space="preserve">3.22645568847656</t>
   </si>
   <si>
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304521560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61344718933105</t>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304545402527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61344695091248</t>
   </si>
   <si>
     <t xml:space="preserve">3.50353240966797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67069458961487</t>
+    <t xml:space="preserve">3.67069435119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70962238311768</t>
+    <t xml:space="preserve">3.70962285995483</t>
   </si>
   <si>
     <t xml:space="preserve">3.6226065158844</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79663801193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168086051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06684541702271</t>
+    <t xml:space="preserve">3.79663848876953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168133735657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06684494018555</t>
   </si>
   <si>
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3828501701355</t>
+    <t xml:space="preserve">4.38284969329834</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722326278687</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432363510132</t>
+    <t xml:space="preserve">4.09432411193848</t>
   </si>
   <si>
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612668991089</t>
+    <t xml:space="preserve">4.45612621307373</t>
   </si>
   <si>
     <t xml:space="preserve">4.35995149612427</t>
@@ -2798,13 +2798,13 @@
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2637767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32331323623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35537147521973</t>
+    <t xml:space="preserve">4.26377630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32331275939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35537242889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.30957412719727</t>
@@ -2813,34 +2813,34 @@
     <t xml:space="preserve">4.30499410629272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17675971984863</t>
+    <t xml:space="preserve">4.17676019668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.67137670516968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5248236656189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38743019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406845092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7515230178833</t>
+    <t xml:space="preserve">4.52482318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48360586166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38742971420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406892776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90036535263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.888916015625</t>
+    <t xml:space="preserve">4.90036582946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88891553878784</t>
   </si>
   <si>
     <t xml:space="preserve">5.04920816421509</t>
@@ -2849,46 +2849,46 @@
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48428821563721</t>
+    <t xml:space="preserve">5.23239946365356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
     <t xml:space="preserve">5.34689426422119</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16370296478271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19805145263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254577636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25529909133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39269161224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20950126647949</t>
+    <t xml:space="preserve">5.16370248794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93471336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19805192947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254625320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25529861450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39269208908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20950078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14080381393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27819728851318</t>
+    <t xml:space="preserve">5.14080429077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27819681167603</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384880065918</t>
@@ -2900,22 +2900,22 @@
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01486015319824</t>
+    <t xml:space="preserve">5.0148606300354</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0606575012207</t>
+    <t xml:space="preserve">5.06065797805786</t>
   </si>
   <si>
     <t xml:space="preserve">5.22094964981079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210683822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645532608032</t>
+    <t xml:space="preserve">5.07210779190063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645580291748</t>
   </si>
   <si>
     <t xml:space="preserve">5.12935447692871</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">5.3239951133728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544445037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03775882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355665206909</t>
+    <t xml:space="preserve">5.33544492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355760574341</t>
   </si>
   <si>
     <t xml:space="preserve">4.96906280517578</t>
@@ -2948,13 +2948,13 @@
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99196147918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00341081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57978057861328</t>
+    <t xml:space="preserve">4.99196100234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00341033935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57978105545044</t>
   </si>
   <si>
     <t xml:space="preserve">4.19049978256226</t>
@@ -2963,25 +2963,25 @@
     <t xml:space="preserve">4.21339845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08058404922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30041408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34163236618042</t>
+    <t xml:space="preserve">4.08058500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30041456222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34163188934326</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412906646729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54153537750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62168073654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907468795776</t>
+    <t xml:space="preserve">5.54153442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62168121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907421112061</t>
   </si>
   <si>
     <t xml:space="preserve">5.73617553710938</t>
@@ -2990,43 +2990,43 @@
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64457988739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66747903823853</t>
+    <t xml:space="preserve">5.64457941055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66747856140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70182752609253</t>
+    <t xml:space="preserve">5.70182657241821</t>
   </si>
   <si>
     <t xml:space="preserve">5.81632137298584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14835643768311</t>
+    <t xml:space="preserve">6.14835548400879</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516418457031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95371580123901</t>
+    <t xml:space="preserve">5.9537148475647</t>
   </si>
   <si>
     <t xml:space="preserve">5.87356901168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91936635971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09110879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1254563331604</t>
+    <t xml:space="preserve">5.91936731338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09110832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415330886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12545680999756</t>
   </si>
   <si>
     <t xml:space="preserve">6.15980529785156</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">6.07965850830078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13690614700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2170524597168</t>
+    <t xml:space="preserve">6.13690567016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
     <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32009744644165</t>
+    <t xml:space="preserve">6.32009792327881</t>
   </si>
   <si>
     <t xml:space="preserve">6.36589479446411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48038959503174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618837356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53763675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56053638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60633373260498</t>
+    <t xml:space="preserve">6.48038911819458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618741989136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53763723373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56053590774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
     <t xml:space="preserve">6.58343505859375</t>
@@ -3074,28 +3074,28 @@
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169261932373</t>
+    <t xml:space="preserve">6.41169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894073486328</t>
+    <t xml:space="preserve">6.46894025802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20560312271118</t>
+    <t xml:space="preserve">6.20560264587402</t>
   </si>
   <si>
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328922271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66358089447021</t>
+    <t xml:space="preserve">6.50328826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147385597229</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">6.78952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75517654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68648052215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70937871932983</t>
+    <t xml:space="preserve">6.75517702102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6864800453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70937919616699</t>
   </si>
   <si>
     <t xml:space="preserve">6.77807569503784</t>
@@ -3122,37 +3122,37 @@
     <t xml:space="preserve">6.40024423599243</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154678344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5490870475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86967086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417850494385</t>
+    <t xml:space="preserve">6.37734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154773712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54908657073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86967134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417755126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17490768432617</t>
+    <t xml:space="preserve">8.17490863800049</t>
   </si>
   <si>
     <t xml:space="preserve">8.01461601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99171829223633</t>
+    <t xml:space="preserve">7.99171733856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041431427002</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">8.02606582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12911128997803</t>
+    <t xml:space="preserve">8.12911033630371</t>
   </si>
   <si>
     <t xml:space="preserve">8.1062126159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03751468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0031681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447113037109</t>
+    <t xml:space="preserve">8.03751373291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447208404541</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331203460693</t>
@@ -3182,13 +3182,13 @@
     <t xml:space="preserve">8.31230163574219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30085182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28940296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33520221710205</t>
+    <t xml:space="preserve">8.30085372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28940391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33520126342773</t>
   </si>
   <si>
     <t xml:space="preserve">8.2779541015625</t>
@@ -3197,52 +3197,52 @@
     <t xml:space="preserve">8.15200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766147613525</t>
+    <t xml:space="preserve">8.11766242980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.18635845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34665107727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215675354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16345977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186317443848</t>
+    <t xml:space="preserve">8.34665012359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215579986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16346073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186508178711</t>
   </si>
   <si>
     <t xml:space="preserve">8.20925712585449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94592046737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8428750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.923020362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997632980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577224731445</t>
+    <t xml:space="preserve">7.94591951370239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84287548065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92302083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997585296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577320098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.38099956512451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15956115722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99926948547363</t>
+    <t xml:space="preserve">9.15956211090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99926853179932</t>
   </si>
   <si>
     <t xml:space="preserve">9.20536041259766</t>
@@ -3254,13 +3254,13 @@
     <t xml:space="preserve">9.65356349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60731887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78073787689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71136856079102</t>
+    <t xml:space="preserve">9.60731983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78073692321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71136951446533</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
@@ -3269,25 +3269,25 @@
     <t xml:space="preserve">10.2894268035889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3009881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3241100311279</t>
+    <t xml:space="preserve">10.300989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
     <t xml:space="preserve">10.5206499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3587951660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5437717437744</t>
+    <t xml:space="preserve">10.3587942123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975290298462</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3356733322144</t>
+    <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.4628448486328</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">10.3703546524048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7403125762939</t>
+    <t xml:space="preserve">10.7403116226196</t>
   </si>
   <si>
     <t xml:space="preserve">10.4744052886963</t>
@@ -3311,13 +3311,13 @@
     <t xml:space="preserve">10.1044483184814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2663040161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3934783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0582056045532</t>
+    <t xml:space="preserve">10.2663059234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3934774398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0582036972046</t>
   </si>
   <si>
     <t xml:space="preserve">9.9541540145874</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">10.1506938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697650909424</t>
+    <t xml:space="preserve">10.0697660446167</t>
   </si>
   <si>
     <t xml:space="preserve">10.092887878418</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">10.2547435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2200613021851</t>
+    <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.4859666824341</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">10.1391315460205</t>
   </si>
   <si>
-    <t xml:space="preserve">11.191198348999</t>
+    <t xml:space="preserve">11.1911964416504</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056610107422</t>
@@ -3371,46 +3371,46 @@
     <t xml:space="preserve">11.9052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9015140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.746132850647</t>
+    <t xml:space="preserve">11.9015159606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7461318969727</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426568984985</t>
+    <t xml:space="preserve">11.5426559448242</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3206825256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6536445617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3946743011475</t>
+    <t xml:space="preserve">11.5796527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4501676559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576784133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3206815719604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6536426544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3946733474731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686651229858</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0975923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8571186065674</t>
+    <t xml:space="preserve">12.0975914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
     <t xml:space="preserve">12.0605964660645</t>
@@ -3425,10 +3425,10 @@
     <t xml:space="preserve">12.3010683059692</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8941144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299945831299</t>
+    <t xml:space="preserve">11.894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299955368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144151687622</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
+    <t xml:space="preserve">13.5034275054932</t>
   </si>
   <si>
     <t xml:space="preserve">13.8178911209106</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">14.631796836853</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0398664474487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7439002990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623987197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4294376373291</t>
+    <t xml:space="preserve">14.0398654937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7438993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4109392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623996734619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4294385910034</t>
   </si>
   <si>
     <t xml:space="preserve">13.0409822463989</t>
@@ -3488,31 +3488,31 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0779781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4468173980713</t>
+    <t xml:space="preserve">12.9114980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.077977180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
     <t xml:space="preserve">15.4457025527954</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7786626815796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.555570602417</t>
+    <t xml:space="preserve">15.5011949539185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7786617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5555725097656</t>
   </si>
   <si>
     <t xml:space="preserve">16.3705959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5370769500732</t>
+    <t xml:space="preserve">16.537073135376</t>
   </si>
   <si>
     <t xml:space="preserve">16.2596073150635</t>
@@ -3521,19 +3521,19 @@
     <t xml:space="preserve">16.3520965576172</t>
   </si>
   <si>
-    <t xml:space="preserve">16.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7971591949463</t>
+    <t xml:space="preserve">16.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7971601486206</t>
   </si>
   <si>
     <t xml:space="preserve">16.1486186981201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0006351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.908148765564</t>
+    <t xml:space="preserve">16.0006370544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9081497192383</t>
   </si>
   <si>
     <t xml:space="preserve">15.5196933746338</t>
@@ -3542,10 +3542,10 @@
     <t xml:space="preserve">15.4642000198364</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8896522521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416677474976</t>
+    <t xml:space="preserve">15.8896512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416687011719</t>
   </si>
   <si>
     <t xml:space="preserve">15.8341579437256</t>
@@ -3566,31 +3566,31 @@
     <t xml:space="preserve">13.6329126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.6514120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369483947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0583639144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1693496704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8918828964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098224639893</t>
+    <t xml:space="preserve">14.0583629608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1693506240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.891884803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098215103149</t>
   </si>
   <si>
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993936538696</t>
+    <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7808961868286</t>
@@ -3599,16 +3599,16 @@
     <t xml:space="preserve">13.2629556655884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5404233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924398422241</t>
+    <t xml:space="preserve">13.5404243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924417495728</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9658756256104</t>
+    <t xml:space="preserve">13.9658737182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
@@ -3617,22 +3617,22 @@
     <t xml:space="preserve">14.2988357543945</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2803382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1138582229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9484920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1334714889526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0594806671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4479341506958</t>
+    <t xml:space="preserve">14.2803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1138572692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9484930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1334705352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0594797134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4479351043701</t>
   </si>
   <si>
     <t xml:space="preserve">12.2085790634155</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">12.6340284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3380641937256</t>
+    <t xml:space="preserve">12.3380651473999</t>
   </si>
   <si>
     <t xml:space="preserve">11.8386220932007</t>
@@ -3668,13 +3668,13 @@
     <t xml:space="preserve">11.9496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6721420288086</t>
+    <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0051021575928</t>
+    <t xml:space="preserve">12.0051031112671</t>
   </si>
   <si>
     <t xml:space="preserve">11.7831287384033</t>
@@ -3686,10 +3686,10 @@
     <t xml:space="preserve">11.9681072235107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0247163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8582353591919</t>
+    <t xml:space="preserve">11.0247173309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8582363128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.5067768096924</t>
@@ -3701,13 +3701,13 @@
     <t xml:space="preserve">11.8201246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4131727218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6710243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265195846558</t>
+    <t xml:space="preserve">11.4131717681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6710252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265186309814</t>
   </si>
   <si>
     <t xml:space="preserve">12.8005104064941</t>
@@ -3716,10 +3716,10 @@
     <t xml:space="preserve">13.2259607315063</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3646945953369</t>
+    <t xml:space="preserve">13.3276987075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3646936416626</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
@@ -3728,16 +3728,16 @@
     <t xml:space="preserve">12.6617765426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3473138809204</t>
+    <t xml:space="preserve">12.4305543899536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028053283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137929916382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3473129272461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288154602051</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155319213867</t>
+    <t xml:space="preserve">12.6155309677124</t>
   </si>
   <si>
     <t xml:space="preserve">12.4398021697998</t>
@@ -3758,22 +3758,22 @@
     <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3565607070923</t>
+    <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
     <t xml:space="preserve">11.764630317688</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8848676681519</t>
+    <t xml:space="preserve">11.8848667144775</t>
   </si>
   <si>
     <t xml:space="preserve">11.6073989868164</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5519046783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2929363250732</t>
+    <t xml:space="preserve">11.551905632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2929353713989</t>
   </si>
   <si>
     <t xml:space="preserve">10.6455106735229</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5704040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4316692352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8293724060059</t>
+    <t xml:space="preserve">11.5704030990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4316682815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605554580688</t>
+    <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">11.569953918457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6827392578125</t>
+    <t xml:space="preserve">11.6827402114868</t>
   </si>
   <si>
     <t xml:space="preserve">12.1432819366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.85191822052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6639423370361</t>
+    <t xml:space="preserve">11.8519172668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6639413833618</t>
   </si>
   <si>
     <t xml:space="preserve">11.7579298019409</t>
@@ -3824,25 +3824,25 @@
     <t xml:space="preserve">11.974102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398960113525</t>
+    <t xml:space="preserve">12.0398950576782</t>
   </si>
   <si>
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658039093018</t>
+    <t xml:space="preserve">11.8895130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658048629761</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5642786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0530185699463</t>
+    <t xml:space="preserve">10.5642795562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.053017616272</t>
   </si>
   <si>
     <t xml:space="preserve">10.5830764770508</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
+    <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">10.9214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0624170303345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4571666717529</t>
+    <t xml:space="preserve">11.0624179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631801605225</t>
+    <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075487136841</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">11.9365072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297334671021</t>
+    <t xml:space="preserve">11.7297325134277</t>
   </si>
   <si>
     <t xml:space="preserve">12.096287727356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3876523971558</t>
+    <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6414194107056</t>
+    <t xml:space="preserve">12.6414184570312</t>
   </si>
   <si>
     <t xml:space="preserve">12.6884136199951</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">12.5474319458008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5286331176758</t>
+    <t xml:space="preserve">12.5286340713501</t>
   </si>
   <si>
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.998574256897</t>
+    <t xml:space="preserve">12.8481941223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9985752105713</t>
   </si>
   <si>
     <t xml:space="preserve">13.1677541732788</t>
@@ -3920,22 +3920,22 @@
     <t xml:space="preserve">13.4685163497925</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6188974380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5625057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6094970703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7034864425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6564922332764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741081237793</t>
+    <t xml:space="preserve">13.618896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5625047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6094980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7034873962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6564931869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6752901077271</t>
@@ -3956,25 +3956,25 @@
     <t xml:space="preserve">13.1583547592163</t>
   </si>
   <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">13.3369312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0643653869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1113605499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9139842987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8199977874756</t>
+    <t xml:space="preserve">13.0925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0643663406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1113595962524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9139852523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8199968338013</t>
   </si>
   <si>
     <t xml:space="preserve">13.0361700057983</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">13.017373085022</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0549688339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8669919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260084152222</t>
+    <t xml:space="preserve">13.054967880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8669900894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260093688965</t>
   </si>
   <si>
     <t xml:space="preserve">12.4628419876099</t>
@@ -3998,10 +3998,10 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5756282806396</t>
+    <t xml:space="preserve">12.5850276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5756273269653</t>
   </si>
   <si>
     <t xml:space="preserve">12.6602172851562</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692138671875</t>
+    <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
     <t xml:space="preserve">11.391375541687</t>
@@ -4031,22 +4031,22 @@
     <t xml:space="preserve">11.1000127792358</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5548801422119</t>
+    <t xml:space="preserve">10.5548791885376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984865188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582670211792</t>
+    <t xml:space="preserve">10.4984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582679748535</t>
   </si>
   <si>
     <t xml:space="preserve">10.3951005935669</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9778270721436</t>
+    <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
     <t xml:space="preserve">11.4665660858154</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">10.7898502349854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9684295654297</t>
+    <t xml:space="preserve">10.9684286117554</t>
   </si>
   <si>
     <t xml:space="preserve">11.3255834579468</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">11.2879886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8707151412964</t>
+    <t xml:space="preserve">11.8707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7955255508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6357450485229</t>
+    <t xml:space="preserve">11.795524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4094,16 +4094,16 @@
     <t xml:space="preserve">11.6451444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7485313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1150856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">11.7485303878784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.115086555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4112,13 +4112,13 @@
     <t xml:space="preserve">12.6790151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4722414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.773003578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0455684661865</t>
+    <t xml:space="preserve">12.472240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7730026245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.0831651687622</t>
@@ -4127,22 +4127,22 @@
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256711959839</t>
+    <t xml:space="preserve">13.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9102621078491</t>
+    <t xml:space="preserve">13.9102611541748</t>
   </si>
   <si>
     <t xml:space="preserve">13.8068733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6282968521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3275337219238</t>
+    <t xml:space="preserve">13.6282958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3275346755981</t>
   </si>
   <si>
     <t xml:space="preserve">13.4779148101807</t>
@@ -4154,13 +4154,13 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2580184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504816055298</t>
+    <t xml:space="preserve">14.258017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504806518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.2805395126343</t>
@@ -4175,16 +4175,16 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463315963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523431777954</t>
+    <t xml:space="preserve">13.3463306427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523441314697</t>
   </si>
   <si>
     <t xml:space="preserve">13.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3933248519897</t>
+    <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">13.5249090194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7598791122437</t>
+    <t xml:space="preserve">13.6470937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.759880065918</t>
   </si>
   <si>
     <t xml:space="preserve">13.7316827774048</t>
@@ -4214,28 +4214,28 @@
     <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8914623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4215211868286</t>
+    <t xml:space="preserve">13.7786769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8914642333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4215221405029</t>
   </si>
   <si>
     <t xml:space="preserve">14.0888376235962</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5587797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749528884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8407440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0193223953247</t>
+    <t xml:space="preserve">14.5587787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749538421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.840744972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0193214416504</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099239349365</t>
@@ -4250,10 +4250,10 @@
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
@@ -4265,28 +4265,28 @@
     <t xml:space="preserve">14.7655544281006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7937507629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6621675491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8125476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6903638839722</t>
+    <t xml:space="preserve">14.7937498092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.662166595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8125486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6903629302979</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1039113998413</t>
+    <t xml:space="preserve">15.1039123535156</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8877391815186</t>
+    <t xml:space="preserve">14.8877382278442</t>
   </si>
   <si>
     <t xml:space="preserve">15.122709274292</t>
@@ -4295,13 +4295,13 @@
     <t xml:space="preserve">14.3708028793335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1734275817871</t>
+    <t xml:space="preserve">14.1734285354614</t>
   </si>
   <si>
     <t xml:space="preserve">14.4929876327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299337387085</t>
+    <t xml:space="preserve">13.2993364334106</t>
   </si>
   <si>
     <t xml:space="preserve">11.513560295105</t>
@@ -4313,13 +4313,13 @@
     <t xml:space="preserve">10.9872255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269190788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2785902023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3067855834961</t>
+    <t xml:space="preserve">11.2691917419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2785892486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3067865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.231595993042</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">11.4477691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4101734161377</t>
+    <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1846017837524</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">11.2221965789795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9966249465942</t>
+    <t xml:space="preserve">10.9966259002686</t>
   </si>
   <si>
     <t xml:space="preserve">11.0812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0342197418213</t>
+    <t xml:space="preserve">11.0342206954956</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744401931763</t>
@@ -4370,46 +4370,46 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146596908569</t>
+    <t xml:space="preserve">10.7146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8650426864624</t>
+    <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
     <t xml:space="preserve">10.4138975143433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3387069702148</t>
+    <t xml:space="preserve">10.3387079238892</t>
   </si>
   <si>
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1549892425537</t>
+    <t xml:space="preserve">10.0303297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.154990196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563623428345</t>
+    <t xml:space="preserve">10.3371849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563632965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5193796157837</t>
+    <t xml:space="preserve">10.519380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235017776489</t>
+    <t xml:space="preserve">11.1235008239746</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412929534912</t>
+    <t xml:space="preserve">10.4906120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412919998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440391540527</t>
+    <t xml:space="preserve">10.6440401077271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960941314697</t>
+    <t xml:space="preserve">10.5960931777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.711163520813</t>
+    <t xml:space="preserve">10.7111644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813404083252</t>
+    <t xml:space="preserve">9.84813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484855651855</t>
+    <t xml:space="preserve">9.92484760284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618444442749</t>
+    <t xml:space="preserve">10.4618434906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361614227295</t>
+    <t xml:space="preserve">9.95361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537982940674</t>
+    <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646450042725</t>
+    <t xml:space="preserve">8.82688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646354675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34741973876953</t>
+    <t xml:space="preserve">8.34742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09810066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960834503174</t>
+    <t xml:space="preserve">8.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084171295166</t>
+    <t xml:space="preserve">8.23234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810676574707</t>
+    <t xml:space="preserve">8.44810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770397186279</t>
+    <t xml:space="preserve">8.80770301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4673,22 +4673,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976409912109</t>
+    <t xml:space="preserve">9.10976314544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14812088012695</t>
+    <t xml:space="preserve">8.67824935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14811992645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798629760742</t>
+    <t xml:space="preserve">9.26798534393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208728790283</t>
+    <t xml:space="preserve">8.82208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907001495361</t>
+    <t xml:space="preserve">8.6590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19127178192139</t>
+    <t xml:space="preserve">9.1912727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921775817871</t>
+    <t xml:space="preserve">9.23921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28237056732178</t>
+    <t xml:space="preserve">9.28236961364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1337366104126</t>
+    <t xml:space="preserve">9.13373565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428199768066</t>
+    <t xml:space="preserve">9.00428295135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8844165802002</t>
+    <t xml:space="preserve">8.88441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318511962891</t>
+    <t xml:space="preserve">8.91318416595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468669891357</t>
+    <t xml:space="preserve">8.64468574523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7166051864624</t>
+    <t xml:space="preserve">8.71660614013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399871826172</t>
+    <t xml:space="preserve">8.54399967193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496292114258</t>
+    <t xml:space="preserve">8.75496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222091674805</t>
+    <t xml:space="preserve">8.70222187042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4850,37 +4850,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605274200439</t>
+    <t xml:space="preserve">8.49605369567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1364574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21796607971191</t>
+    <t xml:space="preserve">8.13645648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2179651260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97344064712524</t>
+    <t xml:space="preserve">7.97343969345093</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467306137085</t>
+    <t xml:space="preserve">7.94467258453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059886932373</t>
+    <t xml:space="preserve">9.79059791564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.42076587677</t>
+    <t xml:space="preserve">11.4207668304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4925,16 +4925,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.593373298645</t>
+    <t xml:space="preserve">11.5933723449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2769289016724</t>
+    <t xml:space="preserve">11.3536424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276927947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796619415283</t>
+    <t xml:space="preserve">10.9796628952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276220321655</t>
+    <t xml:space="preserve">11.1618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276210784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4976,10 +4976,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6084041595459</t>
+    <t xml:space="preserve">9.59881401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60840320587158</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -5828,7 +5828,7 @@
     <t xml:space="preserve">11.210000038147</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8699998855591</t>
+    <t xml:space="preserve">10.8800001144409</t>
   </si>
 </sst>
 </file>
@@ -22903,7 +22903,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G644" t="s">
-        <v>550</v>
+        <v>458</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22929,7 +22929,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G645" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22955,7 +22955,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22981,7 +22981,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G647" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23033,7 +23033,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23085,7 +23085,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G651" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -23137,7 +23137,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G653" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23163,7 +23163,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G654" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23189,7 +23189,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G655" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23215,7 +23215,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23241,7 +23241,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G657" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23267,7 +23267,7 @@
         <v>7.125</v>
       </c>
       <c r="G658" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23319,7 +23319,7 @@
         <v>7.125</v>
       </c>
       <c r="G660" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23345,7 +23345,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23371,7 +23371,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G662" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23423,7 +23423,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G664" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23475,7 +23475,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23501,7 +23501,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G667" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23527,7 +23527,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G668" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23553,7 +23553,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23631,7 +23631,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23657,7 +23657,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G673" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23683,7 +23683,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G674" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23735,7 +23735,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G676" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23761,7 +23761,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23891,7 +23891,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G682" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23917,7 +23917,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G683" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23943,7 +23943,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G684" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23969,7 +23969,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -24021,7 +24021,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G687" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -24047,7 +24047,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G688" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -24073,7 +24073,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G689" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -24099,7 +24099,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G690" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -24125,7 +24125,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G691" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -24151,7 +24151,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -24177,7 +24177,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G693" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -24203,7 +24203,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G694" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -24229,7 +24229,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>406</v>
+        <v>580</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -24281,7 +24281,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G697" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -71271,22 +71271,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6912615741</v>
+        <v>45968.6911921296</v>
       </c>
       <c r="B2505" t="n">
-        <v>168141</v>
+        <v>68418</v>
       </c>
       <c r="C2505" t="n">
-        <v>11.1800003051758</v>
+        <v>10.9799995422363</v>
       </c>
       <c r="D2505" t="n">
-        <v>10.7799997329712</v>
+        <v>10.789999961853</v>
       </c>
       <c r="E2505" t="n">
-        <v>11.1800003051758</v>
+        <v>10.9200000762939</v>
       </c>
       <c r="F2505" t="n">
-        <v>10.8699998855591</v>
+        <v>10.8800001144409</v>
       </c>
       <c r="G2505" t="s">
         <v>1938</v>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1939" uniqueCount="1939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="1941">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.150794506073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13486289978027</t>
+    <t xml:space="preserve">2.15079474449158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13486313819885</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768843650818</t>
@@ -56,34 +56,34 @@
     <t xml:space="preserve">2.07379102706909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02333998680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06316995620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05254912376404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96492385864258</t>
+    <t xml:space="preserve">2.02334022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06316947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05254864692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492350101471</t>
   </si>
   <si>
     <t xml:space="preserve">1.98988330364227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802968978882</t>
+    <t xml:space="preserve">1.96439278125763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802945137024</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696753501892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00209760665894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00156664848328</t>
+    <t xml:space="preserve">2.00209784507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015664100647</t>
   </si>
   <si>
     <t xml:space="preserve">2.05998349189758</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">2.00528407096863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01909160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97820007801056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854073524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774927616119</t>
+    <t xml:space="preserve">2.01909184455872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97820019721985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854121208191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774951457977</t>
   </si>
   <si>
     <t xml:space="preserve">1.93943285942078</t>
@@ -110,43 +110,43 @@
     <t xml:space="preserve">1.91447281837463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93306005001068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712784767151</t>
+    <t xml:space="preserve">1.93305993080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712808609009</t>
   </si>
   <si>
     <t xml:space="preserve">1.94633650779724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95589566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237813949585</t>
+    <t xml:space="preserve">1.95589554309845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368100166321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237837791443</t>
   </si>
   <si>
     <t xml:space="preserve">2.07113552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08441257476807</t>
+    <t xml:space="preserve">2.08441209793091</t>
   </si>
   <si>
     <t xml:space="preserve">2.09450221061707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17203736305237</t>
+    <t xml:space="preserve">2.17203760147095</t>
   </si>
   <si>
     <t xml:space="preserve">2.10830974578857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13964223861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
+    <t xml:space="preserve">2.13964247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299944877625</t>
   </si>
   <si>
     <t xml:space="preserve">2.14442205429077</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">2.14548420906067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15344953536987</t>
+    <t xml:space="preserve">2.15345001220703</t>
   </si>
   <si>
     <t xml:space="preserve">2.14813947677612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15132570266724</t>
+    <t xml:space="preserve">2.15132546424866</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831970214844</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18265843391418</t>
+    <t xml:space="preserve">2.18265819549561</t>
   </si>
   <si>
     <t xml:space="preserve">2.22248768806458</t>
@@ -176,16 +176,16 @@
     <t xml:space="preserve">2.15610504150391</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14495277404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10565495491028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
+    <t xml:space="preserve">2.14495301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706760406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219791412354</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">2.14017343521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12424182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1136200428009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582474708557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05307936668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06848049163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06901144981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11839962005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12477278709412</t>
+    <t xml:space="preserve">2.12424159049988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362051963806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05307960510254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06848001480103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06901097297668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11840009689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12477254867554</t>
   </si>
   <si>
     <t xml:space="preserve">2.16141581535339</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15557432174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17734813690186</t>
+    <t xml:space="preserve">2.15557384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17734789848328</t>
   </si>
   <si>
     <t xml:space="preserve">2.24373030662537</t>
@@ -236,43 +236,43 @@
     <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29418134689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25753736495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21452212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638533592224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098468780518</t>
+    <t xml:space="preserve">2.29418110847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2575376033783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21452188491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2309844493866</t>
   </si>
   <si>
     <t xml:space="preserve">2.32073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888052940369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604432106018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4492506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288796424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775717735291</t>
+    <t xml:space="preserve">2.34888029098511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604455947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44925022125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5028874874115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.5655529499054</t>
@@ -296,76 +296,76 @@
     <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72161531448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346632957458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523966789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894026756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98942279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00248622894287</t>
+    <t xml:space="preserve">2.7216157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894050598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98942255973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00248646736145</t>
   </si>
   <si>
     <t xml:space="preserve">2.94587683677673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8413667678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91757154464722</t>
+    <t xml:space="preserve">2.84136700630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91757202148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.90668535232544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797616004944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959390640259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685646057129</t>
+    <t xml:space="preserve">2.89797639846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959366798401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685669898987</t>
   </si>
   <si>
     <t xml:space="preserve">2.6954882144928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693437576294</t>
+    <t xml:space="preserve">2.7869348526001</t>
   </si>
   <si>
     <t xml:space="preserve">2.86531662940979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98289060592651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84789824485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.776047706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86313939094543</t>
+    <t xml:space="preserve">2.98289084434509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84789872169495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77604794502258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86313962936401</t>
   </si>
   <si>
     <t xml:space="preserve">2.91974902153015</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97200393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99159979820251</t>
+    <t xml:space="preserve">2.97200417518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99160003662109</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418141365051</t>
@@ -377,76 +377,76 @@
     <t xml:space="preserve">2.9785361289978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03514552116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820966720581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998229026794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15707421302795</t>
+    <t xml:space="preserve">3.03514575958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820942878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998252868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
     <t xml:space="preserve">3.29859781265259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30730724334717</t>
+    <t xml:space="preserve">3.30730700492859</t>
   </si>
   <si>
     <t xml:space="preserve">3.34214401245117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29206657409668</t>
+    <t xml:space="preserve">3.29206609725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.28771162033081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26158380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416589736938</t>
+    <t xml:space="preserve">3.26158428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416565895081</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988909721375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27900266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25722932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2659387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17449259757996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25505208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25940680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33125758171082</t>
+    <t xml:space="preserve">3.27900218963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25722980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593899726868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17449235916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25505232810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25940704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33125782012939</t>
   </si>
   <si>
     <t xml:space="preserve">3.35085320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34432125091553</t>
+    <t xml:space="preserve">3.34432101249695</t>
   </si>
   <si>
     <t xml:space="preserve">3.32472562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28553438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247071266174</t>
+    <t xml:space="preserve">3.28553462028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247047424316</t>
   </si>
   <si>
     <t xml:space="preserve">3.35303044319153</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">3.27682518959045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31383919715881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30948448181152</t>
+    <t xml:space="preserve">3.31383895874023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30948424339294</t>
   </si>
   <si>
     <t xml:space="preserve">3.15054225921631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18973326683044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2093288898468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20061993598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239327430725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175515174866</t>
+    <t xml:space="preserve">3.18973350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20932912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20062017440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175539016724</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343505859375</t>
@@ -494,58 +494,58 @@
     <t xml:space="preserve">3.20497465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37262558937073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141269683838</t>
+    <t xml:space="preserve">3.37262582778931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141317367554</t>
   </si>
   <si>
     <t xml:space="preserve">3.59253263473511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67962431907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631186485291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824031829834</t>
+    <t xml:space="preserve">3.67962408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824055671692</t>
   </si>
   <si>
     <t xml:space="preserve">4.010573387146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09330987930298</t>
+    <t xml:space="preserve">4.09330940246582</t>
   </si>
   <si>
     <t xml:space="preserve">3.99533200263977</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95831751823425</t>
+    <t xml:space="preserve">3.95831775665283</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19346475601196</t>
+    <t xml:space="preserve">4.19346523284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483324050903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313877105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47433614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68988752365112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65722799301147</t>
+    <t xml:space="preserve">4.23483467102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313829421997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47433519363403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6898889541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65722846984863</t>
   </si>
   <si>
     <t xml:space="preserve">4.6463418006897</t>
@@ -554,103 +554,103 @@
     <t xml:space="preserve">4.75956153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95334005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245433807373</t>
+    <t xml:space="preserve">4.95334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245338439941</t>
   </si>
   <si>
     <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74214267730713</t>
+    <t xml:space="preserve">4.74214315414429</t>
   </si>
   <si>
     <t xml:space="preserve">4.73778867721558</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64416456222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37418079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35023021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3415207862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22830247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128751754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895540237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22612476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24571990966797</t>
+    <t xml:space="preserve">4.6441650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57231378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37418127059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34152173995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22830295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895587921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22612428665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24572038650513</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547136306763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35458517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33934354782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63763236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61586046218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851903915405</t>
+    <t xml:space="preserve">4.35458469390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940618515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63763332366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545560836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61585998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851999282837</t>
   </si>
   <si>
     <t xml:space="preserve">4.72254800796509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408664703369</t>
+    <t xml:space="preserve">4.59408712387085</t>
   </si>
   <si>
     <t xml:space="preserve">4.6637601852417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58973264694214</t>
+    <t xml:space="preserve">4.58973217010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.51135015487671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52441453933716</t>
+    <t xml:space="preserve">4.52441358566284</t>
   </si>
   <si>
     <t xml:space="preserve">4.73343372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64198732376099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78568840026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77480220794678</t>
+    <t xml:space="preserve">4.64198684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78568935394287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
     <t xml:space="preserve">4.746497631073</t>
@@ -659,37 +659,37 @@
     <t xml:space="preserve">4.7660927772522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09921932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38662195205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29082059860229</t>
+    <t xml:space="preserve">5.09921979904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38662147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29082012176514</t>
   </si>
   <si>
     <t xml:space="preserve">5.25162935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22985649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22767925262451</t>
+    <t xml:space="preserve">5.22985696792603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767877578735</t>
   </si>
   <si>
     <t xml:space="preserve">5.20372915267944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03607797622681</t>
+    <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010599136353</t>
   </si>
   <si>
-    <t xml:space="preserve">5.225501537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27557945251465</t>
+    <t xml:space="preserve">5.22550201416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27557992935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.31041669845581</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">5.17106962203979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14494132995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220579147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979385375977</t>
+    <t xml:space="preserve">5.14494276046753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979433059692</t>
   </si>
   <si>
     <t xml:space="preserve">5.09050989151001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04043245315552</t>
+    <t xml:space="preserve">5.04043197631836</t>
   </si>
   <si>
     <t xml:space="preserve">5.11446046829224</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">5.10139608383179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09268760681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752389907837</t>
+    <t xml:space="preserve">5.09268712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752342224121</t>
   </si>
   <si>
     <t xml:space="preserve">5.11663722991943</t>
@@ -731,43 +731,43 @@
     <t xml:space="preserve">5.04478693008423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736854553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9881763458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8858437538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8662486076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85536193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8466534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8009295463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004335403442</t>
+    <t xml:space="preserve">4.9576940536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736806869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98817682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88584470748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86624908447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85536241531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84665298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80093002319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004287719727</t>
   </si>
   <si>
     <t xml:space="preserve">4.74432039260864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75738382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117809295654</t>
+    <t xml:space="preserve">4.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052564620972</t>
@@ -776,46 +776,46 @@
     <t xml:space="preserve">4.9185037612915</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1384105682373</t>
+    <t xml:space="preserve">5.13841009140015</t>
   </si>
   <si>
     <t xml:space="preserve">5.08397817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19719696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881494522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09486484527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444423675537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55209541320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6827335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63918781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385251998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134929656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94400787353516</t>
+    <t xml:space="preserve">5.19719743728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881399154663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486436843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710329055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55209589004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68273401260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134881973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94400835037231</t>
   </si>
   <si>
     <t xml:space="preserve">6.11383724212646</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">5.81337070465088</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87868928909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75893878936768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957595825195</t>
+    <t xml:space="preserve">5.87868881225586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75893831253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957643508911</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97666835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09641933441162</t>
+    <t xml:space="preserve">5.9766674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09641885757446</t>
   </si>
   <si>
     <t xml:space="preserve">5.94836282730103</t>
@@ -851,31 +851,31 @@
     <t xml:space="preserve">5.98973226547241</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00497245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98755407333374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04198694229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05722761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08335542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96360397338867</t>
+    <t xml:space="preserve">6.0049729347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9875545501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0419864654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05722808837891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08335494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96360349655151</t>
   </si>
   <si>
     <t xml:space="preserve">6.07464551925659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13996458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42301225662231</t>
+    <t xml:space="preserve">6.13996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.26842498779297</t>
@@ -884,25 +884,25 @@
     <t xml:space="preserve">6.52969980239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54276371002197</t>
+    <t xml:space="preserve">6.54276323318481</t>
   </si>
   <si>
     <t xml:space="preserve">6.58848762512207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.804039478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201711654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01088237762451</t>
+    <t xml:space="preserve">6.80403900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201759338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088190078735</t>
   </si>
   <si>
     <t xml:space="preserve">7.06531429290771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11756896972656</t>
+    <t xml:space="preserve">7.1175684928894</t>
   </si>
   <si>
     <t xml:space="preserve">7.3200569152832</t>
@@ -911,28 +911,28 @@
     <t xml:space="preserve">7.1306324005127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22425651550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2220778465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321449279785</t>
+    <t xml:space="preserve">7.22425556182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207880020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321401596069</t>
   </si>
   <si>
     <t xml:space="preserve">7.29392862319946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37666702270508</t>
+    <t xml:space="preserve">7.37666654586792</t>
   </si>
   <si>
     <t xml:space="preserve">7.36360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2852201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30481481552124</t>
+    <t xml:space="preserve">7.28521919250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30481624603271</t>
   </si>
   <si>
     <t xml:space="preserve">7.19595193862915</t>
@@ -941,37 +941,37 @@
     <t xml:space="preserve">6.46655893325806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2270565032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40123987197876</t>
+    <t xml:space="preserve">6.22705602645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40124034881592</t>
   </si>
   <si>
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704122543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316761016846</t>
+    <t xml:space="preserve">6.49704074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316856384277</t>
   </si>
   <si>
     <t xml:space="preserve">6.57760047912598</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52464437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290407180786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891538619995</t>
+    <t xml:space="preserve">6.52464389801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56215381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290454864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
     <t xml:space="preserve">6.45403623580933</t>
@@ -980,34 +980,34 @@
     <t xml:space="preserve">6.55774164199829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91740322113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76294755935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58422040939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50478506088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093849182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48713350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35694932937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488416671753</t>
+    <t xml:space="preserve">6.91740274429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76294660568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652584075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58421993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50478553771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093801498413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48713397979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35694885253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488368988037</t>
   </si>
   <si>
     <t xml:space="preserve">6.43417739868164</t>
@@ -1019,58 +1019,58 @@
     <t xml:space="preserve">6.33267784118652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3746018409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057014465332</t>
+    <t xml:space="preserve">6.37460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057062149048</t>
   </si>
   <si>
     <t xml:space="preserve">6.14291858673096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13850545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91344118118286</t>
+    <t xml:space="preserve">6.13850593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95757102966309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91344165802002</t>
   </si>
   <si>
     <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93771362304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95977783203125</t>
+    <t xml:space="preserve">5.93771314620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95977878570557</t>
   </si>
   <si>
     <t xml:space="preserve">5.9200611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93329954147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94212675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83621406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84724569320679</t>
+    <t xml:space="preserve">5.93330001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94212579727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8362135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84724617004395</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846244812012</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50744390487671</t>
+    <t xml:space="preserve">5.69720315933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50744342803955</t>
   </si>
   <si>
     <t xml:space="preserve">5.46993350982666</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692083358765</t>
+    <t xml:space="preserve">5.73692035675049</t>
   </si>
   <si>
     <t xml:space="preserve">5.76119232177734</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">5.71485567092896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72147560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59129095077515</t>
+    <t xml:space="preserve">5.72147464752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5912914276123</t>
   </si>
   <si>
     <t xml:space="preserve">5.55819416046143</t>
@@ -1106,40 +1106,40 @@
     <t xml:space="preserve">5.54495429992676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44345569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932537078857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41918325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56040048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52730178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45890140533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41256427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979187011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56922674179077</t>
+    <t xml:space="preserve">5.4434552192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007514953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932489395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56040000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52730274200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45890092849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41256475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979139328003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56922626495361</t>
   </si>
   <si>
     <t xml:space="preserve">5.73912715911865</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">5.80311632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86931133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030138015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554887771606</t>
+    <t xml:space="preserve">5.86931180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030090332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
   </si>
   <si>
     <t xml:space="preserve">5.96860456466675</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80532217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762807846069</t>
+    <t xml:space="preserve">5.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762760162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.56481313705444</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">5.36181402206421</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782629013062</t>
+    <t xml:space="preserve">5.2978253364563</t>
   </si>
   <si>
     <t xml:space="preserve">5.22942447662354</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">5.24045658111572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25369548797607</t>
+    <t xml:space="preserve">5.25369596481323</t>
   </si>
   <si>
     <t xml:space="preserve">5.41477060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39711904525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796697616577</t>
+    <t xml:space="preserve">5.39711809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796745300293</t>
   </si>
   <si>
     <t xml:space="preserve">5.2228045463562</t>
@@ -1211,28 +1211,28 @@
     <t xml:space="preserve">5.14116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11909914016724</t>
+    <t xml:space="preserve">5.11909818649292</t>
   </si>
   <si>
     <t xml:space="preserve">5.20735883712769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16764163970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13233757019043</t>
+    <t xml:space="preserve">5.16764259338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13233804702759</t>
   </si>
   <si>
     <t xml:space="preserve">5.13675117492676</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03745746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00656700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96464395523071</t>
+    <t xml:space="preserve">5.0374584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00656747817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9646430015564</t>
   </si>
   <si>
     <t xml:space="preserve">4.95802354812622</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">5.04849004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19412040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576017379761</t>
+    <t xml:space="preserve">5.19411993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576112747192</t>
   </si>
   <si>
     <t xml:space="preserve">5.22501134872437</t>
@@ -1256,25 +1256,25 @@
     <t xml:space="preserve">5.24486970901489</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11689233779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87196969985962</t>
+    <t xml:space="preserve">5.11689186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083848953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87196922302246</t>
   </si>
   <si>
     <t xml:space="preserve">4.72633981704712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131902694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154525756836</t>
+    <t xml:space="preserve">4.71089506149292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154573440552</t>
   </si>
   <si>
     <t xml:space="preserve">5.21839141845703</t>
@@ -1289,49 +1289,49 @@
     <t xml:space="preserve">5.84503984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76781225204468</t>
+    <t xml:space="preserve">5.76781129837036</t>
   </si>
   <si>
     <t xml:space="preserve">5.90461587905884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663898468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307331085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63983488082886</t>
+    <t xml:space="preserve">5.86489915847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307378768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6398344039917</t>
   </si>
   <si>
     <t xml:space="preserve">5.69940996170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.023766040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348323822021</t>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376699447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366788864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348466873169</t>
   </si>
   <si>
     <t xml:space="preserve">6.14071178436279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12526559829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597332000732</t>
+    <t xml:space="preserve">6.12526607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597284317017</t>
   </si>
   <si>
     <t xml:space="preserve">5.96419143676758</t>
@@ -1340,22 +1340,22 @@
     <t xml:space="preserve">6.03479957580566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80973625183105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020227432251</t>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034391403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020275115967</t>
   </si>
   <si>
     <t xml:space="preserve">5.82518100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74353981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65086698532104</t>
+    <t xml:space="preserve">5.74354076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65086650848389</t>
   </si>
   <si>
     <t xml:space="preserve">5.61776924133301</t>
@@ -1367,331 +1367,334 @@
     <t xml:space="preserve">6.01935338973999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85607290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926832199097</t>
+    <t xml:space="preserve">5.85607242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926975250244</t>
   </si>
   <si>
     <t xml:space="preserve">5.84283304214478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0325927734375</t>
+    <t xml:space="preserve">6.03259325027466</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583215713501</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95315885543823</t>
+    <t xml:space="preserve">5.95315837860107</t>
   </si>
   <si>
     <t xml:space="preserve">5.94433259963989</t>
   </si>
   <si>
+    <t xml:space="preserve">6.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413534164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243757247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239456176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996200561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92226791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429054260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396472930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4280104637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339912414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089548110962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543621063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9284348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90636968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054349899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050096511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22851943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0475869178772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082582473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4933009147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560682296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1843900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941133499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528196334839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969366073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6212797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743124008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508375167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717603683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61952447891235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219778060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163307189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.579270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534440994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344900131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817632675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505174636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49429035186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305927276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14095020294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829387664795</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.2885479927063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28413486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235155105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243757247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239456176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1693959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996200561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372493743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543668746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9284348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90637016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22851991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908647537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082582473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4933009147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560682296753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058603286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46240949630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127828598022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56391000747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738918304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965255737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835073471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219730377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247346878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163354873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65977764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534440994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344995498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49428987503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087120056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14095020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669256210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
     <t xml:space="preserve">6.33774709701538</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58821535110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981761932373</t>
+    <t xml:space="preserve">6.58821487426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981666564941</t>
   </si>
   <si>
     <t xml:space="preserve">6.53007078170776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44061803817749</t>
+    <t xml:space="preserve">6.44061851501465</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4003643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352752685547</t>
+    <t xml:space="preserve">6.39141941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40036487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352800369263</t>
   </si>
   <si>
     <t xml:space="preserve">6.42719984054565</t>
@@ -1700,22 +1703,22 @@
     <t xml:space="preserve">6.43167304992676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880115509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298122406006</t>
+    <t xml:space="preserve">6.50323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298170089722</t>
   </si>
   <si>
     <t xml:space="preserve">6.64188718795776</t>
@@ -1724,25 +1727,25 @@
     <t xml:space="preserve">6.10069608688354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39589166641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567752838135</t>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567657470703</t>
   </si>
   <si>
     <t xml:space="preserve">5.98440790176392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47452592849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3358736038208</t>
+    <t xml:space="preserve">5.474524974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33587312698364</t>
   </si>
   <si>
     <t xml:space="preserve">5.24194717407227</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08093214035034</t>
+    <t xml:space="preserve">5.0809326171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.97358846664429</t>
@@ -1751,19 +1754,16 @@
     <t xml:space="preserve">5.13013124465942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01831483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96464347839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0764594078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700618743896</t>
+    <t xml:space="preserve">5.01831531524658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07645893096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05409574508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700666427612</t>
   </si>
   <si>
     <t xml:space="preserve">4.92886209487915</t>
@@ -1772,16 +1772,16 @@
     <t xml:space="preserve">4.73653745651245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
+    <t xml:space="preserve">4.58894014358521</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417474746704</t>
+    <t xml:space="preserve">4.74995565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417427062988</t>
   </si>
   <si>
     <t xml:space="preserve">4.37201642990112</t>
@@ -1790,19 +1790,19 @@
     <t xml:space="preserve">4.12825679779053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876550674438</t>
+    <t xml:space="preserve">4.20876455307007</t>
   </si>
   <si>
     <t xml:space="preserve">4.11483907699585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04104042053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0544581413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829653739929</t>
+    <t xml:space="preserve">4.04103994369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05445861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829677581787</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353090286255</t>
@@ -1811,13 +1811,13 @@
     <t xml:space="preserve">4.1550931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1304931640625</t>
+    <t xml:space="preserve">4.13049364089966</t>
   </si>
   <si>
     <t xml:space="preserve">4.01867723464966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86884307861328</t>
+    <t xml:space="preserve">3.8688428401947</t>
   </si>
   <si>
     <t xml:space="preserve">3.70559144020081</t>
@@ -1832,43 +1832,43 @@
     <t xml:space="preserve">3.73466420173645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8375346660614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84647989273071</t>
+    <t xml:space="preserve">3.83753442764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648060798645</t>
   </si>
   <si>
     <t xml:space="preserve">3.96500587463379</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00302314758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9247510433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146085739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264221191406</t>
+    <t xml:space="preserve">4.15732908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00302267074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92475175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146061897278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264268875122</t>
   </si>
   <si>
     <t xml:space="preserve">3.87331604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86213421821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84424424171448</t>
+    <t xml:space="preserve">3.86213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424376487732</t>
   </si>
   <si>
     <t xml:space="preserve">3.45512294769287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35896158218384</t>
+    <t xml:space="preserve">3.35896134376526</t>
   </si>
   <si>
     <t xml:space="preserve">3.24267220497131</t>
@@ -1877,52 +1877,52 @@
     <t xml:space="preserve">3.03245782852173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04140329360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216468811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38803339004517</t>
+    <t xml:space="preserve">3.04140305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216444969177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3835608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38803315162659</t>
   </si>
   <si>
     <t xml:space="preserve">3.26950812339783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22701835632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4528865814209</t>
+    <t xml:space="preserve">3.22701787948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45288681983948</t>
   </si>
   <si>
     <t xml:space="preserve">3.39474248886108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48866820335388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51550388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870698928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24714493751526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11072897911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92735075950623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93182277679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01009440422058</t>
+    <t xml:space="preserve">3.4886679649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5155041217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870722770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24714517593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1107292175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92735028266907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93182253837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01009464263916</t>
   </si>
   <si>
     <t xml:space="preserve">3.1040198802948</t>
@@ -1940,13 +1940,13 @@
     <t xml:space="preserve">2.92511415481567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77751636505127</t>
+    <t xml:space="preserve">2.77751660346985</t>
   </si>
   <si>
     <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78869819641113</t>
+    <t xml:space="preserve">2.78869843482971</t>
   </si>
   <si>
     <t xml:space="preserve">2.83342456817627</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">2.88933277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07271099090576</t>
+    <t xml:space="preserve">3.0727117061615</t>
   </si>
   <si>
     <t xml:space="preserve">3.10625648498535</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">3.22925400733948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15992832183838</t>
+    <t xml:space="preserve">3.1599280834198</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254538536072</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">3.23596334457397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18676376342773</t>
+    <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
     <t xml:space="preserve">3.19347286224365</t>
@@ -1988,19 +1988,19 @@
     <t xml:space="preserve">3.54234004020691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972273826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339457511902</t>
+    <t xml:space="preserve">3.47972297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5333948135376</t>
   </si>
   <si>
     <t xml:space="preserve">3.4953773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61166596412659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533756256104</t>
+    <t xml:space="preserve">3.61166572570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533780097961</t>
   </si>
   <si>
     <t xml:space="preserve">3.57588458061218</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">3.51103115081787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52221298217773</t>
+    <t xml:space="preserve">3.52221322059631</t>
   </si>
   <si>
     <t xml:space="preserve">3.58259391784668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43723225593567</t>
+    <t xml:space="preserve">3.43723249435425</t>
   </si>
   <si>
     <t xml:space="preserve">3.52444934844971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58483028411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6944100856781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62284779548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61390256881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335483551025</t>
+    <t xml:space="preserve">3.58482980728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69440960884094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62284755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61390233039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335531234741</t>
   </si>
   <si>
     <t xml:space="preserve">3.80398988723755</t>
@@ -2042,19 +2042,19 @@
     <t xml:space="preserve">3.89567995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766124725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040608406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99184131622314</t>
+    <t xml:space="preserve">3.77268171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766172409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040536880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99184107780457</t>
   </si>
   <si>
     <t xml:space="preserve">4.07011270523071</t>
@@ -2063,28 +2063,28 @@
     <t xml:space="preserve">4.13272953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09247589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125551223755</t>
+    <t xml:space="preserve">4.09247541427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9493510723114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
+    <t xml:space="preserve">3.94935131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
   </si>
   <si>
     <t xml:space="preserve">4.02762269973755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112821578979</t>
+    <t xml:space="preserve">3.97842383384705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112869262695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28256368637085</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42792463302612</t>
+    <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.3541259765625</t>
@@ -2102,31 +2102,31 @@
     <t xml:space="preserve">4.16627502441406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20429277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27809143066406</t>
+    <t xml:space="preserve">4.20429182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
     <t xml:space="preserve">4.20205640792847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23783731460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29150867462158</t>
+    <t xml:space="preserve">4.23783779144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24007272720337</t>
+    <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
     <t xml:space="preserve">4.25349140167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19981956481934</t>
+    <t xml:space="preserve">4.19982004165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.07458543777466</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">4.15285682678223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18640184402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26914644241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97171378135681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93369698524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015244483948</t>
+    <t xml:space="preserve">4.1864013671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26914548873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97171473503113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93369674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90015172958374</t>
   </si>
   <si>
     <t xml:space="preserve">3.99631452560425</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">4.03880405426025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03656768798828</t>
+    <t xml:space="preserve">4.03656816482544</t>
   </si>
   <si>
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804265975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778925895691</t>
+    <t xml:space="preserve">3.91804313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778902053833</t>
   </si>
   <si>
     <t xml:space="preserve">3.76820874214172</t>
@@ -2180,25 +2180,25 @@
     <t xml:space="preserve">3.85095262527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0991849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8241171836853</t>
+    <t xml:space="preserve">4.09918451309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411670684814</t>
   </si>
   <si>
     <t xml:space="preserve">3.95693063735962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88136410713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76229023933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76458024978638</t>
+    <t xml:space="preserve">3.88136458396912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76229000091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626088142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76457977294922</t>
   </si>
   <si>
     <t xml:space="preserve">3.68901371955872</t>
@@ -2207,49 +2207,49 @@
     <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73252105712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84243607521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487192153931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96608996391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006108283997</t>
+    <t xml:space="preserve">3.73252129554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84243631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220454216003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487168312073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96608972549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739346504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006060600281</t>
   </si>
   <si>
     <t xml:space="preserve">3.87449479103088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90655255317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440909385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04165601730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19736957550049</t>
+    <t xml:space="preserve">3.90655303001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440980911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04165649414062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19736909866333</t>
   </si>
   <si>
     <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09203433990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11264276504517</t>
+    <t xml:space="preserve">4.09203386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11264324188232</t>
   </si>
   <si>
     <t xml:space="preserve">4.10119342803955</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">4.14470195770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27751493453979</t>
+    <t xml:space="preserve">4.18821001052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27751541137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28438472747803</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">4.31415319442749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40803861618042</t>
+    <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
     <t xml:space="preserve">4.30270433425903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35079193115234</t>
+    <t xml:space="preserve">4.35079145431519</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858737945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22255754470825</t>
+    <t xml:space="preserve">4.23858690261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22255802154541</t>
   </si>
   <si>
     <t xml:space="preserve">4.19507932662964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997610092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09890365600586</t>
+    <t xml:space="preserve">4.24774646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17446994781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997562408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890413284302</t>
   </si>
   <si>
     <t xml:space="preserve">4.15157127380371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16302061080933</t>
+    <t xml:space="preserve">4.16302108764648</t>
   </si>
   <si>
     <t xml:space="preserve">4.11035346984863</t>
@@ -2318,25 +2318,25 @@
     <t xml:space="preserve">4.12409257888794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07600498199463</t>
+    <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
     <t xml:space="preserve">4.00730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05539560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067022323608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945481300354</t>
+    <t xml:space="preserve">4.05539608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9706699848175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94548082351685</t>
   </si>
   <si>
     <t xml:space="preserve">3.84701561927795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88594388961792</t>
+    <t xml:space="preserve">3.88594460487366</t>
   </si>
   <si>
     <t xml:space="preserve">3.87678480148315</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">3.85159540176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95235085487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043869018555</t>
+    <t xml:space="preserve">3.95235133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043916702271</t>
   </si>
   <si>
     <t xml:space="preserve">3.98211908340454</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11493301391602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16760063171387</t>
+    <t xml:space="preserve">4.11493349075317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16760110855103</t>
   </si>
   <si>
     <t xml:space="preserve">4.04394626617432</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">4.0531063079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18592023849487</t>
+    <t xml:space="preserve">4.18591976165771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554191589355</t>
@@ -2378,49 +2378,49 @@
     <t xml:space="preserve">4.06226539611816</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34392166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33705186843872</t>
+    <t xml:space="preserve">4.34392213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33705282211304</t>
   </si>
   <si>
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60268020629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00112056732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17515277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33086538314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35834360122681</t>
+    <t xml:space="preserve">4.60267972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00112104415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17515230178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33086490631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35834407806396</t>
   </si>
   <si>
     <t xml:space="preserve">5.62855100631714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48657703399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39040279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61023187637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70640659332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55527496337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45451879501343</t>
+    <t xml:space="preserve">5.48657751083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39040184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61023139953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70640707015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55527448654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45451927185059</t>
   </si>
   <si>
     <t xml:space="preserve">5.4819974899292</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">5.27590751647949</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36292314529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4499397277832</t>
+    <t xml:space="preserve">5.36292362213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44993877410889</t>
   </si>
   <si>
     <t xml:space="preserve">5.3446044921875</t>
@@ -2444,22 +2444,22 @@
     <t xml:space="preserve">5.47283840179443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55985450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69724750518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72930574417114</t>
+    <t xml:space="preserve">5.45909929275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55985355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69724702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7293062210083</t>
   </si>
   <si>
     <t xml:space="preserve">5.92623615264893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74304580688477</t>
+    <t xml:space="preserve">5.74304533004761</t>
   </si>
   <si>
     <t xml:space="preserve">5.7796835899353</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">5.7247257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67892789840698</t>
+    <t xml:space="preserve">5.67892837524414</t>
   </si>
   <si>
     <t xml:space="preserve">5.71556615829468</t>
@@ -2477,40 +2477,40 @@
     <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098661422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82090091705322</t>
+    <t xml:space="preserve">5.71098709106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82090139389038</t>
   </si>
   <si>
     <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04989099502563</t>
+    <t xml:space="preserve">6.04989051818848</t>
   </si>
   <si>
     <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22392225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99493360519409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02241134643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24224138259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10324001312256</t>
+    <t xml:space="preserve">6.22392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99493312835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02241230010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24224090576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71395921707153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10324048995972</t>
   </si>
   <si>
     <t xml:space="preserve">7.1994161605835</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159706115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617612838745</t>
+    <t xml:space="preserve">7.61159610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617565155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.71235132217407</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83600568771362</t>
+    <t xml:space="preserve">7.83600616455078</t>
   </si>
   <si>
     <t xml:space="preserve">7.67113256454468</t>
@@ -2540,19 +2540,19 @@
     <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28185129165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41924571990967</t>
+    <t xml:space="preserve">7.28185176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41924476623535</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29101133346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27727174758911</t>
+    <t xml:space="preserve">7.29101085662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27727222442627</t>
   </si>
   <si>
     <t xml:space="preserve">7.11697959899902</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">7.26811218261719</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39634561538696</t>
+    <t xml:space="preserve">7.39634609222412</t>
   </si>
   <si>
     <t xml:space="preserve">7.37802743911743</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">7.57495784759521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91844081878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85890340805054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655349731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428785324097</t>
+    <t xml:space="preserve">7.9184422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8589038848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655397415161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428737640381</t>
   </si>
   <si>
     <t xml:space="preserve">7.45130395889282</t>
@@ -2597,67 +2597,67 @@
     <t xml:space="preserve">7.12155961990356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41466569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25895309448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30475044250488</t>
+    <t xml:space="preserve">7.41466522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25895261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30474996566772</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231435775757</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52916049957275</t>
+    <t xml:space="preserve">7.52915954589844</t>
   </si>
   <si>
     <t xml:space="preserve">7.4375638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48794174194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51999998092651</t>
+    <t xml:space="preserve">7.48794221878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52000045776367</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17651700973511</t>
+    <t xml:space="preserve">7.17651653289795</t>
   </si>
   <si>
     <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51244878768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51702833175659</t>
+    <t xml:space="preserve">6.51244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51702785491943</t>
   </si>
   <si>
     <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79639434814453</t>
+    <t xml:space="preserve">6.79639482498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.71853876113892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76891660690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6177830696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538347244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89715051651001</t>
+    <t xml:space="preserve">6.76891613006592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61778354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538394927979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89257049560547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89715003967285</t>
   </si>
   <si>
     <t xml:space="preserve">6.828453540802</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">6.67732048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83303308486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76433706283569</t>
+    <t xml:space="preserve">6.83303356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
     <t xml:space="preserve">6.63610219955444</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">5.63771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77052354812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72014665603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47741746902466</t>
+    <t xml:space="preserve">5.77052402496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72014617919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.1156153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75381278991699</t>
+    <t xml:space="preserve">4.75381231307983</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810018539429</t>
@@ -2717,25 +2717,25 @@
     <t xml:space="preserve">3.8149573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66382455825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32034111022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22416567802429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18294739723206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22645568847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44399523735046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99356937408447</t>
+    <t xml:space="preserve">3.66382479667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32034134864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22416543960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18294787406921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22645545005798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44399499893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99356889724731</t>
   </si>
   <si>
     <t xml:space="preserve">3.86304545402527</t>
@@ -2744,16 +2744,16 @@
     <t xml:space="preserve">3.61344695091248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50353240966797</t>
+    <t xml:space="preserve">3.50353264808655</t>
   </si>
   <si>
     <t xml:space="preserve">3.67069435119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61802697181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70962285995483</t>
+    <t xml:space="preserve">3.6180272102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70962238311768</t>
   </si>
   <si>
     <t xml:space="preserve">3.6226065158844</t>
@@ -2762,34 +2762,34 @@
     <t xml:space="preserve">3.79663848876953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74168133735657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06684494018555</t>
+    <t xml:space="preserve">3.74168062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06684589385986</t>
   </si>
   <si>
     <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38284969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11722326278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01188850402832</t>
+    <t xml:space="preserve">4.3828501701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11722278594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432411193848</t>
+    <t xml:space="preserve">4.09432363510132</t>
   </si>
   <si>
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612621307373</t>
+    <t xml:space="preserve">4.45612668991089</t>
   </si>
   <si>
     <t xml:space="preserve">4.35995149612427</t>
@@ -2798,37 +2798,37 @@
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26377630233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32331275939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35537242889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676019668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137670516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52482318878174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360586166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38742971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406892776489</t>
+    <t xml:space="preserve">4.26377582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32331323623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35537195205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499315261841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676067352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5248236656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48360538482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38743019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406797409058</t>
   </si>
   <si>
     <t xml:space="preserve">4.75152254104614</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">4.90036582946777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88891553878784</t>
+    <t xml:space="preserve">4.88891696929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.04920816421509</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239946365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48428773880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34689426422119</t>
+    <t xml:space="preserve">5.23239994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48428726196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34689474105835</t>
   </si>
   <si>
     <t xml:space="preserve">5.16370248794556</t>
@@ -2864,13 +2864,13 @@
     <t xml:space="preserve">4.93471336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02630996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19805192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254625320435</t>
+    <t xml:space="preserve">5.02630949020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19805145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">5.39269208908081</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20950078964233</t>
+    <t xml:space="preserve">5.20950031280518</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
@@ -2888,22 +2888,22 @@
     <t xml:space="preserve">5.14080429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27819681167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09500646591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.923264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0148606300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1179051399231</t>
+    <t xml:space="preserve">5.27819728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2438497543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09500598907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92326402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01486015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11790561676025</t>
   </si>
   <si>
     <t xml:space="preserve">5.06065797805786</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">5.22094964981079</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210779190063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645580291748</t>
+    <t xml:space="preserve">5.07210731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645532608032</t>
   </si>
   <si>
     <t xml:space="preserve">5.12935447692871</t>
@@ -2924,46 +2924,46 @@
     <t xml:space="preserve">5.3239951133728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33544492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03775930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355760574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96906280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051166534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84311819076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">5.33544397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03775882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96906232833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616365432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98051118850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84311866760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341033935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57978105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19049978256226</t>
+    <t xml:space="preserve">5.00341129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57978057861328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19049882888794</t>
   </si>
   <si>
     <t xml:space="preserve">4.21339845657349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08058500289917</t>
+    <t xml:space="preserve">4.08058452606201</t>
   </si>
   <si>
     <t xml:space="preserve">4.30041456222534</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">4.34163188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61412906646729</t>
+    <t xml:space="preserve">4.61412954330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.54153442382812</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">5.62168121337891</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75907421112061</t>
+    <t xml:space="preserve">5.75907468795776</t>
   </si>
   <si>
     <t xml:space="preserve">5.73617553710938</t>
@@ -2990,37 +2990,37 @@
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64457941055298</t>
+    <t xml:space="preserve">5.64457988739014</t>
   </si>
   <si>
     <t xml:space="preserve">5.66747856140137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89646816253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70182657241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81632137298584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14835548400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96516418457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9537148475647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87356901168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91936731338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09110832214355</t>
+    <t xml:space="preserve">5.89646768569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70182752609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.816321849823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14835596084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96516466140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95371532440186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87356948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91936683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09110879898071</t>
   </si>
   <si>
     <t xml:space="preserve">6.19415330886841</t>
@@ -3035,34 +3035,34 @@
     <t xml:space="preserve">6.18270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07965850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13690567016602</t>
+    <t xml:space="preserve">6.07965898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13690662384033</t>
   </si>
   <si>
     <t xml:space="preserve">6.21705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444593429565</t>
+    <t xml:space="preserve">6.3544454574585</t>
   </si>
   <si>
     <t xml:space="preserve">6.32009792327881</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36589479446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48038911819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618741989136</t>
+    <t xml:space="preserve">6.36589574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4803900718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
     <t xml:space="preserve">6.53763723373413</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56053590774536</t>
+    <t xml:space="preserve">6.5605354309082</t>
   </si>
   <si>
     <t xml:space="preserve">6.60633420944214</t>
@@ -3074,34 +3074,34 @@
     <t xml:space="preserve">6.62923288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169309616089</t>
+    <t xml:space="preserve">6.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894025802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29719877243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20560264587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4231424331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50328826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66358137130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5147385597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78952503204346</t>
+    <t xml:space="preserve">6.46894073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29719829559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20560312271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42314291000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50328874588013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66358089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51473808288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7895245552063</t>
   </si>
   <si>
     <t xml:space="preserve">6.75517702102661</t>
@@ -3110,22 +3110,22 @@
     <t xml:space="preserve">6.6864800453186</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70937919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77807569503784</t>
+    <t xml:space="preserve">6.70937871932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.778076171875</t>
   </si>
   <si>
     <t xml:space="preserve">6.69792985916138</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40024423599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154773712158</t>
+    <t xml:space="preserve">6.40024328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3773455619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
     <t xml:space="preserve">6.3887939453125</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">7.7856273651123</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77417755126953</t>
+    <t xml:space="preserve">7.77417898178101</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">8.01461601257324</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99171733856201</t>
+    <t xml:space="preserve">7.99171829223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041431427002</t>
@@ -3161,40 +3161,40 @@
     <t xml:space="preserve">8.02606582641602</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12911033630371</t>
+    <t xml:space="preserve">8.12911128997803</t>
   </si>
   <si>
     <t xml:space="preserve">8.1062126159668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03751373291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447208404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08331203460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31230163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085372924805</t>
+    <t xml:space="preserve">8.03751564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0031681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08331298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3123025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940391540527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33520126342773</t>
+    <t xml:space="preserve">8.33520221710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.2779541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15200996398926</t>
+    <t xml:space="preserve">8.15200901031494</t>
   </si>
   <si>
     <t xml:space="preserve">8.11766242980957</t>
@@ -3203,79 +3203,79 @@
     <t xml:space="preserve">8.18635845184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34665012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16346073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925712585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94591951370239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736980438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84287548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92302083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577320098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38099956512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15956211090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99926853179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20536041259766</t>
+    <t xml:space="preserve">8.34665107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16345882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186317443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925807952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736932754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84287405014038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92301988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577367782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38099765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15956115722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99927043914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20535945892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.48014736175537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65356349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60731983184814</t>
+    <t xml:space="preserve">9.653564453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60731887817383</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0813264846802</t>
+    <t xml:space="preserve">9.71136856079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0813255310059</t>
   </si>
   <si>
     <t xml:space="preserve">10.2894268035889</t>
   </si>
   <si>
-    <t xml:space="preserve">10.300989151001</t>
+    <t xml:space="preserve">10.3009881973267</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5206499099731</t>
+    <t xml:space="preserve">10.5206508636475</t>
   </si>
   <si>
     <t xml:space="preserve">10.3587942123413</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975290298462</t>
+    <t xml:space="preserve">10.4975280761719</t>
   </si>
   <si>
     <t xml:space="preserve">10.33567237854</t>
@@ -3296,22 +3296,22 @@
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703546524048</t>
+    <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7403116226196</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4744052886963</t>
+    <t xml:space="preserve">10.4744062423706</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044483184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2663059234619</t>
+    <t xml:space="preserve">10.1044502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2663049697876</t>
   </si>
   <si>
     <t xml:space="preserve">10.3934774398804</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">10.0582036972046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9541540145874</t>
+    <t xml:space="preserve">9.95415306091309</t>
   </si>
   <si>
     <t xml:space="preserve">10.0235204696655</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">10.1506938934326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697660446167</t>
+    <t xml:space="preserve">10.0697650909424</t>
   </si>
   <si>
     <t xml:space="preserve">10.092887878418</t>
@@ -3344,13 +3344,13 @@
     <t xml:space="preserve">10.2200603485107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4859666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853771209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0350828170776</t>
+    <t xml:space="preserve">10.4859676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1853761672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0350818634033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4165992736816</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">10.1738157272339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391315460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1911964416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5056610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9052143096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9015159606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7461318969727</t>
+    <t xml:space="preserve">10.1391334533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1911973953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056600570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9052152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.901515007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
@@ -3386,46 +3386,46 @@
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796527862549</t>
+    <t xml:space="preserve">11.5796518325806</t>
   </si>
   <si>
     <t xml:space="preserve">11.4501676559448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3576784133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3206815719604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6536426544189</t>
+    <t xml:space="preserve">11.3576774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3206825256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6536445617676</t>
   </si>
   <si>
     <t xml:space="preserve">11.3946733474731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4686651229858</t>
+    <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
     <t xml:space="preserve">12.0975914001465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8571195602417</t>
+    <t xml:space="preserve">11.8571186065674</t>
   </si>
   <si>
     <t xml:space="preserve">12.0605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0420980453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.894115447998</t>
+    <t xml:space="preserve">12.0420989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8941144943237</t>
   </si>
   <si>
     <t xml:space="preserve">12.9299955368042</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034275054932</t>
+    <t xml:space="preserve">13.5034284591675</t>
   </si>
   <si>
     <t xml:space="preserve">13.8178911209106</t>
@@ -3464,19 +3464,19 @@
     <t xml:space="preserve">13.4109392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7623996734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4294385910034</t>
+    <t xml:space="preserve">13.7623987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4294376373291</t>
   </si>
   <si>
     <t xml:space="preserve">13.0409822463989</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4860467910767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9669914245605</t>
+    <t xml:space="preserve">12.4860458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9669904708862</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3488,22 +3488,22 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.077977180481</t>
+    <t xml:space="preserve">12.9114971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0779781341553</t>
   </si>
   <si>
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457025527954</t>
+    <t xml:space="preserve">15.4457035064697</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011949539185</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7786617279053</t>
+    <t xml:space="preserve">15.7786626815796</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">16.3705959320068</t>
   </si>
   <si>
-    <t xml:space="preserve">16.537073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596073150635</t>
+    <t xml:space="preserve">16.5370750427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596092224121</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520965576172</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">16.0191345214844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7971601486206</t>
+    <t xml:space="preserve">15.7971630096436</t>
   </si>
   <si>
     <t xml:space="preserve">16.1486186981201</t>
@@ -3533,22 +3533,22 @@
     <t xml:space="preserve">16.0006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9081497192383</t>
+    <t xml:space="preserve">15.908148765564</t>
   </si>
   <si>
     <t xml:space="preserve">15.5196933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896512985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8341579437256</t>
+    <t xml:space="preserve">15.4641990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896522521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416677474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8341569900513</t>
   </si>
   <si>
     <t xml:space="preserve">14.9092655181885</t>
@@ -3557,37 +3557,37 @@
     <t xml:space="preserve">14.4283208847046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.502311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2433423995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6329126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514120101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9288787841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0583629608154</t>
+    <t xml:space="preserve">14.5023126602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2433414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6329135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514110565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369464874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.928879737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0583639144897</t>
   </si>
   <si>
     <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.891884803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4098215103149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1508531570435</t>
+    <t xml:space="preserve">13.8918828964233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4098234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1508541107178</t>
   </si>
   <si>
     <t xml:space="preserve">13.7993946075439</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3924417495728</t>
+    <t xml:space="preserve">13.3924407958984</t>
   </si>
   <si>
     <t xml:space="preserve">13.3554449081421</t>
@@ -3626,19 +3626,19 @@
     <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1334705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0594797134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4479351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085790634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3935565948486</t>
+    <t xml:space="preserve">13.1334714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0594806671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4479360580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085781097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3935575485229</t>
   </si>
   <si>
     <t xml:space="preserve">13.18896484375</t>
@@ -3656,7 +3656,7 @@
     <t xml:space="preserve">12.6340284347534</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3380651473999</t>
+    <t xml:space="preserve">12.3380632400513</t>
   </si>
   <si>
     <t xml:space="preserve">11.8386220932007</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">11.9496097564697</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6721410751343</t>
+    <t xml:space="preserve">11.6721420288086</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
@@ -3677,25 +3677,25 @@
     <t xml:space="preserve">12.0051031112671</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681072235107</t>
+    <t xml:space="preserve">11.9681053161621</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582363128662</t>
+    <t xml:space="preserve">10.8582353591919</t>
   </si>
   <si>
     <t xml:space="preserve">10.5067768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1172065734863</t>
+    <t xml:space="preserve">11.117205619812</t>
   </si>
   <si>
     <t xml:space="preserve">11.8201246261597</t>
@@ -3719,40 +3719,40 @@
     <t xml:space="preserve">13.3276987075806</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3646936416626</t>
+    <t xml:space="preserve">13.3646945953369</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617765426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4305543899536</t>
+    <t xml:space="preserve">12.6617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305534362793</t>
   </si>
   <si>
     <t xml:space="preserve">12.4028053283691</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5137929916382</t>
+    <t xml:space="preserve">12.5137939453125</t>
   </si>
   <si>
     <t xml:space="preserve">12.3473129272461</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288154602051</t>
+    <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4952955245972</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6155309677124</t>
+    <t xml:space="preserve">12.6155319213867</t>
   </si>
   <si>
     <t xml:space="preserve">12.4398021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8016262054443</t>
+    <t xml:space="preserve">11.8016271591187</t>
   </si>
   <si>
     <t xml:space="preserve">11.9958543777466</t>
@@ -3761,22 +3761,22 @@
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.764630317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8848667144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6073989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.551905632019</t>
+    <t xml:space="preserve">11.7646312713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8848676681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5519046783447</t>
   </si>
   <si>
     <t xml:space="preserve">11.2929353713989</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">10.6455097198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657470703125</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">11.5704030990601</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4316682815552</t>
+    <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
     <t xml:space="preserve">11.8293733596802</t>
@@ -3800,10 +3800,10 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605545043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.569953918457</t>
+    <t xml:space="preserve">11.5605535507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5699529647827</t>
   </si>
   <si>
     <t xml:space="preserve">11.6827402114868</t>
@@ -3830,16 +3830,16 @@
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658048629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7522554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5642795562744</t>
+    <t xml:space="preserve">11.8895120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7522563934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5642786026001</t>
   </si>
   <si>
     <t xml:space="preserve">11.053017616272</t>
@@ -3848,10 +3848,10 @@
     <t xml:space="preserve">10.5830764770508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.827446937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8838386535645</t>
+    <t xml:space="preserve">10.8274459838867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8838396072388</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">10.9214344024658</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0624179840088</t>
+    <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
     <t xml:space="preserve">11.4571676254272</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">11.4947624206543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4853639602661</t>
+    <t xml:space="preserve">11.4853649139404</t>
   </si>
   <si>
     <t xml:space="preserve">11.3631792068481</t>
@@ -3881,22 +3881,22 @@
     <t xml:space="preserve">11.9365072250366</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7297325134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.096287727356</t>
+    <t xml:space="preserve">11.7297334671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0962867736816</t>
   </si>
   <si>
     <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5380325317383</t>
+    <t xml:space="preserve">12.5380334854126</t>
   </si>
   <si>
     <t xml:space="preserve">12.6414184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6884136199951</t>
+    <t xml:space="preserve">12.6884126663208</t>
   </si>
   <si>
     <t xml:space="preserve">12.5474319458008</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">12.9985752105713</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1677541732788</t>
+    <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.4685163497925</t>
@@ -3926,10 +3926,10 @@
     <t xml:space="preserve">13.5625047683716</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6094980239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7034873962402</t>
+    <t xml:space="preserve">13.6094989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
     <t xml:space="preserve">13.6564931869507</t>
@@ -3938,10 +3938,10 @@
     <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6752901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8726654052734</t>
+    <t xml:space="preserve">13.6752910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8726663589478</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
@@ -3953,10 +3953,10 @@
     <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1583547592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369312286377</t>
+    <t xml:space="preserve">13.158353805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.336932182312</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
@@ -3968,10 +3968,10 @@
     <t xml:space="preserve">13.0643663406372</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1113595962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9139852523804</t>
+    <t xml:space="preserve">13.1113605499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9139842987061</t>
   </si>
   <si>
     <t xml:space="preserve">12.8199968338013</t>
@@ -3980,13 +3980,13 @@
     <t xml:space="preserve">13.0361700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.017373085022</t>
+    <t xml:space="preserve">13.0173721313477</t>
   </si>
   <si>
     <t xml:space="preserve">13.054967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8669900894165</t>
+    <t xml:space="preserve">12.8669910430908</t>
   </si>
   <si>
     <t xml:space="preserve">12.7260093688965</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">12.5850276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5756273269653</t>
+    <t xml:space="preserve">12.5756282806396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6602172851562</t>
@@ -4010,10 +4010,10 @@
     <t xml:space="preserve">13.1207599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1056871414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8237218856812</t>
+    <t xml:space="preserve">12.1056861877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8237209320068</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921377182007</t>
@@ -4028,7 +4028,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548791885376</t>
@@ -4037,7 +4037,7 @@
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984874725342</t>
+    <t xml:space="preserve">10.4984865188599</t>
   </si>
   <si>
     <t xml:space="preserve">10.6582679748535</t>
@@ -4052,13 +4052,13 @@
     <t xml:space="preserve">11.4665660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1939992904663</t>
+    <t xml:space="preserve">11.1940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9496307373047</t>
+    <t xml:space="preserve">10.949631690979</t>
   </si>
   <si>
     <t xml:space="preserve">10.667667388916</t>
@@ -4082,10 +4082,10 @@
     <t xml:space="preserve">11.9929008483887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.795524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6357460021973</t>
+    <t xml:space="preserve">11.7955255508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6357450485229</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4094,10 +4094,10 @@
     <t xml:space="preserve">11.6451444625854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7485303878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.115086555481</t>
+    <t xml:space="preserve">11.7485313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1150856018066</t>
   </si>
   <si>
     <t xml:space="preserve">12.1244831085205</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
-    <t xml:space="preserve">12.895188331604</t>
+    <t xml:space="preserve">12.8951873779297</t>
   </si>
   <si>
     <t xml:space="preserve">12.6790151596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.472240447998</t>
+    <t xml:space="preserve">12.4722414016724</t>
   </si>
   <si>
     <t xml:space="preserve">12.7730026245117</t>
@@ -4127,7 +4127,7 @@
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256721496582</t>
+    <t xml:space="preserve">13.8256711959839</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
@@ -4148,10 +4148,10 @@
     <t xml:space="preserve">13.4779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437059402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7222852706909</t>
+    <t xml:space="preserve">13.5437068939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7222843170166</t>
   </si>
   <si>
     <t xml:space="preserve">14.258017539978</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">13.7504806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2805395126343</t>
+    <t xml:space="preserve">13.2805404663086</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
@@ -4175,10 +4175,10 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523441314697</t>
+    <t xml:space="preserve">13.3463315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523431777954</t>
   </si>
   <si>
     <t xml:space="preserve">13.5719022750854</t>
@@ -4193,10 +4193,10 @@
     <t xml:space="preserve">13.5249090194702</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6470937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.759880065918</t>
+    <t xml:space="preserve">13.6470947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7598791122437</t>
   </si>
   <si>
     <t xml:space="preserve">13.7316827774048</t>
@@ -4211,16 +4211,16 @@
     <t xml:space="preserve">14.0042486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.079439163208</t>
+    <t xml:space="preserve">14.0794401168823</t>
   </si>
   <si>
     <t xml:space="preserve">13.7786769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8914642333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4215221405029</t>
+    <t xml:space="preserve">13.8914632797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4215211868286</t>
   </si>
   <si>
     <t xml:space="preserve">14.0888376235962</t>
@@ -4229,13 +4229,13 @@
     <t xml:space="preserve">14.5587787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7749538421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.840744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0193214416504</t>
+    <t xml:space="preserve">14.7749528884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8407440185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0193204879761</t>
   </si>
   <si>
     <t xml:space="preserve">15.0099239349365</t>
@@ -4244,7 +4244,7 @@
     <t xml:space="preserve">14.6997623443604</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7279586791992</t>
+    <t xml:space="preserve">14.7279596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">14.8031492233276</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7655544281006</t>
+    <t xml:space="preserve">14.7655534744263</t>
   </si>
   <si>
     <t xml:space="preserve">14.7937498092651</t>
   </si>
   <si>
-    <t xml:space="preserve">14.662166595459</t>
+    <t xml:space="preserve">14.6621675491333</t>
   </si>
   <si>
     <t xml:space="preserve">14.8125486373901</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1039123535156</t>
+    <t xml:space="preserve">15.1039113998413</t>
   </si>
   <si>
     <t xml:space="preserve">14.9817266464233</t>
@@ -4307,19 +4307,19 @@
     <t xml:space="preserve">11.513560295105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3725786209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9872255325317</t>
+    <t xml:space="preserve">11.3725776672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9872264862061</t>
   </si>
   <si>
     <t xml:space="preserve">11.2691917419434</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2785892486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3067865371704</t>
+    <t xml:space="preserve">11.2785902023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3067855834961</t>
   </si>
   <si>
     <t xml:space="preserve">11.231595993042</t>
@@ -4349,7 +4349,7 @@
     <t xml:space="preserve">11.0812149047852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0342206954956</t>
+    <t xml:space="preserve">11.0342197418213</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744401931763</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4138975143433</t>
+    <t xml:space="preserve">10.4138984680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387079238892</t>
@@ -4388,28 +4388,28 @@
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303297042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279262542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.154990196228</t>
+    <t xml:space="preserve">10.0303287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1549892425537</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563632965088</t>
+    <t xml:space="preserve">10.3371839523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563623428345</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.519380569458</t>
+    <t xml:space="preserve">10.5193796157837</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235008239746</t>
+    <t xml:space="preserve">11.1235017776489</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4906120300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851308822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645793914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796487808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412919998169</t>
+    <t xml:space="preserve">10.490611076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851299285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645784378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412929534912</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440401077271</t>
+    <t xml:space="preserve">10.6440391540527</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4463,7 +4463,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960931777954</t>
+    <t xml:space="preserve">10.5960941314697</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7111644744873</t>
+    <t xml:space="preserve">10.711163520813</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4508,7 +4508,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813499450684</t>
+    <t xml:space="preserve">9.84813404083252</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484760284424</t>
+    <t xml:space="preserve">9.92484855651855</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4538,7 +4538,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618434906006</t>
+    <t xml:space="preserve">10.4618444442749</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4550,22 +4550,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361518859863</t>
+    <t xml:space="preserve">9.95361614227295</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537887573242</t>
+    <t xml:space="preserve">9.09537982940674</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688236236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646354675293</t>
+    <t xml:space="preserve">8.82688140869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646450042725</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34742069244385</t>
+    <t xml:space="preserve">8.34741973876953</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4604,22 +4604,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09809970855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960929870605</t>
+    <t xml:space="preserve">8.09810066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960834503174</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23234939575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330558776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084075927734</t>
+    <t xml:space="preserve">8.23235034942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330463409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084171295166</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4646,13 +4646,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810771942139</t>
+    <t xml:space="preserve">8.44810676574707</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770301818848</t>
+    <t xml:space="preserve">8.80770397186279</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4673,22 +4673,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976314544678</t>
+    <t xml:space="preserve">9.10976409912109</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824935913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14811992645264</t>
+    <t xml:space="preserve">8.67824840545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14812088012695</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798534393311</t>
+    <t xml:space="preserve">9.26798629760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4700,7 +4700,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208633422852</t>
+    <t xml:space="preserve">8.82208728790283</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6590690612793</t>
+    <t xml:space="preserve">8.65907001495361</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4727,13 +4727,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1912727355957</t>
+    <t xml:space="preserve">9.19127178192139</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921871185303</t>
+    <t xml:space="preserve">9.23921775817871</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28236961364746</t>
+    <t xml:space="preserve">9.28237056732178</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13373565673828</t>
+    <t xml:space="preserve">9.1337366104126</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428295135498</t>
+    <t xml:space="preserve">9.00428199768066</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4781,7 +4781,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88441753387451</t>
+    <t xml:space="preserve">8.8844165802002</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4790,25 +4790,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318416595459</t>
+    <t xml:space="preserve">8.91318511962891</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468574523926</t>
+    <t xml:space="preserve">8.64468669891357</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71660614013672</t>
+    <t xml:space="preserve">8.7166051864624</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399967193604</t>
+    <t xml:space="preserve">8.54399871826172</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4823,7 +4823,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496196746826</t>
+    <t xml:space="preserve">8.75496292114258</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222187042236</t>
+    <t xml:space="preserve">8.70222091674805</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4850,37 +4850,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605369567871</t>
+    <t xml:space="preserve">8.49605274200439</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13645648956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317100524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2179651260376</t>
+    <t xml:space="preserve">8.1364574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317005157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21796607971191</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97343969345093</t>
+    <t xml:space="preserve">7.97344064712524</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467258453369</t>
+    <t xml:space="preserve">7.94467306137085</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059791564941</t>
+    <t xml:space="preserve">9.79059886932373</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4907,7 +4907,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4207668304443</t>
+    <t xml:space="preserve">11.42076587677</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4925,16 +4925,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5933723449707</t>
+    <t xml:space="preserve">11.593373298645</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536424636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.276927947998</t>
+    <t xml:space="preserve">11.3536415100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2769289016724</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4943,16 +4943,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796628952026</t>
+    <t xml:space="preserve">10.9796619415283</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618585586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276210784912</t>
+    <t xml:space="preserve">11.1618576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276220321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4976,10 +4976,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881401062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60840320587158</t>
+    <t xml:space="preserve">9.59881496429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6084041595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -5826,6 +5826,12 @@
   </si>
   <si>
     <t xml:space="preserve">11.210000038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9700002670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8699998855591</t>
   </si>
   <si>
     <t xml:space="preserve">10.8800001144409</t>
@@ -22903,7 +22909,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G644" t="s">
-        <v>458</v>
+        <v>550</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -22929,7 +22935,7 @@
         <v>6.94500017166138</v>
       </c>
       <c r="G645" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -22955,7 +22961,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G646" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -22981,7 +22987,7 @@
         <v>7.36499977111816</v>
       </c>
       <c r="G647" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -23033,7 +23039,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -23085,7 +23091,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G651" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -23137,7 +23143,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G653" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -23163,7 +23169,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G654" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -23189,7 +23195,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G655" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -23215,7 +23221,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -23241,7 +23247,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G657" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -23267,7 +23273,7 @@
         <v>7.125</v>
       </c>
       <c r="G658" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -23319,7 +23325,7 @@
         <v>7.125</v>
       </c>
       <c r="G660" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -23345,7 +23351,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G661" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -23371,7 +23377,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G662" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -23423,7 +23429,7 @@
         <v>7.15500020980835</v>
       </c>
       <c r="G664" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -23475,7 +23481,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G666" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -23501,7 +23507,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G667" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -23527,7 +23533,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G668" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -23553,7 +23559,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -23631,7 +23637,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G672" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -23657,7 +23663,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G673" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -23683,7 +23689,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G674" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -23735,7 +23741,7 @@
         <v>7.42500019073486</v>
       </c>
       <c r="G676" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -23761,7 +23767,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G677" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -23891,7 +23897,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G682" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -23917,7 +23923,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G683" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -23943,7 +23949,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G684" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -23969,7 +23975,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G685" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -24021,7 +24027,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G687" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -24047,7 +24053,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G688" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -24073,7 +24079,7 @@
         <v>5.96500015258789</v>
       </c>
       <c r="G689" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -24099,7 +24105,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G690" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -24125,7 +24131,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G691" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -24151,7 +24157,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G692" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -24177,7 +24183,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G693" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -24203,7 +24209,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G694" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -24229,7 +24235,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G695" t="s">
-        <v>580</v>
+        <v>406</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -24281,7 +24287,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G697" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -71271,27 +71277,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6911921296</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>68418</v>
+        <v>110479</v>
       </c>
       <c r="C2505" t="n">
-        <v>10.9799995422363</v>
+        <v>11.1899995803833</v>
       </c>
       <c r="D2505" t="n">
-        <v>10.789999961853</v>
+        <v>10.8299999237061</v>
       </c>
       <c r="E2505" t="n">
-        <v>10.9200000762939</v>
+        <v>11.1300001144409</v>
       </c>
       <c r="F2505" t="n">
-        <v>10.8800001144409</v>
+        <v>10.9700002670288</v>
       </c>
       <c r="G2505" t="s">
         <v>1938</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>168141</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>10.8699998855591</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1939</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>68418</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>10.789999961853</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6911805556</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>61896</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>11.1099996566772</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>11.0299997329712</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>10.8999996185303</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1943" uniqueCount="1943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1944">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15079474449158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13486289978027</t>
+    <t xml:space="preserve">2.150794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13486313819885</t>
   </si>
   <si>
     <t xml:space="preserve">2.09768867492676</t>
@@ -56,97 +56,97 @@
     <t xml:space="preserve">2.07379102706909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02334022521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0631697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0525484085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.964923620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988354206085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439254283905</t>
+    <t xml:space="preserve">2.02333998680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06316924095154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05254888534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988330364227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439266204834</t>
   </si>
   <si>
     <t xml:space="preserve">2.01802968978882</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01696729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209784507751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00156688690186</t>
+    <t xml:space="preserve">2.0169677734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209808349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015664100647</t>
   </si>
   <si>
     <t xml:space="preserve">2.059983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528407096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909184455872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97820043563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774927616119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943274021149</t>
+    <t xml:space="preserve">2.00528430938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97820031642914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854085445404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9277491569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943297863007</t>
   </si>
   <si>
     <t xml:space="preserve">1.91447269916534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93305993080139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712808609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589542388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237837791443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113575935364</t>
+    <t xml:space="preserve">1.93306028842926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712820529938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633638858795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589566230774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237790107727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113528251648</t>
   </si>
   <si>
     <t xml:space="preserve">2.08441209793091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09450197219849</t>
+    <t xml:space="preserve">2.09450221061707</t>
   </si>
   <si>
     <t xml:space="preserve">2.17203712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10830998420715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13964247703552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299944877625</t>
+    <t xml:space="preserve">2.10831022262573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13964223861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299897193909</t>
   </si>
   <si>
     <t xml:space="preserve">2.14442205429077</t>
@@ -155,58 +155,58 @@
     <t xml:space="preserve">2.14548397064209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15344977378845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14813947677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132546424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16831970214844</t>
+    <t xml:space="preserve">2.15345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813923835754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132594108582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16831994056702</t>
   </si>
   <si>
     <t xml:space="preserve">2.18265819549561</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22248768806458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495301246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955212593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10565447807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706736564636</t>
+    <t xml:space="preserve">2.222487449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495253562927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1056547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706760406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.07219767570496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12158632278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14017367362976</t>
+    <t xml:space="preserve">2.12158608436584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017343521118</t>
   </si>
   <si>
     <t xml:space="preserve">2.12424159049988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11362075805664</t>
+    <t xml:space="preserve">2.11362051963806</t>
   </si>
   <si>
     <t xml:space="preserve">2.06582522392273</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05307960510254</t>
+    <t xml:space="preserve">2.05307984352112</t>
   </si>
   <si>
     <t xml:space="preserve">2.0684802532196</t>
@@ -215,22 +215,22 @@
     <t xml:space="preserve">2.06901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11839985847473</t>
+    <t xml:space="preserve">2.11840033531189</t>
   </si>
   <si>
     <t xml:space="preserve">2.12477278709412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16141605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15557432174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17734742164612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24373030662537</t>
+    <t xml:space="preserve">2.16141581535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15557456016541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17734789848328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24373006820679</t>
   </si>
   <si>
     <t xml:space="preserve">2.25169634819031</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.29418110847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2575376033783</t>
+    <t xml:space="preserve">2.25753784179688</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461199760437</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">2.21452188491821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638533592224</t>
+    <t xml:space="preserve">2.22514295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24638557434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.23098492622375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32073426246643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34888005256653</t>
+    <t xml:space="preserve">2.32073402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888029098511</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604479789734</t>
@@ -269,46 +269,46 @@
     <t xml:space="preserve">2.4492506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50288796424866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775717735291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56555318832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997159957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547255516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555047035217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66718316078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7014753818512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68786716461182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72161555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346609115601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8152391910553</t>
+    <t xml:space="preserve">2.50288772583008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775765419006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5655529499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997183799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555023193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66718292236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70147585868835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68786764144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72161531448364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346656799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81523942947388</t>
   </si>
   <si>
     <t xml:space="preserve">2.95894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98942255973816</t>
+    <t xml:space="preserve">2.98942232131958</t>
   </si>
   <si>
     <t xml:space="preserve">3.00248622894287</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">2.8413667678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9175717830658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668559074402</t>
+    <t xml:space="preserve">2.91757225990295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668511390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797639846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81959366798401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76516151428223</t>
+    <t xml:space="preserve">2.81959390640259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76516127586365</t>
   </si>
   <si>
     <t xml:space="preserve">2.73685646057129</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">2.78693437576294</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86531734466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289084434509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84789848327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77604794502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86313962936401</t>
+    <t xml:space="preserve">2.86531662940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289060592651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84789824485779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77604818344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86313939094543</t>
   </si>
   <si>
     <t xml:space="preserve">2.91974925994873</t>
@@ -365,34 +365,34 @@
     <t xml:space="preserve">2.97200417518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99159979820251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97418117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99813199043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9785361289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03514575958252</t>
+    <t xml:space="preserve">2.99159955978394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97418141365051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99813175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97853589057922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0351459980011</t>
   </si>
   <si>
     <t xml:space="preserve">3.04820942878723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06998229026794</t>
+    <t xml:space="preserve">3.06998252868652</t>
   </si>
   <si>
     <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29859805107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730700492859</t>
+    <t xml:space="preserve">3.29859781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730724334717</t>
   </si>
   <si>
     <t xml:space="preserve">3.34214377403259</t>
@@ -401,10 +401,10 @@
     <t xml:space="preserve">3.2920663356781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28771162033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158404350281</t>
+    <t xml:space="preserve">3.28771185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158380508423</t>
   </si>
   <si>
     <t xml:space="preserve">3.24416565895081</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27900242805481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2572295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2659387588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17449235916138</t>
+    <t xml:space="preserve">3.27900266647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25722908973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593852043152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1744921207428</t>
   </si>
   <si>
     <t xml:space="preserve">3.25505208969116</t>
@@ -431,85 +431,85 @@
     <t xml:space="preserve">3.25940680503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33125734329224</t>
+    <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
     <t xml:space="preserve">3.35085320472717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34432101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28553414344788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35302996635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037091255188</t>
+    <t xml:space="preserve">3.34432125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472562789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28553462028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247023582458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303044319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037115097046</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682495117188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31383943557739</t>
+    <t xml:space="preserve">3.31383919715881</t>
   </si>
   <si>
     <t xml:space="preserve">3.30948448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15054225921631</t>
+    <t xml:space="preserve">3.15054202079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.18973326683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2093288898468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25069761276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20061993598938</t>
+    <t xml:space="preserve">3.20932912826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25069785118103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2006196975708</t>
   </si>
   <si>
     <t xml:space="preserve">3.22239303588867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09175562858582</t>
+    <t xml:space="preserve">3.09175515174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343482017517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26376128196716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20497465133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262582778931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141293525696</t>
+    <t xml:space="preserve">3.26376152038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20497488975525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262606620789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141317367554</t>
   </si>
   <si>
     <t xml:space="preserve">3.59253239631653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67962384223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824007987976</t>
+    <t xml:space="preserve">3.67962431907654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631186485291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90824055671692</t>
   </si>
   <si>
     <t xml:space="preserve">4.01057291030884</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">4.09331035614014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533128738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831751823425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11508321762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19346475601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33716678619385</t>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831727981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11508274078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19346523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
     <t xml:space="preserve">4.23483371734619</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">4.64634275436401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75956153869629</t>
+    <t xml:space="preserve">4.75956106185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334005355835</t>
@@ -563,40 +563,40 @@
     <t xml:space="preserve">4.72036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74214315414429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73778867721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6441650390625</t>
+    <t xml:space="preserve">4.74214267730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73778820037842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64416456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37418031692505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35023021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34152126312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22830247879028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128847122192</t>
+    <t xml:space="preserve">4.37418079376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023069381714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34152030944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22830200195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128799438477</t>
   </si>
   <si>
     <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572038650513</t>
+    <t xml:space="preserve">4.22612571716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24572134017944</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547136306763</t>
@@ -605,13 +605,13 @@
     <t xml:space="preserve">4.35458517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33934307098389</t>
+    <t xml:space="preserve">4.33934354782104</t>
   </si>
   <si>
     <t xml:space="preserve">4.65940570831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63763284683228</t>
+    <t xml:space="preserve">4.63763236999512</t>
   </si>
   <si>
     <t xml:space="preserve">4.63545608520508</t>
@@ -626,61 +626,61 @@
     <t xml:space="preserve">4.72254705429077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59408760070801</t>
+    <t xml:space="preserve">4.59408712387085</t>
   </si>
   <si>
     <t xml:space="preserve">4.66376066207886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5897331237793</t>
+    <t xml:space="preserve">4.58973217010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.51135063171387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73343372344971</t>
+    <t xml:space="preserve">4.52441358566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73343420028687</t>
   </si>
   <si>
     <t xml:space="preserve">4.64198780059814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78568935394287</t>
+    <t xml:space="preserve">4.78568840026855</t>
   </si>
   <si>
     <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74649715423584</t>
+    <t xml:space="preserve">4.746497631073</t>
   </si>
   <si>
     <t xml:space="preserve">4.7660927772522</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09921884536743</t>
+    <t xml:space="preserve">5.09921932220459</t>
   </si>
   <si>
     <t xml:space="preserve">5.38662195205688</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082012176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2516303062439</t>
+    <t xml:space="preserve">5.29082059860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25162935256958</t>
   </si>
   <si>
     <t xml:space="preserve">5.22985649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22767972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372915267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607702255249</t>
+    <t xml:space="preserve">5.22767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010503768921</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17107009887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14494132995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220579147339</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17106962203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14494228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220483779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.90979385375977</t>
@@ -710,49 +710,49 @@
     <t xml:space="preserve">5.09050893783569</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04043197631836</t>
+    <t xml:space="preserve">5.04043245315552</t>
   </si>
   <si>
     <t xml:space="preserve">5.11445999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10139608383179</t>
+    <t xml:space="preserve">5.10139656066895</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268712997437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12752342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663818359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95769453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736806869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98817729949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88584423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86624813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85536193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8466534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80092906951904</t>
+    <t xml:space="preserve">5.12752389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663770675659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478693008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95769548416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736759185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98817682266235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88584470748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8662486076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8553614616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84665298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80093002319336</t>
   </si>
   <si>
     <t xml:space="preserve">4.73561096191406</t>
@@ -767,31 +767,31 @@
     <t xml:space="preserve">4.75738382339478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68117952346802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9185037612915</t>
+    <t xml:space="preserve">4.68117904663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052564620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91850328445435</t>
   </si>
   <si>
     <t xml:space="preserve">5.13841009140015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08397769927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19719743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881494522095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09486436843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30170726776123</t>
+    <t xml:space="preserve">5.08397817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19719696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881446838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09486389160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30170774459839</t>
   </si>
   <si>
     <t xml:space="preserve">5.38444375991821</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">5.41710329055786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55209589004517</t>
+    <t xml:space="preserve">5.55209636688232</t>
   </si>
   <si>
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385347366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134929656982</t>
+    <t xml:space="preserve">5.63918781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385299682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134834289551</t>
   </si>
   <si>
     <t xml:space="preserve">5.94400835037231</t>
@@ -821,31 +821,31 @@
     <t xml:space="preserve">6.11383724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81337118148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87868928909302</t>
+    <t xml:space="preserve">5.81337022781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87868976593018</t>
   </si>
   <si>
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957595825195</t>
+    <t xml:space="preserve">5.76329326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957548141479</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9766674041748</t>
+    <t xml:space="preserve">5.97666835784912</t>
   </si>
   <si>
     <t xml:space="preserve">6.09641885757446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94836235046387</t>
+    <t xml:space="preserve">5.94836282730103</t>
   </si>
   <si>
     <t xml:space="preserve">5.9897313117981</t>
@@ -860,28 +860,28 @@
     <t xml:space="preserve">6.0419864654541</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05722808837891</t>
+    <t xml:space="preserve">6.05722713470459</t>
   </si>
   <si>
     <t xml:space="preserve">6.08335494995117</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96360445022583</t>
+    <t xml:space="preserve">5.96360397338867</t>
   </si>
   <si>
     <t xml:space="preserve">6.07464599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13996458053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42301273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26842594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52970027923584</t>
+    <t xml:space="preserve">6.13996505737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42301321029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26842546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52969980239868</t>
   </si>
   <si>
     <t xml:space="preserve">6.54276371002197</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">6.58848714828491</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80403852462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90201663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01088190078735</t>
+    <t xml:space="preserve">6.80403900146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90201759338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088237762451</t>
   </si>
   <si>
     <t xml:space="preserve">7.06531476974487</t>
@@ -905,31 +905,31 @@
     <t xml:space="preserve">7.11756944656372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3200569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063287734985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425603866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207927703857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321401596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392957687378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666702270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2852201461792</t>
+    <t xml:space="preserve">7.32005739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1306324005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425746917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321449279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2939305305481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666797637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28521966934204</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481624603271</t>
@@ -938,43 +938,43 @@
     <t xml:space="preserve">7.19595098495483</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46655797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40123987197876</t>
+    <t xml:space="preserve">6.4665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22705602645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309064865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4012393951416</t>
   </si>
   <si>
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704027175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316808700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57760000228882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52464437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215524673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45403528213501</t>
+    <t xml:space="preserve">6.49704122543335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316761016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57760047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5246434211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56215476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45403575897217</t>
   </si>
   <si>
     <t xml:space="preserve">6.55774211883545</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294660568237</t>
+    <t xml:space="preserve">6.76294755935669</t>
   </si>
   <si>
     <t xml:space="preserve">6.82252311706543</t>
@@ -992,49 +992,49 @@
     <t xml:space="preserve">6.41652536392212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58421945571899</t>
+    <t xml:space="preserve">6.58422040939331</t>
   </si>
   <si>
     <t xml:space="preserve">6.50478553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42093849182129</t>
+    <t xml:space="preserve">6.42093801498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694980621338</t>
+    <t xml:space="preserve">6.35694932937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.33488416671753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43417692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826519012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33267831802368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3746018409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14291906356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850545883179</t>
+    <t xml:space="preserve">6.43417739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826471328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33267784118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37460136413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057062149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1429181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850498199463</t>
   </si>
   <si>
     <t xml:space="preserve">5.95757150650024</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91344165802002</t>
+    <t xml:space="preserve">5.91344118118286</t>
   </si>
   <si>
     <t xml:space="preserve">5.90240907669067</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">5.95977830886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9200611114502</t>
+    <t xml:space="preserve">5.92006063461304</t>
   </si>
   <si>
     <t xml:space="preserve">5.93330001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94212675094604</t>
+    <t xml:space="preserve">5.94212627410889</t>
   </si>
   <si>
     <t xml:space="preserve">5.83621406555176</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">5.8472466468811</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98846244812012</t>
+    <t xml:space="preserve">5.98846340179443</t>
   </si>
   <si>
     <t xml:space="preserve">5.69720315933228</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">5.50744390487671</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46993350982666</t>
+    <t xml:space="preserve">5.46993398666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894298553467</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">5.7369213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76119184494019</t>
+    <t xml:space="preserve">5.7611927986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.89137697219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71485567092896</t>
+    <t xml:space="preserve">5.7148551940918</t>
   </si>
   <si>
     <t xml:space="preserve">5.72147512435913</t>
@@ -1103,28 +1103,28 @@
     <t xml:space="preserve">5.38608646392822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5449538230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4434552192688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007562637329</t>
+    <t xml:space="preserve">5.54495477676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44345569610596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007514953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932489395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41918420791626</t>
+    <t xml:space="preserve">5.41918325424194</t>
   </si>
   <si>
     <t xml:space="preserve">5.49199819564819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56040048599243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48096656799316</t>
+    <t xml:space="preserve">5.56040000915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48096609115601</t>
   </si>
   <si>
     <t xml:space="preserve">5.52730274200439</t>
@@ -1133,10 +1133,10 @@
     <t xml:space="preserve">5.45890092849731</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41256427764893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979139328003</t>
+    <t xml:space="preserve">5.41256475448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
     <t xml:space="preserve">5.56922626495361</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">5.80311632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86931180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030090332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554935455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860408782959</t>
+    <t xml:space="preserve">5.86931133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554887771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
   </si>
   <si>
     <t xml:space="preserve">5.80532264709473</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">5.56481313705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068281173706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47875881195068</t>
+    <t xml:space="preserve">5.52068328857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875928878784</t>
   </si>
   <si>
     <t xml:space="preserve">5.49420499801636</t>
@@ -1187,34 +1187,34 @@
     <t xml:space="preserve">5.29782629013062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22942447662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24045753479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369596481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477060317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39711904525757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796697616577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2228045463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14116334915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11909914016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20735931396484</t>
+    <t xml:space="preserve">5.22942399978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24045658111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39711856842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796792984009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22280502319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14116430282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11909818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20735883712769</t>
   </si>
   <si>
     <t xml:space="preserve">5.16764163970947</t>
@@ -1223,544 +1223,544 @@
     <t xml:space="preserve">5.13233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13675022125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03745746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00656604766846</t>
+    <t xml:space="preserve">5.13675117492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03745794296265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00656700134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96464252471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04849004745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19412040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576112747192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22501087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689233779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87197017669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72634029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131855010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60453081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8450403213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76781177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663850784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856203079224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307378768921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6398344039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6994104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467149734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.023766040802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348371505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14071226119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526655197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03479957580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80973529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034343719482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020275115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65086698532104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776924133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542175292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935434341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607242584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283256530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583215713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315885543823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854846954346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235298156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996248245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9222674369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396520614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800951004028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372493743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963666915894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198558807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474348068237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543621063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571949005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92843532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90637016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697925567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1005425453186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22852039337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04758739471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378288269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082487106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49330043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560729980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2814769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2594108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2196946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46241092681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62128019332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5374321937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710638046265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738822937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717555999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61952352523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450273513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219778060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163402557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57926988601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534488677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817632675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825437545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593116760254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145795822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12306022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171159744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14094972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669160842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21251249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774709701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821535110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53007125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061756134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44509077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40036487579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42719984054565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323581695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880163192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188718795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.474524974823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3358736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358846664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013124465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831531524658</t>
   </si>
   <si>
     <t xml:space="preserve">4.9646430015564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04849004745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576112747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22501087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87196969985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72634029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131902694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9315447807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60453081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81194257736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503984451294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76781129837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489868164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856155395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307378768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63983392715454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940948486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366788864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348419189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14071178436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526607513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597284317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80973529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034391403198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354028701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65086698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542222976685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935386657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607290267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03259325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2885479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413534164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235250473022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1693959236145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5559868812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92226839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429054260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072677612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4280104637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339912414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372446060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198415756226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474300384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571901321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9284348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90636968612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697830200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050001144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22851991653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908647537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082534790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49330139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1843900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147649765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127923965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390810012817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743267059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508375167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835073471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017419815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717603683472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802539825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6195240020752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219682693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247394561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66424989700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163354873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65977764129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.579270362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534440994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344995498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505174636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49429035186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825485229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985664367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305927276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171207427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14095020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669208526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829387664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2125129699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774662017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821487426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53007078170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061803817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44509029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4003643989563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42720031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4316725730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4629807472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10069608688354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39589166641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.474524974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33587312698364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093166351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358798980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013172149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831483840942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96464347839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07645988464355</t>
+    <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
     <t xml:space="preserve">5.05409669876099</t>
@@ -1775,22 +1775,22 @@
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58893966674805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577606201172</t>
+    <t xml:space="preserve">4.58894062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577653884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.74995517730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71417474746704</t>
+    <t xml:space="preserve">4.71417427062988</t>
   </si>
   <si>
     <t xml:space="preserve">4.37201690673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12825679779053</t>
+    <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
     <t xml:space="preserve">4.20876502990723</t>
@@ -1802,46 +1802,46 @@
     <t xml:space="preserve">4.04104042053223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0544581413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829701423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1550931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13049364089966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01867771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884331703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559144020081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702691078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740784645081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466420173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83753490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648013114929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96500515937805</t>
+    <t xml:space="preserve">4.05445861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353042602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15509271621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1304931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0186767578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8688428401947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559167861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702714920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740760803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466444015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83753442764282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648060798645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96500539779663</t>
   </si>
   <si>
     <t xml:space="preserve">4.15732955932617</t>
@@ -1850,37 +1850,37 @@
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9247510433197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264197349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331628799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8621346950531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84424376487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512294769287</t>
+    <t xml:space="preserve">3.92475080490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146109580994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264221191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331604957581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213445663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512342453003</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896134376526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24267220497131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03245782852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140305519104</t>
+    <t xml:space="preserve">3.24267244338989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03245806694031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
     <t xml:space="preserve">3.16216444969177</t>
@@ -1895,13 +1895,13 @@
     <t xml:space="preserve">3.26950812339783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22701787948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45288705825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39474248886108</t>
+    <t xml:space="preserve">3.22701811790466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4528865814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39474272727966</t>
   </si>
   <si>
     <t xml:space="preserve">3.4886679649353</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">3.5155041217804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31870746612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24714517593384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1107292175293</t>
+    <t xml:space="preserve">3.31870722770691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24714493751526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
     <t xml:space="preserve">2.92735028266907</t>
@@ -1934,10 +1934,10 @@
     <t xml:space="preserve">3.03916645050049</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642256736755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88485980033875</t>
+    <t xml:space="preserve">2.95642280578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88486003875732</t>
   </si>
   <si>
     <t xml:space="preserve">2.92511391639709</t>
@@ -1952,58 +1952,58 @@
     <t xml:space="preserve">2.78869819641113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83342480659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88933300971985</t>
+    <t xml:space="preserve">2.83342456817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88933277130127</t>
   </si>
   <si>
     <t xml:space="preserve">3.07271146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10625648498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16887331008911</t>
+    <t xml:space="preserve">3.10625624656677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16887354850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.22925424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22254514694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23596334457397</t>
+    <t xml:space="preserve">3.1599280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22254538536072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23596358299255</t>
   </si>
   <si>
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347262382507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3209433555603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54233980178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972273826599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339433670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49537706375122</t>
+    <t xml:space="preserve">3.19347310066223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094359397888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54234027862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972297668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53339457511902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4953773021698</t>
   </si>
   <si>
     <t xml:space="preserve">3.61166572570801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66533780097961</t>
+    <t xml:space="preserve">3.66533803939819</t>
   </si>
   <si>
     <t xml:space="preserve">3.57588458061218</t>
@@ -2015,28 +2015,28 @@
     <t xml:space="preserve">3.52221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58259391784668</t>
+    <t xml:space="preserve">3.5825936794281</t>
   </si>
   <si>
     <t xml:space="preserve">3.43723273277283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52444934844971</t>
+    <t xml:space="preserve">3.52444911003113</t>
   </si>
   <si>
     <t xml:space="preserve">3.58483028411865</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6944100856781</t>
+    <t xml:space="preserve">3.69440984725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284755706787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61390209197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70335555076599</t>
+    <t xml:space="preserve">3.61390233039856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70335531234741</t>
   </si>
   <si>
     <t xml:space="preserve">3.80399012565613</t>
@@ -2045,46 +2045,46 @@
     <t xml:space="preserve">3.89567947387695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77268123626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306169509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766196250916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040608406067</t>
+    <t xml:space="preserve">3.77268171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766220092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040632247925</t>
   </si>
   <si>
     <t xml:space="preserve">3.99184107780457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07011270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13272953033447</t>
+    <t xml:space="preserve">4.07011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13273000717163</t>
   </si>
   <si>
     <t xml:space="preserve">4.09247589111328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25125551223755</t>
+    <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94935154914856</t>
+    <t xml:space="preserve">3.94935083389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.00525951385498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02762269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842288017273</t>
+    <t xml:space="preserve">4.02762222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842335700989</t>
   </si>
   <si>
     <t xml:space="preserve">4.23112869262695</t>
@@ -2099,19 +2099,19 @@
     <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35412645339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16627502441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20429277420044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27809047698975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20205593109131</t>
+    <t xml:space="preserve">4.3541259765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1662745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20429182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2780909538269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20205545425415</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783731460571</t>
@@ -2135,28 +2135,28 @@
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285682678223</t>
+    <t xml:space="preserve">4.15285634994507</t>
   </si>
   <si>
     <t xml:space="preserve">4.18640184402466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26914596557617</t>
+    <t xml:space="preserve">4.26914548873901</t>
   </si>
   <si>
     <t xml:space="preserve">3.97171425819397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93369698524475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015196800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631428718567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0388035774231</t>
+    <t xml:space="preserve">3.93369674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90015149116516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631404876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880405426025</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
@@ -2165,22 +2165,22 @@
     <t xml:space="preserve">4.01644039154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778854370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7682089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77491784095764</t>
+    <t xml:space="preserve">3.91804265975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778902053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820921897888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77491736412048</t>
   </si>
   <si>
     <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85095286369324</t>
+    <t xml:space="preserve">3.85095238685608</t>
   </si>
   <si>
     <t xml:space="preserve">4.0991849899292</t>
@@ -2189,64 +2189,64 @@
     <t xml:space="preserve">3.82411694526672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95693039894104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88136458396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76229023933411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626088142395</t>
+    <t xml:space="preserve">3.95693111419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88136434555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76228976249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626111984253</t>
   </si>
   <si>
     <t xml:space="preserve">3.7645800113678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901348114014</t>
+    <t xml:space="preserve">3.68901371955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73252129554749</t>
+    <t xml:space="preserve">3.73252105712891</t>
   </si>
   <si>
     <t xml:space="preserve">3.84243655204773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87220430374146</t>
+    <t xml:space="preserve">3.87220454216003</t>
   </si>
   <si>
     <t xml:space="preserve">3.92487263679504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96609044075012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739346504211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006060600281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449526786804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655326843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
+    <t xml:space="preserve">3.96609020233154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739370346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006155967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8744945526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655303001404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440980911255</t>
   </si>
   <si>
     <t xml:space="preserve">4.04165649414062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15386152267456</t>
+    <t xml:space="preserve">4.19736957550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.09203433990479</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">4.14470148086548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18821001052856</t>
+    <t xml:space="preserve">4.18820953369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.27751541137695</t>
@@ -2276,43 +2276,43 @@
     <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30270433425903</t>
+    <t xml:space="preserve">4.30270385742188</t>
   </si>
   <si>
     <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2454571723938</t>
+    <t xml:space="preserve">4.24545669555664</t>
   </si>
   <si>
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858785629272</t>
+    <t xml:space="preserve">4.23858690261841</t>
   </si>
   <si>
     <t xml:space="preserve">4.22255802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1744704246521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997610092163</t>
+    <t xml:space="preserve">4.19507884979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774646759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17446947097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997562408447</t>
   </si>
   <si>
     <t xml:space="preserve">4.09890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15157127380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16302061080933</t>
+    <t xml:space="preserve">4.15157175064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16302108764648</t>
   </si>
   <si>
     <t xml:space="preserve">4.11035394668579</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">4.05539560317993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97067070007324</t>
+    <t xml:space="preserve">3.97067046165466</t>
   </si>
   <si>
     <t xml:space="preserve">3.945481300354</t>
@@ -2339,55 +2339,55 @@
     <t xml:space="preserve">3.84701585769653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8859441280365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87678480148315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159540176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235109329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043821334839</t>
+    <t xml:space="preserve">3.88594365119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.876784324646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159611701965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235085487366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043869018555</t>
   </si>
   <si>
     <t xml:space="preserve">3.98211932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13096237182617</t>
+    <t xml:space="preserve">4.13096284866333</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16760063171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04394674301147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0531063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18591976165771</t>
+    <t xml:space="preserve">4.16760110855103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04394626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05310583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18592023849487</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554191589355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06226634979248</t>
+    <t xml:space="preserve">4.06226491928101</t>
   </si>
   <si>
     <t xml:space="preserve">4.34392213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33705282211304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31873321533203</t>
+    <t xml:space="preserve">4.3370532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
     <t xml:space="preserve">4.60268020629883</t>
@@ -2408,31 +2408,31 @@
     <t xml:space="preserve">5.62855052947998</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48657655715942</t>
+    <t xml:space="preserve">5.48657703399658</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61023139953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70640659332275</t>
+    <t xml:space="preserve">5.61023187637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70640707015991</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45451879501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48199796676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26674842834473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27590799331665</t>
+    <t xml:space="preserve">5.45451927185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26674795150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27590847015381</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292314529419</t>
@@ -2441,37 +2441,37 @@
     <t xml:space="preserve">5.44993925094604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3446044921875</t>
+    <t xml:space="preserve">5.34460401535034</t>
   </si>
   <si>
     <t xml:space="preserve">5.47283792495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55985450744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69724750518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7293062210083</t>
+    <t xml:space="preserve">5.45909929275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55985403060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69724702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72930574417114</t>
   </si>
   <si>
     <t xml:space="preserve">5.92623615264893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74304580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7796835899353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7247257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67892789840698</t>
+    <t xml:space="preserve">5.74304533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77968311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72472620010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67892742156982</t>
   </si>
   <si>
     <t xml:space="preserve">5.71556663513184</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">5.80716276168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098661422729</t>
+    <t xml:space="preserve">5.71098709106445</t>
   </si>
   <si>
     <t xml:space="preserve">5.82090187072754</t>
@@ -2489,22 +2489,22 @@
     <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04989099502563</t>
+    <t xml:space="preserve">6.04989051818848</t>
   </si>
   <si>
     <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22392225265503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652830123901</t>
+    <t xml:space="preserve">6.22392177581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652925491333</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241134643555</t>
+    <t xml:space="preserve">6.02241230010986</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
@@ -2513,40 +2513,40 @@
     <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28643178939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235036849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6253342628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735696792603</t>
+    <t xml:space="preserve">7.10324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1994161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28643131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61159658432007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113208770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62533521652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735649108887</t>
   </si>
   <si>
     <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41924524307251</t>
+    <t xml:space="preserve">7.41924476623535</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
@@ -2555,85 +2555,85 @@
     <t xml:space="preserve">7.29101085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11697959899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26811218261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39634609222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37802696228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57495737075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91844129562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571258544922</t>
+    <t xml:space="preserve">7.27727174758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15361785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26811170578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39634561538696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37802743911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9184422492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85890293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571353912354</t>
   </si>
   <si>
     <t xml:space="preserve">7.56579780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66655397415161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130348205566</t>
+    <t xml:space="preserve">7.66655302047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130395889282</t>
   </si>
   <si>
     <t xml:space="preserve">7.12155914306641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41466569900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25895261764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30475044250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22231483459473</t>
+    <t xml:space="preserve">7.41466522216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25895357131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30475091934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22231435775757</t>
   </si>
   <si>
     <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4375638961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48794221878052</t>
+    <t xml:space="preserve">7.43756437301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48794269561768</t>
   </si>
   <si>
     <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31849002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17651700973511</t>
+    <t xml:space="preserve">7.31848955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17651653289795</t>
   </si>
   <si>
     <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51244831085205</t>
+    <t xml:space="preserve">6.51244878768921</t>
   </si>
   <si>
     <t xml:space="preserve">6.51702833175659</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">6.7414379119873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79639434814453</t>
+    <t xml:space="preserve">6.79639482498169</t>
   </si>
   <si>
     <t xml:space="preserve">6.71853828430176</t>
@@ -2651,22 +2651,22 @@
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6177830696106</t>
+    <t xml:space="preserve">6.61778354644775</t>
   </si>
   <si>
     <t xml:space="preserve">7.02538394927979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89256954193115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89715051651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097436904907</t>
+    <t xml:space="preserve">6.89257097244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89714956283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82845306396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097484588623</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732048034668</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">6.76433658599854</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6361026763916</t>
+    <t xml:space="preserve">6.63610219955444</t>
   </si>
   <si>
     <t xml:space="preserve">6.11858701705933</t>
@@ -2690,10 +2690,10 @@
     <t xml:space="preserve">5.78884315490723</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63771104812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77052354812622</t>
+    <t xml:space="preserve">5.63771057128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77052450180054</t>
   </si>
   <si>
     <t xml:space="preserve">5.72014617919922</t>
@@ -2702,34 +2702,34 @@
     <t xml:space="preserve">5.47741794586182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11561489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381278991699</t>
+    <t xml:space="preserve">5.1156153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381231307983</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810018539429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63931846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21110820770264</t>
+    <t xml:space="preserve">4.63931798934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21110868453979</t>
   </si>
   <si>
     <t xml:space="preserve">3.8149573802948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66382479667664</t>
+    <t xml:space="preserve">3.66382455825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034134864807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22416543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18294787406921</t>
+    <t xml:space="preserve">3.22416567802429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
     <t xml:space="preserve">3.22645592689514</t>
@@ -2738,34 +2738,34 @@
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304521560669</t>
+    <t xml:space="preserve">3.99356842041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304545402527</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344718933105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50353240966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069435119629</t>
+    <t xml:space="preserve">3.50353264808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069458961487</t>
   </si>
   <si>
     <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70962262153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6226065158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168062210083</t>
+    <t xml:space="preserve">3.70962238311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663801193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168086051941</t>
   </si>
   <si>
     <t xml:space="preserve">4.06684541702271</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">4.03020763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3828501701355</t>
+    <t xml:space="preserve">4.38285064697266</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722278594971</t>
@@ -2786,43 +2786,43 @@
     <t xml:space="preserve">4.17218065261841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09432411193848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4881854057312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45612621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35995149612427</t>
+    <t xml:space="preserve">4.09432363510132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48818492889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45612668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35995101928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2637767791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32331275939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35537147521973</t>
+    <t xml:space="preserve">4.26377630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32331323623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35537195205688</t>
   </si>
   <si>
     <t xml:space="preserve">4.30957412719727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17675971984863</t>
+    <t xml:space="preserve">4.30499362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676019668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52482318878174</t>
+    <t xml:space="preserve">4.52482414245605</t>
   </si>
   <si>
     <t xml:space="preserve">4.48360538482666</t>
@@ -2834,52 +2834,52 @@
     <t xml:space="preserve">4.42406845092773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75152254104614</t>
+    <t xml:space="preserve">4.7515230178833</t>
   </si>
   <si>
     <t xml:space="preserve">4.95761299133301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90036487579346</t>
+    <t xml:space="preserve">4.90036535263062</t>
   </si>
   <si>
     <t xml:space="preserve">4.88891649246216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04920816421509</t>
+    <t xml:space="preserve">5.04920864105225</t>
   </si>
   <si>
     <t xml:space="preserve">5.18660163879395</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23239994049072</t>
+    <t xml:space="preserve">5.23239946365356</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34689426422119</t>
+    <t xml:space="preserve">5.34689474105835</t>
   </si>
   <si>
     <t xml:space="preserve">5.16370248794556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93471431732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630996704102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19805192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31254625320435</t>
+    <t xml:space="preserve">4.93471384048462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630949020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19805145263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39269161224365</t>
+    <t xml:space="preserve">5.39269208908081</t>
   </si>
   <si>
     <t xml:space="preserve">5.20950078964233</t>
@@ -2894,28 +2894,28 @@
     <t xml:space="preserve">5.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09500646591187</t>
+    <t xml:space="preserve">5.24384880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09500694274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.923264503479</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01486015319824</t>
+    <t xml:space="preserve">5.01485967636108</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06065797805786</t>
+    <t xml:space="preserve">5.0606575012207</t>
   </si>
   <si>
     <t xml:space="preserve">5.22095012664795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210731506348</t>
+    <t xml:space="preserve">5.07210683822632</t>
   </si>
   <si>
     <t xml:space="preserve">5.10645532608032</t>
@@ -2930,19 +2930,19 @@
     <t xml:space="preserve">5.33544445037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03775835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355617523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96906232833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94616270065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9805121421814</t>
+    <t xml:space="preserve">5.03775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355665206909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96906280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94616317749023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98051118850708</t>
   </si>
   <si>
     <t xml:space="preserve">4.84311866760254</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9919605255127</t>
+    <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.00341081619263</t>
@@ -2963,7 +2963,7 @@
     <t xml:space="preserve">4.1904993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21339845657349</t>
+    <t xml:space="preserve">4.21339797973633</t>
   </si>
   <si>
     <t xml:space="preserve">4.08058452606201</t>
@@ -2972,43 +2972,43 @@
     <t xml:space="preserve">4.30041408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163236618042</t>
+    <t xml:space="preserve">4.34163188934326</t>
   </si>
   <si>
     <t xml:space="preserve">4.61412858963013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54153537750244</t>
+    <t xml:space="preserve">5.54153490066528</t>
   </si>
   <si>
     <t xml:space="preserve">5.62168073654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75907468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73617601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69037818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64458036422729</t>
+    <t xml:space="preserve">5.75907421112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73617506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69037771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64457988739014</t>
   </si>
   <si>
     <t xml:space="preserve">5.66747903823853</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89646768569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70182704925537</t>
+    <t xml:space="preserve">5.89646816253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70182752609253</t>
   </si>
   <si>
     <t xml:space="preserve">5.816321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14835643768311</t>
+    <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
     <t xml:space="preserve">5.96516466140747</t>
@@ -3017,43 +3017,43 @@
     <t xml:space="preserve">5.95371532440186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91936731338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09110879898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415330886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1254563331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15980529785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07965850830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13690662384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21705198287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35444593429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36589574813843</t>
+    <t xml:space="preserve">5.87356901168823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91936635971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09110832214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415378570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12545680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15980577468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18270397186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07965898513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13690614700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2170524597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3544454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009840011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
     <t xml:space="preserve">6.48038959503174</t>
@@ -3068,25 +3068,25 @@
     <t xml:space="preserve">6.56053590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60633420944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62923288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41169309616089</t>
+    <t xml:space="preserve">6.60633373260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58343553543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62923336029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41169261932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894025802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29719877243042</t>
+    <t xml:space="preserve">6.46894073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29719829559326</t>
   </si>
   <si>
     <t xml:space="preserve">6.20560312271118</t>
@@ -3098,16 +3098,16 @@
     <t xml:space="preserve">6.50328874588013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66358137130737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51473808288574</t>
+    <t xml:space="preserve">6.66358089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.78952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.75517606735229</t>
+    <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.68648052215576</t>
@@ -3116,19 +3116,19 @@
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792985916138</t>
+    <t xml:space="preserve">6.77807521820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792938232422</t>
   </si>
   <si>
     <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734460830688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154678344727</t>
+    <t xml:space="preserve">6.37734508514404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154726028442</t>
   </si>
   <si>
     <t xml:space="preserve">6.38879442214966</t>
@@ -3137,16 +3137,16 @@
     <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86967134475708</t>
+    <t xml:space="preserve">6.86967086791992</t>
   </si>
   <si>
     <t xml:space="preserve">7.78562784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77417802810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24360466003418</t>
+    <t xml:space="preserve">7.77417945861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
     <t xml:space="preserve">8.17490863800049</t>
@@ -3161,37 +3161,37 @@
     <t xml:space="preserve">8.06041526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02606678009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911128997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1062126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03751564025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00316715240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447113037109</t>
+    <t xml:space="preserve">8.02606582641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911224365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03751468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0031681060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447017669678</t>
   </si>
   <si>
     <t xml:space="preserve">8.08331298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3123025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085372924805</t>
+    <t xml:space="preserve">8.31230163574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085277557373</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940296173096</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33520126342773</t>
+    <t xml:space="preserve">8.33520221710205</t>
   </si>
   <si>
     <t xml:space="preserve">8.2779541015625</t>
@@ -3200,43 +3200,43 @@
     <t xml:space="preserve">8.15200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18635749816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34665012359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23215579986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16345977783203</t>
+    <t xml:space="preserve">8.11766147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18635845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34665107727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23215675354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16345882415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.07186317443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20925807952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94592046737671</t>
+    <t xml:space="preserve">8.20925617218018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94591999053955</t>
   </si>
   <si>
     <t xml:space="preserve">7.95736932754517</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8428750038147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.923020362854</t>
+    <t xml:space="preserve">7.84287452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92301988601685</t>
   </si>
   <si>
     <t xml:space="preserve">7.81997585296631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86577320098877</t>
+    <t xml:space="preserve">7.86577272415161</t>
   </si>
   <si>
     <t xml:space="preserve">8.3809986114502</t>
@@ -3245,31 +3245,31 @@
     <t xml:space="preserve">9.15956211090088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99926853179932</t>
+    <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
     <t xml:space="preserve">9.20536041259766</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48014736175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65356349945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60731887817383</t>
+    <t xml:space="preserve">9.48014640808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65356254577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60731983184814</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0813264846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2894277572632</t>
+    <t xml:space="preserve">9.71136856079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0813255310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2894268035889</t>
   </si>
   <si>
     <t xml:space="preserve">10.3009881973267</t>
@@ -3278,22 +3278,22 @@
     <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5206499099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3587951660156</t>
+    <t xml:space="preserve">10.5206508636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
     <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975290298462</t>
+    <t xml:space="preserve">10.4975280761719</t>
   </si>
   <si>
     <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628438949585</t>
+    <t xml:space="preserve">10.4628448486328</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050388336182</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">10.7403125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4744062423706</t>
+    <t xml:space="preserve">10.4744052886963</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819169998169</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">10.3934783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0582046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0235204696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1506938934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697650909424</t>
+    <t xml:space="preserve">10.0582036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0235214233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1506948471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697641372681</t>
   </si>
   <si>
     <t xml:space="preserve">10.092887878418</t>
@@ -3350,25 +3350,25 @@
     <t xml:space="preserve">10.4859666824341</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1853761672974</t>
+    <t xml:space="preserve">10.1853771209717</t>
   </si>
   <si>
     <t xml:space="preserve">10.0350828170776</t>
   </si>
   <si>
-    <t xml:space="preserve">10.416600227356</t>
+    <t xml:space="preserve">10.4165992736816</t>
   </si>
   <si>
     <t xml:space="preserve">10.1738157272339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391324996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1911973953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5056610107422</t>
+    <t xml:space="preserve">10.1391315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.191198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
     <t xml:space="preserve">11.9052143096924</t>
@@ -3377,37 +3377,37 @@
     <t xml:space="preserve">11.901515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.746132850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5611534118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5426559448242</t>
+    <t xml:space="preserve">11.7461318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5611543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5426568984985</t>
   </si>
   <si>
     <t xml:space="preserve">11.42982006073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576765060425</t>
+    <t xml:space="preserve">11.5796518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4501676559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576774597168</t>
   </si>
   <si>
     <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6536436080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3946743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4686641693115</t>
+    <t xml:space="preserve">11.6536445617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3946733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4686651229858</t>
   </si>
   <si>
     <t xml:space="preserve">12.0975914001465</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0605964660645</t>
+    <t xml:space="preserve">12.0605974197388</t>
   </si>
   <si>
     <t xml:space="preserve">12.0420989990234</t>
@@ -3431,10 +3431,10 @@
     <t xml:space="preserve">11.8941144943237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.9299945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
@@ -3455,19 +3455,19 @@
     <t xml:space="preserve">13.7254018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631796836853</t>
+    <t xml:space="preserve">14.6317958831787</t>
   </si>
   <si>
     <t xml:space="preserve">14.0398664474487</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7439002990723</t>
+    <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
     <t xml:space="preserve">13.4109392166138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7623987197876</t>
+    <t xml:space="preserve">13.7623977661133</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294376373291</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669923782349</t>
+    <t xml:space="preserve">12.9669904708862</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8929986953735</t>
+    <t xml:space="preserve">12.8929996490479</t>
   </si>
   <si>
     <t xml:space="preserve">13.3739433288574</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457015991211</t>
+    <t xml:space="preserve">15.4457035064697</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011959075928</t>
@@ -3509,7 +3509,7 @@
     <t xml:space="preserve">15.7786626815796</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5555725097656</t>
+    <t xml:space="preserve">16.555570602417</t>
   </si>
   <si>
     <t xml:space="preserve">16.3705959320068</t>
@@ -3518,46 +3518,46 @@
     <t xml:space="preserve">16.5370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520965576172</t>
+    <t xml:space="preserve">16.2596073150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">16.019136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7971591949463</t>
+    <t xml:space="preserve">15.7971611022949</t>
   </si>
   <si>
     <t xml:space="preserve">16.1486186981201</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0006370544434</t>
+    <t xml:space="preserve">16.000638961792</t>
   </si>
   <si>
     <t xml:space="preserve">15.9081506729126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5196943283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896522521973</t>
+    <t xml:space="preserve">15.5196952819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4641990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896503448486</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341579437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092645645142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283208847046</t>
+    <t xml:space="preserve">15.8341569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092655181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">14.502311706543</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">13.6329126358032</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6514110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369483947754</t>
+    <t xml:space="preserve">13.6514120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369474411011</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993946075439</t>
+    <t xml:space="preserve">13.7993936538696</t>
   </si>
   <si>
     <t xml:space="preserve">13.7808961868286</t>
@@ -3602,22 +3602,22 @@
     <t xml:space="preserve">13.2629566192627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5404243469238</t>
+    <t xml:space="preserve">13.5404233932495</t>
   </si>
   <si>
     <t xml:space="preserve">13.3924407958984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3554449081421</t>
+    <t xml:space="preserve">13.3554439544678</t>
   </si>
   <si>
     <t xml:space="preserve">13.965874671936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1323547363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2988357543945</t>
+    <t xml:space="preserve">14.1323537826538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2988367080688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2803382873535</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">14.1138572692871</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9484920501709</t>
+    <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
     <t xml:space="preserve">13.1334705352783</t>
@@ -3635,40 +3635,40 @@
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479341506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085790634155</t>
+    <t xml:space="preserve">13.4479351043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085781097412</t>
   </si>
   <si>
     <t xml:space="preserve">12.3935565948486</t>
   </si>
   <si>
-    <t xml:space="preserve">13.18896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4664325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8190078735352</t>
+    <t xml:space="preserve">13.1889657974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4664335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8190088272095</t>
   </si>
   <si>
     <t xml:space="preserve">11.9126138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6340284347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3380641937256</t>
+    <t xml:space="preserve">12.6340293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3380632400513</t>
   </si>
   <si>
     <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9496097564697</t>
+    <t xml:space="preserve">12.1345872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9496088027954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6721420288086</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681072235107</t>
+    <t xml:space="preserve">11.9681062698364</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
@@ -3698,25 +3698,25 @@
     <t xml:space="preserve">10.5067768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1172065734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8201236724854</t>
+    <t xml:space="preserve">11.117205619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8201246261597</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6710243225098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265186309814</t>
+    <t xml:space="preserve">12.6710252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265176773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.8005104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2259607315063</t>
+    <t xml:space="preserve">13.225959777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.3276977539062</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">12.6617765426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
+    <t xml:space="preserve">12.4305534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028062820435</t>
   </si>
   <si>
     <t xml:space="preserve">12.5137929916382</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">12.3473138809204</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3288154602051</t>
+    <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
     <t xml:space="preserve">12.4952955245972</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">12.4398021697998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8016262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9958534240723</t>
+    <t xml:space="preserve">11.8016271591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
     <t xml:space="preserve">12.3565607070923</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7646312713623</t>
+    <t xml:space="preserve">11.764630317688</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848676681519</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">11.5519046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2929372787476</t>
+    <t xml:space="preserve">11.2929353713989</t>
   </si>
   <si>
     <t xml:space="preserve">10.6455106735229</t>
@@ -3785,16 +3785,16 @@
     <t xml:space="preserve">10.7657470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0987071990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5704050064087</t>
+    <t xml:space="preserve">11.098708152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5704040527344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293724060059</t>
+    <t xml:space="preserve">11.8293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605554580688</t>
+    <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">11.569953918457</t>
@@ -3812,16 +3812,16 @@
     <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432819366455</t>
+    <t xml:space="preserve">12.1432809829712</t>
   </si>
   <si>
     <t xml:space="preserve">11.85191822052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7579298019409</t>
+    <t xml:space="preserve">11.6639413833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7579307556152</t>
   </si>
   <si>
     <t xml:space="preserve">11.974102973938</t>
@@ -3845,16 +3845,16 @@
     <t xml:space="preserve">10.5642786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0530185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5830764770508</t>
+    <t xml:space="preserve">11.053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5830774307251</t>
   </si>
   <si>
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
+    <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4571666717529</t>
+    <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631801605225</t>
+    <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075487136841</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.096287727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876523971558</t>
+    <t xml:space="preserve">12.0962867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
@@ -3911,13 +3911,13 @@
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
+    <t xml:space="preserve">12.8481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.998574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1677541732788</t>
+    <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.4685163497925</t>
@@ -3926,37 +3926,37 @@
     <t xml:space="preserve">13.6188974380493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5625057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6094970703125</t>
+    <t xml:space="preserve">13.5625047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6094980239868</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564922332764</t>
+    <t xml:space="preserve">13.6564931869507</t>
   </si>
   <si>
     <t xml:space="preserve">13.741081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6752901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8726654052734</t>
+    <t xml:space="preserve">13.6752910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8726663589478</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3087358474731</t>
+    <t xml:space="preserve">13.3087368011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1583547592163</t>
+    <t xml:space="preserve">13.158353805542</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">13.2335453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0643653869629</t>
+    <t xml:space="preserve">13.0925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0643663406372</t>
   </si>
   <si>
     <t xml:space="preserve">13.1113605499268</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850257873535</t>
+    <t xml:space="preserve">12.5850267410278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756282806396</t>
@@ -4013,13 +4013,13 @@
     <t xml:space="preserve">13.1207599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1056871414185</t>
+    <t xml:space="preserve">12.1056861877441</t>
   </si>
   <si>
     <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692138671875</t>
+    <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
     <t xml:space="preserve">11.391375541687</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548801422119</t>
@@ -4046,16 +4046,16 @@
     <t xml:space="preserve">10.6582670211792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9778270721436</t>
+    <t xml:space="preserve">10.3951015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
     <t xml:space="preserve">11.4665660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1939992904663</t>
+    <t xml:space="preserve">11.1940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667667388916</t>
+    <t xml:space="preserve">10.6676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">11.7485313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1150856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">12.1150846481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4121,7 +4121,7 @@
     <t xml:space="preserve">12.773003578186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0455684661865</t>
+    <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.0831651687622</t>
@@ -4157,16 +4157,16 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2580184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504816055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2805395126343</t>
+    <t xml:space="preserve">14.258017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2805404663086</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463315963745</t>
+    <t xml:space="preserve">13.3463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523431777954</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">13.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3933248519897</t>
+    <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">13.7598791122437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7316827774048</t>
+    <t xml:space="preserve">13.7316818237305</t>
   </si>
   <si>
     <t xml:space="preserve">14.0606422424316</t>
@@ -4217,58 +4217,58 @@
     <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8914623260498</t>
+    <t xml:space="preserve">13.7786769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4215211868286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0888376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5587797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749528884888</t>
+    <t xml:space="preserve">14.0888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5587787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749519348145</t>
   </si>
   <si>
     <t xml:space="preserve">14.8407440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0193223953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0099239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6997623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7279586791992</t>
+    <t xml:space="preserve">15.0193214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0099229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6997632980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7279596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031492233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7655544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7937507629395</t>
+    <t xml:space="preserve">14.8031482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7655534744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7937498092651</t>
   </si>
   <si>
     <t xml:space="preserve">14.6621675491333</t>
@@ -4280,7 +4280,7 @@
     <t xml:space="preserve">14.6903638839722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689413070679</t>
+    <t xml:space="preserve">14.8689403533936</t>
   </si>
   <si>
     <t xml:space="preserve">15.1039113998413</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">11.3725786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9872255325317</t>
+    <t xml:space="preserve">10.9872264862061</t>
   </si>
   <si>
     <t xml:space="preserve">11.269190788269</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">11.4477691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4101734161377</t>
+    <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1846017837524</t>
@@ -4343,13 +4343,13 @@
     <t xml:space="preserve">11.1094102859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0812149047852</t>
+    <t xml:space="preserve">11.2221975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0812139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.0342197418213</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">10.8744401931763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9590291976929</t>
+    <t xml:space="preserve">10.9590301513672</t>
   </si>
   <si>
     <t xml:space="preserve">10.9026374816895</t>
@@ -4373,16 +4373,16 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146596908569</t>
+    <t xml:space="preserve">10.7146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8650426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4138975143433</t>
+    <t xml:space="preserve">10.8650417327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4138984680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387069702148</t>
@@ -5841,6 +5841,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.1400003433228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2700004577637</t>
   </si>
 </sst>
 </file>
@@ -71387,7 +71390,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.6909722222</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>73232</v>
@@ -71408,6 +71411,32 @@
         <v>1942</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.6911805556</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>91867</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>11.4099998474121</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>11.1499996185303</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>11.2700004577637</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>1943</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1945">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034370422363</t>
+    <t xml:space="preserve">2.10034394264221</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.150794506073</t>
+    <t xml:space="preserve">2.15079498291016</t>
   </si>
   <si>
     <t xml:space="preserve">2.13486313819885</t>
@@ -53,82 +53,82 @@
     <t xml:space="preserve">2.09768867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07379102706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02333998680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06316924095154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05254888534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96492338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988330364227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802968978882</t>
+    <t xml:space="preserve">2.07379078865051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02334022521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0631697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0525484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.964923620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439278125763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0180299282074</t>
   </si>
   <si>
     <t xml:space="preserve">2.0169677734375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0015664100647</t>
+    <t xml:space="preserve">2.00209784507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00156688690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.059983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528430938721</t>
+    <t xml:space="preserve">2.00528383255005</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97820031642914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89854085445404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9277491569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943297863007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447269916534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93306028842926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712820529938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633638858795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589566230774</t>
+    <t xml:space="preserve">1.97819995880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89854073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774927616119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943274021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447281837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93305993080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712808609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633662700653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589554309845</t>
   </si>
   <si>
     <t xml:space="preserve">1.94368076324463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09237790107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113528251648</t>
+    <t xml:space="preserve">2.09237861633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113575935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.08441209793091</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">2.17203712463379</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10831022262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13964223861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442205429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14548397064209</t>
+    <t xml:space="preserve">2.10830998420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1396427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299921035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442181587219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14548468589783</t>
   </si>
   <si>
     <t xml:space="preserve">2.15345001220703</t>
@@ -161,25 +161,25 @@
     <t xml:space="preserve">2.14813923835754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15132594108582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16831994056702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18265819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.222487449646</t>
+    <t xml:space="preserve">2.15132546424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16831970214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18265843391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22248768806458</t>
   </si>
   <si>
     <t xml:space="preserve">2.15610551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14495253562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955236434937</t>
+    <t xml:space="preserve">2.14495301246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955212593079</t>
   </si>
   <si>
     <t xml:space="preserve">2.1056547164917</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">2.14017343521118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12424159049988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11362051963806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06582522392273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05307984352112</t>
+    <t xml:space="preserve">2.12424182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11362075805664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06582498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05307960510254</t>
   </si>
   <si>
     <t xml:space="preserve">2.0684802532196</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">2.06901121139526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11840033531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12477278709412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16141581535339</t>
+    <t xml:space="preserve">2.11839985847473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12477254867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16141605377197</t>
   </si>
   <si>
     <t xml:space="preserve">2.15557456016541</t>
@@ -230,16 +230,16 @@
     <t xml:space="preserve">2.17734789848328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24373006820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25169634819031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29418110847473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25753784179688</t>
+    <t xml:space="preserve">2.24373078346252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25169610977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29418063163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2575376033783</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461199760437</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">2.22514295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24638557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098492622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34888029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604479789734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4492506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50288772583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51775765419006</t>
+    <t xml:space="preserve">2.24638509750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2309844493866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073426246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888052940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604503631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44925045967102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50288796424866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51775741577148</t>
   </si>
   <si>
     <t xml:space="preserve">2.5655529499054</t>
@@ -284,88 +284,88 @@
     <t xml:space="preserve">2.6154727935791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66555023193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66718292236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70147585868835</t>
+    <t xml:space="preserve">2.66554999351501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66718339920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7014753818512</t>
   </si>
   <si>
     <t xml:space="preserve">2.68786764144897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72161531448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346656799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81523942947388</t>
+    <t xml:space="preserve">2.7216157913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8152391910553</t>
   </si>
   <si>
     <t xml:space="preserve">2.95894050598145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98942232131958</t>
+    <t xml:space="preserve">2.989422082901</t>
   </si>
   <si>
     <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94587635993958</t>
+    <t xml:space="preserve">2.94587659835815</t>
   </si>
   <si>
     <t xml:space="preserve">2.8413667678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91757225990295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668511390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797639846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81959390640259</t>
+    <t xml:space="preserve">2.9175717830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668559074402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797616004944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81959366798401</t>
   </si>
   <si>
     <t xml:space="preserve">2.76516127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73685646057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6954882144928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531662940979</t>
+    <t xml:space="preserve">2.73685669898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69548797607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78693413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531686782837</t>
   </si>
   <si>
     <t xml:space="preserve">2.98289060592651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84789824485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77604818344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86313939094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974925994873</t>
+    <t xml:space="preserve">2.84789872169495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.776047706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86313962936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974902153015</t>
   </si>
   <si>
     <t xml:space="preserve">2.97200417518616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99159955978394</t>
+    <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418141365051</t>
@@ -374,22 +374,22 @@
     <t xml:space="preserve">2.99813175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97853589057922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0351459980011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04820942878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998252868652</t>
+    <t xml:space="preserve">2.9785361289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03514552116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04820919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
     <t xml:space="preserve">3.15707397460938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29859781265259</t>
+    <t xml:space="preserve">3.29859805107117</t>
   </si>
   <si>
     <t xml:space="preserve">3.30730724334717</t>
@@ -398,58 +398,58 @@
     <t xml:space="preserve">3.34214377403259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2920663356781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24416565895081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28988885879517</t>
+    <t xml:space="preserve">3.29206657409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771114349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158404350281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24416589736938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28988909721375</t>
   </si>
   <si>
     <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25722908973694</t>
+    <t xml:space="preserve">3.25722980499268</t>
   </si>
   <si>
     <t xml:space="preserve">3.26593852043152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1744921207428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25505208969116</t>
+    <t xml:space="preserve">3.17449259757996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25505256652832</t>
   </si>
   <si>
     <t xml:space="preserve">3.25940680503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33125758171082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35085320472717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34432125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472562789917</t>
+    <t xml:space="preserve">3.33125734329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35085344314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34432101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472538948059</t>
   </si>
   <si>
     <t xml:space="preserve">3.28553462028503</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27247023582458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303044319153</t>
+    <t xml:space="preserve">3.27247071266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35302996635437</t>
   </si>
   <si>
     <t xml:space="preserve">3.32037115097046</t>
@@ -458,7 +458,7 @@
     <t xml:space="preserve">3.27682495117188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31383919715881</t>
+    <t xml:space="preserve">3.31383895874023</t>
   </si>
   <si>
     <t xml:space="preserve">3.30948448181152</t>
@@ -467,22 +467,22 @@
     <t xml:space="preserve">3.15054202079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18973326683044</t>
+    <t xml:space="preserve">3.18973350524902</t>
   </si>
   <si>
     <t xml:space="preserve">3.20932912826538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25069785118103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2006196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239303588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175515174866</t>
+    <t xml:space="preserve">3.25069761276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20061993598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239255905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175539016724</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343482017517</t>
@@ -491,22 +491,22 @@
     <t xml:space="preserve">3.26376152038574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20497488975525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37262606620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43141317367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59253239631653</t>
+    <t xml:space="preserve">3.20497417449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37262630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43141293525696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59253263473511</t>
   </si>
   <si>
     <t xml:space="preserve">3.67962431907654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78631186485291</t>
+    <t xml:space="preserve">3.78631138801575</t>
   </si>
   <si>
     <t xml:space="preserve">3.90824055671692</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">4.01057291030884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09331035614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533200263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831727981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11508274078369</t>
+    <t xml:space="preserve">4.09330940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533224105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831775665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11508226394653</t>
   </si>
   <si>
     <t xml:space="preserve">4.19346523284912</t>
@@ -533,25 +533,25 @@
     <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483371734619</t>
+    <t xml:space="preserve">4.23483324050903</t>
   </si>
   <si>
     <t xml:space="preserve">4.26313829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47433567047119</t>
+    <t xml:space="preserve">4.47433614730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.68988800048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65722894668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956106185913</t>
+    <t xml:space="preserve">4.65722846984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6463418006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956153869629</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334005355835</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">4.74214267730713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73778820037842</t>
+    <t xml:space="preserve">4.73778867721558</t>
   </si>
   <si>
     <t xml:space="preserve">4.64416456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57231426239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37418079376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35023069381714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34152030944824</t>
+    <t xml:space="preserve">4.57231378555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37418127059937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35023021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34152173995972</t>
   </si>
   <si>
     <t xml:space="preserve">4.22830200195312</t>
@@ -593,106 +593,106 @@
     <t xml:space="preserve">4.08895540237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612571716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24572134017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36547136306763</t>
+    <t xml:space="preserve">4.22612476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24571990966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36547040939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.35458517074585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33934354782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63763236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545608520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61586046218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72254705429077</t>
+    <t xml:space="preserve">4.3393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940618515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63763380050659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545560836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61585998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851999282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72254800796509</t>
   </si>
   <si>
     <t xml:space="preserve">4.59408712387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66376066207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58973217010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51135063171387</t>
+    <t xml:space="preserve">4.66376113891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58973264694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134967803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.52441358566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73343420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64198780059814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78568840026855</t>
+    <t xml:space="preserve">4.73343467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64198732376099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78568887710571</t>
   </si>
   <si>
     <t xml:space="preserve">4.77480268478394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.746497631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7660927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921932220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38662195205688</t>
+    <t xml:space="preserve">4.74649715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609325408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921979904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38662147521973</t>
   </si>
   <si>
     <t xml:space="preserve">5.29082059860229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25162935256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22985649108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22767877578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11010503768921</t>
+    <t xml:space="preserve">5.25162982940674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22985744476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767925262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372915267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607702255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11010551452637</t>
   </si>
   <si>
     <t xml:space="preserve">5.225501537323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27557945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.31041622161865</t>
+    <t xml:space="preserve">5.27558040618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31041574478149</t>
   </si>
   <si>
     <t xml:space="preserve">5.17106962203979</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">5.14494228363037</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220483779907</t>
+    <t xml:space="preserve">5.06220531463623</t>
   </si>
   <si>
     <t xml:space="preserve">4.90979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09050893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043245315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445999145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10139656066895</t>
+    <t xml:space="preserve">5.09050941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043197631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11446046829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10139608383179</t>
   </si>
   <si>
     <t xml:space="preserve">5.09268712997437</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">5.12752389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11663770675659</t>
+    <t xml:space="preserve">5.11663722991943</t>
   </si>
   <si>
     <t xml:space="preserve">5.04478693008423</t>
@@ -734,43 +734,43 @@
     <t xml:space="preserve">4.95769548416138</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02736759185791</t>
+    <t xml:space="preserve">5.02736854553223</t>
   </si>
   <si>
     <t xml:space="preserve">4.98817682266235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88584470748901</t>
+    <t xml:space="preserve">4.88584423065186</t>
   </si>
   <si>
     <t xml:space="preserve">4.8662486076355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8553614616394</t>
+    <t xml:space="preserve">4.85536241531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.84665298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80093002319336</t>
+    <t xml:space="preserve">4.8009295463562</t>
   </si>
   <si>
     <t xml:space="preserve">4.73561096191406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79004383087158</t>
+    <t xml:space="preserve">4.79004335403442</t>
   </si>
   <si>
     <t xml:space="preserve">4.74432039260864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75738382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117904663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82052564620972</t>
+    <t xml:space="preserve">4.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6811785697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82052516937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.91850328445435</t>
@@ -779,40 +779,40 @@
     <t xml:space="preserve">5.13841009140015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08397817611694</t>
+    <t xml:space="preserve">5.08397769927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.19719696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11881446838379</t>
+    <t xml:space="preserve">5.11881399154663</t>
   </si>
   <si>
     <t xml:space="preserve">5.09486389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30170774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55209636688232</t>
+    <t xml:space="preserve">5.30170726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444423675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710424423218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55209541320801</t>
   </si>
   <si>
     <t xml:space="preserve">5.6827335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918781280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134834289551</t>
+    <t xml:space="preserve">5.63918733596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134881973267</t>
   </si>
   <si>
     <t xml:space="preserve">5.94400835037231</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">6.11383724212646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81337022781372</t>
+    <t xml:space="preserve">5.81337118148804</t>
   </si>
   <si>
     <t xml:space="preserve">5.87868976593018</t>
@@ -830,25 +830,25 @@
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329326629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957548141479</t>
+    <t xml:space="preserve">5.76329278945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957595825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97666835784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09641885757446</t>
+    <t xml:space="preserve">5.97666788101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0964183807373</t>
   </si>
   <si>
     <t xml:space="preserve">5.94836282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9897313117981</t>
+    <t xml:space="preserve">5.98973226547241</t>
   </si>
   <si>
     <t xml:space="preserve">6.00497245788574</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">5.9875545501709</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0419864654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05722713470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08335494995117</t>
+    <t xml:space="preserve">6.04198694229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05722761154175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08335542678833</t>
   </si>
   <si>
     <t xml:space="preserve">5.96360397338867</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07464599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13996505737305</t>
+    <t xml:space="preserve">6.07464551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13996458053589</t>
   </si>
   <si>
     <t xml:space="preserve">6.42301321029663</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">6.52969980239868</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54276371002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848714828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80403900146484</t>
+    <t xml:space="preserve">6.54276418685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80403852462769</t>
   </si>
   <si>
     <t xml:space="preserve">6.90201759338379</t>
@@ -899,55 +899,55 @@
     <t xml:space="preserve">7.01088237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06531476974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756944656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32005739212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1306324005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321449279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2939305305481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37666797637939</t>
+    <t xml:space="preserve">7.06531429290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11756896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3200569152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063335418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207927703857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29392957687378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37666654586792</t>
   </si>
   <si>
     <t xml:space="preserve">7.36360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28521966934204</t>
+    <t xml:space="preserve">7.28522062301636</t>
   </si>
   <si>
     <t xml:space="preserve">7.30481624603271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19595098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4665584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705602645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309064865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4012393951416</t>
+    <t xml:space="preserve">7.19595193862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46655941009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309017181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40123987197876</t>
   </si>
   <si>
     <t xml:space="preserve">6.61243724822998</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">6.49704122543335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52316761016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57760047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5246434211731</t>
+    <t xml:space="preserve">6.52316808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57760000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52464389801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.56215476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61290407180786</t>
+    <t xml:space="preserve">6.61290454864502</t>
   </si>
   <si>
     <t xml:space="preserve">6.54891586303711</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">6.45403575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55774211883545</t>
+    <t xml:space="preserve">6.55774116516113</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294755935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252311706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652536392212</t>
+    <t xml:space="preserve">6.76294660568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252264022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652584075928</t>
   </si>
   <si>
     <t xml:space="preserve">6.58422040939331</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">6.50478553771973</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42093801498413</t>
+    <t xml:space="preserve">6.42093849182129</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
@@ -1007,46 +1007,46 @@
     <t xml:space="preserve">6.35694932937622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33488416671753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43417739868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33267784118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37460136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16057062149048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1429181098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850498199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95757150650024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91344118118286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90240907669067</t>
+    <t xml:space="preserve">6.33488368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43417692184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33267879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3746018409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16057014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14291858673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850593566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9575719833374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91344165802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90240955352783</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771314620972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95977830886841</t>
+    <t xml:space="preserve">5.78546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95977878570557</t>
   </si>
   <si>
     <t xml:space="preserve">5.92006063461304</t>
@@ -1055,19 +1055,19 @@
     <t xml:space="preserve">5.93330001831055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94212627410889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83621406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8472466468811</t>
+    <t xml:space="preserve">5.94212675094604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8362135887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84724617004395</t>
   </si>
   <si>
     <t xml:space="preserve">5.98846340179443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720315933228</t>
+    <t xml:space="preserve">5.69720363616943</t>
   </si>
   <si>
     <t xml:space="preserve">5.50744390487671</t>
@@ -1076,31 +1076,31 @@
     <t xml:space="preserve">5.46993398666382</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60894298553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7611927986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89137697219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72147512435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59129190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819416046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608646392822</t>
+    <t xml:space="preserve">5.60894346237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73692083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76119232177734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819368362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608598709106</t>
   </si>
   <si>
     <t xml:space="preserve">5.54495477676392</t>
@@ -1109,19 +1109,19 @@
     <t xml:space="preserve">5.44345569610596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45007514953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39932489395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41918325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.56040000915527</t>
+    <t xml:space="preserve">5.45007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39932584762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4191837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56040096282959</t>
   </si>
   <si>
     <t xml:space="preserve">5.48096609115601</t>
@@ -1130,61 +1130,61 @@
     <t xml:space="preserve">5.52730274200439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45890092849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41256475448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48979187011719</t>
+    <t xml:space="preserve">5.45890045166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41256427764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48979234695435</t>
   </si>
   <si>
     <t xml:space="preserve">5.56922626495361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73912763595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66410636901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80311632156372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86931133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030138015747</t>
+    <t xml:space="preserve">5.73912668228149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6641058921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80311584472656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86931180953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030090332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.08554887771606</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96860456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532264709473</t>
+    <t xml:space="preserve">5.96860408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532312393188</t>
   </si>
   <si>
     <t xml:space="preserve">5.63762760162354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56481313705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52068328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47875928878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49420499801636</t>
+    <t xml:space="preserve">5.56481266021729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52068376541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47875881195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4942045211792</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782629013062</t>
+    <t xml:space="preserve">5.2978253364563</t>
   </si>
   <si>
     <t xml:space="preserve">5.22942399978638</t>
@@ -1193,598 +1193,598 @@
     <t xml:space="preserve">5.24045658111572</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25369548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41477108001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39711856842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27796792984009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22280502319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14116430282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11909818649292</t>
+    <t xml:space="preserve">5.25369596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41477060317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39711809158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27796697616577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22280406951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14116382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11909866333008</t>
   </si>
   <si>
     <t xml:space="preserve">5.20735883712769</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16764163970947</t>
+    <t xml:space="preserve">5.16764259338379</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13675117492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03745794296265</t>
+    <t xml:space="preserve">5.1367506980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03745746612549</t>
   </si>
   <si>
     <t xml:space="preserve">5.00656700134277</t>
   </si>
   <si>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802354812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97126293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04849052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19411993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22501134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24487018585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689233779907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87196922302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72634029388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71089458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131902694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6045298576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8119421005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84503936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76781225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489868164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77663803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81856250762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63983392715454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467197418213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376651763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366836547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348419189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14071226119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526607513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02597332000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96419143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03480052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8097357749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88034391403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90020179748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6508674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61776876449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63542222976685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01935386657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85607290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283304214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315837860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28854751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28413486480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22235250473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52243804931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37239503860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08996152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5559868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202764511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9222674369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79429006576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67072582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396425247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42800998687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76339960098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87372398376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97963714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96198463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474300384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72543621063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68571901321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92843532562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90636920928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10495615005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97697830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106561660767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95050048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22851943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14908647537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04758644104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11378240585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06082534790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49330139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560634613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1843900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.440345287323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941228866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260770797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06523895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25058507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21969413757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46240949630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6212797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56390953063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743267059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062856674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508327484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738870620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965208053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62834978103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017467498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63717651367188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51802539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5445032119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71219730377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30643844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59716081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66425037384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60163354873657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63294219970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.579270362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48534440994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71344900131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75817584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61505126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49428987503052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48087167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145843505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305974960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14094972610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356702804565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669208526611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24829435348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2125129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821535110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48981666564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53007078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44509077072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39141845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352800369263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4271993637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960252761841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298122406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64188814163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1006965637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3958911895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18567705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98440790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47452545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33587265014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97358798980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13013076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831483840942</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.96464252471924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95802354812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04849004745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19412040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576112747192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22501087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486970901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083801269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87197017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72634029388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71089458465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131855010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93154573440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60453081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8119421005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8450403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76781177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461587905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77663850784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81856203079224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65307378768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6398344039917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467149734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.023766040802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348371505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14071226119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526655197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02597332000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96419143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03479957580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80973529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88034343719482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90020275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74354028701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65086698532104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61776924133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63542175292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01935434341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85607242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283256530762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0325927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315885543823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433259963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28413486480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22235298156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52243804931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37239503860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878826141357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08996248245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202716827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79429006576538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67072534561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396520614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42800951004028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76339960098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87372493743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97963666915894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96198558807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822217941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089595794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474348068237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72543621063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68571949005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92843532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90637016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10495615005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106561660767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95050001144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22852039337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14908599853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04758739471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11378288269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06082487106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49330043792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560729980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18439054489136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2594108581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260818481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06523895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25058507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528148651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2196946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62128019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5374321937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738822937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965160369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835025787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63717555999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51802492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54450273513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71219778060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38247346878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30643892288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59716129302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66425037384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60163402557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63294172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54796171188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65977811813354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48534488677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71344995498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75817632675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61505126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49428987503052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3198561668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145795822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12306022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14094972610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356702804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24829435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2885479927063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21251249313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821535110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48981666564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53007125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061756134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44509077072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39141845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40036487579346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42719984054565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4316725730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323581695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014930725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46298122406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64188718795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1006965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3958911895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18567705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98440742492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.474524974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3358736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194717407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97358846664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13013124465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9646430015564</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886161804199</t>
+    <t xml:space="preserve">5.05409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61577653884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74995517730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71417427062988</t>
+    <t xml:space="preserve">4.58894014358521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61577606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74995565414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71417474746704</t>
   </si>
   <si>
     <t xml:space="preserve">4.37201690673828</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483907699585</t>
+    <t xml:space="preserve">4.20876455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483860015869</t>
   </si>
   <si>
     <t xml:space="preserve">4.04104042053223</t>
@@ -1805,55 +1805,55 @@
     <t xml:space="preserve">4.05445861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95829629898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353042602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15509271621704</t>
+    <t xml:space="preserve">3.95829653739929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353090286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1550931930542</t>
   </si>
   <si>
     <t xml:space="preserve">4.1304931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0186767578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8688428401947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559167861938</t>
+    <t xml:space="preserve">4.01867771148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884331703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559144020081</t>
   </si>
   <si>
     <t xml:space="preserve">3.75702714920044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81740760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466444015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83753442764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84648060798645</t>
+    <t xml:space="preserve">3.81740736961365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466396331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83753490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84648036956787</t>
   </si>
   <si>
     <t xml:space="preserve">3.96500539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00302267074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92475080490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146109580994</t>
+    <t xml:space="preserve">4.15732908248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00302362442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92475152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314603805542</t>
   </si>
   <si>
     <t xml:space="preserve">3.94264221191406</t>
@@ -1862,52 +1862,52 @@
     <t xml:space="preserve">3.87331604957581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86213445663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84424352645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512342453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35896134376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24267244338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03245806694031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216444969177</t>
+    <t xml:space="preserve">3.86213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424376487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512294769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35896110534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24267220497131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03245759010315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216492652893</t>
   </si>
   <si>
     <t xml:space="preserve">3.38356065750122</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38803339004517</t>
+    <t xml:space="preserve">3.38803315162659</t>
   </si>
   <si>
     <t xml:space="preserve">3.26950812339783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22701811790466</t>
+    <t xml:space="preserve">3.22701787948608</t>
   </si>
   <si>
     <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39474272727966</t>
+    <t xml:space="preserve">3.39474248886108</t>
   </si>
   <si>
     <t xml:space="preserve">3.4886679649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5155041217804</t>
+    <t xml:space="preserve">3.51550388336182</t>
   </si>
   <si>
     <t xml:space="preserve">3.31870722770691</t>
@@ -1916,19 +1916,19 @@
     <t xml:space="preserve">3.24714493751526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11072897911072</t>
+    <t xml:space="preserve">3.1107292175293</t>
   </si>
   <si>
     <t xml:space="preserve">2.92735028266907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93182277679443</t>
+    <t xml:space="preserve">2.93182253837585</t>
   </si>
   <si>
     <t xml:space="preserve">3.01009440422058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10402011871338</t>
+    <t xml:space="preserve">3.1040198802948</t>
   </si>
   <si>
     <t xml:space="preserve">3.03916645050049</t>
@@ -1937,16 +1937,16 @@
     <t xml:space="preserve">2.95642280578613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88486003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92511391639709</t>
+    <t xml:space="preserve">2.88485980033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92511415481567</t>
   </si>
   <si>
     <t xml:space="preserve">2.77751660346985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74844408035278</t>
+    <t xml:space="preserve">2.74844431877136</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869819641113</t>
@@ -1961,10 +1961,10 @@
     <t xml:space="preserve">3.07271146774292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10625624656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16887354850769</t>
+    <t xml:space="preserve">3.10625648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16887331008911</t>
   </si>
   <si>
     <t xml:space="preserve">3.22925424575806</t>
@@ -1976,91 +1976,91 @@
     <t xml:space="preserve">3.22254538536072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23596358299255</t>
+    <t xml:space="preserve">3.23596334457397</t>
   </si>
   <si>
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347310066223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32094359397888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54234027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972297668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53339457511902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4953773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61166572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533803939819</t>
+    <t xml:space="preserve">3.19347333908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32094407081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54234004020691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972273826599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5333948135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49537754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61166596412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533756256104</t>
   </si>
   <si>
     <t xml:space="preserve">3.57588458061218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51103115081787</t>
+    <t xml:space="preserve">3.51103138923645</t>
   </si>
   <si>
     <t xml:space="preserve">3.52221298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5825936794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444911003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58483028411865</t>
+    <t xml:space="preserve">3.58259391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723249435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58483004570007</t>
   </si>
   <si>
     <t xml:space="preserve">3.69440984725952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62284755706787</t>
+    <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335531234741</t>
+    <t xml:space="preserve">3.70335507392883</t>
   </si>
   <si>
     <t xml:space="preserve">3.80399012565613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89567947387695</t>
+    <t xml:space="preserve">3.89567923545837</t>
   </si>
   <si>
     <t xml:space="preserve">3.77268171310425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83306264877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766220092773</t>
+    <t xml:space="preserve">3.83306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766172409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.94040632247925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99184107780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011318206787</t>
+    <t xml:space="preserve">3.99184155464172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011270523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.13273000717163</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863773345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94935083389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02762222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842335700989</t>
+    <t xml:space="preserve">4.18863821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9493510723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02762269973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842359542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.23112869262695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28256320953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38319826126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42792510986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3541259765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1662745475769</t>
+    <t xml:space="preserve">4.28256368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38319873809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42792463302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16627502441406</t>
   </si>
   <si>
     <t xml:space="preserve">4.20429182052612</t>
@@ -2111,13 +2111,13 @@
     <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20205545425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23783731460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29150915145874</t>
+    <t xml:space="preserve">4.20205640792847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23783779144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29150819778442</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901866912842</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25349187850952</t>
+    <t xml:space="preserve">4.25349140167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.19981956481934</t>
@@ -2135,43 +2135,43 @@
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285634994507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18640184402466</t>
+    <t xml:space="preserve">4.15285682678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1864013671875</t>
   </si>
   <si>
     <t xml:space="preserve">4.26914548873901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97171425819397</t>
+    <t xml:space="preserve">3.97171473503113</t>
   </si>
   <si>
     <t xml:space="preserve">3.93369674682617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90015149116516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880405426025</t>
+    <t xml:space="preserve">3.90015196800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880453109741</t>
   </si>
   <si>
     <t xml:space="preserve">4.03656768798828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01644039154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91804265975952</t>
+    <t xml:space="preserve">4.01643991470337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91804218292236</t>
   </si>
   <si>
     <t xml:space="preserve">3.87778902053833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76820921897888</t>
+    <t xml:space="preserve">3.76820850372314</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491736412048</t>
@@ -2180,67 +2180,67 @@
     <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85095238685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0991849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82411694526672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95693111419678</t>
+    <t xml:space="preserve">3.85095310211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09918451309204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82411670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95693063735962</t>
   </si>
   <si>
     <t xml:space="preserve">3.88136434555054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76228976249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626111984253</t>
+    <t xml:space="preserve">3.76229023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626088142395</t>
   </si>
   <si>
     <t xml:space="preserve">3.7645800113678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901371955872</t>
+    <t xml:space="preserve">3.68901324272156</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73252105712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84243655204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220454216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487263679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96609020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739370346069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006155967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8744945526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
+    <t xml:space="preserve">3.73252129554749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84243631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487192153931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96609044075012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739346504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449479103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655279159546</t>
   </si>
   <si>
     <t xml:space="preserve">3.98440980911255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04165649414062</t>
+    <t xml:space="preserve">4.04165601730347</t>
   </si>
   <si>
     <t xml:space="preserve">4.19736957550049</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09203433990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11264276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10119390487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14470148086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18820953369141</t>
+    <t xml:space="preserve">4.09203481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11264324188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10119342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14470195770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18821001052856</t>
   </si>
   <si>
     <t xml:space="preserve">4.27751541137695</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">4.28438520431519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31415319442749</t>
+    <t xml:space="preserve">4.31415367126465</t>
   </si>
   <si>
     <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30270385742188</t>
+    <t xml:space="preserve">4.30270433425903</t>
   </si>
   <si>
     <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24545669555664</t>
+    <t xml:space="preserve">4.2454571723938</t>
   </si>
   <si>
     <t xml:space="preserve">4.3324728012085</t>
@@ -2300,55 +2300,55 @@
     <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17446947097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05997562408447</t>
+    <t xml:space="preserve">4.1744704246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05997657775879</t>
   </si>
   <si>
     <t xml:space="preserve">4.09890365600586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15157175064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16302108764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11035394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12409257888794</t>
+    <t xml:space="preserve">4.15157127380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16302061080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11035346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1240930557251</t>
   </si>
   <si>
     <t xml:space="preserve">4.07600498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05539560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067046165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945481300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701585769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594365119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.876784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159611701965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235085487366</t>
+    <t xml:space="preserve">4.00730848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97067022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94548034667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701609611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594436645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678456306458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235109329224</t>
   </si>
   <si>
     <t xml:space="preserve">4.00043869018555</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">3.98211932182312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13096284866333</t>
+    <t xml:space="preserve">4.13096189498901</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16760110855103</t>
+    <t xml:space="preserve">4.16760063171387</t>
   </si>
   <si>
     <t xml:space="preserve">4.04394626617432</t>
@@ -2372,13 +2372,13 @@
     <t xml:space="preserve">4.05310583114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18592023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13554191589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06226491928101</t>
+    <t xml:space="preserve">4.18591976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13554239273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06226587295532</t>
   </si>
   <si>
     <t xml:space="preserve">4.34392213821411</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60268020629883</t>
+    <t xml:space="preserve">4.60267972946167</t>
   </si>
   <si>
     <t xml:space="preserve">5.00112056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17515277862549</t>
+    <t xml:space="preserve">5.17515230178833</t>
   </si>
   <si>
     <t xml:space="preserve">5.33086490631104</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">5.35834360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62855052947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48657703399658</t>
+    <t xml:space="preserve">5.6285514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48657655715942</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61023187637329</t>
+    <t xml:space="preserve">5.61023139953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.70640707015991</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45451927185059</t>
+    <t xml:space="preserve">5.45451879501343</t>
   </si>
   <si>
     <t xml:space="preserve">5.4819974899292</t>
@@ -2432,16 +2432,16 @@
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590847015381</t>
+    <t xml:space="preserve">5.27590799331665</t>
   </si>
   <si>
     <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993925094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34460401535034</t>
+    <t xml:space="preserve">5.44993877410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3446044921875</t>
   </si>
   <si>
     <t xml:space="preserve">5.47283792495728</t>
@@ -2450,16 +2450,16 @@
     <t xml:space="preserve">5.45909929275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55985403060913</t>
+    <t xml:space="preserve">5.55985355377197</t>
   </si>
   <si>
     <t xml:space="preserve">5.69724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72930574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.7293062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92623567581177</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304533004761</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">5.72472620010376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67892742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71556663513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80716276168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71098709106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82090187072754</t>
+    <t xml:space="preserve">5.67892789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71556615829468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80716228485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71098661422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82090139389038</t>
   </si>
   <si>
     <t xml:space="preserve">5.89875793457031</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22392177581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08652925491333</t>
+    <t xml:space="preserve">6.22392225265503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08652830123901</t>
   </si>
   <si>
     <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02241230010986</t>
+    <t xml:space="preserve">6.02241182327271</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224138259888</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10324001312256</t>
+    <t xml:space="preserve">7.10324048995972</t>
   </si>
   <si>
     <t xml:space="preserve">7.1994161605835</t>
@@ -2522,31 +2522,31 @@
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159658432007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235132217407</t>
+    <t xml:space="preserve">7.61159563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235227584839</t>
   </si>
   <si>
     <t xml:space="preserve">7.83600521087646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67113208770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62533521652222</t>
+    <t xml:space="preserve">7.67113256454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6253342628479</t>
   </si>
   <si>
     <t xml:space="preserve">7.16735649108887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28185129165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41924476623535</t>
+    <t xml:space="preserve">7.28185176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">7.29101085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727174758911</t>
+    <t xml:space="preserve">7.27727222442627</t>
   </si>
   <si>
     <t xml:space="preserve">7.11697912216187</t>
@@ -2570,7 +2570,7 @@
     <t xml:space="preserve">7.39634561538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802743911743</t>
+    <t xml:space="preserve">7.37802648544312</t>
   </si>
   <si>
     <t xml:space="preserve">7.57495784759521</t>
@@ -2579,10 +2579,10 @@
     <t xml:space="preserve">7.9184422492981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85890293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571353912354</t>
+    <t xml:space="preserve">7.85890340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571258544922</t>
   </si>
   <si>
     <t xml:space="preserve">7.56579780578613</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">7.45130395889282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12155914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41466522216797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25895357131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30475091934204</t>
+    <t xml:space="preserve">7.12155961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41466569900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25895261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30475044250488</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231435775757</t>
@@ -2615,19 +2615,19 @@
     <t xml:space="preserve">7.5291600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43756437301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48794269561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51999998092651</t>
+    <t xml:space="preserve">7.4375638961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48794174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52000093460083</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17651653289795</t>
+    <t xml:space="preserve">7.17651700973511</t>
   </si>
   <si>
     <t xml:space="preserve">7.02996349334717</t>
@@ -2636,34 +2636,34 @@
     <t xml:space="preserve">6.51244878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7414379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79639482498169</t>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74143743515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79639434814453</t>
   </si>
   <si>
     <t xml:space="preserve">6.71853828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76891613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61778354644775</t>
+    <t xml:space="preserve">6.76891660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61778402328491</t>
   </si>
   <si>
     <t xml:space="preserve">7.02538394927979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89257097244263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89714956283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845306396484</t>
+    <t xml:space="preserve">6.89257001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89715003967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82845258712769</t>
   </si>
   <si>
     <t xml:space="preserve">6.80097484588623</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">6.67732048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83303308486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76433658599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63610219955444</t>
+    <t xml:space="preserve">6.83303356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76433610916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6361026763916</t>
   </si>
   <si>
     <t xml:space="preserve">6.11858701705933</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">5.96745443344116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78884315490723</t>
+    <t xml:space="preserve">5.78884363174438</t>
   </si>
   <si>
     <t xml:space="preserve">5.63771057128906</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">5.77052450180054</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72014617919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47741794586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1156153678894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381231307983</t>
+    <t xml:space="preserve">5.72014570236206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47741842269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11561489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.59810018539429</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">4.63931798934937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21110868453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8149573802948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382455825806</t>
+    <t xml:space="preserve">4.21110820770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81495761871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382479667664</t>
   </si>
   <si>
     <t xml:space="preserve">3.32034134864807</t>
@@ -2729,25 +2729,25 @@
     <t xml:space="preserve">3.22416567802429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18294763565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22645592689514</t>
+    <t xml:space="preserve">3.18294739723206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22645545005798</t>
   </si>
   <si>
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356842041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304545402527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61344718933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50353264808655</t>
+    <t xml:space="preserve">3.99356913566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6134467124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50353240966797</t>
   </si>
   <si>
     <t xml:space="preserve">3.67069458961487</t>
@@ -2756,16 +2756,16 @@
     <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70962238311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663801193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168086051941</t>
+    <t xml:space="preserve">3.70962262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6226065158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663825035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168062210083</t>
   </si>
   <si>
     <t xml:space="preserve">4.06684541702271</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">4.03020763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38285064697266</t>
+    <t xml:space="preserve">4.3828501701355</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722278594971</t>
@@ -2783,37 +2783,37 @@
     <t xml:space="preserve">4.01188802719116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17218065261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09432363510132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48818492889404</t>
+    <t xml:space="preserve">4.17218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09432411193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
     <t xml:space="preserve">4.45612668991089</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35995101928711</t>
+    <t xml:space="preserve">4.35995149612427</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26377630233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32331323623657</t>
+    <t xml:space="preserve">4.26377582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32331275939941</t>
   </si>
   <si>
     <t xml:space="preserve">4.35537195205688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30957412719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499362945557</t>
+    <t xml:space="preserve">4.30957365036011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499410629272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17676019668579</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52482414245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38743019104004</t>
+    <t xml:space="preserve">4.5248236656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4836049079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38742971420288</t>
   </si>
   <si>
     <t xml:space="preserve">4.42406845092773</t>
@@ -2843,34 +2843,34 @@
     <t xml:space="preserve">4.90036535263062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88891649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04920864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18660163879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23239946365356</t>
+    <t xml:space="preserve">4.888916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04920816421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1866021156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23239994049072</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34689474105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16370248794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471384048462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630949020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19805145263672</t>
+    <t xml:space="preserve">5.34689378738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1637020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630996704102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19805192947388</t>
   </si>
   <si>
     <t xml:space="preserve">5.31254577636719</t>
@@ -2894,31 +2894,31 @@
     <t xml:space="preserve">5.27819728851318</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09500694274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.923264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01485967636108</t>
+    <t xml:space="preserve">5.24384927749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09500646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92326402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0148606300354</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0606575012207</t>
+    <t xml:space="preserve">5.06065845489502</t>
   </si>
   <si>
     <t xml:space="preserve">5.22095012664795</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07210683822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10645532608032</t>
+    <t xml:space="preserve">5.07210731506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10645580291748</t>
   </si>
   <si>
     <t xml:space="preserve">5.12935447692871</t>
@@ -2930,130 +2930,130 @@
     <t xml:space="preserve">5.33544445037842</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03775930404663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355665206909</t>
+    <t xml:space="preserve">5.03775882720947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355712890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.96906280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94616317749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98051118850708</t>
+    <t xml:space="preserve">4.94616270065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98051166534424</t>
   </si>
   <si>
     <t xml:space="preserve">4.84311866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57978105545044</t>
+    <t xml:space="preserve">5.00341129302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57978057861328</t>
   </si>
   <si>
     <t xml:space="preserve">4.1904993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21339797973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08058452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30041408538818</t>
+    <t xml:space="preserve">4.21339845657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08058500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
     <t xml:space="preserve">4.34163188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61412858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54153490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62168073654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73617506027222</t>
+    <t xml:space="preserve">4.61412954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54153537750244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62168121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73617601394653</t>
   </si>
   <si>
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64457988739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66747903823853</t>
+    <t xml:space="preserve">5.64458036422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66747856140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70182752609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.816321849823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14835596084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96516466140747</t>
+    <t xml:space="preserve">5.70182704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81632137298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14835548400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96516418457031</t>
   </si>
   <si>
     <t xml:space="preserve">5.95371532440186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356901168823</t>
+    <t xml:space="preserve">5.87356853485107</t>
   </si>
   <si>
     <t xml:space="preserve">5.91936635971069</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09110832214355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19415378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12545680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15980577468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18270397186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07965898513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13690614700317</t>
+    <t xml:space="preserve">6.09110927581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19415330886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12545728683472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1598048210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0796594619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13690662384033</t>
   </si>
   <si>
     <t xml:space="preserve">6.2170524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3544454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32009840011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36589527130127</t>
+    <t xml:space="preserve">6.35444593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32009744644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36589479446411</t>
   </si>
   <si>
     <t xml:space="preserve">6.48038959503174</t>
@@ -3062,31 +3062,31 @@
     <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53763675689697</t>
+    <t xml:space="preserve">6.53763723373413</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60633373260498</t>
+    <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
     <t xml:space="preserve">6.58343553543091</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62923336029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41169261932373</t>
+    <t xml:space="preserve">6.62923383712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29719829559326</t>
+    <t xml:space="preserve">6.46894025802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.20560312271118</t>
@@ -3095,10 +3095,10 @@
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328874588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66358089447021</t>
+    <t xml:space="preserve">6.50328826904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
     <t xml:space="preserve">6.5147385597229</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68648052215576</t>
+    <t xml:space="preserve">6.6864800453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77807521820068</t>
+    <t xml:space="preserve">6.77807569503784</t>
   </si>
   <si>
     <t xml:space="preserve">6.69792938232422</t>
@@ -3125,25 +3125,25 @@
     <t xml:space="preserve">6.40024375915527</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37734508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33154726028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38879442214966</t>
+    <t xml:space="preserve">6.37734460830688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33154678344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86967086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417945861816</t>
+    <t xml:space="preserve">6.86967134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417755126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3152,49 +3152,49 @@
     <t xml:space="preserve">8.17490863800049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99171733856201</t>
+    <t xml:space="preserve">8.01461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99171876907349</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02606582641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12911224365234</t>
+    <t xml:space="preserve">8.02606678009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12911128997803</t>
   </si>
   <si>
     <t xml:space="preserve">8.10621166229248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03751468658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0031681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08331298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31230163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28940296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33520221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2779541015625</t>
+    <t xml:space="preserve">8.03751564025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00316715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08331203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3123025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28940391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27795505523682</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200996398926</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">8.11766147613525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18635845184326</t>
+    <t xml:space="preserve">8.18635749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.34665107727051</t>
@@ -3212,52 +3212,52 @@
     <t xml:space="preserve">8.23215675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186317443848</t>
+    <t xml:space="preserve">8.16345977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186508178711</t>
   </si>
   <si>
     <t xml:space="preserve">8.20925617218018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94591999053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95736932754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84287452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92301988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577272415161</t>
+    <t xml:space="preserve">7.94592094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95736980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8428750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92302179336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577367782593</t>
   </si>
   <si>
     <t xml:space="preserve">8.3809986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15956211090088</t>
+    <t xml:space="preserve">9.15956115722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48014640808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65356254577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60731983184814</t>
+    <t xml:space="preserve">9.20535945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48014736175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65356349945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60731887817383</t>
   </si>
   <si>
     <t xml:space="preserve">9.78073692321777</t>
@@ -3266,10 +3266,10 @@
     <t xml:space="preserve">9.71136856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0813255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2894268035889</t>
+    <t xml:space="preserve">10.0813264846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2894277572632</t>
   </si>
   <si>
     <t xml:space="preserve">10.3009881973267</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975280761719</t>
+    <t xml:space="preserve">10.4975290298462</t>
   </si>
   <si>
     <t xml:space="preserve">10.33567237854</t>
@@ -3299,46 +3299,46 @@
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703546524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7403125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4744052886963</t>
+    <t xml:space="preserve">10.3703556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7403116226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4744062423706</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2663049697876</t>
+    <t xml:space="preserve">10.1044502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2663059234619</t>
   </si>
   <si>
     <t xml:space="preserve">10.3934783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0582036972046</t>
+    <t xml:space="preserve">10.0582046508789</t>
   </si>
   <si>
     <t xml:space="preserve">9.95415306091309</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0235214233398</t>
+    <t xml:space="preserve">10.0235204696655</t>
   </si>
   <si>
     <t xml:space="preserve">10.1506948471069</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0697641372681</t>
+    <t xml:space="preserve">10.0697650909424</t>
   </si>
   <si>
     <t xml:space="preserve">10.092887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1160106658936</t>
+    <t xml:space="preserve">10.1160116195679</t>
   </si>
   <si>
     <t xml:space="preserve">10.2547435760498</t>
@@ -3362,7 +3362,7 @@
     <t xml:space="preserve">10.1738157272339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391315460205</t>
+    <t xml:space="preserve">10.1391334533691</t>
   </si>
   <si>
     <t xml:space="preserve">11.191198348999</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">11.5056600570679</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9052143096924</t>
+    <t xml:space="preserve">11.9052152633667</t>
   </si>
   <si>
     <t xml:space="preserve">11.901515007019</t>
@@ -3383,10 +3383,10 @@
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426568984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.42982006073</t>
+    <t xml:space="preserve">11.5426559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
     <t xml:space="preserve">11.5796518325806</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">11.3946733474731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4686651229858</t>
+    <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
     <t xml:space="preserve">12.0975914001465</t>
@@ -3416,22 +3416,22 @@
     <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0605974197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0420989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010683059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8941144943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9299945831299</t>
+    <t xml:space="preserve">12.0605964660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0420999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010692596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.894115447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9299955368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.6144151687622</t>
@@ -3446,10 +3446,10 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8178911209106</t>
+    <t xml:space="preserve">13.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817892074585</t>
   </si>
   <si>
     <t xml:space="preserve">13.7254018783569</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4109392166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623977661133</t>
+    <t xml:space="preserve">13.4109401702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623987197876</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294376373291</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669904708862</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8929996490479</t>
+    <t xml:space="preserve">12.8929986953735</t>
   </si>
   <si>
     <t xml:space="preserve">13.3739433288574</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457035064697</t>
+    <t xml:space="preserve">15.4457025527954</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011959075928</t>
@@ -3509,16 +3509,16 @@
     <t xml:space="preserve">15.7786626815796</t>
   </si>
   <si>
-    <t xml:space="preserve">16.555570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3705959320068</t>
+    <t xml:space="preserve">16.5555725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.5370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596073150635</t>
+    <t xml:space="preserve">16.2596092224121</t>
   </si>
   <si>
     <t xml:space="preserve">16.3520984649658</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">16.000638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9081506729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5196952819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4641990661621</t>
+    <t xml:space="preserve">15.908148765564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5196943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4641981124878</t>
   </si>
   <si>
     <t xml:space="preserve">15.8896503448486</t>
@@ -3557,22 +3557,22 @@
     <t xml:space="preserve">14.9092655181885</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4283218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.502311706543</t>
+    <t xml:space="preserve">14.4283208847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5023126602173</t>
   </si>
   <si>
     <t xml:space="preserve">14.2433414459229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6329126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514120101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.6329135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514110565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369464874268</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993936538696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7808961868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2629566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5404233932495</t>
+    <t xml:space="preserve">13.7993946075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7808952331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2629556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5404243469238</t>
   </si>
   <si>
     <t xml:space="preserve">13.3924407958984</t>
@@ -3611,19 +3611,19 @@
     <t xml:space="preserve">13.3554439544678</t>
   </si>
   <si>
-    <t xml:space="preserve">13.965874671936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1323537826538</t>
+    <t xml:space="preserve">13.9658737182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
     <t xml:space="preserve">14.2988367080688</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2803382873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1138572692871</t>
+    <t xml:space="preserve">14.2803373336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1138582229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.9484930038452</t>
@@ -3635,31 +3635,31 @@
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479351043701</t>
+    <t xml:space="preserve">13.4479360580444</t>
   </si>
   <si>
     <t xml:space="preserve">12.2085781097412</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3935565948486</t>
+    <t xml:space="preserve">12.3935575485229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1889657974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4664335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8190088272095</t>
+    <t xml:space="preserve">13.4664325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8190078735352</t>
   </si>
   <si>
     <t xml:space="preserve">11.9126138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6340293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3380632400513</t>
+    <t xml:space="preserve">12.6340284347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3380641937256</t>
   </si>
   <si>
     <t xml:space="preserve">11.8386220932007</t>
@@ -3668,10 +3668,10 @@
     <t xml:space="preserve">12.1345872879028</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9496088027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6721420288086</t>
+    <t xml:space="preserve">11.9496097564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
     <t xml:space="preserve">11.5981502532959</t>
@@ -3680,13 +3680,13 @@
     <t xml:space="preserve">12.0051021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681062698364</t>
+    <t xml:space="preserve">11.9681053161621</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">10.5067768096924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.117205619812</t>
+    <t xml:space="preserve">11.1172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">11.8201246261597</t>
@@ -3707,37 +3707,37 @@
     <t xml:space="preserve">11.4131727218628</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6710252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7265176773071</t>
+    <t xml:space="preserve">12.6710243225098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7265186309814</t>
   </si>
   <si>
     <t xml:space="preserve">12.8005104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3646945953369</t>
+    <t xml:space="preserve">13.2259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3276987075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3646955490112</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617765426636</t>
+    <t xml:space="preserve">12.6617755889893</t>
   </si>
   <si>
     <t xml:space="preserve">12.4305534362793</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4028062820435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137929916382</t>
+    <t xml:space="preserve">12.4028053283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137939453125</t>
   </si>
   <si>
     <t xml:space="preserve">12.3473138809204</t>
@@ -3746,13 +3746,13 @@
     <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4952955245972</t>
+    <t xml:space="preserve">12.4952964782715</t>
   </si>
   <si>
     <t xml:space="preserve">12.6155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4398021697998</t>
+    <t xml:space="preserve">12.4398012161255</t>
   </si>
   <si>
     <t xml:space="preserve">11.8016271591187</t>
@@ -3761,16 +3761,16 @@
     <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3565607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.764630317688</t>
+    <t xml:space="preserve">12.3565616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7646312713623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848676681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073989868164</t>
+    <t xml:space="preserve">11.6073999404907</t>
   </si>
   <si>
     <t xml:space="preserve">11.5519046783447</t>
@@ -3779,7 +3779,7 @@
     <t xml:space="preserve">11.2929353713989</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">10.6455097198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657470703125</t>
@@ -5844,6 +5844,9 @@
   </si>
   <si>
     <t xml:space="preserve">11.2700004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -71416,7 +71419,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911805556</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>91867</v>
@@ -71437,6 +71440,32 @@
         <v>1943</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6910532407</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>64924</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>11.3400001525879</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>10.8800001144409</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1944" uniqueCount="1944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1945" uniqueCount="1945">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10034394264221</t>
+    <t xml:space="preserve">2.10034418106079</t>
   </si>
   <si>
     <t xml:space="preserve">ELN.MI</t>
@@ -50,91 +50,91 @@
     <t xml:space="preserve">2.13486289978027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09768867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07379031181335</t>
+    <t xml:space="preserve">2.0976881980896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07379078865051</t>
   </si>
   <si>
     <t xml:space="preserve">2.02334046363831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0631697177887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05254864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96492350101471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988354206085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439278125763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802945137024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01696729660034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00209808349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00156712532043</t>
+    <t xml:space="preserve">2.06316995620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0525484085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.964923620224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988330364227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802968978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01696705818176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00209784507751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00156688690186</t>
   </si>
   <si>
     <t xml:space="preserve">2.059983253479</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00528407096863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01909160614014</t>
+    <t xml:space="preserve">2.00528430938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01909136772156</t>
   </si>
   <si>
     <t xml:space="preserve">1.97820019721985</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89854109287262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92774939537048</t>
+    <t xml:space="preserve">1.89854073524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92774927616119</t>
   </si>
   <si>
     <t xml:space="preserve">1.9394326210022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91447257995605</t>
+    <t xml:space="preserve">1.91447281837463</t>
   </si>
   <si>
     <t xml:space="preserve">1.93305993080139</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91712772846222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633662700653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589566230774</t>
+    <t xml:space="preserve">1.9171279668808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589554309845</t>
   </si>
   <si>
     <t xml:space="preserve">1.9436811208725</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09237790107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113552093506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08441233634949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09450221061707</t>
+    <t xml:space="preserve">2.09237813949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113575935364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08441257476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09450244903564</t>
   </si>
   <si>
     <t xml:space="preserve">2.17203712463379</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.10830998420715</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13964247703552</t>
+    <t xml:space="preserve">2.1396427154541</t>
   </si>
   <si>
     <t xml:space="preserve">2.10299921035767</t>
@@ -152,37 +152,37 @@
     <t xml:space="preserve">2.14442205429077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14548420906067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15345025062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1481397151947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15132570266724</t>
+    <t xml:space="preserve">2.14548444747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15345001220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813947677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15132594108582</t>
   </si>
   <si>
     <t xml:space="preserve">2.16831994056702</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18265819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22248792648315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15610527992249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14495253562927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12955212593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
+    <t xml:space="preserve">2.18265795707703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22248816490173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15610480308533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14495277404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
   </si>
   <si>
     <t xml:space="preserve">2.08706736564636</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">2.07219767570496</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12158632278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14017343521118</t>
+    <t xml:space="preserve">2.121586561203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14017367362976</t>
   </si>
   <si>
     <t xml:space="preserve">2.12424159049988</t>
@@ -203,13 +203,13 @@
     <t xml:space="preserve">2.11362051963806</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06582522392273</t>
+    <t xml:space="preserve">2.06582474708557</t>
   </si>
   <si>
     <t xml:space="preserve">2.05307960510254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0684802532196</t>
+    <t xml:space="preserve">2.06848073005676</t>
   </si>
   <si>
     <t xml:space="preserve">2.06901144981384</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">2.11839985847473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12477254867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16141629219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15557456016541</t>
+    <t xml:space="preserve">2.12477278709412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16141605377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15557408332825</t>
   </si>
   <si>
     <t xml:space="preserve">2.1773476600647</t>
@@ -233,34 +233,34 @@
     <t xml:space="preserve">2.24373030662537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25169610977173</t>
+    <t xml:space="preserve">2.25169634819031</t>
   </si>
   <si>
     <t xml:space="preserve">2.29418087005615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2575376033783</t>
+    <t xml:space="preserve">2.25753736495972</t>
   </si>
   <si>
     <t xml:space="preserve">2.22461223602295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21452212333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22514319419861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24638557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098492622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32073402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34887981414795</t>
+    <t xml:space="preserve">2.21452188491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22514343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2463858127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098468780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32073426246643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34888029098511</t>
   </si>
   <si>
     <t xml:space="preserve">2.32604455947876</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">2.51775741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56555271148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997183799744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61547231674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66555047035217</t>
+    <t xml:space="preserve">2.5655529499054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997159957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6154727935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66555023193359</t>
   </si>
   <si>
     <t xml:space="preserve">2.66718339920044</t>
@@ -293,19 +293,19 @@
     <t xml:space="preserve">2.70147562026978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68786764144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72161555290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79346632957458</t>
+    <t xml:space="preserve">2.68786787986755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72161507606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79346609115601</t>
   </si>
   <si>
     <t xml:space="preserve">2.8152391910553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95894050598145</t>
+    <t xml:space="preserve">2.95894074440002</t>
   </si>
   <si>
     <t xml:space="preserve">2.98942232131958</t>
@@ -314,58 +314,58 @@
     <t xml:space="preserve">3.00248622894287</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94587635993958</t>
+    <t xml:space="preserve">2.94587659835815</t>
   </si>
   <si>
     <t xml:space="preserve">2.84136652946472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91757202148438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90668559074402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797616004944</t>
+    <t xml:space="preserve">2.9175717830658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90668535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797639846802</t>
   </si>
   <si>
     <t xml:space="preserve">2.81959366798401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76516127586365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73685669898987</t>
+    <t xml:space="preserve">2.76516151428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73685646057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.69548797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531662940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289084434509</t>
+    <t xml:space="preserve">2.78693461418152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289108276367</t>
   </si>
   <si>
     <t xml:space="preserve">2.84789872169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77604794502258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86313939094543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91974949836731</t>
+    <t xml:space="preserve">2.776047706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86313986778259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91974925994873</t>
   </si>
   <si>
     <t xml:space="preserve">2.97200393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99159955978394</t>
+    <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418141365051</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">2.99813199043274</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9785361289978</t>
+    <t xml:space="preserve">2.97853589057922</t>
   </si>
   <si>
     <t xml:space="preserve">3.03514552116394</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">3.15707421302795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29859805107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730700492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214425086975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29206609725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28771185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26158452033997</t>
+    <t xml:space="preserve">3.29859781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2920663356781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28771138191223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26158404350281</t>
   </si>
   <si>
     <t xml:space="preserve">3.24416542053223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28988862037659</t>
+    <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
     <t xml:space="preserve">3.27900266647339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2572295665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2659387588501</t>
+    <t xml:space="preserve">3.25722980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26593899726868</t>
   </si>
   <si>
     <t xml:space="preserve">3.1744921207428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25505208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25940680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33125734329224</t>
+    <t xml:space="preserve">3.25505256652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25940704345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33125758171082</t>
   </si>
   <si>
     <t xml:space="preserve">3.35085344314575</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">3.32472562789917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28553462028503</t>
+    <t xml:space="preserve">3.28553414344788</t>
   </si>
   <si>
     <t xml:space="preserve">3.27247023582458</t>
@@ -452,10 +452,10 @@
     <t xml:space="preserve">3.35303020477295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32037115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682542800903</t>
+    <t xml:space="preserve">3.32037091255188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682495117188</t>
   </si>
   <si>
     <t xml:space="preserve">3.31383895874023</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">3.3094847202301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15054202079773</t>
+    <t xml:space="preserve">3.15054225921631</t>
   </si>
   <si>
     <t xml:space="preserve">3.18973326683044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2093288898468</t>
+    <t xml:space="preserve">3.20932912826538</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069761276245</t>
@@ -479,52 +479,52 @@
     <t xml:space="preserve">3.20061993598938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22239279747009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175539016724</t>
+    <t xml:space="preserve">3.22239303588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175515174866</t>
   </si>
   <si>
     <t xml:space="preserve">3.33343482017517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26376152038574</t>
+    <t xml:space="preserve">3.26376128196716</t>
   </si>
   <si>
     <t xml:space="preserve">3.20497465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37262582778931</t>
+    <t xml:space="preserve">3.37262606620789</t>
   </si>
   <si>
     <t xml:space="preserve">3.43141269683838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59253287315369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67962431907654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78631138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90824055671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01057291030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09331035614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99533200263977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11508321762085</t>
+    <t xml:space="preserve">3.59253263473511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67962408065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78631162643433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90823984146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01057243347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09330987930298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99533247947693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831751823425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11508274078369</t>
   </si>
   <si>
     <t xml:space="preserve">4.19346523284912</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">4.33716630935669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23483419418335</t>
+    <t xml:space="preserve">4.23483371734619</t>
   </si>
   <si>
     <t xml:space="preserve">4.26313829421997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47433567047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68988847732544</t>
+    <t xml:space="preserve">4.47433614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68988800048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.65722894668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64634275436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75956201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95334005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94245386123657</t>
+    <t xml:space="preserve">4.64634227752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75956153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95334053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94245433807373</t>
   </si>
   <si>
     <t xml:space="preserve">4.72037029266357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74214315414429</t>
+    <t xml:space="preserve">4.74214267730713</t>
   </si>
   <si>
     <t xml:space="preserve">4.73778867721558</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">4.37418031692505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35022974014282</t>
+    <t xml:space="preserve">4.35023069381714</t>
   </si>
   <si>
     <t xml:space="preserve">4.34152126312256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22830152511597</t>
+    <t xml:space="preserve">4.22830200195312</t>
   </si>
   <si>
     <t xml:space="preserve">4.19128799438477</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">4.08895587921143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22612476348877</t>
+    <t xml:space="preserve">4.22612428665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.24571990966797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36547040939331</t>
+    <t xml:space="preserve">4.36547136306763</t>
   </si>
   <si>
     <t xml:space="preserve">4.35458517074585</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">4.65940523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63763284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6158595085144</t>
+    <t xml:space="preserve">4.63763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545608520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61586046218872</t>
   </si>
   <si>
     <t xml:space="preserve">4.64851951599121</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">4.58973264694214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51135015487671</t>
+    <t xml:space="preserve">4.51134967803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.5244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73343467712402</t>
+    <t xml:space="preserve">4.73343372344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.64198780059814</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">4.77480220794678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74649667739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76609325408936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921836853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38662147521973</t>
+    <t xml:space="preserve">4.74649715423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7660927772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921932220459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38662099838257</t>
   </si>
   <si>
     <t xml:space="preserve">5.29082107543945</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25162935256958</t>
+    <t xml:space="preserve">5.25162887573242</t>
   </si>
   <si>
     <t xml:space="preserve">5.22985649108887</t>
@@ -677,52 +677,52 @@
     <t xml:space="preserve">5.22767877578735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20372867584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03607749938965</t>
+    <t xml:space="preserve">5.20372772216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03607797622681</t>
   </si>
   <si>
     <t xml:space="preserve">5.11010503768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.225501537323</t>
+    <t xml:space="preserve">5.22550201416016</t>
   </si>
   <si>
     <t xml:space="preserve">5.27557992935181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17106962203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14494180679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06220436096191</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17107057571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14494228363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06220483779907</t>
   </si>
   <si>
     <t xml:space="preserve">4.90979385375977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09050941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0404314994812</t>
+    <t xml:space="preserve">5.09050989151001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04043197631836</t>
   </si>
   <si>
     <t xml:space="preserve">5.11445999145508</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10139608383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09268712997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752389907837</t>
+    <t xml:space="preserve">5.10139560699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09268617630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752342224121</t>
   </si>
   <si>
     <t xml:space="preserve">5.11663675308228</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">5.04478645324707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95769500732422</t>
+    <t xml:space="preserve">4.95769548416138</t>
   </si>
   <si>
     <t xml:space="preserve">5.02736854553223</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98817729949951</t>
+    <t xml:space="preserve">4.98817682266235</t>
   </si>
   <si>
     <t xml:space="preserve">4.88584423065186</t>
@@ -752,55 +752,55 @@
     <t xml:space="preserve">4.84665298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8009295463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73561096191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79004287719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74431991577148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738477706909</t>
+    <t xml:space="preserve">4.80092906951904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73561143875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79004335403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7443208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738430023193</t>
   </si>
   <si>
     <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82052516937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9185037612915</t>
+    <t xml:space="preserve">4.82052612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91850328445435</t>
   </si>
   <si>
     <t xml:space="preserve">5.1384105682373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19719791412354</t>
+    <t xml:space="preserve">5.08397817611694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19719743728638</t>
   </si>
   <si>
     <t xml:space="preserve">5.11881446838379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09486484527588</t>
+    <t xml:space="preserve">5.09486436843872</t>
   </si>
   <si>
     <t xml:space="preserve">5.30170726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4171028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55209589004517</t>
+    <t xml:space="preserve">5.38444471359253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710329055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55209541320801</t>
   </si>
   <si>
     <t xml:space="preserve">5.68273305892944</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">6.11383771896362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81337118148804</t>
+    <t xml:space="preserve">5.81337070465088</t>
   </si>
   <si>
     <t xml:space="preserve">5.87868976593018</t>
@@ -830,16 +830,16 @@
     <t xml:space="preserve">5.75893878936768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76329231262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88957548141479</t>
+    <t xml:space="preserve">5.76329326629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88957595825195</t>
   </si>
   <si>
     <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97666788101196</t>
+    <t xml:space="preserve">5.97666835784912</t>
   </si>
   <si>
     <t xml:space="preserve">6.09641933441162</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">6.04198694229126</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05722761154175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08335542678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96360397338867</t>
+    <t xml:space="preserve">6.05722713470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08335494995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96360349655151</t>
   </si>
   <si>
     <t xml:space="preserve">6.07464551925659</t>
@@ -878,64 +878,64 @@
     <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26842498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.529700756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276323318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848714828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.804039478302</t>
+    <t xml:space="preserve">6.26842546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52969980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276418685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80403852462769</t>
   </si>
   <si>
     <t xml:space="preserve">6.90201759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01088190078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06531429290771</t>
+    <t xml:space="preserve">7.01088237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06531476974487</t>
   </si>
   <si>
     <t xml:space="preserve">7.11756896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3200569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063335418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22425603866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22207880020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11321401596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29392957687378</t>
+    <t xml:space="preserve">7.32005739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063287734985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22425651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22207832336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11321353912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29392910003662</t>
   </si>
   <si>
     <t xml:space="preserve">7.37666749954224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28522062301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3048152923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19595098495483</t>
+    <t xml:space="preserve">7.36360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2852201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30481624603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19595146179199</t>
   </si>
   <si>
     <t xml:space="preserve">6.46655893325806</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">6.2270565032959</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47309064865112</t>
+    <t xml:space="preserve">6.47309017181396</t>
   </si>
   <si>
     <t xml:space="preserve">6.40123987197876</t>
@@ -953,106 +953,106 @@
     <t xml:space="preserve">6.61243724822998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49704027175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52316904067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57760047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52464437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56215476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891633987427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45403671264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55774164199829</t>
+    <t xml:space="preserve">6.49704074859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52316808700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57760000228882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5246434211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56215524673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61290502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45403575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55774211883545</t>
   </si>
   <si>
     <t xml:space="preserve">6.91740274429321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76294660568237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82252264022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41652584075928</t>
+    <t xml:space="preserve">6.76294708251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82252311706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41652536392212</t>
   </si>
   <si>
     <t xml:space="preserve">6.58421945571899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50478553771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093801498413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48713397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35694980621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33488464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43417692184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32826471328735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33267879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37460136413574</t>
+    <t xml:space="preserve">6.50478601455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093849182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48713302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35694932937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33488368988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43417739868164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32826519012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33267831802368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37460088729858</t>
   </si>
   <si>
     <t xml:space="preserve">6.16057014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14291763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13850545883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9575719833374</t>
+    <t xml:space="preserve">6.1429181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13850498199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95757150650024</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344165802002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90240859985352</t>
+    <t xml:space="preserve">5.90240907669067</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771314620972</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78546380996704</t>
+    <t xml:space="preserve">5.7854642868042</t>
   </si>
   <si>
     <t xml:space="preserve">5.95977830886841</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92006158828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93329906463623</t>
+    <t xml:space="preserve">5.9200611114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93330001831055</t>
   </si>
   <si>
     <t xml:space="preserve">5.94212627410889</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">5.83621406555176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84724617004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98846340179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69720363616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50744342803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46993350982666</t>
+    <t xml:space="preserve">5.8472466468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98846244812012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69720315933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50744390487671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46993398666382</t>
   </si>
   <si>
     <t xml:space="preserve">5.60894346237183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73692035675049</t>
+    <t xml:space="preserve">5.73692083358765</t>
   </si>
   <si>
     <t xml:space="preserve">5.7611927986145</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">5.89137697219849</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71485567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72147560119629</t>
+    <t xml:space="preserve">5.71485614776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72147464752197</t>
   </si>
   <si>
     <t xml:space="preserve">5.59129190444946</t>
@@ -1100,25 +1100,25 @@
     <t xml:space="preserve">5.55819368362427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38608598709106</t>
+    <t xml:space="preserve">5.38608646392822</t>
   </si>
   <si>
     <t xml:space="preserve">5.54495477676392</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44345569610596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45007562637329</t>
+    <t xml:space="preserve">5.4434552192688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45007467269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932489395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4191837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199771881104</t>
+    <t xml:space="preserve">5.41918325424194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199819564819</t>
   </si>
   <si>
     <t xml:space="preserve">5.56040000915527</t>
@@ -1130,19 +1130,19 @@
     <t xml:space="preserve">5.52730226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45890140533447</t>
+    <t xml:space="preserve">5.45890092849731</t>
   </si>
   <si>
     <t xml:space="preserve">5.41256475448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48979139328003</t>
+    <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
     <t xml:space="preserve">5.56922626495361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73912715911865</t>
+    <t xml:space="preserve">5.73912763595581</t>
   </si>
   <si>
     <t xml:space="preserve">5.66410636901855</t>
@@ -1154,28 +1154,28 @@
     <t xml:space="preserve">5.86931180953979</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73030185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08554887771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96860361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80532217025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762807846069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5648136138916</t>
+    <t xml:space="preserve">5.73030138015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08554935455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96860456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80532264709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762760162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.56481313705444</t>
   </si>
   <si>
     <t xml:space="preserve">5.52068328857422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47875928878784</t>
+    <t xml:space="preserve">5.47875881195068</t>
   </si>
   <si>
     <t xml:space="preserve">5.49420499801636</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">5.22942447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24045658111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25369548797607</t>
+    <t xml:space="preserve">5.24045705795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25369501113892</t>
   </si>
   <si>
     <t xml:space="preserve">5.41477060317993</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">5.39711856842041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27796697616577</t>
+    <t xml:space="preserve">5.27796745300293</t>
   </si>
   <si>
     <t xml:space="preserve">5.2228045463562</t>
@@ -1211,43 +1211,43 @@
     <t xml:space="preserve">5.14116334915161</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11909866333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20735931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16764116287231</t>
+    <t xml:space="preserve">5.11909914016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20735883712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16764211654663</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233757019043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13675117492676</t>
+    <t xml:space="preserve">5.1367506980896</t>
   </si>
   <si>
     <t xml:space="preserve">5.03745794296265</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00656700134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9646430015564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95802307128906</t>
+    <t xml:space="preserve">5.00656652450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96464347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95802402496338</t>
   </si>
   <si>
     <t xml:space="preserve">4.97126340866089</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04848957061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19411993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.27576112747192</t>
+    <t xml:space="preserve">5.04849052429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19412040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.27576065063477</t>
   </si>
   <si>
     <t xml:space="preserve">5.22501134872437</t>
@@ -1262,40 +1262,40 @@
     <t xml:space="preserve">5.03083848953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87196969985962</t>
+    <t xml:space="preserve">4.87196922302246</t>
   </si>
   <si>
     <t xml:space="preserve">4.72633981704712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71089506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65131902694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9315447807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21839141845703</t>
+    <t xml:space="preserve">4.71089458465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65131950378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93154573440552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21839094161987</t>
   </si>
   <si>
     <t xml:space="preserve">5.60453033447266</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81194162368774</t>
+    <t xml:space="preserve">5.81194257736206</t>
   </si>
   <si>
     <t xml:space="preserve">5.84503984451294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76781129837036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90461540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
+    <t xml:space="preserve">5.76781177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90461492538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489868164062</t>
   </si>
   <si>
     <t xml:space="preserve">5.77663850784302</t>
@@ -1304,58 +1304,58 @@
     <t xml:space="preserve">5.81856203079224</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65307378768921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63983488082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6994104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467102050781</t>
+    <t xml:space="preserve">5.65307426452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6398344039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69940996170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467149734497</t>
   </si>
   <si>
     <t xml:space="preserve">6.02376651763916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19366788864136</t>
+    <t xml:space="preserve">6.19366836547852</t>
   </si>
   <si>
     <t xml:space="preserve">6.06348371505737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14071226119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12526607513428</t>
+    <t xml:space="preserve">6.14071178436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12526655197144</t>
   </si>
   <si>
     <t xml:space="preserve">6.02597284317017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96419191360474</t>
+    <t xml:space="preserve">5.96419095993042</t>
   </si>
   <si>
     <t xml:space="preserve">6.03480005264282</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8097357749939</t>
+    <t xml:space="preserve">5.80973529815674</t>
   </si>
   <si>
     <t xml:space="preserve">5.88034343719482</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90020275115967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82518148422241</t>
+    <t xml:space="preserve">5.90020322799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82518100738525</t>
   </si>
   <si>
     <t xml:space="preserve">5.74354076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6508674621582</t>
+    <t xml:space="preserve">5.65086698532104</t>
   </si>
   <si>
     <t xml:space="preserve">5.61776924133301</t>
@@ -1364,28 +1364,28 @@
     <t xml:space="preserve">5.63542175292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01935386657715</t>
+    <t xml:space="preserve">6.01935338973999</t>
   </si>
   <si>
     <t xml:space="preserve">5.85607242584229</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71926879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283351898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03259325027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04583215713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95315837860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94433259963989</t>
+    <t xml:space="preserve">5.71926832199097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283304214478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04583168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95315790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94433307647705</t>
   </si>
   <si>
     <t xml:space="preserve">6.28854846954346</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">6.28413486480713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22235298156738</t>
+    <t xml:space="preserve">6.22235250473022</t>
   </si>
   <si>
     <t xml:space="preserve">6.52243804931641</t>
@@ -1403,31 +1403,31 @@
     <t xml:space="preserve">6.37239456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16939640045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
+    <t xml:space="preserve">6.16939687728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878730773926</t>
   </si>
   <si>
     <t xml:space="preserve">6.08996200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55598735809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9222674369812</t>
+    <t xml:space="preserve">5.5559868812561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92226791381836</t>
   </si>
   <si>
     <t xml:space="preserve">5.79428958892822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67072629928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396472930908</t>
+    <t xml:space="preserve">5.67072582244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396520614624</t>
   </si>
   <si>
     <t xml:space="preserve">5.42800998687744</t>
@@ -1439,19 +1439,19 @@
     <t xml:space="preserve">5.87372446060181</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97963619232178</t>
+    <t xml:space="preserve">5.97963666915894</t>
   </si>
   <si>
     <t xml:space="preserve">5.96198463439941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089548110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35474300384521</t>
+    <t xml:space="preserve">6.17822170257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35474348068237</t>
   </si>
   <si>
     <t xml:space="preserve">6.72543621063232</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">7.10495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97697925567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1005425453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87106657028198</t>
+    <t xml:space="preserve">6.97697877883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054302215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87106609344482</t>
   </si>
   <si>
     <t xml:space="preserve">6.95050001144409</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">7.22851991653442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14908647537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0475869178772</t>
+    <t xml:space="preserve">7.14908599853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04758644104004</t>
   </si>
   <si>
     <t xml:space="preserve">7.11378240585327</t>
@@ -1496,31 +1496,31 @@
     <t xml:space="preserve">7.06082630157471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4933009147644</t>
+    <t xml:space="preserve">7.49330043792725</t>
   </si>
   <si>
     <t xml:space="preserve">7.32560729980469</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18439102172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44034481048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28147745132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941133499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
+    <t xml:space="preserve">7.18439054489136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44034576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2814769744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2594108581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
   </si>
   <si>
     <t xml:space="preserve">7.06523847579956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25058555603027</t>
+    <t xml:space="preserve">7.25058603286743</t>
   </si>
   <si>
     <t xml:space="preserve">7.21528100967407</t>
@@ -1529,16 +1529,16 @@
     <t xml:space="preserve">7.19321584701538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21969413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62127876281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390905380249</t>
+    <t xml:space="preserve">7.2196946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46241140365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62127923965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56391000747681</t>
   </si>
   <si>
     <t xml:space="preserve">7.53743124008179</t>
@@ -1547,10 +1547,10 @@
     <t xml:space="preserve">7.40062808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55508422851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
+    <t xml:space="preserve">7.55508470535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4271068572998</t>
   </si>
   <si>
     <t xml:space="preserve">7.38738870620728</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">7.06965208053589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62835073471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84017515182495</t>
+    <t xml:space="preserve">6.62835025787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84017419815063</t>
   </si>
   <si>
     <t xml:space="preserve">6.63717651367188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51802492141724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61952447891235</t>
+    <t xml:space="preserve">6.51802539825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6195240020752</t>
   </si>
   <si>
     <t xml:space="preserve">6.5445032119751</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38247299194336</t>
+    <t xml:space="preserve">6.38247394561768</t>
   </si>
   <si>
     <t xml:space="preserve">6.30643844604492</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">6.59716081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66425085067749</t>
+    <t xml:space="preserve">6.66424989700317</t>
   </si>
   <si>
     <t xml:space="preserve">6.60163307189941</t>
@@ -1598,88 +1598,88 @@
     <t xml:space="preserve">6.63294219970703</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54796123504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6597785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926940917969</t>
+    <t xml:space="preserve">6.54796171188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65977764129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57927083969116</t>
   </si>
   <si>
     <t xml:space="preserve">6.48534488677979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71344900131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75370407104492</t>
+    <t xml:space="preserve">6.71344947814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75370311737061</t>
   </si>
   <si>
     <t xml:space="preserve">6.75817537307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61505126953125</t>
+    <t xml:space="preserve">6.61505174636841</t>
   </si>
   <si>
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087167739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956350326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825532913208</t>
+    <t xml:space="preserve">6.48087215423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
   </si>
   <si>
     <t xml:space="preserve">6.3198561668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22593116760254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22145843505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12305974960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26171159744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14095020294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18120384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20356798171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34669208526611</t>
+    <t xml:space="preserve">6.22593069076538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22145795822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12305927276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26171207427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14095067977905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18120431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20356750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34669160842896</t>
   </si>
   <si>
     <t xml:space="preserve">6.24829435348511</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21251344680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33774709701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58821535110474</t>
+    <t xml:space="preserve">6.2125129699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33774662017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58821582794189</t>
   </si>
   <si>
     <t xml:space="preserve">6.48981714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53007125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44061851501465</t>
+    <t xml:space="preserve">6.53007078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44061803817749</t>
   </si>
   <si>
     <t xml:space="preserve">6.44509077072144</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">6.42719984054565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43167304992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50323486328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32880163192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23934888839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014883041382</t>
+    <t xml:space="preserve">6.4316725730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50323534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32880115509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23934841156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
   </si>
   <si>
     <t xml:space="preserve">6.27960205078125</t>
@@ -1724,22 +1724,22 @@
     <t xml:space="preserve">6.1006965637207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3958911895752</t>
+    <t xml:space="preserve">6.39589166641235</t>
   </si>
   <si>
     <t xml:space="preserve">6.18567657470703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98440790176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.474524974823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3358736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24194765090942</t>
+    <t xml:space="preserve">5.98440742492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47452545166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33587312698364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24194717407227</t>
   </si>
   <si>
     <t xml:space="preserve">5.08093166351318</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">4.97358846664429</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13013029098511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01831483840942</t>
+    <t xml:space="preserve">5.13013076782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01831436157227</t>
   </si>
   <si>
     <t xml:space="preserve">5.0764594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05409669876099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98700666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886161804199</t>
+    <t xml:space="preserve">5.05409622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98700618743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
+    <t xml:space="preserve">4.58894014358521</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577653884888</t>
@@ -1781,61 +1781,61 @@
     <t xml:space="preserve">4.71417427062988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37201595306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12825727462769</t>
+    <t xml:space="preserve">4.37201690673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12825679779053</t>
   </si>
   <si>
     <t xml:space="preserve">4.20876455307007</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11483955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04104042053223</t>
+    <t xml:space="preserve">4.11483907699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04103994369507</t>
   </si>
   <si>
     <t xml:space="preserve">4.05445861816406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95829677581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08353090286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15509366989136</t>
+    <t xml:space="preserve">3.95829629898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08353137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1550931930542</t>
   </si>
   <si>
     <t xml:space="preserve">4.13049364089966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01867771148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86884307861328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70559167861938</t>
+    <t xml:space="preserve">4.01867723464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86884355545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70559144020081</t>
   </si>
   <si>
     <t xml:space="preserve">3.75702714920044</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81740784645081</t>
+    <t xml:space="preserve">3.81740760803223</t>
   </si>
   <si>
     <t xml:space="preserve">3.73466396331787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83753490447998</t>
+    <t xml:space="preserve">3.8375346660614</t>
   </si>
   <si>
     <t xml:space="preserve">3.84648036956787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96500492095947</t>
+    <t xml:space="preserve">3.96500611305237</t>
   </si>
   <si>
     <t xml:space="preserve">4.15732955932617</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9314603805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331604957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86213445663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8442440032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45512294769287</t>
+    <t xml:space="preserve">3.92475175857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93146085739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264245033264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331628799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86213493347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84424376487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45512318611145</t>
   </si>
   <si>
     <t xml:space="preserve">3.35896134376526</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">3.24267244338989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03245759010315</t>
+    <t xml:space="preserve">3.03245782852173</t>
   </si>
   <si>
     <t xml:space="preserve">3.04140281677246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16216444969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38356065750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38803291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26950788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22701835632324</t>
+    <t xml:space="preserve">3.16216468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3835608959198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38803315162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26950812339783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22701787948608</t>
   </si>
   <si>
     <t xml:space="preserve">3.4528865814209</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">3.4886679649353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51550388336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31870746612549</t>
+    <t xml:space="preserve">3.5155041217804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31870722770691</t>
   </si>
   <si>
     <t xml:space="preserve">3.24714493751526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1107292175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92735004425049</t>
+    <t xml:space="preserve">3.11072897911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92735028266907</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182277679443</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">3.03916668891907</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95642280578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88486003875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92511415481567</t>
+    <t xml:space="preserve">2.95642256736755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88485980033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92511391639709</t>
   </si>
   <si>
     <t xml:space="preserve">2.77751636505127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74844408035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78869819641113</t>
+    <t xml:space="preserve">2.74844455718994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78869795799255</t>
   </si>
   <si>
     <t xml:space="preserve">2.83342480659485</t>
@@ -1952,16 +1952,16 @@
     <t xml:space="preserve">2.88933277130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07271099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625672340393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16887354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22925424575806</t>
+    <t xml:space="preserve">3.07271146774292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625648498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16887331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22925400733948</t>
   </si>
   <si>
     <t xml:space="preserve">3.1599280834198</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">3.18676400184631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19347286224365</t>
+    <t xml:space="preserve">3.19347310066223</t>
   </si>
   <si>
     <t xml:space="preserve">3.32094383239746</t>
@@ -2003,25 +2003,25 @@
     <t xml:space="preserve">3.57588458061218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51103115081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52221322059631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5825936794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43723273277283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52444934844971</t>
+    <t xml:space="preserve">3.51103138923645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52221298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58259391784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43723249435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52444958686829</t>
   </si>
   <si>
     <t xml:space="preserve">3.58483004570007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6944100856781</t>
+    <t xml:space="preserve">3.69440984725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.62284779548645</t>
@@ -2030,25 +2030,25 @@
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
+    <t xml:space="preserve">3.70335531234741</t>
   </si>
   <si>
     <t xml:space="preserve">3.80398988723755</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89567923545837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77268147468567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83306241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766172409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040584564209</t>
+    <t xml:space="preserve">3.89567947387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77268171310425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83306193351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85766220092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040560722351</t>
   </si>
   <si>
     <t xml:space="preserve">3.99184155464172</t>
@@ -2066,22 +2066,22 @@
     <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18863725662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94935083389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02762269973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842311859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23112773895264</t>
+    <t xml:space="preserve">4.18863821029663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94935059547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525903701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02762317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842359542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23112869262695</t>
   </si>
   <si>
     <t xml:space="preserve">4.28256368637085</t>
@@ -2090,10 +2090,10 @@
     <t xml:space="preserve">4.38319873809814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42792415618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35412549972534</t>
+    <t xml:space="preserve">4.42792510986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3541259765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.1662745475769</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">4.20205640792847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23783779144287</t>
+    <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
     <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24901914596558</t>
+    <t xml:space="preserve">4.24901866912842</t>
   </si>
   <si>
     <t xml:space="preserve">4.24007320404053</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">4.25349140167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19981956481934</t>
+    <t xml:space="preserve">4.19982004165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285634994507</t>
+    <t xml:space="preserve">4.15285682678223</t>
   </si>
   <si>
     <t xml:space="preserve">4.1864013671875</t>
@@ -2138,40 +2138,40 @@
     <t xml:space="preserve">4.26914548873901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97171378135681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93369722366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9001522064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631404876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03880405426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0365686416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01643991470337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91804313659668</t>
+    <t xml:space="preserve">3.97171425819397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93369674682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90015196800232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03880453109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03656816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01644086837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91804218292236</t>
   </si>
   <si>
     <t xml:space="preserve">3.87778878211975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76820874214172</t>
+    <t xml:space="preserve">3.7682089805603</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491736412048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65191960334778</t>
+    <t xml:space="preserve">3.65191984176636</t>
   </si>
   <si>
     <t xml:space="preserve">3.85095262527466</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">4.0991849899292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82411694526672</t>
+    <t xml:space="preserve">3.8241171836853</t>
   </si>
   <si>
     <t xml:space="preserve">3.95693063735962</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">3.7645800113678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68901371955872</t>
+    <t xml:space="preserve">3.68901324272156</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
@@ -2207,13 +2207,13 @@
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243607521057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220454216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487239837646</t>
+    <t xml:space="preserve">3.84243631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487192153931</t>
   </si>
   <si>
     <t xml:space="preserve">3.96609044075012</t>
@@ -2222,19 +2222,19 @@
     <t xml:space="preserve">3.89739346504211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95006084442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87449431419373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90655303001404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98440933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04165649414062</t>
+    <t xml:space="preserve">3.95006132125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87449479103088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90655279159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98440980911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04165601730347</t>
   </si>
   <si>
     <t xml:space="preserve">4.19736957550049</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">4.1538610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09203433990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11264276504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10119390487671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14470148086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18820953369141</t>
+    <t xml:space="preserve">4.09203481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11264324188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10119342803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14470195770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18821001052856</t>
   </si>
   <si>
     <t xml:space="preserve">4.27751541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28438472747803</t>
+    <t xml:space="preserve">4.28438520431519</t>
   </si>
   <si>
     <t xml:space="preserve">4.31415367126465</t>
@@ -2270,19 +2270,19 @@
     <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30270481109619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3507924079895</t>
+    <t xml:space="preserve">4.30270433425903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35079193115234</t>
   </si>
   <si>
     <t xml:space="preserve">4.2454571723938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33247232437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23858737945557</t>
+    <t xml:space="preserve">4.3324728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23858690261841</t>
   </si>
   <si>
     <t xml:space="preserve">4.22255802154541</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774694442749</t>
+    <t xml:space="preserve">4.24774646759033</t>
   </si>
   <si>
     <t xml:space="preserve">4.1744704246521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05997514724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0989031791687</t>
+    <t xml:space="preserve">4.05997657775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09890365600586</t>
   </si>
   <si>
     <t xml:space="preserve">4.15157127380371</t>
@@ -2312,61 +2312,61 @@
     <t xml:space="preserve">4.11035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12409257888794</t>
+    <t xml:space="preserve">4.1240930557251</t>
   </si>
   <si>
     <t xml:space="preserve">4.07600498199463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05539560317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97066974639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945481300354</t>
+    <t xml:space="preserve">4.00730848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97067022323608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94548034667969</t>
   </si>
   <si>
     <t xml:space="preserve">3.84701609611511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8859441280365</t>
+    <t xml:space="preserve">3.88594436645508</t>
   </si>
   <si>
     <t xml:space="preserve">3.87678456306458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8515956401825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235085487366</t>
+    <t xml:space="preserve">3.85159587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235109329224</t>
   </si>
   <si>
     <t xml:space="preserve">4.00043869018555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98211884498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13096237182617</t>
+    <t xml:space="preserve">3.98211932182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13096189498901</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16760110855103</t>
+    <t xml:space="preserve">4.16760063171387</t>
   </si>
   <si>
     <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0531063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18592023849487</t>
+    <t xml:space="preserve">4.05310583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18591976165771</t>
   </si>
   <si>
     <t xml:space="preserve">4.13554239273071</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">4.3370532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31873321533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60268020629883</t>
+    <t xml:space="preserve">4.31873369216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60267972946167</t>
   </si>
   <si>
     <t xml:space="preserve">5.00112056732178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17515277862549</t>
+    <t xml:space="preserve">5.17515230178833</t>
   </si>
   <si>
     <t xml:space="preserve">5.33086490631104</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">5.35834360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62855100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48657703399658</t>
+    <t xml:space="preserve">5.6285514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48657655715942</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
@@ -2411,19 +2411,19 @@
     <t xml:space="preserve">5.61023139953613</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70640754699707</t>
+    <t xml:space="preserve">5.70640707015991</t>
   </si>
   <si>
     <t xml:space="preserve">5.55527448654175</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45451831817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48199796676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26674842834473</t>
+    <t xml:space="preserve">5.45451879501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.4819974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
     <t xml:space="preserve">5.27590799331665</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">5.36292314529419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44993925094604</t>
+    <t xml:space="preserve">5.44993877410889</t>
   </si>
   <si>
     <t xml:space="preserve">5.3446044921875</t>
@@ -2444,16 +2444,16 @@
     <t xml:space="preserve">5.45909929275513</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55985403060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69724750518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72930574417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92623615264893</t>
+    <t xml:space="preserve">5.55985355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69724702835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7293062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92623567581177</t>
   </si>
   <si>
     <t xml:space="preserve">5.74304533004761</t>
@@ -2468,13 +2468,13 @@
     <t xml:space="preserve">5.67892789840698</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71556663513184</t>
+    <t xml:space="preserve">5.71556615829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716228485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098709106445</t>
+    <t xml:space="preserve">5.71098661422729</t>
   </si>
   <si>
     <t xml:space="preserve">5.82090139389038</t>
@@ -2486,16 +2486,16 @@
     <t xml:space="preserve">6.04989051818848</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12316656112671</t>
+    <t xml:space="preserve">6.12316703796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.22392225265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99493265151978</t>
+    <t xml:space="preserve">6.08652830123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99493312835693</t>
   </si>
   <si>
     <t xml:space="preserve">6.02241182327271</t>
@@ -2504,43 +2504,43 @@
     <t xml:space="preserve">6.24224138259888</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71395921707153</t>
+    <t xml:space="preserve">6.71395874023438</t>
   </si>
   <si>
     <t xml:space="preserve">7.10324048995972</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19941568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28643178939819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61159610748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617612838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235084533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600568771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113304138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62533473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16735696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28185129165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41924571990967</t>
+    <t xml:space="preserve">7.1994161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28643131256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61159563064575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235227584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600521087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113256454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6253342628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16735649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28185176849365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41924524307251</t>
   </si>
   <si>
     <t xml:space="preserve">7.35512781143188</t>
@@ -2549,49 +2549,49 @@
     <t xml:space="preserve">7.29101085662842</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27727174758911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11698007583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15361738204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26811218261719</t>
+    <t xml:space="preserve">7.27727222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11697912216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15361785888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26811170578003</t>
   </si>
   <si>
     <t xml:space="preserve">7.39634561538696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802743911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57495737075806</t>
+    <t xml:space="preserve">7.37802648544312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57495784759521</t>
   </si>
   <si>
     <t xml:space="preserve">7.9184422492981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85890293121338</t>
+    <t xml:space="preserve">7.85890340805054</t>
   </si>
   <si>
     <t xml:space="preserve">7.67571258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56579828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655349731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36428785324097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45130348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12155866622925</t>
+    <t xml:space="preserve">7.56579780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655302047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36428737640381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45130395889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12155961990356</t>
   </si>
   <si>
     <t xml:space="preserve">7.41466569900513</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30474996566772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22231483459473</t>
+    <t xml:space="preserve">7.30475044250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22231435775757</t>
   </si>
   <si>
     <t xml:space="preserve">7.5291600227356</t>
@@ -2612,28 +2612,28 @@
     <t xml:space="preserve">7.4375638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48794221878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51999998092651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31849002838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17651653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02996397018433</t>
+    <t xml:space="preserve">7.48794174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52000093460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31848955154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17651700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02996349334717</t>
   </si>
   <si>
     <t xml:space="preserve">6.51244878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7414379119873</t>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639434814453</t>
@@ -2642,34 +2642,34 @@
     <t xml:space="preserve">6.71853828430176</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76891613006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61778354644775</t>
+    <t xml:space="preserve">6.76891660690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61778402328491</t>
   </si>
   <si>
     <t xml:space="preserve">7.02538394927979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89257049560547</t>
+    <t xml:space="preserve">6.89257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">6.89715003967285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82845306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097436904907</t>
+    <t xml:space="preserve">6.82845258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097484588623</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732048034668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83303308486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76433706283569</t>
+    <t xml:space="preserve">6.83303356170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76433610916138</t>
   </si>
   <si>
     <t xml:space="preserve">6.6361026763916</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">6.11858701705933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96745491027832</t>
+    <t xml:space="preserve">5.96745443344116</t>
   </si>
   <si>
     <t xml:space="preserve">5.78884363174438</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">5.63771057128906</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77052402496338</t>
+    <t xml:space="preserve">5.77052450180054</t>
   </si>
   <si>
     <t xml:space="preserve">5.72014570236206</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47741794586182</t>
+    <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
     <t xml:space="preserve">5.11561489105225</t>
@@ -2726,19 +2726,19 @@
     <t xml:space="preserve">3.18294739723206</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22645568847656</t>
+    <t xml:space="preserve">3.22645545005798</t>
   </si>
   <si>
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356865882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304521560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61344695091248</t>
+    <t xml:space="preserve">3.99356913566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304569244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6134467124939</t>
   </si>
   <si>
     <t xml:space="preserve">3.50353240966797</t>
@@ -2750,31 +2750,31 @@
     <t xml:space="preserve">3.61802697181702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70962285995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62260675430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663848876953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74168086051941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06684494018555</t>
+    <t xml:space="preserve">3.70962262153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6226065158844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663825035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74168062210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06684541702271</t>
   </si>
   <si>
     <t xml:space="preserve">4.03020763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38285064697266</t>
+    <t xml:space="preserve">4.3828501701355</t>
   </si>
   <si>
     <t xml:space="preserve">4.11722278594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01188898086548</t>
+    <t xml:space="preserve">4.01188802719116</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218017578125</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">4.35995149612427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26835489273071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2637767791748</t>
+    <t xml:space="preserve">4.26835536956787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26377582550049</t>
   </si>
   <si>
     <t xml:space="preserve">4.32331275939941</t>
@@ -2810,28 +2810,28 @@
     <t xml:space="preserve">4.30499410629272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17675971984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137575149536</t>
+    <t xml:space="preserve">4.17676019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137622833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.5248236656189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48360538482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38743019104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42406797409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75152254104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95761251449585</t>
+    <t xml:space="preserve">4.4836049079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38742971420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42406845092773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7515230178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95761299133301</t>
   </si>
   <si>
     <t xml:space="preserve">4.90036535263062</t>
@@ -2843,40 +2843,40 @@
     <t xml:space="preserve">5.04920816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18660163879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23239946365356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48428726196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34689426422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16370248794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93471336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02630949020386</t>
+    <t xml:space="preserve">5.1866021156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23239994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48428773880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34689378738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1637020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9347128868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02630996704102</t>
   </si>
   <si>
     <t xml:space="preserve">5.19805192947388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31254625320435</t>
+    <t xml:space="preserve">5.31254577636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.25529861450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39269161224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20950031280518</t>
+    <t xml:space="preserve">5.39269208908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20950078964233</t>
   </si>
   <si>
     <t xml:space="preserve">5.1522536277771</t>
@@ -2885,19 +2885,19 @@
     <t xml:space="preserve">5.14080429077148</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27819776535034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.27819728851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.09500646591187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.923264503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01486015319824</t>
+    <t xml:space="preserve">4.92326402664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0148606300354</t>
   </si>
   <si>
     <t xml:space="preserve">5.1179051399231</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">5.06065845489502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22094964981079</t>
+    <t xml:space="preserve">5.22095012664795</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210731506348</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">5.03775882720947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08355665206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96906232833862</t>
+    <t xml:space="preserve">5.08355712890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96906280517578</t>
   </si>
   <si>
     <t xml:space="preserve">4.94616270065308</t>
@@ -2942,13 +2942,13 @@
     <t xml:space="preserve">4.84311866760254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91181516647339</t>
+    <t xml:space="preserve">4.91181468963623</t>
   </si>
   <si>
     <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00341081619263</t>
+    <t xml:space="preserve">5.00341129302979</t>
   </si>
   <si>
     <t xml:space="preserve">4.57978057861328</t>
@@ -2957,49 +2957,49 @@
     <t xml:space="preserve">4.1904993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21339893341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08058452606201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30041408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34163236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61412906646729</t>
+    <t xml:space="preserve">4.21339845657349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08058500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30041456222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34163188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61412954330444</t>
   </si>
   <si>
     <t xml:space="preserve">5.54153537750244</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62168073654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907421112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73617553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69037818908691</t>
+    <t xml:space="preserve">5.62168121337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73617601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
     <t xml:space="preserve">5.64458036422729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66747903823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89646768569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70182657241821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.816321849823</t>
+    <t xml:space="preserve">5.66747856140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89646816253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70182704925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81632137298584</t>
   </si>
   <si>
     <t xml:space="preserve">6.14835548400879</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">5.96516418457031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9537148475647</t>
+    <t xml:space="preserve">5.95371532440186</t>
   </si>
   <si>
     <t xml:space="preserve">5.87356853485107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91936683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09110879898071</t>
+    <t xml:space="preserve">5.91936635971069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09110927581787</t>
   </si>
   <si>
     <t xml:space="preserve">6.19415330886841</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">6.12545728683472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15980529785156</t>
+    <t xml:space="preserve">6.1598048210144</t>
   </si>
   <si>
     <t xml:space="preserve">6.18270444869995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07965898513794</t>
+    <t xml:space="preserve">6.0796594619751</t>
   </si>
   <si>
     <t xml:space="preserve">6.13690662384033</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">6.2170524597168</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35444641113281</t>
+    <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.32009744644165</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">6.36589479446411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4803900718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52618741989136</t>
+    <t xml:space="preserve">6.48038959503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
     <t xml:space="preserve">6.53763723373413</t>
@@ -3065,16 +3065,16 @@
     <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62923336029053</t>
+    <t xml:space="preserve">6.58343553543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62923383712769</t>
   </si>
   <si>
     <t xml:space="preserve">6.41169309616089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3429970741272</t>
+    <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
     <t xml:space="preserve">6.46894025802612</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20560359954834</t>
+    <t xml:space="preserve">6.20560312271118</t>
   </si>
   <si>
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328874588013</t>
+    <t xml:space="preserve">6.50328826904297</t>
   </si>
   <si>
     <t xml:space="preserve">6.66358137130737</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51473808288574</t>
+    <t xml:space="preserve">6.5147385597229</t>
   </si>
   <si>
     <t xml:space="preserve">6.78952503204346</t>
@@ -3104,40 +3104,40 @@
     <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68648052215576</t>
+    <t xml:space="preserve">6.6864800453186</t>
   </si>
   <si>
     <t xml:space="preserve">6.70937871932983</t>
   </si>
   <si>
-    <t xml:space="preserve">6.778076171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69792985916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40024471282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37734508514404</t>
+    <t xml:space="preserve">6.77807569503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69792938232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40024375915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37734460830688</t>
   </si>
   <si>
     <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38879442214966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54908609390259</t>
+    <t xml:space="preserve">6.3887939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
     <t xml:space="preserve">6.86967134475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78562831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417850494385</t>
+    <t xml:space="preserve">7.7856273651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417755126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
@@ -3146,58 +3146,58 @@
     <t xml:space="preserve">8.17490863800049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99171781539917</t>
+    <t xml:space="preserve">8.01461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99171876907349</t>
   </si>
   <si>
     <t xml:space="preserve">8.06041526794434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02606582641602</t>
+    <t xml:space="preserve">8.02606678009033</t>
   </si>
   <si>
     <t xml:space="preserve">8.12911128997803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1062126159668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03751468658447</t>
+    <t xml:space="preserve">8.10621166229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03751564025879</t>
   </si>
   <si>
     <t xml:space="preserve">8.00316715240479</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93447017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08331298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31230163574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085277557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28940296173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33520221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2779541015625</t>
+    <t xml:space="preserve">7.93447113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08331203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3123025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085372924805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28940391540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33520126342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27795505523682</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11766242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18635845184326</t>
+    <t xml:space="preserve">8.11766147613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18635749816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.34665107727051</t>
@@ -3206,31 +3206,31 @@
     <t xml:space="preserve">8.23215675354004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16346073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925807952881</t>
+    <t xml:space="preserve">8.16345977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925617218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.94592094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95736885070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84287548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92302083969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997632980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577320098877</t>
+    <t xml:space="preserve">7.95736980438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8428750038147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92302179336548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577367782593</t>
   </si>
   <si>
     <t xml:space="preserve">8.3809986114502</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536041259766</t>
+    <t xml:space="preserve">9.20535945892334</t>
   </si>
   <si>
     <t xml:space="preserve">9.48014736175537</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">9.78073692321777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71136951446533</t>
+    <t xml:space="preserve">9.71136856079102</t>
   </si>
   <si>
     <t xml:space="preserve">10.0813264846802</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">10.3009881973267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3241100311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5206499099731</t>
+    <t xml:space="preserve">10.3241109848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5206508636475</t>
   </si>
   <si>
     <t xml:space="preserve">10.3587942123413</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5437717437744</t>
+    <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
     <t xml:space="preserve">10.4975290298462</t>
@@ -3296,34 +3296,34 @@
     <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7403125762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4744052886963</t>
+    <t xml:space="preserve">10.7403116226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4744062423706</t>
   </si>
   <si>
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044492721558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2663049697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.393479347229</t>
+    <t xml:space="preserve">10.1044502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2663059234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3934783935547</t>
   </si>
   <si>
     <t xml:space="preserve">10.0582046508789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9541540145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0235214233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1506938934326</t>
+    <t xml:space="preserve">9.95415306091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0235204696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1506948471069</t>
   </si>
   <si>
     <t xml:space="preserve">10.0697650909424</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">10.092887878418</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1160106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2547426223755</t>
+    <t xml:space="preserve">10.1160116195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2547435760498</t>
   </si>
   <si>
     <t xml:space="preserve">10.2200613021851</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">10.1853771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0350818634033</t>
+    <t xml:space="preserve">10.0350828170776</t>
   </si>
   <si>
     <t xml:space="preserve">10.4165992736816</t>
@@ -3356,79 +3356,79 @@
     <t xml:space="preserve">10.1738157272339</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1391315460205</t>
+    <t xml:space="preserve">10.1391334533691</t>
   </si>
   <si>
     <t xml:space="preserve">11.191198348999</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5056610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9052143096924</t>
+    <t xml:space="preserve">11.5056600570679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9052152633667</t>
   </si>
   <si>
     <t xml:space="preserve">11.901515007019</t>
   </si>
   <si>
-    <t xml:space="preserve">11.746132850647</t>
+    <t xml:space="preserve">11.7461318969727</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611543655396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5426568984985</t>
+    <t xml:space="preserve">11.5426559448242</t>
   </si>
   <si>
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576765060425</t>
+    <t xml:space="preserve">11.5796518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4501676559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576774597168</t>
   </si>
   <si>
     <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6536436080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3946743011475</t>
+    <t xml:space="preserve">11.6536445617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3946733474731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686641693115</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0975923538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8571186065674</t>
+    <t xml:space="preserve">12.0975914001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8571195602417</t>
   </si>
   <si>
     <t xml:space="preserve">12.0605964660645</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0420980453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2455749511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3010683059692</t>
+    <t xml:space="preserve">12.0420999526978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2455739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3010692596436</t>
   </si>
   <si>
     <t xml:space="preserve">11.894115447998</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9299945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6144161224365</t>
+    <t xml:space="preserve">12.9299955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6144151687622</t>
   </si>
   <si>
     <t xml:space="preserve">13.854887008667</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
+    <t xml:space="preserve">13.5034284591675</t>
   </si>
   <si>
     <t xml:space="preserve">13.817892074585</t>
@@ -3449,19 +3449,19 @@
     <t xml:space="preserve">13.7254018783569</t>
   </si>
   <si>
-    <t xml:space="preserve">14.631796836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0398654937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7439002990723</t>
+    <t xml:space="preserve">14.6317958831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0398664474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
     <t xml:space="preserve">13.4109401702881</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7623977661133</t>
+    <t xml:space="preserve">13.7623987197876</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294376373291</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">12.4860467910767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9669904708862</t>
+    <t xml:space="preserve">12.9669914245605</t>
   </si>
   <si>
     <t xml:space="preserve">13.0964756011963</t>
@@ -3485,67 +3485,67 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114980697632</t>
+    <t xml:space="preserve">12.9114971160889</t>
   </si>
   <si>
     <t xml:space="preserve">13.0779781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4468173980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4457015991211</t>
+    <t xml:space="preserve">14.4468183517456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4457025527954</t>
   </si>
   <si>
     <t xml:space="preserve">15.5011959075928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7786636352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.555570602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3705959320068</t>
+    <t xml:space="preserve">15.7786626815796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5555725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3705940246582</t>
   </si>
   <si>
     <t xml:space="preserve">16.5370750427246</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2596073150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520965576172</t>
+    <t xml:space="preserve">16.2596092224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520984649658</t>
   </si>
   <si>
     <t xml:space="preserve">16.019136428833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7971601486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1486206054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0006370544434</t>
+    <t xml:space="preserve">15.7971611022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1486186981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.000638961792</t>
   </si>
   <si>
     <t xml:space="preserve">15.908148765564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5196933746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896522521973</t>
+    <t xml:space="preserve">15.5196943283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4641981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896503448486</t>
   </si>
   <si>
     <t xml:space="preserve">15.7416677474976</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8341588973999</t>
+    <t xml:space="preserve">15.8341569900513</t>
   </si>
   <si>
     <t xml:space="preserve">14.9092655181885</t>
@@ -3557,16 +3557,16 @@
     <t xml:space="preserve">14.5023126602173</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2433423995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6329126358032</t>
+    <t xml:space="preserve">14.2433414459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6329135894775</t>
   </si>
   <si>
     <t xml:space="preserve">13.6514110565186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.3369464874268</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">14.1693506240845</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8918828964233</t>
+    <t xml:space="preserve">13.8918838500977</t>
   </si>
   <si>
     <t xml:space="preserve">14.4098224639893</t>
@@ -3587,31 +3587,31 @@
     <t xml:space="preserve">14.1508531570435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7993936538696</t>
+    <t xml:space="preserve">13.7993946075439</t>
   </si>
   <si>
     <t xml:space="preserve">13.7808952331543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629566192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5404233932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924398422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3554449081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9658756256104</t>
+    <t xml:space="preserve">13.2629556655884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5404243469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924407958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3554439544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9658737182617</t>
   </si>
   <si>
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988357543945</t>
+    <t xml:space="preserve">14.2988367080688</t>
   </si>
   <si>
     <t xml:space="preserve">14.2803373336792</t>
@@ -3623,16 +3623,16 @@
     <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1334714889526</t>
+    <t xml:space="preserve">13.1334705352783</t>
   </si>
   <si>
     <t xml:space="preserve">13.0594806671143</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4479351043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2085790634155</t>
+    <t xml:space="preserve">13.4479360580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2085781097412</t>
   </si>
   <si>
     <t xml:space="preserve">12.3935575485229</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">13.1889657974243</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4664335250854</t>
+    <t xml:space="preserve">13.4664325714111</t>
   </si>
   <si>
     <t xml:space="preserve">12.8190078735352</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">11.9126138687134</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6340293884277</t>
+    <t xml:space="preserve">12.6340284347534</t>
   </si>
   <si>
     <t xml:space="preserve">12.3380641937256</t>
@@ -3659,7 +3659,7 @@
     <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1345882415771</t>
+    <t xml:space="preserve">12.1345872879028</t>
   </si>
   <si>
     <t xml:space="preserve">11.9496097564697</t>
@@ -3674,13 +3674,13 @@
     <t xml:space="preserve">12.0051021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831287384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0235996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9681062698364</t>
+    <t xml:space="preserve">11.783127784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0236005783081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9681053161621</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
@@ -3698,7 +3698,7 @@
     <t xml:space="preserve">11.8201246261597</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4131717681885</t>
+    <t xml:space="preserve">11.4131727218628</t>
   </si>
   <si>
     <t xml:space="preserve">12.6710243225098</t>
@@ -3710,28 +3710,28 @@
     <t xml:space="preserve">12.8005104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3276977539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3646945953369</t>
+    <t xml:space="preserve">13.2259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3276987075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3646955490112</t>
   </si>
   <si>
     <t xml:space="preserve">12.7172698974609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6617765426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.430552482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4028072357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5137920379639</t>
+    <t xml:space="preserve">12.6617755889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4305534362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4028053283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5137939453125</t>
   </si>
   <si>
     <t xml:space="preserve">12.3473138809204</t>
@@ -3740,16 +3740,16 @@
     <t xml:space="preserve">12.3288145065308</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4952955245972</t>
+    <t xml:space="preserve">12.4952964782715</t>
   </si>
   <si>
     <t xml:space="preserve">12.6155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8016262054443</t>
+    <t xml:space="preserve">12.4398012161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8016271591187</t>
   </si>
   <si>
     <t xml:space="preserve">11.9958543777466</t>
@@ -3758,22 +3758,22 @@
     <t xml:space="preserve">12.3565616607666</t>
   </si>
   <si>
-    <t xml:space="preserve">11.764630317688</t>
+    <t xml:space="preserve">11.7646312713623</t>
   </si>
   <si>
     <t xml:space="preserve">11.8848676681519</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6073989868164</t>
+    <t xml:space="preserve">11.6073999404907</t>
   </si>
   <si>
     <t xml:space="preserve">11.5519046783447</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2929363250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6455106735229</t>
+    <t xml:space="preserve">11.2929353713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6455097198486</t>
   </si>
   <si>
     <t xml:space="preserve">10.7657470703125</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5704030990601</t>
+    <t xml:space="preserve">11.5704040527344</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293724060059</t>
+    <t xml:space="preserve">11.8293733596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">11.4007749557495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5605554580688</t>
+    <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
     <t xml:space="preserve">11.569953918457</t>
@@ -3806,16 +3806,16 @@
     <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432819366455</t>
+    <t xml:space="preserve">12.1432809829712</t>
   </si>
   <si>
     <t xml:space="preserve">11.85191822052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6639423370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7579298019409</t>
+    <t xml:space="preserve">11.6639413833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7579307556152</t>
   </si>
   <si>
     <t xml:space="preserve">11.974102973938</t>
@@ -3839,16 +3839,16 @@
     <t xml:space="preserve">10.5642786026001</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0530185699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5830764770508</t>
+    <t xml:space="preserve">11.053017616272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5830774307251</t>
   </si>
   <si>
     <t xml:space="preserve">10.827446937561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8838396072388</t>
+    <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
     <t xml:space="preserve">11.0248212814331</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4571666717529</t>
+    <t xml:space="preserve">11.4571676254272</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">11.4853639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3631801605225</t>
+    <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
     <t xml:space="preserve">11.6075487136841</t>
@@ -3881,10 +3881,10 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.096287727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876523971558</t>
+    <t xml:space="preserve">12.0962867736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876514434814</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">12.7636041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8481931686401</t>
+    <t xml:space="preserve">12.8481941223145</t>
   </si>
   <si>
     <t xml:space="preserve">12.998574256897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1677541732788</t>
+    <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
     <t xml:space="preserve">13.4685163497925</t>
@@ -3920,37 +3920,37 @@
     <t xml:space="preserve">13.6188974380493</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5625057220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6094970703125</t>
+    <t xml:space="preserve">13.5625047683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6094980239868</t>
   </si>
   <si>
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564922332764</t>
+    <t xml:space="preserve">13.6564931869507</t>
   </si>
   <si>
     <t xml:space="preserve">13.741081237793</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6752901077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8726654052734</t>
+    <t xml:space="preserve">13.6752910614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8726663589478</t>
   </si>
   <si>
     <t xml:space="preserve">13.6376953125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3087358474731</t>
+    <t xml:space="preserve">13.3087368011475</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1583547592163</t>
+    <t xml:space="preserve">13.158353805542</t>
   </si>
   <si>
     <t xml:space="preserve">13.336932182312</t>
@@ -3959,10 +3959,10 @@
     <t xml:space="preserve">13.2335453033447</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0925626754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0643653869629</t>
+    <t xml:space="preserve">13.0925636291504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0643663406372</t>
   </si>
   <si>
     <t xml:space="preserve">13.1113605499268</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">12.8857889175415</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5850257873535</t>
+    <t xml:space="preserve">12.5850267410278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5756282806396</t>
@@ -4007,13 +4007,13 @@
     <t xml:space="preserve">13.1207599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1056871414185</t>
+    <t xml:space="preserve">12.1056861877441</t>
   </si>
   <si>
     <t xml:space="preserve">11.8237218856812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.692138671875</t>
+    <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
     <t xml:space="preserve">11.391375541687</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000127792358</t>
+    <t xml:space="preserve">11.1000118255615</t>
   </si>
   <si>
     <t xml:space="preserve">10.5548801422119</t>
@@ -4040,16 +4040,16 @@
     <t xml:space="preserve">10.6582670211792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3951005935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9778270721436</t>
+    <t xml:space="preserve">10.3951015472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
     <t xml:space="preserve">11.4665660858154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1939992904663</t>
+    <t xml:space="preserve">11.1940002441406</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">10.9496307373047</t>
   </si>
   <si>
-    <t xml:space="preserve">10.667667388916</t>
+    <t xml:space="preserve">10.6676664352417</t>
   </si>
   <si>
     <t xml:space="preserve">10.7898502349854</t>
@@ -4094,13 +4094,13 @@
     <t xml:space="preserve">11.7485313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1150856018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244840621948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.735408782959</t>
+    <t xml:space="preserve">12.1150846481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244831085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7354078292847</t>
   </si>
   <si>
     <t xml:space="preserve">12.895188331604</t>
@@ -4115,7 +4115,7 @@
     <t xml:space="preserve">12.773003578186</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0455684661865</t>
+    <t xml:space="preserve">13.0455694198608</t>
   </si>
   <si>
     <t xml:space="preserve">13.0831651687622</t>
@@ -4151,16 +4151,16 @@
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2580184936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7504816055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2805395126343</t>
+    <t xml:space="preserve">14.258017539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170358657837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7504806518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2805404663086</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
@@ -4172,7 +4172,7 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463315963745</t>
+    <t xml:space="preserve">13.3463306427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.2523431777954</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">13.5719022750854</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3933248519897</t>
+    <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
     <t xml:space="preserve">13.2711410522461</t>
@@ -4196,7 +4196,7 @@
     <t xml:space="preserve">13.7598791122437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7316827774048</t>
+    <t xml:space="preserve">13.7316818237305</t>
   </si>
   <si>
     <t xml:space="preserve">14.0606422424316</t>
@@ -4211,58 +4211,58 @@
     <t xml:space="preserve">14.079439163208</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7786779403687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8914623260498</t>
+    <t xml:space="preserve">13.7786769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
     <t xml:space="preserve">13.4215211868286</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0888376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5587797164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7749528884888</t>
+    <t xml:space="preserve">14.0888385772705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5587787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7749519348145</t>
   </si>
   <si>
     <t xml:space="preserve">14.8407440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0193223953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0099239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6997623443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7279586791992</t>
+    <t xml:space="preserve">15.0193214416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0099229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6997632980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7279596328735</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.944130897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9347324371338</t>
+    <t xml:space="preserve">14.9441318511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9347333908081</t>
   </si>
   <si>
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031492233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7655544281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7937507629395</t>
+    <t xml:space="preserve">14.8031482696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7655534744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7937498092651</t>
   </si>
   <si>
     <t xml:space="preserve">14.6621675491333</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">14.6903638839722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689413070679</t>
+    <t xml:space="preserve">14.8689403533936</t>
   </si>
   <si>
     <t xml:space="preserve">15.1039113998413</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.3725786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9872255325317</t>
+    <t xml:space="preserve">10.9872264862061</t>
   </si>
   <si>
     <t xml:space="preserve">11.269190788269</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">11.4477691650391</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4101734161377</t>
+    <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
     <t xml:space="preserve">11.1846017837524</t>
@@ -4337,13 +4337,13 @@
     <t xml:space="preserve">11.1094102859497</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2221965789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966249465942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0812149047852</t>
+    <t xml:space="preserve">11.2221975326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966259002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0812139511108</t>
   </si>
   <si>
     <t xml:space="preserve">11.0342197418213</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">10.8744401931763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9590291976929</t>
+    <t xml:space="preserve">10.9590301513672</t>
   </si>
   <si>
     <t xml:space="preserve">10.9026374816895</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146596908569</t>
+    <t xml:space="preserve">10.7146606445312</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8650426864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4138975143433</t>
+    <t xml:space="preserve">10.8650417327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4138984680176</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387069702148</t>
@@ -5844,6 +5844,9 @@
   </si>
   <si>
     <t xml:space="preserve">10.9799995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.289999961853</t>
   </si>
 </sst>
 </file>
@@ -71468,7 +71471,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6915046296</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>99979</v>
@@ -71489,6 +71492,32 @@
         <v>1943</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6912037037</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>146647</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>11.3000001907349</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>10.8900003433228</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>10.9899997711182</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>11.289999961853</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ELN.MI.xlsx
+++ b/data/ELN.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="1952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1953" uniqueCount="1953">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,28 +53,28 @@
     <t xml:space="preserve">2.09768867492676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07379078865051</t>
+    <t xml:space="preserve">2.07379102706909</t>
   </si>
   <si>
     <t xml:space="preserve">2.02334046363831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06316947937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05254864692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.964923620224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98988354206085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96439242362976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01802968978882</t>
+    <t xml:space="preserve">2.0631697177887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05254888534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96492373943329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98988330364227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96439266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01802945137024</t>
   </si>
   <si>
     <t xml:space="preserve">2.01696729660034</t>
@@ -83,127 +83,127 @@
     <t xml:space="preserve">2.00209784507751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00156664848328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05998349189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00528407096863</t>
+    <t xml:space="preserve">2.00156688690186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05998301506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00528383255005</t>
   </si>
   <si>
     <t xml:space="preserve">2.01909160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97820007801056</t>
+    <t xml:space="preserve">1.97820031642914</t>
   </si>
   <si>
     <t xml:space="preserve">1.89854109287262</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92774939537048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93943250179291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91447257995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9330598115921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91712784767151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94633650779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95589566230774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94368100166321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09237790107727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07113528251648</t>
+    <t xml:space="preserve">1.92774951457977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93943274021149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91447281837463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93306005001068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91712808609009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94633674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95589578151703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94368159770966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09237837791443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07113575935364</t>
   </si>
   <si>
     <t xml:space="preserve">2.08441209793091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09450221061707</t>
+    <t xml:space="preserve">2.09450244903564</t>
   </si>
   <si>
     <t xml:space="preserve">2.17203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10831022262573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13964247703552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10299897193909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14442229270935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14548444747925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15345001220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14813947677612</t>
+    <t xml:space="preserve">2.10830998420715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13964223861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10299944877625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14442205429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14548420906067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15344977378845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14813923835754</t>
   </si>
   <si>
     <t xml:space="preserve">2.15132570266724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16831970214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18265819549561</t>
+    <t xml:space="preserve">2.1683201789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18265795707703</t>
   </si>
   <si>
     <t xml:space="preserve">2.22248768806458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15610551834106</t>
+    <t xml:space="preserve">2.15610504150391</t>
   </si>
   <si>
     <t xml:space="preserve">2.14495277404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12955212593079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1056547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08706784248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07219743728638</t>
+    <t xml:space="preserve">2.12955236434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10565447807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08706736564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07219767570496</t>
   </si>
   <si>
     <t xml:space="preserve">2.12158632278442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14017343521118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12424182891846</t>
+    <t xml:space="preserve">2.1401731967926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12424159049988</t>
   </si>
   <si>
     <t xml:space="preserve">2.11362028121948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06582498550415</t>
+    <t xml:space="preserve">2.06582522392273</t>
   </si>
   <si>
     <t xml:space="preserve">2.05307960510254</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">2.06848049163818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06901144981384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11840009689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12477254867554</t>
+    <t xml:space="preserve">2.06901168823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11839962005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12477278709412</t>
   </si>
   <si>
     <t xml:space="preserve">2.16141581535339</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">2.1773476600647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24373006820679</t>
+    <t xml:space="preserve">2.24373030662537</t>
   </si>
   <si>
     <t xml:space="preserve">2.25169634819031</t>
@@ -239,34 +239,34 @@
     <t xml:space="preserve">2.29418063163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2575376033783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22461199760437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21452212333679</t>
+    <t xml:space="preserve">2.25753784179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22461175918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21452164649963</t>
   </si>
   <si>
     <t xml:space="preserve">2.22514319419861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24638557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23098468780518</t>
+    <t xml:space="preserve">2.24638533592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23098492622375</t>
   </si>
   <si>
     <t xml:space="preserve">2.32073402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34888005256653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32604455947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44925045967102</t>
+    <t xml:space="preserve">2.34888052940369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32604432106018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4492506980896</t>
   </si>
   <si>
     <t xml:space="preserve">2.50288796424866</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">2.51775741577148</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5655529499054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52997136116028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6154727935791</t>
+    <t xml:space="preserve">2.56555342674255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52997183799744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61547231674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.66555047035217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66718339920044</t>
+    <t xml:space="preserve">2.66718363761902</t>
   </si>
   <si>
     <t xml:space="preserve">2.70147562026978</t>
@@ -302,10 +302,10 @@
     <t xml:space="preserve">2.79346632957458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8152391910553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95894026756287</t>
+    <t xml:space="preserve">2.81523942947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95894050598145</t>
   </si>
   <si>
     <t xml:space="preserve">2.98942232131958</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">2.84136652946472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91757225990295</t>
+    <t xml:space="preserve">2.91757202148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.90668559074402</t>
@@ -329,43 +329,43 @@
     <t xml:space="preserve">2.89797639846802</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81959366798401</t>
+    <t xml:space="preserve">2.81959390640259</t>
   </si>
   <si>
     <t xml:space="preserve">2.76516127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73685669898987</t>
+    <t xml:space="preserve">2.73685646057129</t>
   </si>
   <si>
     <t xml:space="preserve">2.69548797607422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78693437576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86531662940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98289060592651</t>
+    <t xml:space="preserve">2.78693413734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86531686782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98289036750793</t>
   </si>
   <si>
     <t xml:space="preserve">2.84789872169495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77604794502258</t>
+    <t xml:space="preserve">2.776047706604</t>
   </si>
   <si>
     <t xml:space="preserve">2.86313939094543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91974902153015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97200417518616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99159955978394</t>
+    <t xml:space="preserve">2.91974925994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972003698349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99159979820251</t>
   </si>
   <si>
     <t xml:space="preserve">2.97418165206909</t>
@@ -374,31 +374,31 @@
     <t xml:space="preserve">2.99813175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9785361289978</t>
+    <t xml:space="preserve">2.97853636741638</t>
   </si>
   <si>
     <t xml:space="preserve">3.03514575958252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04820942878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06998252868652</t>
+    <t xml:space="preserve">3.04820919036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06998229026794</t>
   </si>
   <si>
     <t xml:space="preserve">3.15707421302795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29859805107117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30730748176575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34214377403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2920663356781</t>
+    <t xml:space="preserve">3.29859781265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30730724334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34214401245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29206609725952</t>
   </si>
   <si>
     <t xml:space="preserve">3.28771185874939</t>
@@ -407,28 +407,28 @@
     <t xml:space="preserve">3.26158404350281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24416589736938</t>
+    <t xml:space="preserve">3.24416542053223</t>
   </si>
   <si>
     <t xml:space="preserve">3.28988885879517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27900266647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25722932815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26593852043152</t>
+    <t xml:space="preserve">3.27900242805481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2572295665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2659387588501</t>
   </si>
   <si>
     <t xml:space="preserve">3.17449235916138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25505208969116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25940656661987</t>
+    <t xml:space="preserve">3.25505232810974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25940680503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.33125758171082</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">3.35085344314575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34432101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32472562789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28553438186646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27247071266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35303044319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32037115097046</t>
+    <t xml:space="preserve">3.34432125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32472538948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28553462028503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27247047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35303020477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32037091255188</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682518959045</t>
@@ -461,40 +461,40 @@
     <t xml:space="preserve">3.31383895874023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30948448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15054202079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18973350524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2093288898468</t>
+    <t xml:space="preserve">3.30948424339294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15054225921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18973326683044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20932936668396</t>
   </si>
   <si>
     <t xml:space="preserve">3.25069785118103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2006196975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22239279747009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09175562858582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33343505859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26376128196716</t>
+    <t xml:space="preserve">3.20061993598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22239327430725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09175539016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33343482017517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26376175880432</t>
   </si>
   <si>
     <t xml:space="preserve">3.20497465133667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37262606620789</t>
+    <t xml:space="preserve">3.37262582778931</t>
   </si>
   <si>
     <t xml:space="preserve">3.43141293525696</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">4.09330987930298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99533152580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95831775665283</t>
+    <t xml:space="preserve">3.99533200263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95831751823425</t>
   </si>
   <si>
     <t xml:space="preserve">4.11508321762085</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">4.19346523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33716630935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23483371734619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26313829421997</t>
+    <t xml:space="preserve">4.33716583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23483419418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26313877105713</t>
   </si>
   <si>
     <t xml:space="preserve">4.47433567047119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68988847732544</t>
+    <t xml:space="preserve">4.6898889541626</t>
   </si>
   <si>
     <t xml:space="preserve">4.65722846984863</t>
@@ -551,28 +551,28 @@
     <t xml:space="preserve">4.64634275436401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75956153869629</t>
+    <t xml:space="preserve">4.75956106185913</t>
   </si>
   <si>
     <t xml:space="preserve">4.95334005355835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94245433807373</t>
+    <t xml:space="preserve">4.94245386123657</t>
   </si>
   <si>
     <t xml:space="preserve">4.72037029266357</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74214363098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73778820037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64416456222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57231378555298</t>
+    <t xml:space="preserve">4.74214315414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73778867721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64416551589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57231426239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.37418031692505</t>
@@ -584,49 +584,49 @@
     <t xml:space="preserve">4.34152030944824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22830104827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19128847122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08895540237427</t>
+    <t xml:space="preserve">4.22830152511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19128799438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08895444869995</t>
   </si>
   <si>
     <t xml:space="preserve">4.22612428665161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24572038650513</t>
+    <t xml:space="preserve">4.24571990966797</t>
   </si>
   <si>
     <t xml:space="preserve">4.36547088623047</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35458517074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33934354782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65940570831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63763284683228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63545513153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6158595085144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64851951599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72254705429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59408760070801</t>
+    <t xml:space="preserve">4.35458469390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3393440246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65940523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63763236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63545656204224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61585998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64851903915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72254753112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59408664703369</t>
   </si>
   <si>
     <t xml:space="preserve">4.6637601852417</t>
@@ -635,55 +635,55 @@
     <t xml:space="preserve">4.58973264694214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51135015487671</t>
+    <t xml:space="preserve">4.51134967803955</t>
   </si>
   <si>
     <t xml:space="preserve">4.5244140625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73343372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64198780059814</t>
+    <t xml:space="preserve">4.73343467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64198732376099</t>
   </si>
   <si>
     <t xml:space="preserve">4.78568887710571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77480173110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74649715423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7660927772522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09921836853027</t>
+    <t xml:space="preserve">4.77480220794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74649667739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76609373092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09921884536743</t>
   </si>
   <si>
     <t xml:space="preserve">5.38662147521973</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29082012176514</t>
+    <t xml:space="preserve">5.29082059860229</t>
   </si>
   <si>
     <t xml:space="preserve">5.25162935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22985696792603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22767925262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20372915267944</t>
+    <t xml:space="preserve">5.22985649108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22767877578735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20372867584229</t>
   </si>
   <si>
     <t xml:space="preserve">5.03607749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11010503768921</t>
+    <t xml:space="preserve">5.11010551452637</t>
   </si>
   <si>
     <t xml:space="preserve">5.22550201416016</t>
@@ -692,82 +692,82 @@
     <t xml:space="preserve">5.27557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31041669845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17107009887695</t>
+    <t xml:space="preserve">5.31041622161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17106962203979</t>
   </si>
   <si>
     <t xml:space="preserve">5.14494180679321</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06220483779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90979433059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09050893783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04043197631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11445951461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1013970375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09268665313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12752342224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11663770675659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04478740692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02736806869507</t>
+    <t xml:space="preserve">5.06220531463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90979337692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09050941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0404314994812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11446094512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10139656066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09268712997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12752389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11663722991943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04478645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95769453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02736854553223</t>
   </si>
   <si>
     <t xml:space="preserve">4.98817682266235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88584470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8662486076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85536241531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8466534614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8009295463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73561143875122</t>
+    <t xml:space="preserve">4.88584423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86624813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8553614616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84665250778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80092859268188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73561096191406</t>
   </si>
   <si>
     <t xml:space="preserve">4.79004335403442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74432039260864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75738382339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68117904663086</t>
+    <t xml:space="preserve">4.7443208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75738430023193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6811785697937</t>
   </si>
   <si>
     <t xml:space="preserve">4.82052564620972</t>
@@ -782,49 +782,49 @@
     <t xml:space="preserve">5.08397817611694</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19719743728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11881399154663</t>
+    <t xml:space="preserve">5.19719791412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11881494522095</t>
   </si>
   <si>
     <t xml:space="preserve">5.09486389160156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30170726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38444375991821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41710329055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55209589004517</t>
+    <t xml:space="preserve">5.30170679092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38444423675537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41710376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55209541320801</t>
   </si>
   <si>
     <t xml:space="preserve">5.68273305892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63918733596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84385299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91134881973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94400835037231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11383771896362</t>
+    <t xml:space="preserve">5.63918781280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84385347366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91134834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.944007396698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11383676528931</t>
   </si>
   <si>
     <t xml:space="preserve">5.81337118148804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87868928909302</t>
+    <t xml:space="preserve">5.87868881225586</t>
   </si>
   <si>
     <t xml:space="preserve">5.75893878936768</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">5.88957595825195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89610767364502</t>
+    <t xml:space="preserve">5.89610815048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.97666788101196</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09641885757446</t>
+    <t xml:space="preserve">6.0964183807373</t>
   </si>
   <si>
     <t xml:space="preserve">5.94836330413818</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">6.00497245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98755407333374</t>
+    <t xml:space="preserve">5.98755359649658</t>
   </si>
   <si>
     <t xml:space="preserve">6.0419864654541</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">6.05722761154175</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08335494995117</t>
+    <t xml:space="preserve">6.08335542678833</t>
   </si>
   <si>
     <t xml:space="preserve">5.96360397338867</t>
@@ -872,43 +872,43 @@
     <t xml:space="preserve">6.07464599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13996505737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42301225662231</t>
+    <t xml:space="preserve">6.13996458053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42301273345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.26842498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52970027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54276275634766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58848714828491</t>
+    <t xml:space="preserve">6.52969980239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54276323318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58848667144775</t>
   </si>
   <si>
     <t xml:space="preserve">6.80403900146484</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90201759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01088237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06531429290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11756896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3200569152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13063335418701</t>
+    <t xml:space="preserve">6.90201711654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01088190078735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06531381607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1175684928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32005739212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13063287734985</t>
   </si>
   <si>
     <t xml:space="preserve">7.22425651550293</t>
@@ -926,64 +926,64 @@
     <t xml:space="preserve">7.37666702270508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36360359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28522109985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30481576919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19595098495483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46655893325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22705698013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309017181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4012393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61243724822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49704122543335</t>
+    <t xml:space="preserve">7.36360311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28522062301636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3048152923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19595050811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4665584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2270565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40123987197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61243772506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49703979492188</t>
   </si>
   <si>
     <t xml:space="preserve">6.52316808700562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57760047912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52464485168457</t>
+    <t xml:space="preserve">6.57759952545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52464437484741</t>
   </si>
   <si>
     <t xml:space="preserve">6.56215476989746</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61290454864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.54891633987427</t>
+    <t xml:space="preserve">6.61290407180786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54891586303711</t>
   </si>
   <si>
     <t xml:space="preserve">6.45403623580933</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55774164199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91740274429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76294660568237</t>
+    <t xml:space="preserve">6.55774116516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91740322113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76294708251953</t>
   </si>
   <si>
     <t xml:space="preserve">6.82252264022827</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">6.41652536392212</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58421993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50478506088257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42093849182129</t>
+    <t xml:space="preserve">6.58421897888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50478601455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42093801498413</t>
   </si>
   <si>
     <t xml:space="preserve">6.48713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35694932937622</t>
+    <t xml:space="preserve">6.35694980621338</t>
   </si>
   <si>
     <t xml:space="preserve">6.33488416671753</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">6.32826471328735</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33267879486084</t>
+    <t xml:space="preserve">6.33267831802368</t>
   </si>
   <si>
     <t xml:space="preserve">6.37460136413574</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16057014465332</t>
+    <t xml:space="preserve">6.16057062149048</t>
   </si>
   <si>
     <t xml:space="preserve">6.1429181098938</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">6.13850545883179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95757150650024</t>
+    <t xml:space="preserve">5.95757102966309</t>
   </si>
   <si>
     <t xml:space="preserve">5.91344165802002</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90240907669067</t>
+    <t xml:space="preserve">5.90240859985352</t>
   </si>
   <si>
     <t xml:space="preserve">5.93771362304688</t>
@@ -1052,13 +1052,13 @@
     <t xml:space="preserve">5.9200611114502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93329954147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94212675094604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83621311187744</t>
+    <t xml:space="preserve">5.93330001831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94212627410889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8362135887146</t>
   </si>
   <si>
     <t xml:space="preserve">5.84724617004395</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">5.98846292495728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69720315933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50744390487671</t>
+    <t xml:space="preserve">5.69720363616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50744342803955</t>
   </si>
   <si>
     <t xml:space="preserve">5.46993350982666</t>
@@ -1079,55 +1079,55 @@
     <t xml:space="preserve">5.60894298553467</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7369213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76119327545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89137697219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71485567092896</t>
+    <t xml:space="preserve">5.73692083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7611927986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89137649536133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71485614776611</t>
   </si>
   <si>
     <t xml:space="preserve">5.72147512435913</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59129190444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55819368362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.38608694076538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54495477676392</t>
+    <t xml:space="preserve">5.5912914276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55819416046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.38608598709106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54495429992676</t>
   </si>
   <si>
     <t xml:space="preserve">5.44345569610596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45007467269897</t>
+    <t xml:space="preserve">5.45007514953613</t>
   </si>
   <si>
     <t xml:space="preserve">5.39932489395142</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41918325424194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49199819564819</t>
+    <t xml:space="preserve">5.41918277740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">5.56040048599243</t>
   </si>
   <si>
-    <t xml:space="preserve">5.48096561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52730274200439</t>
+    <t xml:space="preserve">5.48096609115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52730226516724</t>
   </si>
   <si>
     <t xml:space="preserve">5.45890092849731</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">5.48979187011719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56922626495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73912763595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66410636901855</t>
+    <t xml:space="preserve">5.56922674179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73912715911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6641058921814</t>
   </si>
   <si>
     <t xml:space="preserve">5.80311584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86931180953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73030185699463</t>
+    <t xml:space="preserve">5.86931133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73030090332031</t>
   </si>
   <si>
     <t xml:space="preserve">6.08554935455322</t>
@@ -1163,34 +1163,34 @@
     <t xml:space="preserve">5.96860408782959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80532264709473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63762855529785</t>
+    <t xml:space="preserve">5.80532217025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63762760162354</t>
   </si>
   <si>
     <t xml:space="preserve">5.56481313705444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52068328857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47875928878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.49420547485352</t>
+    <t xml:space="preserve">5.52068281173706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.478759765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.49420499801636</t>
   </si>
   <si>
     <t xml:space="preserve">5.36181449890137</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29782581329346</t>
+    <t xml:space="preserve">5.2978253364563</t>
   </si>
   <si>
     <t xml:space="preserve">5.22942447662354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24045705795288</t>
+    <t xml:space="preserve">5.24045658111572</t>
   </si>
   <si>
     <t xml:space="preserve">5.25369548797607</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">5.41477108001709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.39711856842041</t>
+    <t xml:space="preserve">5.39711809158325</t>
   </si>
   <si>
     <t xml:space="preserve">5.27796745300293</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">5.11909914016724</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20735931396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16764116287231</t>
+    <t xml:space="preserve">5.20735883712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16764163970947</t>
   </si>
   <si>
     <t xml:space="preserve">5.13233757019043</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">5.00656747817993</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96464252471924</t>
+    <t xml:space="preserve">4.96464347839355</t>
   </si>
   <si>
     <t xml:space="preserve">4.95802307128906</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">5.04849004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19411993026733</t>
+    <t xml:space="preserve">5.19412040710449</t>
   </si>
   <si>
     <t xml:space="preserve">5.27576065063477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22501087188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24486923217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11689233779907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03083848953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87196969985962</t>
+    <t xml:space="preserve">5.22501134872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24486970901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11689186096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03083801269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87197017669678</t>
   </si>
   <si>
     <t xml:space="preserve">4.72633981704712</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">4.9315447807312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21839094161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6045298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81194162368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84503984451294</t>
+    <t xml:space="preserve">5.21839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60453033447266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81194257736206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8450403213501</t>
   </si>
   <si>
     <t xml:space="preserve">5.76781177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90461540222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86489820480347</t>
+    <t xml:space="preserve">5.90461587905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86489868164062</t>
   </si>
   <si>
     <t xml:space="preserve">5.77663850784302</t>
@@ -1307,22 +1307,22 @@
     <t xml:space="preserve">5.65307378768921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63983488082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69940996170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58467102050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02376699447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06348323822021</t>
+    <t xml:space="preserve">5.6398344039917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6994104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58467149734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02376556396484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19366884231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06348419189453</t>
   </si>
   <si>
     <t xml:space="preserve">6.14071178436279</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">6.12526607513428</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02597332000732</t>
+    <t xml:space="preserve">6.02597284317017</t>
   </si>
   <si>
     <t xml:space="preserve">5.96419191360474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03480005264282</t>
+    <t xml:space="preserve">6.03479909896851</t>
   </si>
   <si>
     <t xml:space="preserve">5.8097357749939</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">5.90020275115967</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82518148422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74353981018066</t>
+    <t xml:space="preserve">5.82518100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74354028701782</t>
   </si>
   <si>
     <t xml:space="preserve">5.6508674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61777019500732</t>
+    <t xml:space="preserve">5.61776924133301</t>
   </si>
   <si>
     <t xml:space="preserve">5.63542175292969</t>
@@ -1367,16 +1367,16 @@
     <t xml:space="preserve">6.01935386657715</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85607242584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71926832199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84283304214478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03259372711182</t>
+    <t xml:space="preserve">5.85607290267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71926879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84283351898193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0325927734375</t>
   </si>
   <si>
     <t xml:space="preserve">6.04583168029785</t>
@@ -1385,10 +1385,10 @@
     <t xml:space="preserve">5.95315837860107</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94433307647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28854846954346</t>
+    <t xml:space="preserve">5.94433259963989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2885479927063</t>
   </si>
   <si>
     <t xml:space="preserve">6.28413534164429</t>
@@ -1397,43 +1397,43 @@
     <t xml:space="preserve">6.22235250473022</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52243804931641</t>
+    <t xml:space="preserve">6.52243757247925</t>
   </si>
   <si>
     <t xml:space="preserve">6.37239456176758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16939687728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09878778457642</t>
+    <t xml:space="preserve">6.16939640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09878826141357</t>
   </si>
   <si>
     <t xml:space="preserve">6.08996200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55598783493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11202764511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92226791381836</t>
+    <t xml:space="preserve">5.55598735809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11202716827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92226839065552</t>
   </si>
   <si>
     <t xml:space="preserve">5.79429006576538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67072582244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68396520614624</t>
+    <t xml:space="preserve">5.67072534561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68396472930908</t>
   </si>
   <si>
     <t xml:space="preserve">5.42800951004028</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76339960098267</t>
+    <t xml:space="preserve">5.76339864730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.87372446060181</t>
@@ -1442,46 +1442,46 @@
     <t xml:space="preserve">5.97963619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96198511123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27089643478394</t>
+    <t xml:space="preserve">5.96198415756226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17822217941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27089595794678</t>
   </si>
   <si>
     <t xml:space="preserve">6.35474348068237</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72543668746948</t>
+    <t xml:space="preserve">6.72543716430664</t>
   </si>
   <si>
     <t xml:space="preserve">6.68571901321411</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92843532562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90637016296387</t>
+    <t xml:space="preserve">6.9284348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90636968612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.10495615005493</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97697877883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10054302215576</t>
+    <t xml:space="preserve">6.97697830200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10054349899292</t>
   </si>
   <si>
     <t xml:space="preserve">6.87106609344482</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95050048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22852087020874</t>
+    <t xml:space="preserve">6.95050001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22851991653442</t>
   </si>
   <si>
     <t xml:space="preserve">7.14908599853516</t>
@@ -1496,70 +1496,70 @@
     <t xml:space="preserve">7.06082534790039</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4933009147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32560777664185</t>
+    <t xml:space="preserve">7.49330043792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32560682296753</t>
   </si>
   <si>
     <t xml:space="preserve">7.18439102172852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.440345287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2814769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25941181182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12260770797729</t>
+    <t xml:space="preserve">7.44034624099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28147649765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25941133499146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12260818481445</t>
   </si>
   <si>
     <t xml:space="preserve">7.06523847579956</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25058507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21528100967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21969413757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46241092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62128019332886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56390953063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53743124008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55508470535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42710638046265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38738870620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06965208053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62835025787354</t>
+    <t xml:space="preserve">7.25058555603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21528148651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2196946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46241044998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6212797164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56391048431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53743076324463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40062761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55508422851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42710590362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38738918304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06965160369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62834978103638</t>
   </si>
   <si>
     <t xml:space="preserve">6.84017467498779</t>
@@ -1571,16 +1571,16 @@
     <t xml:space="preserve">6.51802492141724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61952352523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5445032119751</t>
+    <t xml:space="preserve">6.6195240020752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.54450273513794</t>
   </si>
   <si>
     <t xml:space="preserve">6.71219730377197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38247346878052</t>
+    <t xml:space="preserve">6.38247394561768</t>
   </si>
   <si>
     <t xml:space="preserve">6.30643892288208</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">6.66425037384033</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60163307189941</t>
+    <t xml:space="preserve">6.60163354873657</t>
   </si>
   <si>
     <t xml:space="preserve">6.63294172286987</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">6.54796171188354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6597785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57926988601685</t>
+    <t xml:space="preserve">6.65977811813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.579270362854</t>
   </si>
   <si>
     <t xml:space="preserve">6.48534440994263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71344947814941</t>
+    <t xml:space="preserve">6.71344995498657</t>
   </si>
   <si>
     <t xml:space="preserve">6.75370359420776</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">6.75817584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61505222320557</t>
+    <t xml:space="preserve">6.61505174636841</t>
   </si>
   <si>
     <t xml:space="preserve">6.49428987503052</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48087215423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44956302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41825437545776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31985712051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22593116760254</t>
+    <t xml:space="preserve">6.48087167739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44956350326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41825485229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3198561668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22593069076538</t>
   </si>
   <si>
     <t xml:space="preserve">6.22145795822144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12305974960327</t>
+    <t xml:space="preserve">6.12305927276611</t>
   </si>
   <si>
     <t xml:space="preserve">6.26171159744263</t>
@@ -1655,7 +1655,7 @@
     <t xml:space="preserve">6.18120384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20356702804565</t>
+    <t xml:space="preserve">6.20356750488281</t>
   </si>
   <si>
     <t xml:space="preserve">6.34669256210327</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">6.24829387664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21251344680786</t>
+    <t xml:space="preserve">6.2125129699707</t>
   </si>
   <si>
     <t xml:space="preserve">6.33774709701538</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">6.58821535110474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48981714248657</t>
+    <t xml:space="preserve">6.48981761932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.53007125854492</t>
@@ -1685,16 +1685,16 @@
     <t xml:space="preserve">6.44509077072144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39141941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40036392211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37352800369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42719984054565</t>
+    <t xml:space="preserve">6.39141893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4003643989563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37352848052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42720031738281</t>
   </si>
   <si>
     <t xml:space="preserve">6.43167304992676</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">6.32880163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23934841156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19014978408813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27960252761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4629807472229</t>
+    <t xml:space="preserve">6.23934888839722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19014930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27960300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46298122406006</t>
   </si>
   <si>
     <t xml:space="preserve">6.64188718795776</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1006965637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3958911895752</t>
+    <t xml:space="preserve">6.10069608688354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39589166641235</t>
   </si>
   <si>
     <t xml:space="preserve">6.18567657470703</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">5.3358736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24194717407227</t>
+    <t xml:space="preserve">5.24194765090942</t>
   </si>
   <si>
     <t xml:space="preserve">5.08093214035034</t>
@@ -1751,25 +1751,25 @@
     <t xml:space="preserve">5.13013124465942</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01831531524658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07645893096924</t>
+    <t xml:space="preserve">5.01831436157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07645988464355</t>
   </si>
   <si>
     <t xml:space="preserve">5.05409622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92886257171631</t>
+    <t xml:space="preserve">4.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92886209487915</t>
   </si>
   <si>
     <t xml:space="preserve">4.73653793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58894062042236</t>
+    <t xml:space="preserve">4.58894109725952</t>
   </si>
   <si>
     <t xml:space="preserve">4.61577606201172</t>
@@ -1778,28 +1778,28 @@
     <t xml:space="preserve">4.74995565414429</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71417474746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37201642990112</t>
+    <t xml:space="preserve">4.71417427062988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37201690673828</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825727462769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20876455307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11483860015869</t>
+    <t xml:space="preserve">4.20876550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11483907699585</t>
   </si>
   <si>
     <t xml:space="preserve">4.04104089736938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0544581413269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829677581787</t>
+    <t xml:space="preserve">4.05445861816406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829606056213</t>
   </si>
   <si>
     <t xml:space="preserve">4.08353090286255</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">4.15509271621704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1304931640625</t>
+    <t xml:space="preserve">4.13049364089966</t>
   </si>
   <si>
     <t xml:space="preserve">4.01867723464966</t>
@@ -1817,46 +1817,46 @@
     <t xml:space="preserve">3.8688428401947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70559167861938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75702714920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81740760803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73466396331787</t>
+    <t xml:space="preserve">3.70559144020081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75702691078186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81740784645081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73466444015503</t>
   </si>
   <si>
     <t xml:space="preserve">3.8375346660614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84648036956787</t>
+    <t xml:space="preserve">3.84648013114929</t>
   </si>
   <si>
     <t xml:space="preserve">3.96500539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15732955932617</t>
+    <t xml:space="preserve">4.15733003616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.00302267074585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92475128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93146014213562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94264221191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87331604957581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86213421821594</t>
+    <t xml:space="preserve">3.9247510433197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314603805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94264149665833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87331581115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8621346950531</t>
   </si>
   <si>
     <t xml:space="preserve">3.8442440032959</t>
@@ -1865,43 +1865,43 @@
     <t xml:space="preserve">3.45512294769287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35896110534668</t>
+    <t xml:space="preserve">3.35896134376526</t>
   </si>
   <si>
     <t xml:space="preserve">3.24267220497131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03245759010315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04140281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16216444969177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38356113433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38803291320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26950788497925</t>
+    <t xml:space="preserve">3.03245782852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04140305519104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16216468811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38356065750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38803315162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26950836181641</t>
   </si>
   <si>
     <t xml:space="preserve">3.22701811790466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45288681983948</t>
+    <t xml:space="preserve">3.4528865814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.3947422504425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4886679649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51550388336182</t>
+    <t xml:space="preserve">3.48866820335388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5155041217804</t>
   </si>
   <si>
     <t xml:space="preserve">3.31870722770691</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">3.11072897911072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92735028266907</t>
+    <t xml:space="preserve">2.92735052108765</t>
   </si>
   <si>
     <t xml:space="preserve">2.93182277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01009440422058</t>
+    <t xml:space="preserve">3.010094165802</t>
   </si>
   <si>
     <t xml:space="preserve">3.10402011871338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03916692733765</t>
+    <t xml:space="preserve">3.03916668891907</t>
   </si>
   <si>
     <t xml:space="preserve">2.95642256736755</t>
@@ -1934,13 +1934,13 @@
     <t xml:space="preserve">2.88485980033875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92511415481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77751636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74844431877136</t>
+    <t xml:space="preserve">2.92511391639709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77751660346985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7484438419342</t>
   </si>
   <si>
     <t xml:space="preserve">2.78869819641113</t>
@@ -1949,13 +1949,13 @@
     <t xml:space="preserve">2.83342480659485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88933277130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0727117061615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10625672340393</t>
+    <t xml:space="preserve">2.88933253288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07271122932434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10625648498535</t>
   </si>
   <si>
     <t xml:space="preserve">3.16887354850769</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">3.22925424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15992856025696</t>
+    <t xml:space="preserve">3.1599280834198</t>
   </si>
   <si>
     <t xml:space="preserve">3.22254538536072</t>
@@ -1973,40 +1973,40 @@
     <t xml:space="preserve">3.23596334457397</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18676400184631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19347286224365</t>
+    <t xml:space="preserve">3.18676424026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19347310066223</t>
   </si>
   <si>
     <t xml:space="preserve">3.32094359397888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54234027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47972249984741</t>
+    <t xml:space="preserve">3.54233980178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47972273826599</t>
   </si>
   <si>
     <t xml:space="preserve">3.53339457511902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49537682533264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61166572570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66533756256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57588481903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51103091239929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52221274375916</t>
+    <t xml:space="preserve">3.4953773021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61166596412659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66533780097961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57588458061218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51103115081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52221298217773</t>
   </si>
   <si>
     <t xml:space="preserve">3.5825936794281</t>
@@ -2015,25 +2015,25 @@
     <t xml:space="preserve">3.43723249435425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52444911003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58483052253723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69441032409668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62284755706787</t>
+    <t xml:space="preserve">3.52444934844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58483004570007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6944100856781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62284779548645</t>
   </si>
   <si>
     <t xml:space="preserve">3.61390233039856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70335507392883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80399012565613</t>
+    <t xml:space="preserve">3.70335531234741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80398964881897</t>
   </si>
   <si>
     <t xml:space="preserve">3.89567899703979</t>
@@ -2042,112 +2042,112 @@
     <t xml:space="preserve">3.77268147468567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83306241035461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85766172409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94040584564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99184203147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07011270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13272953033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09247589111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25125455856323</t>
+    <t xml:space="preserve">3.83306217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.857661485672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94040560722351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9918417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07011318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13273048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09247636795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25125503540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.18863773345947</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94935131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00525951385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02762222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97842335700989</t>
+    <t xml:space="preserve">3.9493510723114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00525999069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02762317657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97842311859131</t>
   </si>
   <si>
     <t xml:space="preserve">4.23112821578979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28256320953369</t>
+    <t xml:space="preserve">4.28256368637085</t>
   </si>
   <si>
     <t xml:space="preserve">4.38319826126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42792463302612</t>
+    <t xml:space="preserve">4.42792510986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.3541259765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1662745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20429229736328</t>
+    <t xml:space="preserve">4.16627407073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20429277420044</t>
   </si>
   <si>
     <t xml:space="preserve">4.2780909538269</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20205593109131</t>
+    <t xml:space="preserve">4.20205640792847</t>
   </si>
   <si>
     <t xml:space="preserve">4.23783731460571</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2915096282959</t>
+    <t xml:space="preserve">4.29150915145874</t>
   </si>
   <si>
     <t xml:space="preserve">4.24901866912842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24007368087769</t>
+    <t xml:space="preserve">4.24007320404053</t>
   </si>
   <si>
     <t xml:space="preserve">4.25349187850952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19981956481934</t>
+    <t xml:space="preserve">4.19982004165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.07458543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15285682678223</t>
+    <t xml:space="preserve">4.15285730361938</t>
   </si>
   <si>
     <t xml:space="preserve">4.1864013671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26914548873901</t>
+    <t xml:space="preserve">4.26914596557617</t>
   </si>
   <si>
     <t xml:space="preserve">3.97171473503113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93369674682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90015196800232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99631404876709</t>
+    <t xml:space="preserve">3.93369698524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9001522064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99631452560425</t>
   </si>
   <si>
     <t xml:space="preserve">4.03880405426025</t>
@@ -2159,25 +2159,25 @@
     <t xml:space="preserve">4.01644086837769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91804265975952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87778902053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76820850372314</t>
+    <t xml:space="preserve">3.91804242134094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87778854370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76820874214172</t>
   </si>
   <si>
     <t xml:space="preserve">3.77491760253906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65191984176636</t>
+    <t xml:space="preserve">3.65191960334778</t>
   </si>
   <si>
     <t xml:space="preserve">3.85095286369324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09918451309204</t>
+    <t xml:space="preserve">4.0991849899292</t>
   </si>
   <si>
     <t xml:space="preserve">3.82411670684814</t>
@@ -2186,19 +2186,19 @@
     <t xml:space="preserve">3.95693111419678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88136458396912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76229000091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74626064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76458024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68901371955872</t>
+    <t xml:space="preserve">3.88136434555054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76229023933411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74626088142395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7645800113678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68901348114014</t>
   </si>
   <si>
     <t xml:space="preserve">3.67298436164856</t>
@@ -2207,22 +2207,22 @@
     <t xml:space="preserve">3.73252129554749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84243679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87220454216003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92487263679504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96609020233154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89739322662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95006108283997</t>
+    <t xml:space="preserve">3.84243631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87220478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92487239837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96608948707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89739346504211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95006060600281</t>
   </si>
   <si>
     <t xml:space="preserve">3.8744945526123</t>
@@ -2231,22 +2231,22 @@
     <t xml:space="preserve">3.90655303001404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98440933227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04165697097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19736909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1538610458374</t>
+    <t xml:space="preserve">3.98440957069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04165601730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19736862182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15386152267456</t>
   </si>
   <si>
     <t xml:space="preserve">4.09203386306763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11264324188232</t>
+    <t xml:space="preserve">4.11264228820801</t>
   </si>
   <si>
     <t xml:space="preserve">4.10119390487671</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">4.27751541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28438520431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31415319442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40803956985474</t>
+    <t xml:space="preserve">4.28438472747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31415414810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40803909301758</t>
   </si>
   <si>
     <t xml:space="preserve">4.30270433425903</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">4.3324728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23858690261841</t>
+    <t xml:space="preserve">4.23858737945557</t>
   </si>
   <si>
     <t xml:space="preserve">4.22255754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19507932662964</t>
+    <t xml:space="preserve">4.19507884979248</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774694442749</t>
@@ -2300,10 +2300,10 @@
     <t xml:space="preserve">4.05997562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09890365600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15157079696655</t>
+    <t xml:space="preserve">4.09890413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15157127380371</t>
   </si>
   <si>
     <t xml:space="preserve">4.16302061080933</t>
@@ -2312,46 +2312,46 @@
     <t xml:space="preserve">4.11035346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12409257888794</t>
+    <t xml:space="preserve">4.12409210205078</t>
   </si>
   <si>
     <t xml:space="preserve">4.07600450515747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00730800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05539608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97067046165466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.945481300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84701609611511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88594436645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.876784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85159540176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95235085487366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00043821334839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98211932182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13096284866333</t>
+    <t xml:space="preserve">4.00730848312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05539512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97066974639893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94548082351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84701585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88594388961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87678408622742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85159587860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95235133171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00043869018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98211908340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13096237182617</t>
   </si>
   <si>
     <t xml:space="preserve">4.11493301391602</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">4.04394626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0531063079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18592023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1355414390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06226539611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34392213821411</t>
+    <t xml:space="preserve">4.05310583114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18591928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13554191589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06226634979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34392166137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.33705282211304</t>
@@ -2384,25 +2384,25 @@
     <t xml:space="preserve">4.31873369216919</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60268020629883</t>
+    <t xml:space="preserve">4.60267972946167</t>
   </si>
   <si>
     <t xml:space="preserve">5.00112104415894</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17515277862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33086490631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35834360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62855100631714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.48657703399658</t>
+    <t xml:space="preserve">5.17515230178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33086538314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35834312438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62855052947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.48657751083374</t>
   </si>
   <si>
     <t xml:space="preserve">5.39040231704712</t>
@@ -2414,10 +2414,10 @@
     <t xml:space="preserve">5.70640659332275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55527448654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45451879501343</t>
+    <t xml:space="preserve">5.55527496337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45451927185059</t>
   </si>
   <si>
     <t xml:space="preserve">5.48199796676636</t>
@@ -2426,25 +2426,25 @@
     <t xml:space="preserve">5.26674795150757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.27590751647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.36292314529419</t>
+    <t xml:space="preserve">5.27590799331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36292362213135</t>
   </si>
   <si>
     <t xml:space="preserve">5.44993925094604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3446044921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47283792495728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45909881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55985403060913</t>
+    <t xml:space="preserve">5.34460496902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47283840179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45909833908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55985450744629</t>
   </si>
   <si>
     <t xml:space="preserve">5.69724750518799</t>
@@ -2453,34 +2453,34 @@
     <t xml:space="preserve">5.7293062210083</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92623662948608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74304580688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77968311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72472620010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67892837524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71556663513184</t>
+    <t xml:space="preserve">5.92623615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74304533004761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7796835899353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72472667694092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67892789840698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71556615829468</t>
   </si>
   <si>
     <t xml:space="preserve">5.80716276168823</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71098756790161</t>
+    <t xml:space="preserve">5.71098661422729</t>
   </si>
   <si>
     <t xml:space="preserve">5.82090139389038</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89875841140747</t>
+    <t xml:space="preserve">5.89875793457031</t>
   </si>
   <si>
     <t xml:space="preserve">6.04989099502563</t>
@@ -2492,43 +2492,43 @@
     <t xml:space="preserve">6.22392225265503</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08652877807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99493312835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02241182327271</t>
+    <t xml:space="preserve">6.08652925491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99493265151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02241134643555</t>
   </si>
   <si>
     <t xml:space="preserve">6.24224090576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71395874023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10324048995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19941568374634</t>
+    <t xml:space="preserve">6.71395826339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10324001312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19941520690918</t>
   </si>
   <si>
     <t xml:space="preserve">7.28643131256104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61159563064575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61617565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71235179901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83600616455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67113304138184</t>
+    <t xml:space="preserve">7.61159610748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61617469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71235132217407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83600568771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67113351821899</t>
   </si>
   <si>
     <t xml:space="preserve">7.6253342628479</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">7.16735696792603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28185176849365</t>
+    <t xml:space="preserve">7.28185129165649</t>
   </si>
   <si>
     <t xml:space="preserve">7.41924524307251</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">7.35512781143188</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29101085662842</t>
+    <t xml:space="preserve">7.29101133346558</t>
   </si>
   <si>
     <t xml:space="preserve">7.27727174758911</t>
@@ -2564,25 +2564,25 @@
     <t xml:space="preserve">7.39634609222412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37802743911743</t>
+    <t xml:space="preserve">7.37802696228027</t>
   </si>
   <si>
     <t xml:space="preserve">7.57495737075806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91844129562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8589038848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67571258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56579875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66655397415161</t>
+    <t xml:space="preserve">7.91844081878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85890340805054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67571306228638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56579828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66655349731445</t>
   </si>
   <si>
     <t xml:space="preserve">7.36428737640381</t>
@@ -2591,31 +2591,31 @@
     <t xml:space="preserve">7.45130395889282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12155914306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41466569900513</t>
+    <t xml:space="preserve">7.12155961990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41466522216797</t>
   </si>
   <si>
     <t xml:space="preserve">7.25895261764526</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30474996566772</t>
+    <t xml:space="preserve">7.30475044250488</t>
   </si>
   <si>
     <t xml:space="preserve">7.22231483459473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52916049957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43756437301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48794221878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51999950408936</t>
+    <t xml:space="preserve">7.5291600227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43756341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48794174194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51999998092651</t>
   </si>
   <si>
     <t xml:space="preserve">7.31848955154419</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">7.17651653289795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02996349334717</t>
+    <t xml:space="preserve">7.02996397018433</t>
   </si>
   <si>
     <t xml:space="preserve">6.51244878768921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51702833175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7414379119873</t>
+    <t xml:space="preserve">6.51702785491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74143743515015</t>
   </si>
   <si>
     <t xml:space="preserve">6.79639482498169</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">6.76891613006592</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6177830696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02538394927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89257049560547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89715003967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82845306396484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80097484588623</t>
+    <t xml:space="preserve">6.61778354644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02538347244263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89257001876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89715051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.828453540802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80097436904907</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732048034668</t>
@@ -2681,7 +2681,7 @@
     <t xml:space="preserve">5.96745443344116</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78884363174438</t>
+    <t xml:space="preserve">5.78884267807007</t>
   </si>
   <si>
     <t xml:space="preserve">5.63771057128906</t>
@@ -2696,76 +2696,76 @@
     <t xml:space="preserve">5.47741842269897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11561489105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75381231307983</t>
+    <t xml:space="preserve">5.1156153678894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75381278991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.59809970855713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63931846618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21110820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81495785713196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66382479667664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32034134864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22416567802429</t>
+    <t xml:space="preserve">4.63931798934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21110868453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8149573802948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66382455825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32034111022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22416591644287</t>
   </si>
   <si>
     <t xml:space="preserve">3.18294763565063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22645592689514</t>
+    <t xml:space="preserve">3.22645568847656</t>
   </si>
   <si>
     <t xml:space="preserve">3.44399523735046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99356889724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86304521560669</t>
+    <t xml:space="preserve">3.99356937408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86304569244385</t>
   </si>
   <si>
     <t xml:space="preserve">3.61344742774963</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50353264808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069458961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61802697181702</t>
+    <t xml:space="preserve">3.50353240966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069435119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61802673339844</t>
   </si>
   <si>
     <t xml:space="preserve">3.70962262153625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6226065158844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79663848876953</t>
+    <t xml:space="preserve">3.62260675430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79663825035095</t>
   </si>
   <si>
     <t xml:space="preserve">3.74168086051941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06684541702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03020763397217</t>
+    <t xml:space="preserve">4.06684589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03020715713501</t>
   </si>
   <si>
     <t xml:space="preserve">4.3828501701355</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">4.11722326278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01188802719116</t>
+    <t xml:space="preserve">4.01188850402832</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218065261841</t>
@@ -2786,52 +2786,52 @@
     <t xml:space="preserve">4.4881854057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45612621307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35995149612427</t>
+    <t xml:space="preserve">4.45612668991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35995101928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.26835536956787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2637767791748</t>
+    <t xml:space="preserve">4.26377630233765</t>
   </si>
   <si>
     <t xml:space="preserve">4.32331275939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35537195205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30957365036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30499410629272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17676067352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67137622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52482414245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4836049079895</t>
+    <t xml:space="preserve">4.35537147521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30957412719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30499362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17676019668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67137670516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52482318878174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48360586166382</t>
   </si>
   <si>
     <t xml:space="preserve">4.38743019104004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42406797409058</t>
+    <t xml:space="preserve">4.42406892776489</t>
   </si>
   <si>
     <t xml:space="preserve">4.75152254104614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95761299133301</t>
+    <t xml:space="preserve">4.95761251449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.90036535263062</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">5.04920816421509</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18660163879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23239946365356</t>
+    <t xml:space="preserve">5.1866021156311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23239898681641</t>
   </si>
   <si>
     <t xml:space="preserve">5.48428773880005</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">5.16370296478271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93471384048462</t>
+    <t xml:space="preserve">4.93471431732178</t>
   </si>
   <si>
     <t xml:space="preserve">5.02630996704102</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">5.31254625320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25529861450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.39269208908081</t>
+    <t xml:space="preserve">5.25529909133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.39269161224365</t>
   </si>
   <si>
     <t xml:space="preserve">5.20950078964233</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">5.15225315093994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14080429077148</t>
+    <t xml:space="preserve">5.14080381393433</t>
   </si>
   <si>
     <t xml:space="preserve">5.27819728851318</t>
@@ -2891,43 +2891,43 @@
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09500598907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.923264503479</t>
+    <t xml:space="preserve">5.09500646591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92326402664185</t>
   </si>
   <si>
     <t xml:space="preserve">5.01486015319824</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11790561676025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06065797805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.22095060348511</t>
+    <t xml:space="preserve">5.1179051399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06065845489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.22094964981079</t>
   </si>
   <si>
     <t xml:space="preserve">5.07210731506348</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10645580291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12935495376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3239951133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33544445037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03775882720947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08355665206909</t>
+    <t xml:space="preserve">5.10645532608032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12935447692871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.32399559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33544492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03775930404663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08355712890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.96906232833862</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">4.98051118850708</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84311866760254</t>
+    <t xml:space="preserve">4.84311771392822</t>
   </si>
   <si>
     <t xml:space="preserve">4.91181516647339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9919605255127</t>
+    <t xml:space="preserve">4.99196100234985</t>
   </si>
   <si>
     <t xml:space="preserve">5.00341081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57978105545044</t>
+    <t xml:space="preserve">4.57978057861328</t>
   </si>
   <si>
     <t xml:space="preserve">4.1904993057251</t>
@@ -2966,19 +2966,19 @@
     <t xml:space="preserve">4.30041456222534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34163188934326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61412858963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54153490066528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62168073654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75907468795776</t>
+    <t xml:space="preserve">4.34163236618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61412954330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54153442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62168025970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75907373428345</t>
   </si>
   <si>
     <t xml:space="preserve">5.73617553710938</t>
@@ -2987,13 +2987,13 @@
     <t xml:space="preserve">5.69037771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64457941055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66747903823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89646768569946</t>
+    <t xml:space="preserve">5.64457988739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66747856140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89646816253662</t>
   </si>
   <si>
     <t xml:space="preserve">5.70182704925537</t>
@@ -3005,25 +3005,25 @@
     <t xml:space="preserve">6.14835596084595</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96516418457031</t>
+    <t xml:space="preserve">5.96516466140747</t>
   </si>
   <si>
     <t xml:space="preserve">5.9537148475647</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87356901168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91936731338501</t>
+    <t xml:space="preserve">5.87356948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91936683654785</t>
   </si>
   <si>
     <t xml:space="preserve">6.09110879898071</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19415378570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12545680999756</t>
+    <t xml:space="preserve">6.19415330886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12545728683472</t>
   </si>
   <si>
     <t xml:space="preserve">6.15980529785156</t>
@@ -3032,16 +3032,16 @@
     <t xml:space="preserve">6.18270397186279</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07965898513794</t>
+    <t xml:space="preserve">6.07965850830078</t>
   </si>
   <si>
     <t xml:space="preserve">6.13690614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2170524597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35444641113281</t>
+    <t xml:space="preserve">6.21705293655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35444593429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.32009744644165</t>
@@ -3050,19 +3050,19 @@
     <t xml:space="preserve">6.36589527130127</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4803900718689</t>
+    <t xml:space="preserve">6.48038959503174</t>
   </si>
   <si>
     <t xml:space="preserve">6.52618789672852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53763723373413</t>
+    <t xml:space="preserve">6.53763675689697</t>
   </si>
   <si>
     <t xml:space="preserve">6.56053590774536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60633373260498</t>
+    <t xml:space="preserve">6.60633420944214</t>
   </si>
   <si>
     <t xml:space="preserve">6.58343505859375</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">6.62923336029053</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41169261932373</t>
+    <t xml:space="preserve">6.41169309616089</t>
   </si>
   <si>
     <t xml:space="preserve">6.34299659729004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46894073486328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29719924926758</t>
+    <t xml:space="preserve">6.46894025802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29719877243042</t>
   </si>
   <si>
     <t xml:space="preserve">6.20560312271118</t>
@@ -3089,19 +3089,19 @@
     <t xml:space="preserve">6.4231424331665</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50328826904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66358089447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51473808288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78952503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.75517654418945</t>
+    <t xml:space="preserve">6.50328922271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66358184814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5147385597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7895245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.75517702102661</t>
   </si>
   <si>
     <t xml:space="preserve">6.68648052215576</t>
@@ -3125,61 +3125,61 @@
     <t xml:space="preserve">6.33154678344727</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38879442214966</t>
+    <t xml:space="preserve">6.3887939453125</t>
   </si>
   <si>
     <t xml:space="preserve">6.54908657073975</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86967086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77417802810669</t>
+    <t xml:space="preserve">6.86967134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78562641143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77417755126953</t>
   </si>
   <si>
     <t xml:space="preserve">8.2436056137085</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1749095916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01461601257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99171733856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06041526794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02606582641602</t>
+    <t xml:space="preserve">8.17490863800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01461696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99171829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06041431427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0260648727417</t>
   </si>
   <si>
     <t xml:space="preserve">8.12911128997803</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1062126159668</t>
+    <t xml:space="preserve">8.10621166229248</t>
   </si>
   <si>
     <t xml:space="preserve">8.03751468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0031681060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93447017669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08331394195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3123025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30085372924805</t>
+    <t xml:space="preserve">8.00316715240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93447113037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08331203460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31230354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30085182189941</t>
   </si>
   <si>
     <t xml:space="preserve">8.28940391540527</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">8.33520126342773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2779541015625</t>
+    <t xml:space="preserve">8.27795314788818</t>
   </si>
   <si>
     <t xml:space="preserve">8.15200901031494</t>
@@ -3197,82 +3197,82 @@
     <t xml:space="preserve">8.11766242980957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18635940551758</t>
+    <t xml:space="preserve">8.18635845184326</t>
   </si>
   <si>
     <t xml:space="preserve">8.34665012359619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23215484619141</t>
+    <t xml:space="preserve">8.23215579986572</t>
   </si>
   <si>
     <t xml:space="preserve">8.16345977783203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07186317443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20925807952881</t>
+    <t xml:space="preserve">8.07186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20925617218018</t>
   </si>
   <si>
     <t xml:space="preserve">7.94592046737671</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95736932754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84287548065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92301988601685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81997585296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86577367782593</t>
+    <t xml:space="preserve">7.95736885070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84287452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92302083969116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81997680664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86577320098877</t>
   </si>
   <si>
     <t xml:space="preserve">8.3809986114502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15956211090088</t>
+    <t xml:space="preserve">9.15956115722656</t>
   </si>
   <si>
     <t xml:space="preserve">8.99926948547363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20536041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48014736175537</t>
+    <t xml:space="preserve">9.20535945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48014640808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.65356349945068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60731887817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78073692321777</t>
+    <t xml:space="preserve">9.60731983184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78073596954346</t>
   </si>
   <si>
     <t xml:space="preserve">9.71136856079102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0813255310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2894277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.300989151001</t>
+    <t xml:space="preserve">10.0813264846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2894268035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3009881973267</t>
   </si>
   <si>
     <t xml:space="preserve">10.3241109848022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5206508636475</t>
+    <t xml:space="preserve">10.5206499099731</t>
   </si>
   <si>
     <t xml:space="preserve">10.3587942123413</t>
@@ -3281,19 +3281,19 @@
     <t xml:space="preserve">10.5437726974487</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4975290298462</t>
+    <t xml:space="preserve">10.4975280761719</t>
   </si>
   <si>
     <t xml:space="preserve">10.33567237854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4628448486328</t>
+    <t xml:space="preserve">10.4628438949585</t>
   </si>
   <si>
     <t xml:space="preserve">10.4050388336182</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3703546524048</t>
+    <t xml:space="preserve">10.3703556060791</t>
   </si>
   <si>
     <t xml:space="preserve">10.7403125762939</t>
@@ -3305,61 +3305,61 @@
     <t xml:space="preserve">10.3819169998169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1044502258301</t>
+    <t xml:space="preserve">10.1044483184814</t>
   </si>
   <si>
     <t xml:space="preserve">10.2663049697876</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3934783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0582046508789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95415306091309</t>
+    <t xml:space="preserve">10.3934774398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0582036972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9541540145874</t>
   </si>
   <si>
     <t xml:space="preserve">10.0235214233398</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1506948471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0697650909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.092887878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1160116195679</t>
+    <t xml:space="preserve">10.1506938934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0697660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0928888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1160106658936</t>
   </si>
   <si>
     <t xml:space="preserve">10.2547435760498</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2200613021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4859676361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1853771209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0350828170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4165992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1738157272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1391324996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.191198348999</t>
+    <t xml:space="preserve">10.2200603485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4859657287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.185378074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0350818634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.416600227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1738147735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1391315460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1911973953247</t>
   </si>
   <si>
     <t xml:space="preserve">11.5056610107422</t>
@@ -3368,13 +3368,13 @@
     <t xml:space="preserve">11.9052143096924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.901515007019</t>
+    <t xml:space="preserve">11.9015140533447</t>
   </si>
   <si>
     <t xml:space="preserve">11.746132850647</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611543655396</t>
+    <t xml:space="preserve">11.5611553192139</t>
   </si>
   <si>
     <t xml:space="preserve">11.5426568984985</t>
@@ -3383,22 +3383,22 @@
     <t xml:space="preserve">11.4298191070557</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5796518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4501667022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3576765060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3206834793091</t>
+    <t xml:space="preserve">11.5796527862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4501676559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3576774597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3206825256348</t>
   </si>
   <si>
     <t xml:space="preserve">11.6536436080933</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3946733474731</t>
+    <t xml:space="preserve">11.3946743011475</t>
   </si>
   <si>
     <t xml:space="preserve">11.4686641693115</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">12.2455739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3010692596436</t>
+    <t xml:space="preserve">12.3010683059692</t>
   </si>
   <si>
     <t xml:space="preserve">11.894115447998</t>
@@ -3434,22 +3434,22 @@
     <t xml:space="preserve">13.854887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7069044113159</t>
+    <t xml:space="preserve">13.7069034576416</t>
   </si>
   <si>
     <t xml:space="preserve">13.151969909668</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5034294128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8178911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7254018783569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6317958831787</t>
+    <t xml:space="preserve">13.5034284591675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.817892074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7254028320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.631796836853</t>
   </si>
   <si>
     <t xml:space="preserve">14.0398664474487</t>
@@ -3458,10 +3458,10 @@
     <t xml:space="preserve">13.7438993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4109401702881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7623987197876</t>
+    <t xml:space="preserve">13.4109392166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7623977661133</t>
   </si>
   <si>
     <t xml:space="preserve">13.4294376373291</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">13.3739433288574</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9114971160889</t>
+    <t xml:space="preserve">12.9114980697632</t>
   </si>
   <si>
     <t xml:space="preserve">13.0779781341553</t>
@@ -3494,64 +3494,64 @@
     <t xml:space="preserve">14.4468183517456</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4457025527954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5011959075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7786626815796</t>
+    <t xml:space="preserve">15.4457035064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5011968612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7786636352539</t>
   </si>
   <si>
     <t xml:space="preserve">16.5555725097656</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3705959320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5370750427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2596092224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3520984649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.019136428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7971591949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1486186981201</t>
+    <t xml:space="preserve">16.3705940246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.537073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2596054077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3520965576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0191345214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7971620559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1486206054688</t>
   </si>
   <si>
     <t xml:space="preserve">16.000638961792</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9081506729126</t>
+    <t xml:space="preserve">15.9081478118896</t>
   </si>
   <si>
     <t xml:space="preserve">15.5196943283081</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4642000198364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8896503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7416677474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8341588973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9092655181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4283218383789</t>
+    <t xml:space="preserve">15.4641990661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8896512985229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7416687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8341579437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9092645645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4283208847046</t>
   </si>
   <si>
     <t xml:space="preserve">14.502311706543</t>
@@ -3560,19 +3560,19 @@
     <t xml:space="preserve">14.2433423995972</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6329126358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6514110565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3369474411011</t>
+    <t xml:space="preserve">13.6329135894775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6514120101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369483947754</t>
   </si>
   <si>
     <t xml:space="preserve">13.9288787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0583639144897</t>
+    <t xml:space="preserve">14.0583629608154</t>
   </si>
   <si>
     <t xml:space="preserve">14.1693506240845</t>
@@ -3593,16 +3593,16 @@
     <t xml:space="preserve">13.7808961868286</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2629556655884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5404243469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3924407958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3554439544678</t>
+    <t xml:space="preserve">13.2629566192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5404233932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3924417495728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3554449081421</t>
   </si>
   <si>
     <t xml:space="preserve">13.965874671936</t>
@@ -3611,22 +3611,22 @@
     <t xml:space="preserve">14.1323547363281</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2988357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2803373336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1138572692871</t>
+    <t xml:space="preserve">14.2988367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2803382873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1138582229614</t>
   </si>
   <si>
     <t xml:space="preserve">12.9484930038452</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1334705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0594806671143</t>
+    <t xml:space="preserve">13.1334714889526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0594787597656</t>
   </si>
   <si>
     <t xml:space="preserve">13.4479351043701</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">12.3935575485229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1889657974243</t>
+    <t xml:space="preserve">13.18896484375</t>
   </si>
   <si>
     <t xml:space="preserve">13.4664325714111</t>
@@ -3659,34 +3659,34 @@
     <t xml:space="preserve">11.8386220932007</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1345882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9496097564697</t>
+    <t xml:space="preserve">12.1345872879028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9496088027954</t>
   </si>
   <si>
     <t xml:space="preserve">11.6721410751343</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5981502532959</t>
+    <t xml:space="preserve">11.5981492996216</t>
   </si>
   <si>
     <t xml:space="preserve">12.0051021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7831287384033</t>
+    <t xml:space="preserve">11.783127784729</t>
   </si>
   <si>
     <t xml:space="preserve">12.0236005783081</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9681062698364</t>
+    <t xml:space="preserve">11.9681072235107</t>
   </si>
   <si>
     <t xml:space="preserve">11.0247173309326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8582353591919</t>
+    <t xml:space="preserve">10.8582363128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.5067768096924</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">11.1172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8201246261597</t>
+    <t xml:space="preserve">11.8201236724854</t>
   </si>
   <si>
     <t xml:space="preserve">11.4131727218628</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">12.6710252761841</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7265176773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8005104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2259607315063</t>
+    <t xml:space="preserve">12.7265186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8005094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.225959777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.3276987075806</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">13.3646945953369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7172698974609</t>
+    <t xml:space="preserve">12.7172708511353</t>
   </si>
   <si>
     <t xml:space="preserve">12.6617765426636</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">12.4028062820435</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5137929916382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3473138809204</t>
+    <t xml:space="preserve">12.5137939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3473129272461</t>
   </si>
   <si>
     <t xml:space="preserve">12.3288145065308</t>
@@ -3746,91 +3746,91 @@
     <t xml:space="preserve">12.6155319213867</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4398021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8016262054443</t>
+    <t xml:space="preserve">12.4398012161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8016271591187</t>
   </si>
   <si>
     <t xml:space="preserve">11.9958543777466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3565607070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7646312713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8848676681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6073989868164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5519046783447</t>
+    <t xml:space="preserve">12.3565626144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.764630317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8848667144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6073999404907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.551905632019</t>
   </si>
   <si>
     <t xml:space="preserve">11.2929363250732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6455097198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7657470703125</t>
+    <t xml:space="preserve">10.6455116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7657480239868</t>
   </si>
   <si>
     <t xml:space="preserve">11.098708152771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5704040527344</t>
+    <t xml:space="preserve">11.5704030990601</t>
   </si>
   <si>
     <t xml:space="preserve">11.4316692352295</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8293724060059</t>
+    <t xml:space="preserve">11.8293714523315</t>
   </si>
   <si>
     <t xml:space="preserve">11.8331203460693</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4007749557495</t>
+    <t xml:space="preserve">11.4007759094238</t>
   </si>
   <si>
     <t xml:space="preserve">11.5605545043945</t>
   </si>
   <si>
-    <t xml:space="preserve">11.569953918457</t>
+    <t xml:space="preserve">11.5699548721313</t>
   </si>
   <si>
     <t xml:space="preserve">11.6827392578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1432809829712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.85191822052</t>
+    <t xml:space="preserve">12.1432819366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8519172668457</t>
   </si>
   <si>
     <t xml:space="preserve">11.6639413833618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7579307556152</t>
+    <t xml:space="preserve">11.7579298019409</t>
   </si>
   <si>
     <t xml:space="preserve">11.974102973938</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0398960113525</t>
+    <t xml:space="preserve">12.0398950576782</t>
   </si>
   <si>
     <t xml:space="preserve">12.133882522583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8895120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1658039093018</t>
+    <t xml:space="preserve">11.8895130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1658048629761</t>
   </si>
   <si>
     <t xml:space="preserve">10.7522554397583</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">11.053017616272</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5830774307251</t>
+    <t xml:space="preserve">10.5830764770508</t>
   </si>
   <si>
     <t xml:space="preserve">10.827446937561</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">10.8838386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0248212814331</t>
+    <t xml:space="preserve">11.0248203277588</t>
   </si>
   <si>
     <t xml:space="preserve">10.9214344024658</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">11.0624170303345</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4571676254272</t>
+    <t xml:space="preserve">11.4571666717529</t>
   </si>
   <si>
     <t xml:space="preserve">11.4947624206543</t>
@@ -3872,7 +3872,7 @@
     <t xml:space="preserve">11.3631792068481</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6075487136841</t>
+    <t xml:space="preserve">11.6075496673584</t>
   </si>
   <si>
     <t xml:space="preserve">11.9365072250366</t>
@@ -3881,16 +3881,16 @@
     <t xml:space="preserve">11.7297334671021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0962867736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3876514434814</t>
+    <t xml:space="preserve">12.096287727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3876523971558</t>
   </si>
   <si>
     <t xml:space="preserve">12.5380325317383</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6414194107056</t>
+    <t xml:space="preserve">12.6414184570312</t>
   </si>
   <si>
     <t xml:space="preserve">12.6884136199951</t>
@@ -3914,10 +3914,10 @@
     <t xml:space="preserve">13.1677532196045</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4685163497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6188974380493</t>
+    <t xml:space="preserve">13.4685153961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.618896484375</t>
   </si>
   <si>
     <t xml:space="preserve">13.5625047683716</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">13.7034864425659</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6564931869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.741081237793</t>
+    <t xml:space="preserve">13.6564922332764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7410821914673</t>
   </si>
   <si>
     <t xml:space="preserve">13.6752910614014</t>
@@ -3941,19 +3941,19 @@
     <t xml:space="preserve">13.8726663589478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3087368011475</t>
+    <t xml:space="preserve">13.6376943588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3087358474731</t>
   </si>
   <si>
     <t xml:space="preserve">12.9891757965088</t>
   </si>
   <si>
-    <t xml:space="preserve">13.158353805542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.336932182312</t>
+    <t xml:space="preserve">13.1583547592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3369312286377</t>
   </si>
   <si>
     <t xml:space="preserve">13.2335453033447</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">13.1113605499268</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9139842987061</t>
+    <t xml:space="preserve">12.9139862060547</t>
   </si>
   <si>
     <t xml:space="preserve">12.8199977874756</t>
@@ -3983,22 +3983,22 @@
     <t xml:space="preserve">13.0549688339233</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8669919967651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7260084152222</t>
+    <t xml:space="preserve">12.8669910430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7260093688965</t>
   </si>
   <si>
     <t xml:space="preserve">12.4628419876099</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8857889175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5850267410278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5756282806396</t>
+    <t xml:space="preserve">12.8857898712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5850276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5756273269653</t>
   </si>
   <si>
     <t xml:space="preserve">12.6602172851562</t>
@@ -4007,16 +4007,16 @@
     <t xml:space="preserve">13.1207599639893</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1056861877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8237218856812</t>
+    <t xml:space="preserve">12.1056871414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8237209320068</t>
   </si>
   <si>
     <t xml:space="preserve">11.6921377182007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.391375541687</t>
+    <t xml:space="preserve">11.3913745880127</t>
   </si>
   <si>
     <t xml:space="preserve">11.1470060348511</t>
@@ -4025,31 +4025,31 @@
     <t xml:space="preserve">10.8180475234985</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1000118255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5548801422119</t>
+    <t xml:space="preserve">11.1000137329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5548791885376</t>
   </si>
   <si>
     <t xml:space="preserve">10.5454816818237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4984865188599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6582670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3951015472412</t>
+    <t xml:space="preserve">10.4984874725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6582679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3951005935669</t>
   </si>
   <si>
     <t xml:space="preserve">10.9778280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4665660858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1940002441406</t>
+    <t xml:space="preserve">11.4665670394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1939992904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.1188097000122</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">11.2879886627197</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8707151412964</t>
+    <t xml:space="preserve">11.8707160949707</t>
   </si>
   <si>
     <t xml:space="preserve">11.9929008483887</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">11.7955255508423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6357450485229</t>
+    <t xml:space="preserve">11.6357460021973</t>
   </si>
   <si>
     <t xml:space="preserve">11.4759654998779</t>
@@ -4094,10 +4094,10 @@
     <t xml:space="preserve">11.7485313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1150846481323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1244831085205</t>
+    <t xml:space="preserve">12.1150856018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1244840621948</t>
   </si>
   <si>
     <t xml:space="preserve">12.7354078292847</t>
@@ -4106,13 +4106,13 @@
     <t xml:space="preserve">12.895188331604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6790151596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4722414016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.773003578186</t>
+    <t xml:space="preserve">12.6790142059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.472240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7730026245117</t>
   </si>
   <si>
     <t xml:space="preserve">13.0455694198608</t>
@@ -4124,19 +4124,19 @@
     <t xml:space="preserve">13.8350706100464</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8256711959839</t>
+    <t xml:space="preserve">13.8256721496582</t>
   </si>
   <si>
     <t xml:space="preserve">13.515510559082</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9102621078491</t>
+    <t xml:space="preserve">13.9102611541748</t>
   </si>
   <si>
     <t xml:space="preserve">13.8068733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6282968521118</t>
+    <t xml:space="preserve">13.6282958984375</t>
   </si>
   <si>
     <t xml:space="preserve">13.3275337219238</t>
@@ -4145,22 +4145,22 @@
     <t xml:space="preserve">13.4779148101807</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5437059402466</t>
+    <t xml:space="preserve">13.5437068939209</t>
   </si>
   <si>
     <t xml:space="preserve">13.7222852706909</t>
   </si>
   <si>
-    <t xml:space="preserve">14.258017539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1170358657837</t>
+    <t xml:space="preserve">14.2580165863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1170349121094</t>
   </si>
   <si>
     <t xml:space="preserve">13.7504806518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2805404663086</t>
+    <t xml:space="preserve">13.2805395126343</t>
   </si>
   <si>
     <t xml:space="preserve">13.3745279312134</t>
@@ -4172,10 +4172,10 @@
     <t xml:space="preserve">13.5531053543091</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3463306427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2523431777954</t>
+    <t xml:space="preserve">13.3463315963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2523441314697</t>
   </si>
   <si>
     <t xml:space="preserve">13.5719022750854</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">13.3933258056641</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2711410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5249090194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6470947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7598791122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7316818237305</t>
+    <t xml:space="preserve">13.2711400985718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5249099731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6470937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.759880065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7316827774048</t>
   </si>
   <si>
     <t xml:space="preserve">14.0606422424316</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">14.0512428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0042486190796</t>
+    <t xml:space="preserve">14.0042495727539</t>
   </si>
   <si>
     <t xml:space="preserve">14.079439163208</t>
@@ -4217,37 +4217,37 @@
     <t xml:space="preserve">13.8914632797241</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4215211868286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0888385772705</t>
+    <t xml:space="preserve">13.4215221405029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0888376235962</t>
   </si>
   <si>
     <t xml:space="preserve">14.5587787628174</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7749519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8407440185547</t>
+    <t xml:space="preserve">14.7749528884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.840744972229</t>
   </si>
   <si>
     <t xml:space="preserve">15.0193214416504</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0099229812622</t>
+    <t xml:space="preserve">15.0099239349365</t>
   </si>
   <si>
     <t xml:space="preserve">14.6997632980347</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7279596328735</t>
+    <t xml:space="preserve">14.7279586791992</t>
   </si>
   <si>
     <t xml:space="preserve">14.8783397674561</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9441318511963</t>
+    <t xml:space="preserve">14.944130897522</t>
   </si>
   <si>
     <t xml:space="preserve">14.9347333908081</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">14.7373580932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8031482696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7655534744263</t>
+    <t xml:space="preserve">14.803150177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7655544281006</t>
   </si>
   <si>
     <t xml:space="preserve">14.7937498092651</t>
@@ -4268,13 +4268,13 @@
     <t xml:space="preserve">14.6621675491333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8125476837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6903638839722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689403533936</t>
+    <t xml:space="preserve">14.8125486373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6903629302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689413070679</t>
   </si>
   <si>
     <t xml:space="preserve">15.1039113998413</t>
@@ -4283,22 +4283,22 @@
     <t xml:space="preserve">14.9817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8877391815186</t>
+    <t xml:space="preserve">14.8877382278442</t>
   </si>
   <si>
     <t xml:space="preserve">15.122709274292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3708028793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1734275817871</t>
+    <t xml:space="preserve">14.3708038330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1734285354614</t>
   </si>
   <si>
     <t xml:space="preserve">14.4929876327515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.299337387085</t>
+    <t xml:space="preserve">13.2993364334106</t>
   </si>
   <si>
     <t xml:space="preserve">11.513560295105</t>
@@ -4307,16 +4307,16 @@
     <t xml:space="preserve">11.3725786209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9872264862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.269190788269</t>
+    <t xml:space="preserve">10.9872255325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2691917419434</t>
   </si>
   <si>
     <t xml:space="preserve">11.2785902023315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3067855834961</t>
+    <t xml:space="preserve">11.3067865371704</t>
   </si>
   <si>
     <t xml:space="preserve">11.231595993042</t>
@@ -4331,28 +4331,28 @@
     <t xml:space="preserve">11.410174369812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1846017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1094102859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2221975326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9966259002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0812139511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0342197418213</t>
+    <t xml:space="preserve">11.1846008300781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.109411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2221956253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9966249465942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0812149047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0342206954956</t>
   </si>
   <si>
     <t xml:space="preserve">10.8744401931763</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9590301513672</t>
+    <t xml:space="preserve">10.9590291976929</t>
   </si>
   <si>
     <t xml:space="preserve">10.9026374816895</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">10.7992496490479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7146606445312</t>
+    <t xml:space="preserve">10.7146596908569</t>
   </si>
   <si>
     <t xml:space="preserve">10.6958627700806</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">10.8650417327881</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4138984680176</t>
+    <t xml:space="preserve">10.4138975143433</t>
   </si>
   <si>
     <t xml:space="preserve">10.3387069702148</t>
@@ -4385,28 +4385,28 @@
     <t xml:space="preserve">10.3180065155029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97279357910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1549892425537</t>
+    <t xml:space="preserve">10.0303297042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97279262542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.154990196228</t>
   </si>
   <si>
     <t xml:space="preserve">10.5002012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3371839523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3563623428345</t>
+    <t xml:space="preserve">10.3371849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3563632965088</t>
   </si>
   <si>
     <t xml:space="preserve">10.4234867095947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5193796157837</t>
+    <t xml:space="preserve">10.519380569458</t>
   </si>
   <si>
     <t xml:space="preserve">10.9413051605225</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">11.0371980667114</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1235017776489</t>
+    <t xml:space="preserve">11.1235008239746</t>
   </si>
   <si>
     <t xml:space="preserve">11.1714468002319</t>
@@ -4433,25 +4433,25 @@
     <t xml:space="preserve">10.5481472015381</t>
   </si>
   <si>
-    <t xml:space="preserve">10.490611076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3851299285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1645784378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2796497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2412929534912</t>
+    <t xml:space="preserve">10.4906120300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3851308822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1645793914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2796487808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2412919998169</t>
   </si>
   <si>
     <t xml:space="preserve">10.5385580062866</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6440391540527</t>
+    <t xml:space="preserve">10.6440401077271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4043092727661</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">10.66321849823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5960941314697</t>
+    <t xml:space="preserve">10.5960931777954</t>
   </si>
   <si>
     <t xml:space="preserve">10.6728076934814</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">10.7207536697388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.711163520813</t>
+    <t xml:space="preserve">10.7111644744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.3275957107544</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">9.73306274414062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84813404083252</t>
+    <t xml:space="preserve">9.84813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">9.76183128356934</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">10.0111503601074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92484855651855</t>
+    <t xml:space="preserve">9.92484760284424</t>
   </si>
   <si>
     <t xml:space="preserve">10.0207405090332</t>
@@ -4535,7 +4535,7 @@
     <t xml:space="preserve">10.5289688110352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4618444442749</t>
+    <t xml:space="preserve">10.4618434906006</t>
   </si>
   <si>
     <t xml:space="preserve">10.4522542953491</t>
@@ -4547,22 +4547,22 @@
     <t xml:space="preserve">9.86731243133545</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95361614227295</t>
+    <t xml:space="preserve">9.95361518859863</t>
   </si>
   <si>
     <t xml:space="preserve">9.30154800415039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09537982940674</t>
+    <t xml:space="preserve">9.09537887573242</t>
   </si>
   <si>
     <t xml:space="preserve">8.9659252166748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82688140869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48646450042725</t>
+    <t xml:space="preserve">8.82688236236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48646354675293</t>
   </si>
   <si>
     <t xml:space="preserve">8.63030242919922</t>
@@ -4586,7 +4586,7 @@
     <t xml:space="preserve">8.29467868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34741973876953</t>
+    <t xml:space="preserve">8.34742069244385</t>
   </si>
   <si>
     <t xml:space="preserve">8.25152778625488</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">8.28988552093506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09810066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17960834503174</t>
+    <t xml:space="preserve">8.09809970855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17960929870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.12686824798584</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23235034942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09330463409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15084171295166</t>
+    <t xml:space="preserve">8.23234939575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09330558776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15084075927734</t>
   </si>
   <si>
     <t xml:space="preserve">8.11248397827148</t>
@@ -4643,13 +4643,13 @@
     <t xml:space="preserve">8.08851146697998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44810676574707</t>
+    <t xml:space="preserve">8.44810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">8.33303642272949</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80770397186279</t>
+    <t xml:space="preserve">8.80770301818848</t>
   </si>
   <si>
     <t xml:space="preserve">9.14332580566406</t>
@@ -4670,22 +4670,22 @@
     <t xml:space="preserve">9.29195785522461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10976409912109</t>
+    <t xml:space="preserve">9.10976314544678</t>
   </si>
   <si>
     <t xml:space="preserve">9.44059181213379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67824840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14812088012695</t>
+    <t xml:space="preserve">8.67824935913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14811992645264</t>
   </si>
   <si>
     <t xml:space="preserve">9.20086193084717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26798629760742</t>
+    <t xml:space="preserve">9.26798534393311</t>
   </si>
   <si>
     <t xml:space="preserve">9.24880790710449</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">9.00907802581787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82208728790283</t>
+    <t xml:space="preserve">8.82208633422852</t>
   </si>
   <si>
     <t xml:space="preserve">8.89880084991455</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">8.97071933746338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907001495361</t>
+    <t xml:space="preserve">8.6590690612793</t>
   </si>
   <si>
     <t xml:space="preserve">8.81249713897705</t>
@@ -4724,13 +4724,13 @@
     <t xml:space="preserve">9.21524524688721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19127178192139</t>
+    <t xml:space="preserve">9.1912727355957</t>
   </si>
   <si>
     <t xml:space="preserve">9.08579063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23921775817871</t>
+    <t xml:space="preserve">9.23921871185303</t>
   </si>
   <si>
     <t xml:space="preserve">9.38785076141357</t>
@@ -4751,7 +4751,7 @@
     <t xml:space="preserve">9.34949493408203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28237056732178</t>
+    <t xml:space="preserve">9.28236961364746</t>
   </si>
   <si>
     <t xml:space="preserve">9.17688846588135</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">9.10017395019531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1337366104126</t>
+    <t xml:space="preserve">9.13373565673828</t>
   </si>
   <si>
     <t xml:space="preserve">9.16250514984131</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">9.04263973236084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00428199768066</t>
+    <t xml:space="preserve">9.00428295135498</t>
   </si>
   <si>
     <t xml:space="preserve">8.94674682617188</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">9.06661224365234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8844165802002</t>
+    <t xml:space="preserve">8.88441753387451</t>
   </si>
   <si>
     <t xml:space="preserve">8.88921165466309</t>
@@ -4787,25 +4787,25 @@
     <t xml:space="preserve">8.96113109588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91318511962891</t>
+    <t xml:space="preserve">8.91318416595459</t>
   </si>
   <si>
     <t xml:space="preserve">9.01387119293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64468669891357</t>
+    <t xml:space="preserve">8.64468574523926</t>
   </si>
   <si>
     <t xml:space="preserve">8.77414035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7166051864624</t>
+    <t xml:space="preserve">8.71660614013672</t>
   </si>
   <si>
     <t xml:space="preserve">8.52482128143311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54399871826172</t>
+    <t xml:space="preserve">8.54399967193604</t>
   </si>
   <si>
     <t xml:space="preserve">8.64948081970215</t>
@@ -4820,7 +4820,7 @@
     <t xml:space="preserve">8.68783855438232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75496292114258</t>
+    <t xml:space="preserve">8.75496196746826</t>
   </si>
   <si>
     <t xml:space="preserve">8.71181106567383</t>
@@ -4832,7 +4832,7 @@
     <t xml:space="preserve">8.76455211639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70222091674805</t>
+    <t xml:space="preserve">8.70222187042236</t>
   </si>
   <si>
     <t xml:space="preserve">8.86044406890869</t>
@@ -4847,37 +4847,37 @@
     <t xml:space="preserve">8.62550735473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49605274200439</t>
+    <t xml:space="preserve">8.49605369567871</t>
   </si>
   <si>
     <t xml:space="preserve">8.26591205596924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1364574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21317005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21796607971191</t>
+    <t xml:space="preserve">8.13645648956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21317100524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2179651260376</t>
   </si>
   <si>
     <t xml:space="preserve">8.19399261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97344064712524</t>
+    <t xml:space="preserve">7.97343969345093</t>
   </si>
   <si>
     <t xml:space="preserve">8.06453800201416</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94467306137085</t>
+    <t xml:space="preserve">7.94467258453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.36867332458496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79059886932373</t>
+    <t xml:space="preserve">9.79059791564941</t>
   </si>
   <si>
     <t xml:space="preserve">10.1837568283081</t>
@@ -4904,7 +4904,7 @@
     <t xml:space="preserve">11.4303560256958</t>
   </si>
   <si>
-    <t xml:space="preserve">11.42076587677</t>
+    <t xml:space="preserve">11.4207668304443</t>
   </si>
   <si>
     <t xml:space="preserve">11.0467872619629</t>
@@ -4922,16 +4922,16 @@
     <t xml:space="preserve">11.2193927764893</t>
   </si>
   <si>
-    <t xml:space="preserve">11.593373298645</t>
+    <t xml:space="preserve">11.5933723449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.4783029556274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3536415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2769289016724</t>
+    <t xml:space="preserve">11.3536424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.276927947998</t>
   </si>
   <si>
     <t xml:space="preserve">11.1330890655518</t>
@@ -4940,16 +4940,16 @@
     <t xml:space="preserve">10.931715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9796619415283</t>
+    <t xml:space="preserve">10.9796628952026</t>
   </si>
   <si>
     <t xml:space="preserve">11.02760887146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1618576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7276220321655</t>
+    <t xml:space="preserve">11.1618585586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7276210784912</t>
   </si>
   <si>
     <t xml:space="preserve">11.3440532684326</t>
@@ -4973,10 +4973,10 @@
     <t xml:space="preserve">11.1906261444092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.59881496429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6084041595459</t>
+    <t xml:space="preserve">9.59881401062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60840320587158</t>
   </si>
   <si>
     <t xml:space="preserve">9.52034282684326</t>
@@ -5868,6 +5868,9 @@
   </si>
   <si>
     <t xml:space="preserve">12.6999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6599998474121</t>
   </si>
 </sst>
 </file>
@